--- a/data/metas.xlsx
+++ b/data/metas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sercomunicaciones2-my.sharepoint.com/personal/auxcomisiones_sercomunicaciones_com/Documents/PAOLA/Liquidacióncvs/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="129" documentId="8_{787D9E49-702D-43BD-B99B-4B64F775E77B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ED721459-2937-4472-B019-66DF810AF62C}"/>
+  <xr:revisionPtr revIDLastSave="131" documentId="8_{787D9E49-702D-43BD-B99B-4B64F775E77B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{260EEC2E-8F85-4917-BB17-9C6972E9D512}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D1391136-BBFC-43C7-B899-B77B0ECC5956}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$A$1:$D$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$A$1:$D$111</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -2096,7 +2096,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D1" xr:uid="{6956BB2C-DA9E-4412-BCD4-BB80A11153FE}"/>
+  <autoFilter ref="A1:D111" xr:uid="{6956BB2C-DA9E-4412-BCD4-BB80A11153FE}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/data/metas.xlsx
+++ b/data/metas.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sercomunicaciones2-my.sharepoint.com/personal/auxcomisiones_sercomunicaciones_com/Documents/PAOLA/Liquidacióncvs/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sercomunicaciones2-my.sharepoint.com/personal/auxcomisiones_sercomunicaciones_com/Documents/PAOLA/Liquidacióncvs - copia/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="131" documentId="8_{787D9E49-702D-43BD-B99B-4B64F775E77B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{260EEC2E-8F85-4917-BB17-9C6972E9D512}"/>
+  <xr:revisionPtr revIDLastSave="485" documentId="8_{787D9E49-702D-43BD-B99B-4B64F775E77B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E36E46B0-C4A9-44B0-A485-DEF0474E71DD}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D1391136-BBFC-43C7-B899-B77B0ECC5956}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$A$1:$D$111</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$A$1:$D$133</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="32">
   <si>
     <t>BARBOSA</t>
   </si>
@@ -132,6 +132,9 @@
   </si>
   <si>
     <t>OTROS</t>
+  </si>
+  <si>
+    <t>FOCO</t>
   </si>
 </sst>
 </file>
@@ -533,7 +536,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6956BB2C-DA9E-4412-BCD4-BB80A11153FE}">
-  <dimension ref="A1:D111"/>
+  <dimension ref="A1:D134"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="25" customWidth="1"/>
@@ -566,7 +569,7 @@
         <v>1500</v>
       </c>
       <c r="D2" s="3">
-        <v>4000</v>
+        <v>2800</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -577,10 +580,10 @@
         <v>27</v>
       </c>
       <c r="C3" s="3">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D3" s="3">
-        <v>4000</v>
+        <v>2800</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -591,10 +594,10 @@
         <v>28</v>
       </c>
       <c r="C4" s="3">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="D4" s="3">
-        <v>4000</v>
+        <v>2800</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -605,10 +608,10 @@
         <v>29</v>
       </c>
       <c r="C5" s="3">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="D5" s="3">
-        <v>4000</v>
+        <v>2800</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -616,27 +619,27 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C6" s="3">
-        <v>682</v>
+        <v>29</v>
       </c>
       <c r="D6" s="3">
-        <v>4000</v>
+        <v>2800</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="C7" s="3">
-        <v>1500</v>
+        <v>146</v>
       </c>
       <c r="D7" s="3">
-        <v>3500</v>
+        <v>2800</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -644,13 +647,13 @@
         <v>0</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="C8" s="3">
-        <v>27</v>
+        <v>1500</v>
       </c>
       <c r="D8" s="3">
-        <v>3500</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -658,13 +661,13 @@
         <v>0</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C9" s="3">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="D9" s="3">
-        <v>3500</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -672,13 +675,13 @@
         <v>0</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="C10">
-        <v>78</v>
+        <v>28</v>
+      </c>
+      <c r="C10" s="3">
+        <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>3500</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -686,41 +689,41 @@
         <v>0</v>
       </c>
       <c r="B11" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C11">
+        <v>82</v>
+      </c>
+      <c r="D11" s="3">
+        <v>2400</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C12">
+        <v>25</v>
+      </c>
+      <c r="D12" s="3">
+        <v>2400</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B13" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C11">
-        <v>10</v>
-      </c>
-      <c r="D11" s="3">
-        <v>3500</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>2</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C12" s="3">
-        <v>1500</v>
-      </c>
-      <c r="D12" s="3">
-        <v>1800</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>2</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>27</v>
-      </c>
       <c r="C13">
-        <v>7</v>
+        <v>95</v>
       </c>
       <c r="D13" s="3">
-        <v>1800</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -728,13 +731,13 @@
         <v>2</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C14" s="3">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D14" s="3">
-        <v>1800</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -742,13 +745,13 @@
         <v>2</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C15">
-        <v>46</v>
+        <v>12</v>
       </c>
       <c r="D15" s="3">
-        <v>1800</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -756,55 +759,55 @@
         <v>2</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="C16">
-        <v>10</v>
+        <v>28</v>
+      </c>
+      <c r="C16" s="3">
+        <v>4</v>
       </c>
       <c r="D16" s="3">
-        <v>1800</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C17" s="3">
-        <v>1500</v>
+        <v>29</v>
+      </c>
+      <c r="C17">
+        <v>50</v>
       </c>
       <c r="D17" s="3">
-        <v>2100</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C18">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="D18" s="3">
-        <v>2100</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="C19" s="3">
-        <v>4</v>
+        <v>30</v>
+      </c>
+      <c r="C19">
+        <v>32</v>
       </c>
       <c r="D19" s="3">
-        <v>2100</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -812,13 +815,13 @@
         <v>3</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="C20">
-        <v>57</v>
+        <v>22</v>
+      </c>
+      <c r="C20" s="3">
+        <v>800</v>
       </c>
       <c r="D20" s="3">
-        <v>2100</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -826,69 +829,69 @@
         <v>3</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C21">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="D21" s="3">
-        <v>2100</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="C22" s="3">
-        <v>1500</v>
+        <v>1</v>
       </c>
       <c r="D22" s="3">
-        <v>1800</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C23">
-        <v>15</v>
+        <v>65</v>
       </c>
       <c r="D23" s="3">
-        <v>1800</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="C24" s="3">
-        <v>4</v>
+        <v>31</v>
+      </c>
+      <c r="C24">
+        <v>20</v>
       </c>
       <c r="D24" s="3">
-        <v>1800</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C25">
-        <v>50</v>
+        <v>135</v>
       </c>
       <c r="D25" s="3">
-        <v>1800</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -896,928 +899,928 @@
         <v>8</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="C26">
-        <v>15</v>
+        <v>22</v>
+      </c>
+      <c r="C26" s="3">
+        <v>1200</v>
       </c>
       <c r="D26" s="3">
-        <v>1800</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C27" s="3">
-        <v>1500</v>
+        <v>27</v>
+      </c>
+      <c r="C27">
+        <v>18</v>
       </c>
       <c r="D27" s="3">
-        <v>2100</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="C28">
-        <v>31</v>
+        <v>28</v>
+      </c>
+      <c r="C28" s="3">
+        <v>1</v>
       </c>
       <c r="D28" s="3">
-        <v>2100</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="C29" s="3">
-        <v>4</v>
+        <v>29</v>
+      </c>
+      <c r="C29">
+        <v>50</v>
       </c>
       <c r="D29" s="3">
-        <v>2100</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C30">
-        <v>47</v>
+        <v>15</v>
       </c>
       <c r="D30" s="3">
-        <v>2100</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B31" s="3" t="s">
         <v>30</v>
       </c>
       <c r="C31">
-        <v>14</v>
+        <v>69</v>
       </c>
       <c r="D31" s="3">
-        <v>2100</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B32" s="3" t="s">
         <v>22</v>
       </c>
       <c r="C32" s="3">
+        <v>1200</v>
+      </c>
+      <c r="D32" s="3">
         <v>1500</v>
-      </c>
-      <c r="D32" s="3">
-        <v>4000</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B33" s="3" t="s">
         <v>27</v>
       </c>
       <c r="C33">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="D33" s="3">
-        <v>4000</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B34" s="3" t="s">
         <v>28</v>
       </c>
       <c r="C34" s="3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D34" s="3">
-        <v>4000</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B35" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C35">
-        <v>162</v>
+        <v>45</v>
       </c>
       <c r="D35" s="3">
-        <v>4000</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C36">
         <v>14</v>
       </c>
       <c r="D36" s="3">
-        <v>4000</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C37" s="3">
+        <v>30</v>
+      </c>
+      <c r="C37">
+        <v>68</v>
+      </c>
+      <c r="D37" s="3">
         <v>1500</v>
-      </c>
-      <c r="D37" s="3">
-        <v>3200</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="C38">
-        <v>29</v>
+        <v>22</v>
+      </c>
+      <c r="C38" s="3">
+        <v>1500</v>
       </c>
       <c r="D38" s="3">
-        <v>3200</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="C39" s="3">
-        <v>4</v>
+        <v>27</v>
+      </c>
+      <c r="C39">
+        <v>42</v>
       </c>
       <c r="D39" s="3">
-        <v>3200</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="C40">
-        <v>125</v>
+        <v>28</v>
+      </c>
+      <c r="C40" s="3">
+        <v>1</v>
       </c>
       <c r="D40" s="3">
-        <v>3200</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C41">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="D41" s="3">
-        <v>3200</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C42" s="3">
-        <v>1500</v>
+        <v>31</v>
+      </c>
+      <c r="C42">
+        <v>48</v>
       </c>
       <c r="D42" s="3">
-        <v>3000</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C43">
-        <v>25</v>
+        <v>176</v>
       </c>
       <c r="D43" s="3">
-        <v>3000</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C44" s="3">
-        <v>8</v>
+        <v>1500</v>
       </c>
       <c r="D44" s="3">
-        <v>3000</v>
+        <v>2600</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C45">
-        <v>48</v>
+        <v>26</v>
       </c>
       <c r="D45" s="3">
-        <v>3000</v>
+        <v>2600</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="C46">
-        <v>14</v>
+        <v>28</v>
+      </c>
+      <c r="C46" s="3">
+        <v>1</v>
       </c>
       <c r="D46" s="3">
-        <v>3000</v>
+        <v>2600</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A47" s="1" t="s">
-        <v>12</v>
+      <c r="A47" t="s">
+        <v>13</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C47" s="3">
-        <v>1500</v>
+        <v>29</v>
+      </c>
+      <c r="C47">
+        <v>140</v>
       </c>
       <c r="D47" s="3">
-        <v>1300</v>
+        <v>2600</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C48">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="D48" s="3">
-        <v>1300</v>
+        <v>2600</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="C49" s="3">
-        <v>8</v>
+        <v>30</v>
+      </c>
+      <c r="C49">
+        <v>98</v>
       </c>
       <c r="D49" s="3">
-        <v>1300</v>
+        <v>2600</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="C50">
-        <v>26</v>
+        <v>22</v>
+      </c>
+      <c r="C50" s="3">
+        <v>1200</v>
       </c>
       <c r="D50" s="3">
-        <v>1300</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C51">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="D51" s="3">
-        <v>1300</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="C52" s="3">
-        <v>1500</v>
+        <v>6</v>
       </c>
       <c r="D52" s="3">
-        <v>2500</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C53">
-        <v>12</v>
+        <v>56</v>
       </c>
       <c r="D53" s="3">
-        <v>2500</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
+        <v>7</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C54">
         <v>17</v>
       </c>
-      <c r="B54" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="C54" s="3">
-        <v>4</v>
-      </c>
       <c r="D54" s="3">
-        <v>2500</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C55">
-        <v>85</v>
+        <v>128</v>
       </c>
       <c r="D55" s="3">
-        <v>2500</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A56" t="s">
-        <v>17</v>
+      <c r="A56" s="1" t="s">
+        <v>12</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="C56">
-        <v>15</v>
+        <v>22</v>
+      </c>
+      <c r="C56" s="3">
+        <v>1200</v>
       </c>
       <c r="D56" s="3">
-        <v>2500</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C57" s="3">
+        <v>27</v>
+      </c>
+      <c r="C57">
+        <v>17</v>
+      </c>
+      <c r="D57" s="3">
         <v>1500</v>
-      </c>
-      <c r="D57" s="3">
-        <v>1300</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="C58">
-        <v>14</v>
+        <v>28</v>
+      </c>
+      <c r="C58" s="3">
+        <v>6</v>
       </c>
       <c r="D58" s="3">
-        <v>1300</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="C59" s="3">
-        <v>8</v>
+        <v>29</v>
+      </c>
+      <c r="C59">
+        <v>25</v>
       </c>
       <c r="D59" s="3">
-        <v>1300</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C60">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="D60" s="3">
-        <v>1300</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="B61" s="3" t="s">
         <v>30</v>
       </c>
       <c r="C61">
-        <v>14</v>
+        <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>1300</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B62" s="3" t="s">
         <v>22</v>
       </c>
       <c r="C62" s="3">
-        <v>1500</v>
+        <v>800</v>
       </c>
       <c r="D62" s="3">
-        <v>3000</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B63" s="3" t="s">
         <v>27</v>
       </c>
       <c r="C63">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="D63" s="3">
-        <v>3000</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B64" s="3" t="s">
         <v>28</v>
       </c>
       <c r="C64" s="3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D64" s="3">
-        <v>3000</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B65" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C65">
-        <v>59</v>
+        <v>82</v>
       </c>
       <c r="D65" s="3">
-        <v>3000</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C66">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="D66" s="3">
-        <v>3000</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C67" s="3">
-        <v>1500</v>
+        <v>30</v>
+      </c>
+      <c r="C67">
+        <v>60</v>
       </c>
       <c r="D67" s="3">
-        <v>2100</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="C68">
-        <v>20</v>
+        <v>22</v>
+      </c>
+      <c r="C68" s="3">
+        <v>1200</v>
       </c>
       <c r="D68" s="3">
-        <v>2100</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="C69" s="3">
-        <v>12</v>
+        <v>27</v>
+      </c>
+      <c r="C69">
+        <v>16</v>
       </c>
       <c r="D69" s="3">
-        <v>2100</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="C70">
-        <v>61</v>
+        <v>28</v>
+      </c>
+      <c r="C70" s="3">
+        <v>4</v>
       </c>
       <c r="D70" s="3">
-        <v>2100</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B71" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C71">
         <v>30</v>
       </c>
-      <c r="C71">
-        <v>16</v>
-      </c>
       <c r="D71" s="3">
-        <v>2100</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C72" s="3">
-        <v>1500</v>
+        <v>31</v>
+      </c>
+      <c r="C72">
+        <v>9</v>
       </c>
       <c r="D72" s="3">
-        <v>2800</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C73">
-        <v>19</v>
+        <v>74</v>
       </c>
       <c r="D73" s="3">
-        <v>2800</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C74" s="3">
-        <v>4</v>
+        <v>1200</v>
       </c>
       <c r="D74" s="3">
-        <v>2800</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C75">
-        <v>71</v>
+        <v>34</v>
       </c>
       <c r="D75" s="3">
-        <v>2800</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="C76">
-        <v>13</v>
+        <v>28</v>
+      </c>
+      <c r="C76" s="3">
+        <v>1</v>
       </c>
       <c r="D76" s="3">
-        <v>2800</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C77" s="3">
-        <v>1500</v>
+        <v>29</v>
+      </c>
+      <c r="C77">
+        <v>60</v>
       </c>
       <c r="D77" s="3">
-        <v>4000</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C78">
-        <v>45</v>
+        <v>18</v>
       </c>
       <c r="D78" s="3">
-        <v>4000</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="C79" s="3">
-        <v>16</v>
+        <v>30</v>
+      </c>
+      <c r="C79">
+        <v>183</v>
       </c>
       <c r="D79" s="3">
-        <v>4000</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="C80">
-        <v>99</v>
+        <v>22</v>
+      </c>
+      <c r="C80" s="3">
+        <v>1200</v>
       </c>
       <c r="D80" s="3">
-        <v>4000</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C81">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="D81" s="3">
-        <v>4000</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C82">
-        <v>14</v>
+        <v>28</v>
+      </c>
+      <c r="C82" s="3">
+        <v>6</v>
       </c>
       <c r="D82" s="3">
-        <v>4800</v>
-      </c>
-    </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C83">
-        <v>156</v>
+        <v>60</v>
       </c>
       <c r="D83" s="3">
-        <v>4800</v>
-      </c>
-    </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C84">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D84" s="3">
-        <v>4800</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C85">
-        <v>110</v>
+        <v>168</v>
       </c>
       <c r="D85" s="3">
-        <v>4800</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="C86">
-        <v>11</v>
+        <v>22</v>
+      </c>
+      <c r="C86" s="3">
+        <v>1200</v>
       </c>
       <c r="D86" s="3">
-        <v>4800</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C87" s="3">
-        <v>1500</v>
+        <v>27</v>
+      </c>
+      <c r="C87">
+        <v>23</v>
       </c>
       <c r="D87" s="3">
-        <v>4600</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="C88">
-        <v>66</v>
+        <v>28</v>
+      </c>
+      <c r="C88" s="3">
+        <v>1</v>
       </c>
       <c r="D88" s="3">
-        <v>4600</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="C89" s="3">
-        <v>18</v>
+        <v>29</v>
+      </c>
+      <c r="C89">
+        <v>72</v>
       </c>
       <c r="D89" s="3">
-        <v>4600</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C90">
-        <v>77</v>
+        <v>22</v>
       </c>
       <c r="D90" s="3">
-        <v>4600</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="B91" s="3" t="s">
         <v>30</v>
       </c>
       <c r="C91">
-        <v>13</v>
+        <v>92</v>
       </c>
       <c r="D91" s="3">
-        <v>4600</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="B92" s="3" t="s">
         <v>22</v>
@@ -1826,144 +1829,144 @@
         <v>1500</v>
       </c>
       <c r="D92" s="3">
-        <v>3000</v>
+        <v>2850</v>
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="B93" s="3" t="s">
         <v>27</v>
       </c>
       <c r="C93">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="D93" s="3">
-        <v>3000</v>
+        <v>2850</v>
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="B94" s="3" t="s">
         <v>28</v>
       </c>
       <c r="C94" s="3">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="D94" s="3">
-        <v>3000</v>
+        <v>2850</v>
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="B95" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C95">
-        <v>68</v>
+        <v>102</v>
       </c>
       <c r="D95" s="3">
-        <v>3000</v>
+        <v>2850</v>
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C96">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="D96" s="3">
-        <v>3000</v>
+        <v>2850</v>
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C97" s="3">
-        <v>1500</v>
+        <v>30</v>
+      </c>
+      <c r="C97">
+        <v>129</v>
       </c>
       <c r="D97" s="3">
-        <v>8000</v>
+        <v>2850</v>
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="C98">
-        <v>111</v>
+        <v>1500</v>
       </c>
       <c r="D98" s="3">
-        <v>8000</v>
+        <v>3500</v>
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="C99" s="3">
-        <v>24</v>
+        <v>27</v>
+      </c>
+      <c r="C99">
+        <v>62</v>
       </c>
       <c r="D99" s="3">
-        <v>8000</v>
+        <v>3500</v>
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C100">
-        <v>210</v>
+        <v>10</v>
       </c>
       <c r="D100" s="3">
-        <v>8000</v>
+        <v>3500</v>
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C101">
-        <v>14</v>
+        <v>124</v>
       </c>
       <c r="D101" s="3">
-        <v>8000</v>
+        <v>3500</v>
       </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C102" s="3">
-        <v>1500</v>
+        <v>31</v>
+      </c>
+      <c r="C102">
+        <v>37</v>
       </c>
       <c r="D102" s="3">
         <v>3500</v>
@@ -1971,13 +1974,13 @@
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C103">
-        <v>66</v>
+        <v>183</v>
       </c>
       <c r="D103" s="3">
         <v>3500</v>
@@ -1985,13 +1988,13 @@
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C104" s="3">
-        <v>16</v>
+        <v>1500</v>
       </c>
       <c r="D104" s="3">
         <v>3500</v>
@@ -1999,13 +2002,13 @@
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C105">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="D105" s="3">
         <v>3500</v>
@@ -2013,13 +2016,13 @@
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="B106" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="C106">
-        <v>18</v>
+        <v>28</v>
+      </c>
+      <c r="C106" s="3">
+        <v>16</v>
       </c>
       <c r="D106" s="3">
         <v>3500</v>
@@ -2027,13 +2030,13 @@
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B107" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C107" s="3">
-        <v>1500</v>
+        <v>29</v>
+      </c>
+      <c r="C107">
+        <v>96</v>
       </c>
       <c r="D107" s="3">
         <v>3500</v>
@@ -2041,10 +2044,10 @@
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B108" s="3" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C108">
         <v>29</v>
@@ -2055,13 +2058,13 @@
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B109" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="C109" s="3">
-        <v>20</v>
+        <v>30</v>
+      </c>
+      <c r="C109">
+        <v>198</v>
       </c>
       <c r="D109" s="3">
         <v>3500</v>
@@ -2069,34 +2072,346 @@
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B110" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="C110">
-        <v>93</v>
+        <v>22</v>
+      </c>
+      <c r="C110" s="3">
+        <v>1500</v>
       </c>
       <c r="D110" s="3">
-        <v>3500</v>
+        <v>2300</v>
       </c>
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
+        <v>14</v>
+      </c>
+      <c r="B111" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C111">
+        <v>44</v>
+      </c>
+      <c r="D111" s="3">
+        <v>2300</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>14</v>
+      </c>
+      <c r="B112" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C112" s="3">
+        <v>10</v>
+      </c>
+      <c r="D112" s="3">
+        <v>2300</v>
+      </c>
+    </row>
+    <row r="113" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>14</v>
+      </c>
+      <c r="B113" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C113">
+        <v>72</v>
+      </c>
+      <c r="D113" s="3">
+        <v>2300</v>
+      </c>
+    </row>
+    <row r="114" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>14</v>
+      </c>
+      <c r="B114" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C114">
+        <v>22</v>
+      </c>
+      <c r="D114" s="3">
+        <v>2300</v>
+      </c>
+    </row>
+    <row r="115" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>14</v>
+      </c>
+      <c r="B115" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C115">
+        <v>151</v>
+      </c>
+      <c r="D115" s="3">
+        <v>2300</v>
+      </c>
+    </row>
+    <row r="116" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>16</v>
+      </c>
+      <c r="B116" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C116" s="3">
+        <v>1500</v>
+      </c>
+      <c r="D116" s="3">
+        <v>5700</v>
+      </c>
+    </row>
+    <row r="117" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>16</v>
+      </c>
+      <c r="B117" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C117">
+        <v>103</v>
+      </c>
+      <c r="D117" s="3">
+        <v>5700</v>
+      </c>
+    </row>
+    <row r="118" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>16</v>
+      </c>
+      <c r="B118" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C118" s="3">
+        <v>14</v>
+      </c>
+      <c r="D118" s="3">
+        <v>5700</v>
+      </c>
+    </row>
+    <row r="119" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>16</v>
+      </c>
+      <c r="B119" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C119">
+        <v>236</v>
+      </c>
+      <c r="D119" s="3">
+        <v>5700</v>
+      </c>
+    </row>
+    <row r="120" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>16</v>
+      </c>
+      <c r="B120" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C120">
+        <v>71</v>
+      </c>
+      <c r="D120" s="3">
+        <v>5700</v>
+      </c>
+    </row>
+    <row r="121" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>16</v>
+      </c>
+      <c r="B121" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C121">
+        <v>192</v>
+      </c>
+      <c r="D121" s="3">
+        <v>5700</v>
+      </c>
+    </row>
+    <row r="122" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>19</v>
+      </c>
+      <c r="B122" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C122" s="3">
+        <v>1500</v>
+      </c>
+      <c r="D122" s="3">
+        <v>2600</v>
+      </c>
+    </row>
+    <row r="123" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>19</v>
+      </c>
+      <c r="B123" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C123">
+        <v>62</v>
+      </c>
+      <c r="D123" s="3">
+        <v>2600</v>
+      </c>
+    </row>
+    <row r="124" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>19</v>
+      </c>
+      <c r="B124" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C124" s="3">
+        <v>11</v>
+      </c>
+      <c r="D124" s="3">
+        <v>2600</v>
+      </c>
+    </row>
+    <row r="125" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>19</v>
+      </c>
+      <c r="B125" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C125">
+        <v>74</v>
+      </c>
+      <c r="D125" s="3">
+        <v>2600</v>
+      </c>
+    </row>
+    <row r="126" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>19</v>
+      </c>
+      <c r="B126" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C126">
+        <v>22</v>
+      </c>
+      <c r="D126" s="3">
+        <v>2600</v>
+      </c>
+    </row>
+    <row r="127" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>19</v>
+      </c>
+      <c r="B127" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C127">
+        <v>181</v>
+      </c>
+      <c r="D127" s="3">
+        <v>2600</v>
+      </c>
+    </row>
+    <row r="128" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
         <v>15</v>
       </c>
-      <c r="B111" s="3" t="s">
+      <c r="B128" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C128" s="3">
+        <v>1500</v>
+      </c>
+      <c r="D128" s="3">
+        <v>2650</v>
+      </c>
+    </row>
+    <row r="129" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
+        <v>15</v>
+      </c>
+      <c r="B129" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C129">
         <v>30</v>
       </c>
-      <c r="C111">
-        <v>19</v>
-      </c>
-      <c r="D111" s="3">
-        <v>3500</v>
-      </c>
+      <c r="D129" s="3">
+        <v>2650</v>
+      </c>
+    </row>
+    <row r="130" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
+        <v>15</v>
+      </c>
+      <c r="B130" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C130" s="3">
+        <v>10</v>
+      </c>
+      <c r="D130" s="3">
+        <v>2650</v>
+      </c>
+    </row>
+    <row r="131" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A131" t="s">
+        <v>15</v>
+      </c>
+      <c r="B131" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C131">
+        <v>92</v>
+      </c>
+      <c r="D131" s="3">
+        <v>2650</v>
+      </c>
+    </row>
+    <row r="132" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A132" t="s">
+        <v>15</v>
+      </c>
+      <c r="B132" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C132">
+        <v>28</v>
+      </c>
+      <c r="D132" s="3">
+        <v>2650</v>
+      </c>
+    </row>
+    <row r="133" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A133" t="s">
+        <v>15</v>
+      </c>
+      <c r="B133" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C133">
+        <v>126</v>
+      </c>
+      <c r="D133" s="3">
+        <v>2650</v>
+      </c>
+    </row>
+    <row r="134" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B134" s="3"/>
+      <c r="D134" s="3"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D111" xr:uid="{6956BB2C-DA9E-4412-BCD4-BB80A11153FE}"/>
+  <autoFilter ref="A1:D133" xr:uid="{6956BB2C-DA9E-4412-BCD4-BB80A11153FE}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/data/metas.xlsx
+++ b/data/metas.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sercomunicaciones2-my.sharepoint.com/personal/auxcomisiones_sercomunicaciones_com/Documents/PAOLA/Liquidacióncvs - copia/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sercomunicaciones2-my.sharepoint.com/personal/auxcomisiones_sercomunicaciones_com/Documents/PAOLA/Liquidacióncvs/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="485" documentId="8_{787D9E49-702D-43BD-B99B-4B64F775E77B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E36E46B0-C4A9-44B0-A485-DEF0474E71DD}"/>
+  <xr:revisionPtr revIDLastSave="498" documentId="8_{787D9E49-702D-43BD-B99B-4B64F775E77B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{721347E6-3311-4F3E-BE72-BF5D977AA3E8}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D1391136-BBFC-43C7-B899-B77B0ECC5956}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="33">
   <si>
     <t>BARBOSA</t>
   </si>
@@ -135,6 +135,9 @@
   </si>
   <si>
     <t>FOCO</t>
+  </si>
+  <si>
+    <t>GENERAL</t>
   </si>
 </sst>
 </file>
@@ -536,7 +539,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6956BB2C-DA9E-4412-BCD4-BB80A11153FE}">
-  <dimension ref="A1:D134"/>
+  <dimension ref="A1:D139"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="25" customWidth="1"/>
@@ -2407,8 +2410,88 @@
       </c>
     </row>
     <row r="134" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B134" s="3"/>
-      <c r="D134" s="3"/>
+      <c r="A134" t="s">
+        <v>32</v>
+      </c>
+      <c r="B134" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C134">
+        <v>27700</v>
+      </c>
+      <c r="D134" s="3">
+        <v>53500</v>
+      </c>
+    </row>
+    <row r="135" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A135" t="s">
+        <v>32</v>
+      </c>
+      <c r="B135" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C135">
+        <v>840</v>
+      </c>
+      <c r="D135" s="3">
+        <v>53500</v>
+      </c>
+    </row>
+    <row r="136" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A136" t="s">
+        <v>32</v>
+      </c>
+      <c r="B136" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C136">
+        <v>131</v>
+      </c>
+      <c r="D136" s="3">
+        <v>53500</v>
+      </c>
+    </row>
+    <row r="137" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A137" t="s">
+        <v>32</v>
+      </c>
+      <c r="B137" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C137">
+        <v>1868</v>
+      </c>
+      <c r="D137" s="3">
+        <v>53500</v>
+      </c>
+    </row>
+    <row r="138" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A138" t="s">
+        <v>32</v>
+      </c>
+      <c r="B138" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C138">
+        <v>565</v>
+      </c>
+      <c r="D138" s="3">
+        <v>53500</v>
+      </c>
+    </row>
+    <row r="139" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A139" t="s">
+        <v>32</v>
+      </c>
+      <c r="B139" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C139">
+        <v>2738</v>
+      </c>
+      <c r="D139" s="3">
+        <v>53500</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:D133" xr:uid="{6956BB2C-DA9E-4412-BCD4-BB80A11153FE}"/>

--- a/data/metas.xlsx
+++ b/data/metas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sercomunicaciones2-my.sharepoint.com/personal/auxcomisiones_sercomunicaciones_com/Documents/PAOLA/Liquidacióncvs/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="498" documentId="8_{787D9E49-702D-43BD-B99B-4B64F775E77B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{721347E6-3311-4F3E-BE72-BF5D977AA3E8}"/>
+  <xr:revisionPtr revIDLastSave="512" documentId="8_{787D9E49-702D-43BD-B99B-4B64F775E77B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{36E9D8F0-8C88-4591-B248-CA2B35854662}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D1391136-BBFC-43C7-B899-B77B0ECC5956}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$A$1:$D$133</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$B$1:$E$133</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="419" uniqueCount="35">
   <si>
     <t>BARBOSA</t>
   </si>
@@ -139,6 +139,12 @@
   <si>
     <t>GENERAL</t>
   </si>
+  <si>
+    <t>Mes</t>
+  </si>
+  <si>
+    <t>Febrero</t>
+  </si>
 </sst>
 </file>
 
@@ -196,7 +202,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -205,6 +211,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -539,1962 +546,2992 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6956BB2C-DA9E-4412-BCD4-BB80A11153FE}">
-  <dimension ref="A1:D139"/>
+  <dimension ref="A1:E277"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="25" customWidth="1"/>
-    <col min="2" max="2" width="12.85546875" customWidth="1"/>
-    <col min="3" max="3" width="15.7109375" customWidth="1"/>
+    <col min="1" max="1" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25" customWidth="1"/>
+    <col min="3" max="3" width="12.85546875" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="C1" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="D1" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="E1" s="2" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="C2" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C2" s="3">
+      <c r="D2" s="3">
         <v>1500</v>
       </c>
-      <c r="D2" s="3">
+      <c r="E2" s="3">
         <v>2800</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="C3" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="C3" s="3">
+      <c r="D3" s="3">
         <v>47</v>
       </c>
-      <c r="D3" s="3">
+      <c r="E3" s="3">
         <v>2800</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="C4" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="C4" s="3">
+      <c r="D4" s="3">
         <v>10</v>
       </c>
-      <c r="D4" s="3">
+      <c r="E4" s="3">
         <v>2800</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>34</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="C5" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C5" s="3">
+      <c r="D5" s="3">
         <v>95</v>
       </c>
-      <c r="D5" s="3">
+      <c r="E5" s="3">
         <v>2800</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>34</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="C6" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C6" s="3">
+      <c r="D6" s="3">
         <v>29</v>
       </c>
-      <c r="D6" s="3">
+      <c r="E6" s="3">
         <v>2800</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>34</v>
+      </c>
+      <c r="B7" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="C7" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C7" s="3">
+      <c r="D7" s="3">
         <v>146</v>
       </c>
-      <c r="D7" s="3">
+      <c r="E7" s="3">
         <v>2800</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="3" t="s">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>34</v>
+      </c>
+      <c r="B8" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="C8" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C8" s="3">
+      <c r="D8" s="3">
         <v>1500</v>
       </c>
-      <c r="D8" s="3">
+      <c r="E8" s="3">
         <v>2400</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="3" t="s">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>34</v>
+      </c>
+      <c r="B9" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="C9" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="C9" s="3">
+      <c r="D9" s="3">
         <v>37</v>
       </c>
-      <c r="D9" s="3">
+      <c r="E9" s="3">
         <v>2400</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="3" t="s">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>34</v>
+      </c>
+      <c r="B10" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="C10" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="C10" s="3">
+      <c r="D10" s="3">
         <v>6</v>
       </c>
-      <c r="D10" s="3">
+      <c r="E10" s="3">
         <v>2400</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="3" t="s">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>34</v>
+      </c>
+      <c r="B11" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="C11" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C11">
+      <c r="D11">
         <v>82</v>
       </c>
-      <c r="D11" s="3">
+      <c r="E11" s="3">
         <v>2400</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="3" t="s">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>34</v>
+      </c>
+      <c r="B12" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="C12" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C12">
+      <c r="D12">
         <v>25</v>
       </c>
-      <c r="D12" s="3">
+      <c r="E12" s="3">
         <v>2400</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="3" t="s">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>34</v>
+      </c>
+      <c r="B13" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="C13" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C13">
+      <c r="D13">
         <v>95</v>
       </c>
-      <c r="D13" s="3">
+      <c r="E13" s="3">
         <v>2400</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
+        <v>34</v>
+      </c>
+      <c r="B14" t="s">
         <v>2</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="C14" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C14" s="3">
+      <c r="D14" s="3">
         <v>0</v>
       </c>
-      <c r="D14" s="3">
+      <c r="E14" s="3">
         <v>1350</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
+        <v>34</v>
+      </c>
+      <c r="B15" t="s">
         <v>2</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="C15" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="C15">
+      <c r="D15">
         <v>12</v>
       </c>
-      <c r="D15" s="3">
+      <c r="E15" s="3">
         <v>1350</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
+        <v>34</v>
+      </c>
+      <c r="B16" t="s">
         <v>2</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="C16" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="C16" s="3">
+      <c r="D16" s="3">
         <v>4</v>
       </c>
-      <c r="D16" s="3">
+      <c r="E16" s="3">
         <v>1350</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
+        <v>34</v>
+      </c>
+      <c r="B17" t="s">
         <v>2</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="C17" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C17">
+      <c r="D17">
         <v>50</v>
       </c>
-      <c r="D17" s="3">
+      <c r="E17" s="3">
         <v>1350</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
+        <v>34</v>
+      </c>
+      <c r="B18" t="s">
         <v>2</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="C18" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C18">
+      <c r="D18">
         <v>15</v>
       </c>
-      <c r="D18" s="3">
+      <c r="E18" s="3">
         <v>1350</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
+        <v>34</v>
+      </c>
+      <c r="B19" t="s">
         <v>2</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="C19" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C19">
+      <c r="D19">
         <v>32</v>
       </c>
-      <c r="D19" s="3">
+      <c r="E19" s="3">
         <v>1350</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
+        <v>34</v>
+      </c>
+      <c r="B20" t="s">
         <v>3</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="C20" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C20" s="3">
+      <c r="D20" s="3">
         <v>800</v>
       </c>
-      <c r="D20" s="3">
+      <c r="E20" s="3">
         <v>1700</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
+        <v>34</v>
+      </c>
+      <c r="B21" t="s">
         <v>3</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="C21" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="C21">
+      <c r="D21">
         <v>33</v>
       </c>
-      <c r="D21" s="3">
+      <c r="E21" s="3">
         <v>1700</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
+        <v>34</v>
+      </c>
+      <c r="B22" t="s">
         <v>3</v>
       </c>
-      <c r="B22" s="3" t="s">
+      <c r="C22" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="C22" s="3">
+      <c r="D22" s="3">
         <v>1</v>
       </c>
-      <c r="D22" s="3">
+      <c r="E22" s="3">
         <v>1700</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
+        <v>34</v>
+      </c>
+      <c r="B23" t="s">
         <v>3</v>
       </c>
-      <c r="B23" s="3" t="s">
+      <c r="C23" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C23">
+      <c r="D23">
         <v>65</v>
       </c>
-      <c r="D23" s="3">
+      <c r="E23" s="3">
         <v>1700</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
+        <v>34</v>
+      </c>
+      <c r="B24" t="s">
         <v>3</v>
       </c>
-      <c r="B24" s="3" t="s">
+      <c r="C24" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C24">
+      <c r="D24">
         <v>20</v>
       </c>
-      <c r="D24" s="3">
+      <c r="E24" s="3">
         <v>1700</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
+        <v>34</v>
+      </c>
+      <c r="B25" t="s">
         <v>3</v>
       </c>
-      <c r="B25" s="3" t="s">
+      <c r="C25" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C25">
+      <c r="D25">
         <v>135</v>
       </c>
-      <c r="D25" s="3">
+      <c r="E25" s="3">
         <v>1700</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
+        <v>34</v>
+      </c>
+      <c r="B26" t="s">
         <v>8</v>
       </c>
-      <c r="B26" s="3" t="s">
+      <c r="C26" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C26" s="3">
+      <c r="D26" s="3">
         <v>1200</v>
       </c>
-      <c r="D26" s="3">
+      <c r="E26" s="3">
         <v>1450</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
+        <v>34</v>
+      </c>
+      <c r="B27" t="s">
         <v>8</v>
       </c>
-      <c r="B27" s="3" t="s">
+      <c r="C27" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="C27">
+      <c r="D27">
         <v>18</v>
       </c>
-      <c r="D27" s="3">
+      <c r="E27" s="3">
         <v>1450</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
+        <v>34</v>
+      </c>
+      <c r="B28" t="s">
         <v>8</v>
       </c>
-      <c r="B28" s="3" t="s">
+      <c r="C28" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="C28" s="3">
+      <c r="D28" s="3">
         <v>1</v>
       </c>
-      <c r="D28" s="3">
+      <c r="E28" s="3">
         <v>1450</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
+        <v>34</v>
+      </c>
+      <c r="B29" t="s">
         <v>8</v>
       </c>
-      <c r="B29" s="3" t="s">
+      <c r="C29" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C29">
+      <c r="D29">
         <v>50</v>
       </c>
-      <c r="D29" s="3">
+      <c r="E29" s="3">
         <v>1450</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
+        <v>34</v>
+      </c>
+      <c r="B30" t="s">
         <v>8</v>
       </c>
-      <c r="B30" s="3" t="s">
+      <c r="C30" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C30">
+      <c r="D30">
         <v>15</v>
       </c>
-      <c r="D30" s="3">
+      <c r="E30" s="3">
         <v>1450</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
+        <v>34</v>
+      </c>
+      <c r="B31" t="s">
         <v>8</v>
       </c>
-      <c r="B31" s="3" t="s">
+      <c r="C31" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C31">
+      <c r="D31">
         <v>69</v>
       </c>
-      <c r="D31" s="3">
+      <c r="E31" s="3">
         <v>1450</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
+        <v>34</v>
+      </c>
+      <c r="B32" t="s">
         <v>10</v>
       </c>
-      <c r="B32" s="3" t="s">
+      <c r="C32" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C32" s="3">
+      <c r="D32" s="3">
         <v>1200</v>
       </c>
-      <c r="D32" s="3">
+      <c r="E32" s="3">
         <v>1500</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
+        <v>34</v>
+      </c>
+      <c r="B33" t="s">
         <v>10</v>
       </c>
-      <c r="B33" s="3" t="s">
+      <c r="C33" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="C33">
+      <c r="D33">
         <v>37</v>
       </c>
-      <c r="D33" s="3">
+      <c r="E33" s="3">
         <v>1500</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
+        <v>34</v>
+      </c>
+      <c r="B34" t="s">
         <v>10</v>
       </c>
-      <c r="B34" s="3" t="s">
+      <c r="C34" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="C34" s="3">
+      <c r="D34" s="3">
         <v>1</v>
       </c>
-      <c r="D34" s="3">
+      <c r="E34" s="3">
         <v>1500</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
+        <v>34</v>
+      </c>
+      <c r="B35" t="s">
         <v>10</v>
       </c>
-      <c r="B35" s="3" t="s">
+      <c r="C35" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C35">
+      <c r="D35">
         <v>45</v>
       </c>
-      <c r="D35" s="3">
+      <c r="E35" s="3">
         <v>1500</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
+        <v>34</v>
+      </c>
+      <c r="B36" t="s">
         <v>10</v>
       </c>
-      <c r="B36" s="3" t="s">
+      <c r="C36" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C36">
+      <c r="D36">
         <v>14</v>
       </c>
-      <c r="D36" s="3">
+      <c r="E36" s="3">
         <v>1500</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
+        <v>34</v>
+      </c>
+      <c r="B37" t="s">
         <v>10</v>
       </c>
-      <c r="B37" s="3" t="s">
+      <c r="C37" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C37">
+      <c r="D37">
         <v>68</v>
       </c>
-      <c r="D37" s="3">
+      <c r="E37" s="3">
         <v>1500</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
+        <v>34</v>
+      </c>
+      <c r="B38" t="s">
         <v>9</v>
       </c>
-      <c r="B38" s="3" t="s">
+      <c r="C38" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C38" s="3">
+      <c r="D38" s="3">
         <v>1500</v>
       </c>
-      <c r="D38" s="3">
+      <c r="E38" s="3">
         <v>4000</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
+        <v>34</v>
+      </c>
+      <c r="B39" t="s">
         <v>9</v>
       </c>
-      <c r="B39" s="3" t="s">
+      <c r="C39" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="C39">
+      <c r="D39">
         <v>42</v>
       </c>
-      <c r="D39" s="3">
+      <c r="E39" s="3">
         <v>4000</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
+        <v>34</v>
+      </c>
+      <c r="B40" t="s">
         <v>9</v>
       </c>
-      <c r="B40" s="3" t="s">
+      <c r="C40" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="C40" s="3">
+      <c r="D40" s="3">
         <v>1</v>
       </c>
-      <c r="D40" s="3">
+      <c r="E40" s="3">
         <v>4000</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
+        <v>34</v>
+      </c>
+      <c r="B41" t="s">
         <v>9</v>
       </c>
-      <c r="B41" s="3" t="s">
+      <c r="C41" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C41">
+      <c r="D41">
         <v>160</v>
       </c>
-      <c r="D41" s="3">
+      <c r="E41" s="3">
         <v>4000</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
+        <v>34</v>
+      </c>
+      <c r="B42" t="s">
         <v>9</v>
       </c>
-      <c r="B42" s="3" t="s">
+      <c r="C42" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C42">
+      <c r="D42">
         <v>48</v>
       </c>
-      <c r="D42" s="3">
+      <c r="E42" s="3">
         <v>4000</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
+        <v>34</v>
+      </c>
+      <c r="B43" t="s">
         <v>9</v>
       </c>
-      <c r="B43" s="3" t="s">
+      <c r="C43" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C43">
+      <c r="D43">
         <v>176</v>
       </c>
-      <c r="D43" s="3">
+      <c r="E43" s="3">
         <v>4000</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
+        <v>34</v>
+      </c>
+      <c r="B44" t="s">
         <v>13</v>
       </c>
-      <c r="B44" s="3" t="s">
+      <c r="C44" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C44" s="3">
+      <c r="D44" s="3">
         <v>1500</v>
       </c>
-      <c r="D44" s="3">
+      <c r="E44" s="3">
         <v>2600</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
+        <v>34</v>
+      </c>
+      <c r="B45" t="s">
         <v>13</v>
       </c>
-      <c r="B45" s="3" t="s">
+      <c r="C45" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="C45">
+      <c r="D45">
         <v>26</v>
       </c>
-      <c r="D45" s="3">
+      <c r="E45" s="3">
         <v>2600</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
+        <v>34</v>
+      </c>
+      <c r="B46" t="s">
         <v>13</v>
       </c>
-      <c r="B46" s="3" t="s">
+      <c r="C46" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="C46" s="3">
+      <c r="D46" s="3">
         <v>1</v>
       </c>
-      <c r="D46" s="3">
+      <c r="E46" s="3">
         <v>2600</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
+        <v>34</v>
+      </c>
+      <c r="B47" t="s">
         <v>13</v>
       </c>
-      <c r="B47" s="3" t="s">
+      <c r="C47" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C47">
+      <c r="D47">
         <v>140</v>
       </c>
-      <c r="D47" s="3">
+      <c r="E47" s="3">
         <v>2600</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
+        <v>34</v>
+      </c>
+      <c r="B48" t="s">
         <v>13</v>
       </c>
-      <c r="B48" s="3" t="s">
+      <c r="C48" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C48">
+      <c r="D48">
         <v>42</v>
       </c>
-      <c r="D48" s="3">
+      <c r="E48" s="3">
         <v>2600</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
+        <v>34</v>
+      </c>
+      <c r="B49" t="s">
         <v>13</v>
       </c>
-      <c r="B49" s="3" t="s">
+      <c r="C49" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C49">
+      <c r="D49">
         <v>98</v>
       </c>
-      <c r="D49" s="3">
+      <c r="E49" s="3">
         <v>2600</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
+        <v>34</v>
+      </c>
+      <c r="B50" t="s">
         <v>7</v>
       </c>
-      <c r="B50" s="3" t="s">
+      <c r="C50" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C50" s="3">
+      <c r="D50" s="3">
         <v>1200</v>
       </c>
-      <c r="D50" s="3">
+      <c r="E50" s="3">
         <v>2000</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
+        <v>34</v>
+      </c>
+      <c r="B51" t="s">
         <v>7</v>
       </c>
-      <c r="B51" s="3" t="s">
+      <c r="C51" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="C51">
+      <c r="D51">
         <v>32</v>
       </c>
-      <c r="D51" s="3">
+      <c r="E51" s="3">
         <v>2000</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
+        <v>34</v>
+      </c>
+      <c r="B52" t="s">
         <v>7</v>
       </c>
-      <c r="B52" s="3" t="s">
+      <c r="C52" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="C52" s="3">
+      <c r="D52" s="3">
         <v>6</v>
       </c>
-      <c r="D52" s="3">
+      <c r="E52" s="3">
         <v>2000</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
+        <v>34</v>
+      </c>
+      <c r="B53" t="s">
         <v>7</v>
       </c>
-      <c r="B53" s="3" t="s">
+      <c r="C53" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C53">
+      <c r="D53">
         <v>56</v>
       </c>
-      <c r="D53" s="3">
+      <c r="E53" s="3">
         <v>2000</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
+        <v>34</v>
+      </c>
+      <c r="B54" t="s">
         <v>7</v>
       </c>
-      <c r="B54" s="3" t="s">
+      <c r="C54" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C54">
+      <c r="D54">
         <v>17</v>
       </c>
-      <c r="D54" s="3">
+      <c r="E54" s="3">
         <v>2000</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
+        <v>34</v>
+      </c>
+      <c r="B55" t="s">
         <v>7</v>
       </c>
-      <c r="B55" s="3" t="s">
+      <c r="C55" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C55">
+      <c r="D55">
         <v>128</v>
       </c>
-      <c r="D55" s="3">
+      <c r="E55" s="3">
         <v>2000</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A56" s="1" t="s">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>34</v>
+      </c>
+      <c r="B56" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B56" s="3" t="s">
+      <c r="C56" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C56" s="3">
+      <c r="D56" s="3">
         <v>1200</v>
       </c>
-      <c r="D56" s="3">
+      <c r="E56" s="3">
         <v>1500</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
+        <v>34</v>
+      </c>
+      <c r="B57" t="s">
         <v>12</v>
       </c>
-      <c r="B57" s="3" t="s">
+      <c r="C57" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="C57">
+      <c r="D57">
         <v>17</v>
       </c>
-      <c r="D57" s="3">
+      <c r="E57" s="3">
         <v>1500</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
+        <v>34</v>
+      </c>
+      <c r="B58" t="s">
         <v>12</v>
       </c>
-      <c r="B58" s="3" t="s">
+      <c r="C58" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="C58" s="3">
+      <c r="D58" s="3">
         <v>6</v>
       </c>
-      <c r="D58" s="3">
+      <c r="E58" s="3">
         <v>1500</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
+        <v>34</v>
+      </c>
+      <c r="B59" t="s">
         <v>12</v>
       </c>
-      <c r="B59" s="3" t="s">
+      <c r="C59" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C59">
+      <c r="D59">
         <v>25</v>
       </c>
-      <c r="D59" s="3">
+      <c r="E59" s="3">
         <v>1500</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
+        <v>34</v>
+      </c>
+      <c r="B60" t="s">
         <v>12</v>
       </c>
-      <c r="B60" s="3" t="s">
+      <c r="C60" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C60">
+      <c r="D60">
         <v>8</v>
       </c>
-      <c r="D60" s="3">
+      <c r="E60" s="3">
         <v>1500</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
+        <v>34</v>
+      </c>
+      <c r="B61" t="s">
         <v>12</v>
       </c>
-      <c r="B61" s="3" t="s">
+      <c r="C61" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C61">
+      <c r="D61">
         <v>54</v>
       </c>
-      <c r="D61" s="3">
+      <c r="E61" s="3">
         <v>1500</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
+        <v>34</v>
+      </c>
+      <c r="B62" t="s">
         <v>17</v>
       </c>
-      <c r="B62" s="3" t="s">
+      <c r="C62" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C62" s="3">
+      <c r="D62" s="3">
         <v>800</v>
       </c>
-      <c r="D62" s="3">
+      <c r="E62" s="3">
         <v>2000</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
+        <v>34</v>
+      </c>
+      <c r="B63" t="s">
         <v>17</v>
       </c>
-      <c r="B63" s="3" t="s">
+      <c r="C63" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="C63">
+      <c r="D63">
         <v>13</v>
       </c>
-      <c r="D63" s="3">
+      <c r="E63" s="3">
         <v>2000</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
+        <v>34</v>
+      </c>
+      <c r="B64" t="s">
         <v>17</v>
       </c>
-      <c r="B64" s="3" t="s">
+      <c r="C64" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="C64" s="3">
+      <c r="D64" s="3">
         <v>1</v>
       </c>
-      <c r="D64" s="3">
+      <c r="E64" s="3">
         <v>2000</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
+        <v>34</v>
+      </c>
+      <c r="B65" t="s">
         <v>17</v>
       </c>
-      <c r="B65" s="3" t="s">
+      <c r="C65" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C65">
+      <c r="D65">
         <v>82</v>
       </c>
-      <c r="D65" s="3">
+      <c r="E65" s="3">
         <v>2000</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
+        <v>34</v>
+      </c>
+      <c r="B66" t="s">
         <v>17</v>
       </c>
-      <c r="B66" s="3" t="s">
+      <c r="C66" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C66">
+      <c r="D66">
         <v>25</v>
       </c>
-      <c r="D66" s="3">
+      <c r="E66" s="3">
         <v>2000</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
+        <v>34</v>
+      </c>
+      <c r="B67" t="s">
         <v>17</v>
       </c>
-      <c r="B67" s="3" t="s">
+      <c r="C67" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C67">
+      <c r="D67">
         <v>60</v>
       </c>
-      <c r="D67" s="3">
+      <c r="E67" s="3">
         <v>2000</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
+        <v>34</v>
+      </c>
+      <c r="B68" t="s">
         <v>18</v>
       </c>
-      <c r="B68" s="3" t="s">
+      <c r="C68" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C68" s="3">
+      <c r="D68" s="3">
         <v>1200</v>
       </c>
-      <c r="D68" s="3">
+      <c r="E68" s="3">
         <v>1100</v>
       </c>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
+        <v>34</v>
+      </c>
+      <c r="B69" t="s">
         <v>18</v>
       </c>
-      <c r="B69" s="3" t="s">
+      <c r="C69" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="C69">
+      <c r="D69">
         <v>16</v>
       </c>
-      <c r="D69" s="3">
+      <c r="E69" s="3">
         <v>1100</v>
       </c>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
+        <v>34</v>
+      </c>
+      <c r="B70" t="s">
         <v>18</v>
       </c>
-      <c r="B70" s="3" t="s">
+      <c r="C70" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="C70" s="3">
+      <c r="D70" s="3">
         <v>4</v>
       </c>
-      <c r="D70" s="3">
+      <c r="E70" s="3">
         <v>1100</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
+        <v>34</v>
+      </c>
+      <c r="B71" t="s">
         <v>18</v>
       </c>
-      <c r="B71" s="3" t="s">
+      <c r="C71" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C71">
+      <c r="D71">
         <v>30</v>
       </c>
-      <c r="D71" s="3">
+      <c r="E71" s="3">
         <v>1100</v>
       </c>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
+        <v>34</v>
+      </c>
+      <c r="B72" t="s">
         <v>18</v>
       </c>
-      <c r="B72" s="3" t="s">
+      <c r="C72" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C72">
+      <c r="D72">
         <v>9</v>
       </c>
-      <c r="D72" s="3">
+      <c r="E72" s="3">
         <v>1100</v>
       </c>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
+        <v>34</v>
+      </c>
+      <c r="B73" t="s">
         <v>18</v>
       </c>
-      <c r="B73" s="3" t="s">
+      <c r="C73" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C73">
+      <c r="D73">
         <v>74</v>
       </c>
-      <c r="D73" s="3">
+      <c r="E73" s="3">
         <v>1100</v>
       </c>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
+        <v>34</v>
+      </c>
+      <c r="B74" t="s">
         <v>20</v>
       </c>
-      <c r="B74" s="3" t="s">
+      <c r="C74" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C74" s="3">
+      <c r="D74" s="3">
         <v>1200</v>
       </c>
-      <c r="D74" s="3">
+      <c r="E74" s="3">
         <v>2200</v>
       </c>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
+        <v>34</v>
+      </c>
+      <c r="B75" t="s">
         <v>20</v>
       </c>
-      <c r="B75" s="3" t="s">
+      <c r="C75" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="C75">
-        <v>34</v>
-      </c>
-      <c r="D75" s="3">
+      <c r="D75">
+        <v>34</v>
+      </c>
+      <c r="E75" s="3">
         <v>2200</v>
       </c>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
+        <v>34</v>
+      </c>
+      <c r="B76" t="s">
         <v>20</v>
       </c>
-      <c r="B76" s="3" t="s">
+      <c r="C76" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="C76" s="3">
+      <c r="D76" s="3">
         <v>1</v>
       </c>
-      <c r="D76" s="3">
+      <c r="E76" s="3">
         <v>2200</v>
       </c>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
+        <v>34</v>
+      </c>
+      <c r="B77" t="s">
         <v>20</v>
       </c>
-      <c r="B77" s="3" t="s">
+      <c r="C77" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C77">
+      <c r="D77">
         <v>60</v>
       </c>
-      <c r="D77" s="3">
+      <c r="E77" s="3">
         <v>2200</v>
       </c>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
+        <v>34</v>
+      </c>
+      <c r="B78" t="s">
         <v>20</v>
       </c>
-      <c r="B78" s="3" t="s">
+      <c r="C78" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C78">
+      <c r="D78">
         <v>18</v>
       </c>
-      <c r="D78" s="3">
+      <c r="E78" s="3">
         <v>2200</v>
       </c>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
+        <v>34</v>
+      </c>
+      <c r="B79" t="s">
         <v>20</v>
       </c>
-      <c r="B79" s="3" t="s">
+      <c r="C79" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C79">
+      <c r="D79">
         <v>183</v>
       </c>
-      <c r="D79" s="3">
+      <c r="E79" s="3">
         <v>2200</v>
       </c>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
+        <v>34</v>
+      </c>
+      <c r="B80" t="s">
         <v>21</v>
       </c>
-      <c r="B80" s="3" t="s">
+      <c r="C80" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C80" s="3">
+      <c r="D80" s="3">
         <v>1200</v>
       </c>
-      <c r="D80" s="3">
+      <c r="E80" s="3">
         <v>1600</v>
       </c>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
+        <v>34</v>
+      </c>
+      <c r="B81" t="s">
         <v>21</v>
       </c>
-      <c r="B81" s="3" t="s">
+      <c r="C81" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="C81">
+      <c r="D81">
         <v>22</v>
       </c>
-      <c r="D81" s="3">
+      <c r="E81" s="3">
         <v>1600</v>
       </c>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
+        <v>34</v>
+      </c>
+      <c r="B82" t="s">
         <v>21</v>
       </c>
-      <c r="B82" s="3" t="s">
+      <c r="C82" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="C82" s="3">
+      <c r="D82" s="3">
         <v>6</v>
       </c>
-      <c r="D82" s="3">
+      <c r="E82" s="3">
         <v>1600</v>
       </c>
     </row>
-    <row r="83" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
+        <v>34</v>
+      </c>
+      <c r="B83" t="s">
         <v>21</v>
       </c>
-      <c r="B83" s="3" t="s">
+      <c r="C83" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C83">
+      <c r="D83">
         <v>60</v>
       </c>
-      <c r="D83" s="3">
+      <c r="E83" s="3">
         <v>1600</v>
       </c>
     </row>
-    <row r="84" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
+        <v>34</v>
+      </c>
+      <c r="B84" t="s">
         <v>21</v>
       </c>
-      <c r="B84" s="3" t="s">
+      <c r="C84" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C84">
+      <c r="D84">
         <v>18</v>
       </c>
-      <c r="D84" s="3">
+      <c r="E84" s="3">
         <v>1600</v>
       </c>
     </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
+        <v>34</v>
+      </c>
+      <c r="B85" t="s">
         <v>21</v>
       </c>
-      <c r="B85" s="3" t="s">
+      <c r="C85" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C85">
+      <c r="D85">
         <v>168</v>
       </c>
-      <c r="D85" s="3">
+      <c r="E85" s="3">
         <v>1600</v>
       </c>
     </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
+        <v>34</v>
+      </c>
+      <c r="B86" t="s">
         <v>6</v>
       </c>
-      <c r="B86" s="3" t="s">
+      <c r="C86" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C86" s="3">
+      <c r="D86" s="3">
         <v>1200</v>
       </c>
-      <c r="D86" s="3">
+      <c r="E86" s="3">
         <v>2200</v>
       </c>
     </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
+        <v>34</v>
+      </c>
+      <c r="B87" t="s">
         <v>6</v>
       </c>
-      <c r="B87" s="3" t="s">
+      <c r="C87" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="C87">
+      <c r="D87">
         <v>23</v>
       </c>
-      <c r="D87" s="3">
+      <c r="E87" s="3">
         <v>2200</v>
       </c>
     </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
+        <v>34</v>
+      </c>
+      <c r="B88" t="s">
         <v>6</v>
       </c>
-      <c r="B88" s="3" t="s">
+      <c r="C88" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="C88" s="3">
+      <c r="D88" s="3">
         <v>1</v>
       </c>
-      <c r="D88" s="3">
+      <c r="E88" s="3">
         <v>2200</v>
       </c>
     </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
+        <v>34</v>
+      </c>
+      <c r="B89" t="s">
         <v>6</v>
       </c>
-      <c r="B89" s="3" t="s">
+      <c r="C89" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C89">
+      <c r="D89">
         <v>72</v>
       </c>
-      <c r="D89" s="3">
+      <c r="E89" s="3">
         <v>2200</v>
       </c>
     </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
+        <v>34</v>
+      </c>
+      <c r="B90" t="s">
         <v>6</v>
       </c>
-      <c r="B90" s="3" t="s">
+      <c r="C90" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C90">
+      <c r="D90">
         <v>22</v>
       </c>
-      <c r="D90" s="3">
+      <c r="E90" s="3">
         <v>2200</v>
       </c>
     </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
+        <v>34</v>
+      </c>
+      <c r="B91" t="s">
         <v>6</v>
       </c>
-      <c r="B91" s="3" t="s">
+      <c r="C91" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C91">
+      <c r="D91">
         <v>92</v>
       </c>
-      <c r="D91" s="3">
+      <c r="E91" s="3">
         <v>2200</v>
       </c>
     </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
+        <v>34</v>
+      </c>
+      <c r="B92" t="s">
         <v>1</v>
       </c>
-      <c r="B92" s="3" t="s">
+      <c r="C92" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C92" s="3">
+      <c r="D92" s="3">
         <v>1500</v>
       </c>
-      <c r="D92" s="3">
+      <c r="E92" s="3">
         <v>2850</v>
       </c>
     </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
+        <v>34</v>
+      </c>
+      <c r="B93" t="s">
         <v>1</v>
       </c>
-      <c r="B93" s="3" t="s">
+      <c r="C93" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="C93">
+      <c r="D93">
         <v>52</v>
       </c>
-      <c r="D93" s="3">
+      <c r="E93" s="3">
         <v>2850</v>
       </c>
     </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
+        <v>34</v>
+      </c>
+      <c r="B94" t="s">
         <v>1</v>
       </c>
-      <c r="B94" s="3" t="s">
+      <c r="C94" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="C94" s="3">
+      <c r="D94" s="3">
         <v>10</v>
       </c>
-      <c r="D94" s="3">
+      <c r="E94" s="3">
         <v>2850</v>
       </c>
     </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
+        <v>34</v>
+      </c>
+      <c r="B95" t="s">
         <v>1</v>
       </c>
-      <c r="B95" s="3" t="s">
+      <c r="C95" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C95">
+      <c r="D95">
         <v>102</v>
       </c>
-      <c r="D95" s="3">
+      <c r="E95" s="3">
         <v>2850</v>
       </c>
     </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
+        <v>34</v>
+      </c>
+      <c r="B96" t="s">
         <v>1</v>
       </c>
-      <c r="B96" s="3" t="s">
+      <c r="C96" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C96">
+      <c r="D96">
         <v>31</v>
       </c>
-      <c r="D96" s="3">
+      <c r="E96" s="3">
         <v>2850</v>
       </c>
     </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
+        <v>34</v>
+      </c>
+      <c r="B97" t="s">
         <v>1</v>
       </c>
-      <c r="B97" s="3" t="s">
+      <c r="C97" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C97">
+      <c r="D97">
         <v>129</v>
       </c>
-      <c r="D97" s="3">
+      <c r="E97" s="3">
         <v>2850</v>
       </c>
     </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
+        <v>34</v>
+      </c>
+      <c r="B98" t="s">
         <v>4</v>
       </c>
-      <c r="B98" s="3" t="s">
+      <c r="C98" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C98">
+      <c r="D98">
         <v>1500</v>
       </c>
-      <c r="D98" s="3">
+      <c r="E98" s="3">
         <v>3500</v>
       </c>
     </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
+        <v>34</v>
+      </c>
+      <c r="B99" t="s">
         <v>4</v>
       </c>
-      <c r="B99" s="3" t="s">
+      <c r="C99" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="C99">
+      <c r="D99">
         <v>62</v>
       </c>
-      <c r="D99" s="3">
+      <c r="E99" s="3">
         <v>3500</v>
       </c>
     </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
+        <v>34</v>
+      </c>
+      <c r="B100" t="s">
         <v>4</v>
       </c>
-      <c r="B100" s="3" t="s">
+      <c r="C100" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="C100">
+      <c r="D100">
         <v>10</v>
       </c>
-      <c r="D100" s="3">
+      <c r="E100" s="3">
         <v>3500</v>
       </c>
     </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
+        <v>34</v>
+      </c>
+      <c r="B101" t="s">
         <v>4</v>
       </c>
-      <c r="B101" s="3" t="s">
+      <c r="C101" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C101">
+      <c r="D101">
         <v>124</v>
       </c>
-      <c r="D101" s="3">
+      <c r="E101" s="3">
         <v>3500</v>
       </c>
     </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
+        <v>34</v>
+      </c>
+      <c r="B102" t="s">
         <v>4</v>
       </c>
-      <c r="B102" s="3" t="s">
+      <c r="C102" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C102">
+      <c r="D102">
         <v>37</v>
       </c>
-      <c r="D102" s="3">
+      <c r="E102" s="3">
         <v>3500</v>
       </c>
     </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
+        <v>34</v>
+      </c>
+      <c r="B103" t="s">
         <v>4</v>
       </c>
-      <c r="B103" s="3" t="s">
+      <c r="C103" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C103">
+      <c r="D103">
         <v>183</v>
       </c>
-      <c r="D103" s="3">
+      <c r="E103" s="3">
         <v>3500</v>
       </c>
     </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
+        <v>34</v>
+      </c>
+      <c r="B104" t="s">
         <v>11</v>
       </c>
-      <c r="B104" s="3" t="s">
+      <c r="C104" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C104" s="3">
+      <c r="D104" s="3">
         <v>1500</v>
       </c>
-      <c r="D104" s="3">
+      <c r="E104" s="3">
         <v>3500</v>
       </c>
     </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
+        <v>34</v>
+      </c>
+      <c r="B105" t="s">
         <v>11</v>
       </c>
-      <c r="B105" s="3" t="s">
+      <c r="C105" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="C105">
+      <c r="D105">
         <v>78</v>
       </c>
-      <c r="D105" s="3">
+      <c r="E105" s="3">
         <v>3500</v>
       </c>
     </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
+        <v>34</v>
+      </c>
+      <c r="B106" t="s">
         <v>11</v>
       </c>
-      <c r="B106" s="3" t="s">
+      <c r="C106" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="C106" s="3">
+      <c r="D106" s="3">
         <v>16</v>
       </c>
-      <c r="D106" s="3">
+      <c r="E106" s="3">
         <v>3500</v>
       </c>
     </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
+        <v>34</v>
+      </c>
+      <c r="B107" t="s">
         <v>11</v>
       </c>
-      <c r="B107" s="3" t="s">
+      <c r="C107" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C107">
+      <c r="D107">
         <v>96</v>
       </c>
-      <c r="D107" s="3">
+      <c r="E107" s="3">
         <v>3500</v>
       </c>
     </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
+        <v>34</v>
+      </c>
+      <c r="B108" t="s">
         <v>11</v>
       </c>
-      <c r="B108" s="3" t="s">
+      <c r="C108" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C108">
+      <c r="D108">
         <v>29</v>
       </c>
-      <c r="D108" s="3">
+      <c r="E108" s="3">
         <v>3500</v>
       </c>
     </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
+        <v>34</v>
+      </c>
+      <c r="B109" t="s">
         <v>11</v>
       </c>
-      <c r="B109" s="3" t="s">
+      <c r="C109" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C109">
+      <c r="D109">
         <v>198</v>
       </c>
-      <c r="D109" s="3">
+      <c r="E109" s="3">
         <v>3500</v>
       </c>
     </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
+        <v>34</v>
+      </c>
+      <c r="B110" t="s">
         <v>14</v>
       </c>
-      <c r="B110" s="3" t="s">
+      <c r="C110" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C110" s="3">
+      <c r="D110" s="3">
         <v>1500</v>
       </c>
-      <c r="D110" s="3">
+      <c r="E110" s="3">
         <v>2300</v>
       </c>
     </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
+        <v>34</v>
+      </c>
+      <c r="B111" t="s">
         <v>14</v>
       </c>
-      <c r="B111" s="3" t="s">
+      <c r="C111" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="C111">
+      <c r="D111">
         <v>44</v>
       </c>
-      <c r="D111" s="3">
+      <c r="E111" s="3">
         <v>2300</v>
       </c>
     </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
+        <v>34</v>
+      </c>
+      <c r="B112" t="s">
         <v>14</v>
       </c>
-      <c r="B112" s="3" t="s">
+      <c r="C112" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="C112" s="3">
+      <c r="D112" s="3">
         <v>10</v>
       </c>
-      <c r="D112" s="3">
+      <c r="E112" s="3">
         <v>2300</v>
       </c>
     </row>
-    <row r="113" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
+        <v>34</v>
+      </c>
+      <c r="B113" t="s">
         <v>14</v>
       </c>
-      <c r="B113" s="3" t="s">
+      <c r="C113" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C113">
+      <c r="D113">
         <v>72</v>
       </c>
-      <c r="D113" s="3">
+      <c r="E113" s="3">
         <v>2300</v>
       </c>
     </row>
-    <row r="114" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
+        <v>34</v>
+      </c>
+      <c r="B114" t="s">
         <v>14</v>
       </c>
-      <c r="B114" s="3" t="s">
+      <c r="C114" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C114">
+      <c r="D114">
         <v>22</v>
       </c>
-      <c r="D114" s="3">
+      <c r="E114" s="3">
         <v>2300</v>
       </c>
     </row>
-    <row r="115" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
+        <v>34</v>
+      </c>
+      <c r="B115" t="s">
         <v>14</v>
       </c>
-      <c r="B115" s="3" t="s">
+      <c r="C115" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C115">
+      <c r="D115">
         <v>151</v>
       </c>
-      <c r="D115" s="3">
+      <c r="E115" s="3">
         <v>2300</v>
       </c>
     </row>
-    <row r="116" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
+        <v>34</v>
+      </c>
+      <c r="B116" t="s">
         <v>16</v>
       </c>
-      <c r="B116" s="3" t="s">
+      <c r="C116" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C116" s="3">
+      <c r="D116" s="3">
         <v>1500</v>
       </c>
-      <c r="D116" s="3">
+      <c r="E116" s="3">
         <v>5700</v>
       </c>
     </row>
-    <row r="117" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
+        <v>34</v>
+      </c>
+      <c r="B117" t="s">
         <v>16</v>
       </c>
-      <c r="B117" s="3" t="s">
+      <c r="C117" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="C117">
+      <c r="D117">
         <v>103</v>
       </c>
-      <c r="D117" s="3">
+      <c r="E117" s="3">
         <v>5700</v>
       </c>
     </row>
-    <row r="118" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
+        <v>34</v>
+      </c>
+      <c r="B118" t="s">
         <v>16</v>
       </c>
-      <c r="B118" s="3" t="s">
+      <c r="C118" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="C118" s="3">
+      <c r="D118" s="3">
         <v>14</v>
       </c>
-      <c r="D118" s="3">
+      <c r="E118" s="3">
         <v>5700</v>
       </c>
     </row>
-    <row r="119" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
+        <v>34</v>
+      </c>
+      <c r="B119" t="s">
         <v>16</v>
       </c>
-      <c r="B119" s="3" t="s">
+      <c r="C119" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C119">
+      <c r="D119">
         <v>236</v>
       </c>
-      <c r="D119" s="3">
+      <c r="E119" s="3">
         <v>5700</v>
       </c>
     </row>
-    <row r="120" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
+        <v>34</v>
+      </c>
+      <c r="B120" t="s">
         <v>16</v>
       </c>
-      <c r="B120" s="3" t="s">
+      <c r="C120" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C120">
+      <c r="D120">
         <v>71</v>
       </c>
-      <c r="D120" s="3">
+      <c r="E120" s="3">
         <v>5700</v>
       </c>
     </row>
-    <row r="121" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
+        <v>34</v>
+      </c>
+      <c r="B121" t="s">
         <v>16</v>
       </c>
-      <c r="B121" s="3" t="s">
+      <c r="C121" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C121">
+      <c r="D121">
         <v>192</v>
       </c>
-      <c r="D121" s="3">
+      <c r="E121" s="3">
         <v>5700</v>
       </c>
     </row>
-    <row r="122" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
+        <v>34</v>
+      </c>
+      <c r="B122" t="s">
         <v>19</v>
       </c>
-      <c r="B122" s="3" t="s">
+      <c r="C122" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C122" s="3">
+      <c r="D122" s="3">
         <v>1500</v>
       </c>
-      <c r="D122" s="3">
+      <c r="E122" s="3">
         <v>2600</v>
       </c>
     </row>
-    <row r="123" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
+        <v>34</v>
+      </c>
+      <c r="B123" t="s">
         <v>19</v>
       </c>
-      <c r="B123" s="3" t="s">
+      <c r="C123" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="C123">
+      <c r="D123">
         <v>62</v>
       </c>
-      <c r="D123" s="3">
+      <c r="E123" s="3">
         <v>2600</v>
       </c>
     </row>
-    <row r="124" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
+        <v>34</v>
+      </c>
+      <c r="B124" t="s">
         <v>19</v>
       </c>
-      <c r="B124" s="3" t="s">
+      <c r="C124" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="C124" s="3">
+      <c r="D124" s="3">
         <v>11</v>
       </c>
-      <c r="D124" s="3">
+      <c r="E124" s="3">
         <v>2600</v>
       </c>
     </row>
-    <row r="125" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
+        <v>34</v>
+      </c>
+      <c r="B125" t="s">
         <v>19</v>
       </c>
-      <c r="B125" s="3" t="s">
+      <c r="C125" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C125">
+      <c r="D125">
         <v>74</v>
       </c>
-      <c r="D125" s="3">
+      <c r="E125" s="3">
         <v>2600</v>
       </c>
     </row>
-    <row r="126" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
+        <v>34</v>
+      </c>
+      <c r="B126" t="s">
         <v>19</v>
       </c>
-      <c r="B126" s="3" t="s">
+      <c r="C126" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C126">
+      <c r="D126">
         <v>22</v>
       </c>
-      <c r="D126" s="3">
+      <c r="E126" s="3">
         <v>2600</v>
       </c>
     </row>
-    <row r="127" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
+        <v>34</v>
+      </c>
+      <c r="B127" t="s">
         <v>19</v>
       </c>
-      <c r="B127" s="3" t="s">
+      <c r="C127" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C127">
+      <c r="D127">
         <v>181</v>
       </c>
-      <c r="D127" s="3">
+      <c r="E127" s="3">
         <v>2600</v>
       </c>
     </row>
-    <row r="128" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
+        <v>34</v>
+      </c>
+      <c r="B128" t="s">
         <v>15</v>
       </c>
-      <c r="B128" s="3" t="s">
+      <c r="C128" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C128" s="3">
+      <c r="D128" s="3">
         <v>1500</v>
       </c>
-      <c r="D128" s="3">
+      <c r="E128" s="3">
         <v>2650</v>
       </c>
     </row>
-    <row r="129" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
+        <v>34</v>
+      </c>
+      <c r="B129" t="s">
         <v>15</v>
       </c>
-      <c r="B129" s="3" t="s">
+      <c r="C129" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="C129">
+      <c r="D129">
         <v>30</v>
       </c>
-      <c r="D129" s="3">
+      <c r="E129" s="3">
         <v>2650</v>
       </c>
     </row>
-    <row r="130" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
+        <v>34</v>
+      </c>
+      <c r="B130" t="s">
         <v>15</v>
       </c>
-      <c r="B130" s="3" t="s">
+      <c r="C130" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="C130" s="3">
+      <c r="D130" s="3">
         <v>10</v>
       </c>
-      <c r="D130" s="3">
+      <c r="E130" s="3">
         <v>2650</v>
       </c>
     </row>
-    <row r="131" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
+        <v>34</v>
+      </c>
+      <c r="B131" t="s">
         <v>15</v>
       </c>
-      <c r="B131" s="3" t="s">
+      <c r="C131" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C131">
+      <c r="D131">
         <v>92</v>
       </c>
-      <c r="D131" s="3">
+      <c r="E131" s="3">
         <v>2650</v>
       </c>
     </row>
-    <row r="132" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
+        <v>34</v>
+      </c>
+      <c r="B132" t="s">
         <v>15</v>
       </c>
-      <c r="B132" s="3" t="s">
+      <c r="C132" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C132">
+      <c r="D132">
         <v>28</v>
       </c>
-      <c r="D132" s="3">
+      <c r="E132" s="3">
         <v>2650</v>
       </c>
     </row>
-    <row r="133" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
+        <v>34</v>
+      </c>
+      <c r="B133" t="s">
         <v>15</v>
       </c>
-      <c r="B133" s="3" t="s">
+      <c r="C133" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C133">
+      <c r="D133">
         <v>126</v>
       </c>
-      <c r="D133" s="3">
+      <c r="E133" s="3">
         <v>2650</v>
       </c>
     </row>
-    <row r="134" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
+        <v>34</v>
+      </c>
+      <c r="B134" t="s">
         <v>32</v>
       </c>
-      <c r="B134" s="3" t="s">
+      <c r="C134" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C134">
+      <c r="D134">
         <v>27700</v>
       </c>
-      <c r="D134" s="3">
+      <c r="E134" s="3">
         <v>53500</v>
       </c>
     </row>
-    <row r="135" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
+        <v>34</v>
+      </c>
+      <c r="B135" t="s">
         <v>32</v>
       </c>
-      <c r="B135" s="3" t="s">
+      <c r="C135" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="C135">
+      <c r="D135">
         <v>840</v>
       </c>
-      <c r="D135" s="3">
+      <c r="E135" s="3">
         <v>53500</v>
       </c>
     </row>
-    <row r="136" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
+        <v>34</v>
+      </c>
+      <c r="B136" t="s">
         <v>32</v>
       </c>
-      <c r="B136" s="3" t="s">
+      <c r="C136" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="C136">
+      <c r="D136">
         <v>131</v>
       </c>
-      <c r="D136" s="3">
+      <c r="E136" s="3">
         <v>53500</v>
       </c>
     </row>
-    <row r="137" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
+        <v>34</v>
+      </c>
+      <c r="B137" t="s">
         <v>32</v>
       </c>
-      <c r="B137" s="3" t="s">
+      <c r="C137" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C137">
+      <c r="D137">
         <v>1868</v>
       </c>
-      <c r="D137" s="3">
+      <c r="E137" s="3">
         <v>53500</v>
       </c>
     </row>
-    <row r="138" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
+        <v>34</v>
+      </c>
+      <c r="B138" t="s">
         <v>32</v>
       </c>
-      <c r="B138" s="3" t="s">
+      <c r="C138" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C138">
+      <c r="D138">
         <v>565</v>
       </c>
-      <c r="D138" s="3">
+      <c r="E138" s="3">
         <v>53500</v>
       </c>
     </row>
-    <row r="139" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
+        <v>34</v>
+      </c>
+      <c r="B139" t="s">
         <v>32</v>
       </c>
-      <c r="B139" s="3" t="s">
+      <c r="C139" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C139">
+      <c r="D139">
         <v>2738</v>
       </c>
-      <c r="D139" s="3">
+      <c r="E139" s="3">
         <v>53500</v>
       </c>
     </row>
+    <row r="140" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B140" s="3"/>
+      <c r="C140" s="3"/>
+      <c r="D140" s="3"/>
+      <c r="E140" s="3"/>
+    </row>
+    <row r="141" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B141" s="3"/>
+      <c r="C141" s="3"/>
+      <c r="D141" s="3"/>
+      <c r="E141" s="3"/>
+    </row>
+    <row r="142" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B142" s="3"/>
+      <c r="C142" s="3"/>
+      <c r="D142" s="3"/>
+      <c r="E142" s="3"/>
+    </row>
+    <row r="143" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B143" s="3"/>
+      <c r="C143" s="3"/>
+      <c r="D143" s="3"/>
+      <c r="E143" s="3"/>
+    </row>
+    <row r="144" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B144" s="3"/>
+      <c r="C144" s="3"/>
+      <c r="D144" s="3"/>
+      <c r="E144" s="3"/>
+    </row>
+    <row r="145" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B145" s="3"/>
+      <c r="C145" s="3"/>
+      <c r="D145" s="3"/>
+      <c r="E145" s="3"/>
+    </row>
+    <row r="146" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B146" s="3"/>
+      <c r="C146" s="3"/>
+      <c r="D146" s="3"/>
+      <c r="E146" s="3"/>
+    </row>
+    <row r="147" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B147" s="3"/>
+      <c r="C147" s="3"/>
+      <c r="D147" s="3"/>
+      <c r="E147" s="3"/>
+    </row>
+    <row r="148" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B148" s="3"/>
+      <c r="C148" s="3"/>
+      <c r="D148" s="3"/>
+      <c r="E148" s="3"/>
+    </row>
+    <row r="149" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B149" s="3"/>
+      <c r="C149" s="3"/>
+      <c r="E149" s="3"/>
+    </row>
+    <row r="150" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B150" s="3"/>
+      <c r="C150" s="3"/>
+      <c r="E150" s="3"/>
+    </row>
+    <row r="151" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B151" s="3"/>
+      <c r="C151" s="3"/>
+      <c r="E151" s="3"/>
+    </row>
+    <row r="152" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="C152" s="3"/>
+      <c r="D152" s="3"/>
+      <c r="E152" s="3"/>
+    </row>
+    <row r="153" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="C153" s="3"/>
+      <c r="E153" s="3"/>
+    </row>
+    <row r="154" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="C154" s="3"/>
+      <c r="D154" s="3"/>
+      <c r="E154" s="3"/>
+    </row>
+    <row r="155" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="C155" s="3"/>
+      <c r="E155" s="3"/>
+    </row>
+    <row r="156" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="C156" s="3"/>
+      <c r="E156" s="3"/>
+    </row>
+    <row r="157" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="C157" s="3"/>
+      <c r="E157" s="3"/>
+    </row>
+    <row r="158" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="C158" s="3"/>
+      <c r="D158" s="3"/>
+      <c r="E158" s="3"/>
+    </row>
+    <row r="159" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="C159" s="3"/>
+      <c r="E159" s="3"/>
+    </row>
+    <row r="160" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="C160" s="3"/>
+      <c r="D160" s="3"/>
+      <c r="E160" s="3"/>
+    </row>
+    <row r="161" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C161" s="3"/>
+      <c r="E161" s="3"/>
+    </row>
+    <row r="162" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C162" s="3"/>
+      <c r="E162" s="3"/>
+    </row>
+    <row r="163" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C163" s="3"/>
+      <c r="E163" s="3"/>
+    </row>
+    <row r="164" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C164" s="3"/>
+      <c r="D164" s="3"/>
+      <c r="E164" s="3"/>
+    </row>
+    <row r="165" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C165" s="3"/>
+      <c r="E165" s="3"/>
+    </row>
+    <row r="166" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C166" s="3"/>
+      <c r="D166" s="3"/>
+      <c r="E166" s="3"/>
+    </row>
+    <row r="167" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C167" s="3"/>
+      <c r="E167" s="3"/>
+    </row>
+    <row r="168" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C168" s="3"/>
+      <c r="E168" s="3"/>
+    </row>
+    <row r="169" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C169" s="3"/>
+      <c r="E169" s="3"/>
+    </row>
+    <row r="170" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C170" s="3"/>
+      <c r="D170" s="3"/>
+      <c r="E170" s="3"/>
+    </row>
+    <row r="171" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C171" s="3"/>
+      <c r="E171" s="3"/>
+    </row>
+    <row r="172" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C172" s="3"/>
+      <c r="D172" s="3"/>
+      <c r="E172" s="3"/>
+    </row>
+    <row r="173" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C173" s="3"/>
+      <c r="E173" s="3"/>
+    </row>
+    <row r="174" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C174" s="3"/>
+      <c r="E174" s="3"/>
+    </row>
+    <row r="175" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C175" s="3"/>
+      <c r="E175" s="3"/>
+    </row>
+    <row r="176" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C176" s="3"/>
+      <c r="D176" s="3"/>
+      <c r="E176" s="3"/>
+    </row>
+    <row r="177" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C177" s="3"/>
+      <c r="E177" s="3"/>
+    </row>
+    <row r="178" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C178" s="3"/>
+      <c r="D178" s="3"/>
+      <c r="E178" s="3"/>
+    </row>
+    <row r="179" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C179" s="3"/>
+      <c r="E179" s="3"/>
+    </row>
+    <row r="180" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C180" s="3"/>
+      <c r="E180" s="3"/>
+    </row>
+    <row r="181" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C181" s="3"/>
+      <c r="E181" s="3"/>
+    </row>
+    <row r="182" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C182" s="3"/>
+      <c r="D182" s="3"/>
+      <c r="E182" s="3"/>
+    </row>
+    <row r="183" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C183" s="3"/>
+      <c r="E183" s="3"/>
+    </row>
+    <row r="184" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C184" s="3"/>
+      <c r="D184" s="3"/>
+      <c r="E184" s="3"/>
+    </row>
+    <row r="185" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C185" s="3"/>
+      <c r="E185" s="3"/>
+    </row>
+    <row r="186" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C186" s="3"/>
+      <c r="E186" s="3"/>
+    </row>
+    <row r="187" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C187" s="3"/>
+      <c r="E187" s="3"/>
+    </row>
+    <row r="188" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C188" s="3"/>
+      <c r="D188" s="3"/>
+      <c r="E188" s="3"/>
+    </row>
+    <row r="189" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C189" s="3"/>
+      <c r="E189" s="3"/>
+    </row>
+    <row r="190" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C190" s="3"/>
+      <c r="D190" s="3"/>
+      <c r="E190" s="3"/>
+    </row>
+    <row r="191" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C191" s="3"/>
+      <c r="E191" s="3"/>
+    </row>
+    <row r="192" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C192" s="3"/>
+      <c r="E192" s="3"/>
+    </row>
+    <row r="193" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="C193" s="3"/>
+      <c r="E193" s="3"/>
+    </row>
+    <row r="194" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B194" s="1"/>
+      <c r="C194" s="3"/>
+      <c r="D194" s="3"/>
+      <c r="E194" s="3"/>
+    </row>
+    <row r="195" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="C195" s="3"/>
+      <c r="E195" s="3"/>
+    </row>
+    <row r="196" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="C196" s="3"/>
+      <c r="D196" s="3"/>
+      <c r="E196" s="3"/>
+    </row>
+    <row r="197" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="C197" s="3"/>
+      <c r="E197" s="3"/>
+    </row>
+    <row r="198" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="C198" s="3"/>
+      <c r="E198" s="3"/>
+    </row>
+    <row r="199" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="C199" s="3"/>
+      <c r="E199" s="3"/>
+    </row>
+    <row r="200" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="C200" s="3"/>
+      <c r="D200" s="3"/>
+      <c r="E200" s="3"/>
+    </row>
+    <row r="201" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="C201" s="3"/>
+      <c r="E201" s="3"/>
+    </row>
+    <row r="202" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="C202" s="3"/>
+      <c r="D202" s="3"/>
+      <c r="E202" s="3"/>
+    </row>
+    <row r="203" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="C203" s="3"/>
+      <c r="E203" s="3"/>
+    </row>
+    <row r="204" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="C204" s="3"/>
+      <c r="E204" s="3"/>
+    </row>
+    <row r="205" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="C205" s="3"/>
+      <c r="E205" s="3"/>
+    </row>
+    <row r="206" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="C206" s="3"/>
+      <c r="D206" s="3"/>
+      <c r="E206" s="3"/>
+    </row>
+    <row r="207" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="C207" s="3"/>
+      <c r="E207" s="3"/>
+    </row>
+    <row r="208" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="C208" s="3"/>
+      <c r="D208" s="3"/>
+      <c r="E208" s="3"/>
+    </row>
+    <row r="209" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C209" s="3"/>
+      <c r="E209" s="3"/>
+    </row>
+    <row r="210" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C210" s="3"/>
+      <c r="E210" s="3"/>
+    </row>
+    <row r="211" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C211" s="3"/>
+      <c r="E211" s="3"/>
+    </row>
+    <row r="212" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C212" s="3"/>
+      <c r="D212" s="3"/>
+      <c r="E212" s="3"/>
+    </row>
+    <row r="213" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C213" s="3"/>
+      <c r="E213" s="3"/>
+    </row>
+    <row r="214" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C214" s="3"/>
+      <c r="D214" s="3"/>
+      <c r="E214" s="3"/>
+    </row>
+    <row r="215" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C215" s="3"/>
+      <c r="E215" s="3"/>
+    </row>
+    <row r="216" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C216" s="3"/>
+      <c r="E216" s="3"/>
+    </row>
+    <row r="217" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C217" s="3"/>
+      <c r="E217" s="3"/>
+    </row>
+    <row r="218" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C218" s="3"/>
+      <c r="D218" s="3"/>
+      <c r="E218" s="3"/>
+    </row>
+    <row r="219" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C219" s="3"/>
+      <c r="E219" s="3"/>
+    </row>
+    <row r="220" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C220" s="3"/>
+      <c r="D220" s="3"/>
+      <c r="E220" s="3"/>
+    </row>
+    <row r="221" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C221" s="3"/>
+      <c r="E221" s="3"/>
+    </row>
+    <row r="222" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C222" s="3"/>
+      <c r="E222" s="3"/>
+    </row>
+    <row r="223" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C223" s="3"/>
+      <c r="E223" s="3"/>
+    </row>
+    <row r="224" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C224" s="3"/>
+      <c r="D224" s="3"/>
+      <c r="E224" s="3"/>
+    </row>
+    <row r="225" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C225" s="3"/>
+      <c r="E225" s="3"/>
+    </row>
+    <row r="226" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C226" s="3"/>
+      <c r="D226" s="3"/>
+      <c r="E226" s="3"/>
+    </row>
+    <row r="227" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C227" s="3"/>
+      <c r="E227" s="3"/>
+    </row>
+    <row r="228" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C228" s="3"/>
+      <c r="E228" s="3"/>
+    </row>
+    <row r="229" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C229" s="3"/>
+      <c r="E229" s="3"/>
+    </row>
+    <row r="230" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C230" s="3"/>
+      <c r="D230" s="3"/>
+      <c r="E230" s="3"/>
+    </row>
+    <row r="231" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C231" s="3"/>
+      <c r="E231" s="3"/>
+    </row>
+    <row r="232" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C232" s="3"/>
+      <c r="D232" s="3"/>
+      <c r="E232" s="3"/>
+    </row>
+    <row r="233" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C233" s="3"/>
+      <c r="E233" s="3"/>
+    </row>
+    <row r="234" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C234" s="3"/>
+      <c r="E234" s="3"/>
+    </row>
+    <row r="235" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C235" s="3"/>
+      <c r="E235" s="3"/>
+    </row>
+    <row r="236" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C236" s="3"/>
+      <c r="E236" s="3"/>
+    </row>
+    <row r="237" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C237" s="3"/>
+      <c r="E237" s="3"/>
+    </row>
+    <row r="238" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C238" s="3"/>
+      <c r="E238" s="3"/>
+    </row>
+    <row r="239" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C239" s="3"/>
+      <c r="E239" s="3"/>
+    </row>
+    <row r="240" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C240" s="3"/>
+      <c r="E240" s="3"/>
+    </row>
+    <row r="241" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C241" s="3"/>
+      <c r="E241" s="3"/>
+    </row>
+    <row r="242" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C242" s="3"/>
+      <c r="D242" s="3"/>
+      <c r="E242" s="3"/>
+    </row>
+    <row r="243" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C243" s="3"/>
+      <c r="E243" s="3"/>
+    </row>
+    <row r="244" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C244" s="3"/>
+      <c r="D244" s="3"/>
+      <c r="E244" s="3"/>
+    </row>
+    <row r="245" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C245" s="3"/>
+      <c r="E245" s="3"/>
+    </row>
+    <row r="246" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C246" s="3"/>
+      <c r="E246" s="3"/>
+    </row>
+    <row r="247" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C247" s="3"/>
+      <c r="E247" s="3"/>
+    </row>
+    <row r="248" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C248" s="3"/>
+      <c r="D248" s="3"/>
+      <c r="E248" s="3"/>
+    </row>
+    <row r="249" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C249" s="3"/>
+      <c r="E249" s="3"/>
+    </row>
+    <row r="250" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C250" s="3"/>
+      <c r="D250" s="3"/>
+      <c r="E250" s="3"/>
+    </row>
+    <row r="251" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C251" s="3"/>
+      <c r="E251" s="3"/>
+    </row>
+    <row r="252" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C252" s="3"/>
+      <c r="E252" s="3"/>
+    </row>
+    <row r="253" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C253" s="3"/>
+      <c r="E253" s="3"/>
+    </row>
+    <row r="254" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C254" s="3"/>
+      <c r="D254" s="3"/>
+      <c r="E254" s="3"/>
+    </row>
+    <row r="255" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C255" s="3"/>
+      <c r="E255" s="3"/>
+    </row>
+    <row r="256" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C256" s="3"/>
+      <c r="D256" s="3"/>
+      <c r="E256" s="3"/>
+    </row>
+    <row r="257" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C257" s="3"/>
+      <c r="E257" s="3"/>
+    </row>
+    <row r="258" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C258" s="3"/>
+      <c r="E258" s="3"/>
+    </row>
+    <row r="259" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C259" s="3"/>
+      <c r="E259" s="3"/>
+    </row>
+    <row r="260" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C260" s="3"/>
+      <c r="D260" s="3"/>
+      <c r="E260" s="3"/>
+    </row>
+    <row r="261" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C261" s="3"/>
+      <c r="E261" s="3"/>
+    </row>
+    <row r="262" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C262" s="3"/>
+      <c r="D262" s="3"/>
+      <c r="E262" s="3"/>
+    </row>
+    <row r="263" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C263" s="3"/>
+      <c r="E263" s="3"/>
+    </row>
+    <row r="264" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C264" s="3"/>
+      <c r="E264" s="3"/>
+    </row>
+    <row r="265" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C265" s="3"/>
+      <c r="E265" s="3"/>
+    </row>
+    <row r="266" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C266" s="3"/>
+      <c r="D266" s="3"/>
+      <c r="E266" s="3"/>
+    </row>
+    <row r="267" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C267" s="3"/>
+      <c r="E267" s="3"/>
+    </row>
+    <row r="268" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C268" s="3"/>
+      <c r="D268" s="3"/>
+      <c r="E268" s="3"/>
+    </row>
+    <row r="269" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C269" s="3"/>
+      <c r="E269" s="3"/>
+    </row>
+    <row r="270" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C270" s="3"/>
+      <c r="E270" s="3"/>
+    </row>
+    <row r="271" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C271" s="3"/>
+      <c r="E271" s="3"/>
+    </row>
+    <row r="272" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C272" s="3"/>
+      <c r="E272" s="3"/>
+    </row>
+    <row r="273" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C273" s="3"/>
+      <c r="E273" s="3"/>
+    </row>
+    <row r="274" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C274" s="3"/>
+      <c r="E274" s="3"/>
+    </row>
+    <row r="275" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C275" s="3"/>
+      <c r="E275" s="3"/>
+    </row>
+    <row r="276" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C276" s="3"/>
+      <c r="E276" s="3"/>
+    </row>
+    <row r="277" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C277" s="3"/>
+      <c r="E277" s="3"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D133" xr:uid="{6956BB2C-DA9E-4412-BCD4-BB80A11153FE}"/>
+  <autoFilter ref="B1:E133" xr:uid="{6956BB2C-DA9E-4412-BCD4-BB80A11153FE}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/data/metas.xlsx
+++ b/data/metas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sercomunicaciones2-my.sharepoint.com/personal/auxcomisiones_sercomunicaciones_com/Documents/PAOLA/Liquidacióncvs/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="512" documentId="8_{787D9E49-702D-43BD-B99B-4B64F775E77B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{36E9D8F0-8C88-4591-B248-CA2B35854662}"/>
+  <xr:revisionPtr revIDLastSave="514" documentId="8_{787D9E49-702D-43BD-B99B-4B64F775E77B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{212945BE-825C-4D35-AD01-AE528E1CC2B2}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D1391136-BBFC-43C7-B899-B77B0ECC5956}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="419" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="437" uniqueCount="36">
   <si>
     <t>BARBOSA</t>
   </si>
@@ -144,6 +144,9 @@
   </si>
   <si>
     <t>Febrero</t>
+  </si>
+  <si>
+    <t>NUMERARIO</t>
   </si>
 </sst>
 </file>
@@ -2919,110 +2922,176 @@
       </c>
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B140" s="3"/>
-      <c r="C140" s="3"/>
-      <c r="D140" s="3"/>
-      <c r="E140" s="3"/>
+      <c r="A140" t="s">
+        <v>34</v>
+      </c>
+      <c r="B140" t="s">
+        <v>35</v>
+      </c>
+      <c r="C140" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D140" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E140" s="3">
+        <v>5700</v>
+      </c>
     </row>
     <row r="141" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B141" s="3"/>
-      <c r="C141" s="3"/>
-      <c r="D141" s="3"/>
-      <c r="E141" s="3"/>
+      <c r="A141" t="s">
+        <v>34</v>
+      </c>
+      <c r="B141" t="s">
+        <v>35</v>
+      </c>
+      <c r="C141" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D141">
+        <v>103</v>
+      </c>
+      <c r="E141" s="3">
+        <v>5700</v>
+      </c>
     </row>
     <row r="142" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B142" s="3"/>
-      <c r="C142" s="3"/>
-      <c r="D142" s="3"/>
-      <c r="E142" s="3"/>
+      <c r="A142" t="s">
+        <v>34</v>
+      </c>
+      <c r="B142" t="s">
+        <v>35</v>
+      </c>
+      <c r="C142" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D142" s="3">
+        <v>14</v>
+      </c>
+      <c r="E142" s="3">
+        <v>5700</v>
+      </c>
     </row>
     <row r="143" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B143" s="3"/>
-      <c r="C143" s="3"/>
-      <c r="D143" s="3"/>
-      <c r="E143" s="3"/>
+      <c r="A143" t="s">
+        <v>34</v>
+      </c>
+      <c r="B143" t="s">
+        <v>35</v>
+      </c>
+      <c r="C143" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D143">
+        <v>236</v>
+      </c>
+      <c r="E143" s="3">
+        <v>5700</v>
+      </c>
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B144" s="3"/>
-      <c r="C144" s="3"/>
-      <c r="D144" s="3"/>
-      <c r="E144" s="3"/>
-    </row>
-    <row r="145" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B145" s="3"/>
-      <c r="C145" s="3"/>
-      <c r="D145" s="3"/>
-      <c r="E145" s="3"/>
-    </row>
-    <row r="146" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="A144" t="s">
+        <v>34</v>
+      </c>
+      <c r="B144" t="s">
+        <v>35</v>
+      </c>
+      <c r="C144" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D144">
+        <v>71</v>
+      </c>
+      <c r="E144" s="3">
+        <v>5700</v>
+      </c>
+    </row>
+    <row r="145" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A145" t="s">
+        <v>34</v>
+      </c>
+      <c r="B145" t="s">
+        <v>35</v>
+      </c>
+      <c r="C145" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D145">
+        <v>192</v>
+      </c>
+      <c r="E145" s="3">
+        <v>5700</v>
+      </c>
+    </row>
+    <row r="146" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B146" s="3"/>
       <c r="C146" s="3"/>
       <c r="D146" s="3"/>
       <c r="E146" s="3"/>
     </row>
-    <row r="147" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B147" s="3"/>
       <c r="C147" s="3"/>
       <c r="D147" s="3"/>
       <c r="E147" s="3"/>
     </row>
-    <row r="148" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B148" s="3"/>
       <c r="C148" s="3"/>
       <c r="D148" s="3"/>
       <c r="E148" s="3"/>
     </row>
-    <row r="149" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B149" s="3"/>
       <c r="C149" s="3"/>
       <c r="E149" s="3"/>
     </row>
-    <row r="150" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B150" s="3"/>
       <c r="C150" s="3"/>
       <c r="E150" s="3"/>
     </row>
-    <row r="151" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B151" s="3"/>
       <c r="C151" s="3"/>
       <c r="E151" s="3"/>
     </row>
-    <row r="152" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C152" s="3"/>
       <c r="D152" s="3"/>
       <c r="E152" s="3"/>
     </row>
-    <row r="153" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C153" s="3"/>
       <c r="E153" s="3"/>
     </row>
-    <row r="154" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C154" s="3"/>
       <c r="D154" s="3"/>
       <c r="E154" s="3"/>
     </row>
-    <row r="155" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C155" s="3"/>
       <c r="E155" s="3"/>
     </row>
-    <row r="156" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C156" s="3"/>
       <c r="E156" s="3"/>
     </row>
-    <row r="157" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C157" s="3"/>
       <c r="E157" s="3"/>
     </row>
-    <row r="158" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C158" s="3"/>
       <c r="D158" s="3"/>
       <c r="E158" s="3"/>
     </row>
-    <row r="159" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C159" s="3"/>
       <c r="E159" s="3"/>
     </row>
-    <row r="160" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C160" s="3"/>
       <c r="D160" s="3"/>
       <c r="E160" s="3"/>

--- a/data/metas.xlsx
+++ b/data/metas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sercomunicaciones2-my.sharepoint.com/personal/auxcomisiones_sercomunicaciones_com/Documents/PAOLA/Liquidacióncvs/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="514" documentId="8_{787D9E49-702D-43BD-B99B-4B64F775E77B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{212945BE-825C-4D35-AD01-AE528E1CC2B2}"/>
+  <xr:revisionPtr revIDLastSave="524" documentId="8_{787D9E49-702D-43BD-B99B-4B64F775E77B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{57D09A15-DF49-415A-9132-BDEFB122DD43}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D1391136-BBFC-43C7-B899-B77B0ECC5956}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$B$1:$E$133</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$B$1:$E$145</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -637,7 +637,7 @@
         <v>29</v>
       </c>
       <c r="D5" s="3">
-        <v>95</v>
+        <v>66</v>
       </c>
       <c r="E5" s="3">
         <v>2800</v>
@@ -738,8 +738,8 @@
       <c r="C11" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="D11">
-        <v>82</v>
+      <c r="D11" s="3">
+        <v>57</v>
       </c>
       <c r="E11" s="3">
         <v>2400</v>
@@ -840,8 +840,8 @@
       <c r="C17" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="D17">
-        <v>50</v>
+      <c r="D17" s="3">
+        <v>35</v>
       </c>
       <c r="E17" s="3">
         <v>1350</v>
@@ -942,8 +942,8 @@
       <c r="C23" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="D23">
-        <v>65</v>
+      <c r="D23" s="3">
+        <v>45</v>
       </c>
       <c r="E23" s="3">
         <v>1700</v>
@@ -1044,8 +1044,8 @@
       <c r="C29" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="D29">
-        <v>50</v>
+      <c r="D29" s="3">
+        <v>35</v>
       </c>
       <c r="E29" s="3">
         <v>1450</v>
@@ -1146,8 +1146,8 @@
       <c r="C35" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="D35">
-        <v>45</v>
+      <c r="D35" s="3">
+        <v>31</v>
       </c>
       <c r="E35" s="3">
         <v>1500</v>
@@ -1248,8 +1248,8 @@
       <c r="C41" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="D41">
-        <v>160</v>
+      <c r="D41" s="3">
+        <v>112</v>
       </c>
       <c r="E41" s="3">
         <v>4000</v>
@@ -1350,8 +1350,8 @@
       <c r="C47" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="D47">
-        <v>140</v>
+      <c r="D47" s="3">
+        <v>98</v>
       </c>
       <c r="E47" s="3">
         <v>2600</v>
@@ -1452,8 +1452,8 @@
       <c r="C53" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="D53">
-        <v>56</v>
+      <c r="D53" s="3">
+        <v>39</v>
       </c>
       <c r="E53" s="3">
         <v>2000</v>
@@ -1554,8 +1554,8 @@
       <c r="C59" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="D59">
-        <v>25</v>
+      <c r="D59" s="3">
+        <v>17</v>
       </c>
       <c r="E59" s="3">
         <v>1500</v>
@@ -1656,8 +1656,8 @@
       <c r="C65" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="D65">
-        <v>82</v>
+      <c r="D65" s="3">
+        <v>57</v>
       </c>
       <c r="E65" s="3">
         <v>2000</v>
@@ -1758,8 +1758,8 @@
       <c r="C71" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="D71">
-        <v>30</v>
+      <c r="D71" s="3">
+        <v>21</v>
       </c>
       <c r="E71" s="3">
         <v>1100</v>
@@ -1860,8 +1860,8 @@
       <c r="C77" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="D77">
-        <v>60</v>
+      <c r="D77" s="3">
+        <v>42</v>
       </c>
       <c r="E77" s="3">
         <v>2200</v>
@@ -1962,8 +1962,8 @@
       <c r="C83" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="D83">
-        <v>60</v>
+      <c r="D83" s="3">
+        <v>42</v>
       </c>
       <c r="E83" s="3">
         <v>1600</v>
@@ -2064,8 +2064,8 @@
       <c r="C89" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="D89">
-        <v>72</v>
+      <c r="D89" s="3">
+        <v>50</v>
       </c>
       <c r="E89" s="3">
         <v>2200</v>
@@ -2166,8 +2166,8 @@
       <c r="C95" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="D95">
-        <v>102</v>
+      <c r="D95" s="3">
+        <v>71</v>
       </c>
       <c r="E95" s="3">
         <v>2850</v>
@@ -2268,8 +2268,8 @@
       <c r="C101" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="D101">
-        <v>124</v>
+      <c r="D101" s="3">
+        <v>87</v>
       </c>
       <c r="E101" s="3">
         <v>3500</v>
@@ -2370,8 +2370,8 @@
       <c r="C107" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="D107">
-        <v>96</v>
+      <c r="D107" s="3">
+        <v>67</v>
       </c>
       <c r="E107" s="3">
         <v>3500</v>
@@ -2472,8 +2472,8 @@
       <c r="C113" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="D113">
-        <v>72</v>
+      <c r="D113" s="3">
+        <v>50</v>
       </c>
       <c r="E113" s="3">
         <v>2300</v>
@@ -2574,8 +2574,8 @@
       <c r="C119" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="D119">
-        <v>236</v>
+      <c r="D119" s="3">
+        <v>165</v>
       </c>
       <c r="E119" s="3">
         <v>5700</v>
@@ -2676,8 +2676,8 @@
       <c r="C125" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="D125">
-        <v>74</v>
+      <c r="D125" s="3">
+        <v>52</v>
       </c>
       <c r="E125" s="3">
         <v>2600</v>
@@ -2778,8 +2778,8 @@
       <c r="C131" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="D131">
-        <v>92</v>
+      <c r="D131" s="3">
+        <v>64</v>
       </c>
       <c r="E131" s="3">
         <v>2650</v>
@@ -2880,8 +2880,8 @@
       <c r="C137" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="D137">
-        <v>1868</v>
+      <c r="D137" s="3">
+        <v>1303</v>
       </c>
       <c r="E137" s="3">
         <v>53500</v>
@@ -2982,8 +2982,8 @@
       <c r="C143" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="D143">
-        <v>236</v>
+      <c r="D143" s="3">
+        <v>1303</v>
       </c>
       <c r="E143" s="3">
         <v>5700</v>
@@ -3600,7 +3600,7 @@
       <c r="E277" s="3"/>
     </row>
   </sheetData>
-  <autoFilter ref="B1:E133" xr:uid="{6956BB2C-DA9E-4412-BCD4-BB80A11153FE}"/>
+  <autoFilter ref="B1:E145" xr:uid="{6956BB2C-DA9E-4412-BCD4-BB80A11153FE}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/data/metas.xlsx
+++ b/data/metas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sercomunicaciones2-my.sharepoint.com/personal/auxcomisiones_sercomunicaciones_com/Documents/PAOLA/Liquidacióncvs/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="524" documentId="8_{787D9E49-702D-43BD-B99B-4B64F775E77B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{57D09A15-DF49-415A-9132-BDEFB122DD43}"/>
+  <xr:revisionPtr revIDLastSave="603" documentId="8_{787D9E49-702D-43BD-B99B-4B64F775E77B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C61F76DD-677E-4486-8090-2AFB3CF5C9A1}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D1391136-BBFC-43C7-B899-B77B0ECC5956}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="437" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="506" uniqueCount="37">
   <si>
     <t>BARBOSA</t>
   </si>
@@ -147,6 +147,9 @@
   </si>
   <si>
     <t>NUMERARIO</t>
+  </si>
+  <si>
+    <t>PORTA PRE</t>
   </si>
 </sst>
 </file>
@@ -3024,143 +3027,427 @@
       </c>
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B146" s="3"/>
-      <c r="C146" s="3"/>
-      <c r="D146" s="3"/>
-      <c r="E146" s="3"/>
+      <c r="A146" t="s">
+        <v>34</v>
+      </c>
+      <c r="B146" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C146" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D146" s="3">
+        <v>4</v>
+      </c>
+      <c r="E146" s="3">
+        <v>2400</v>
+      </c>
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B147" s="3"/>
-      <c r="C147" s="3"/>
-      <c r="D147" s="3"/>
-      <c r="E147" s="3"/>
+      <c r="A147" t="s">
+        <v>34</v>
+      </c>
+      <c r="B147" t="s">
+        <v>2</v>
+      </c>
+      <c r="C147" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D147" s="3">
+        <v>4</v>
+      </c>
+      <c r="E147" s="3">
+        <v>1350</v>
+      </c>
     </row>
     <row r="148" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B148" s="3"/>
-      <c r="C148" s="3"/>
-      <c r="D148" s="3"/>
-      <c r="E148" s="3"/>
+      <c r="A148" t="s">
+        <v>34</v>
+      </c>
+      <c r="B148" t="s">
+        <v>3</v>
+      </c>
+      <c r="C148" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D148" s="3">
+        <v>4</v>
+      </c>
+      <c r="E148" s="3">
+        <v>1700</v>
+      </c>
     </row>
     <row r="149" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B149" s="3"/>
-      <c r="C149" s="3"/>
-      <c r="E149" s="3"/>
+      <c r="A149" t="s">
+        <v>34</v>
+      </c>
+      <c r="B149" t="s">
+        <v>8</v>
+      </c>
+      <c r="C149" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D149" s="3">
+        <v>4</v>
+      </c>
+      <c r="E149" s="3">
+        <v>1450</v>
+      </c>
     </row>
     <row r="150" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B150" s="3"/>
-      <c r="C150" s="3"/>
-      <c r="E150" s="3"/>
+      <c r="A150" t="s">
+        <v>34</v>
+      </c>
+      <c r="B150" t="s">
+        <v>10</v>
+      </c>
+      <c r="C150" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D150" s="3">
+        <v>4</v>
+      </c>
+      <c r="E150" s="3">
+        <v>1500</v>
+      </c>
     </row>
     <row r="151" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B151" s="3"/>
-      <c r="C151" s="3"/>
-      <c r="E151" s="3"/>
+      <c r="A151" t="s">
+        <v>34</v>
+      </c>
+      <c r="B151" t="s">
+        <v>9</v>
+      </c>
+      <c r="C151" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D151" s="3">
+        <v>4</v>
+      </c>
+      <c r="E151" s="3">
+        <v>4000</v>
+      </c>
     </row>
     <row r="152" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C152" s="3"/>
-      <c r="D152" s="3"/>
-      <c r="E152" s="3"/>
+      <c r="A152" t="s">
+        <v>34</v>
+      </c>
+      <c r="B152" t="s">
+        <v>13</v>
+      </c>
+      <c r="C152" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D152" s="3">
+        <v>4</v>
+      </c>
+      <c r="E152" s="3">
+        <v>2600</v>
+      </c>
     </row>
     <row r="153" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C153" s="3"/>
-      <c r="E153" s="3"/>
+      <c r="A153" t="s">
+        <v>34</v>
+      </c>
+      <c r="B153" t="s">
+        <v>7</v>
+      </c>
+      <c r="C153" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D153" s="3">
+        <v>4</v>
+      </c>
+      <c r="E153" s="3">
+        <v>2000</v>
+      </c>
     </row>
     <row r="154" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C154" s="3"/>
-      <c r="D154" s="3"/>
-      <c r="E154" s="3"/>
+      <c r="A154" t="s">
+        <v>34</v>
+      </c>
+      <c r="B154" t="s">
+        <v>12</v>
+      </c>
+      <c r="C154" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D154" s="3">
+        <v>4</v>
+      </c>
+      <c r="E154" s="3">
+        <v>1500</v>
+      </c>
     </row>
     <row r="155" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C155" s="3"/>
-      <c r="E155" s="3"/>
+      <c r="A155" t="s">
+        <v>34</v>
+      </c>
+      <c r="B155" t="s">
+        <v>17</v>
+      </c>
+      <c r="C155" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D155" s="3">
+        <v>4</v>
+      </c>
+      <c r="E155" s="3">
+        <v>2000</v>
+      </c>
     </row>
     <row r="156" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C156" s="3"/>
-      <c r="E156" s="3"/>
+      <c r="A156" t="s">
+        <v>34</v>
+      </c>
+      <c r="B156" t="s">
+        <v>18</v>
+      </c>
+      <c r="C156" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D156" s="3">
+        <v>4</v>
+      </c>
+      <c r="E156" s="3">
+        <v>1100</v>
+      </c>
     </row>
     <row r="157" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C157" s="3"/>
-      <c r="E157" s="3"/>
+      <c r="A157" t="s">
+        <v>34</v>
+      </c>
+      <c r="B157" t="s">
+        <v>20</v>
+      </c>
+      <c r="C157" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D157" s="3">
+        <v>4</v>
+      </c>
+      <c r="E157" s="3">
+        <v>2200</v>
+      </c>
     </row>
     <row r="158" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C158" s="3"/>
-      <c r="D158" s="3"/>
-      <c r="E158" s="3"/>
+      <c r="A158" t="s">
+        <v>34</v>
+      </c>
+      <c r="B158" t="s">
+        <v>21</v>
+      </c>
+      <c r="C158" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D158" s="3">
+        <v>4</v>
+      </c>
+      <c r="E158" s="3">
+        <v>1600</v>
+      </c>
     </row>
     <row r="159" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C159" s="3"/>
-      <c r="E159" s="3"/>
+      <c r="A159" t="s">
+        <v>34</v>
+      </c>
+      <c r="B159" t="s">
+        <v>6</v>
+      </c>
+      <c r="C159" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D159" s="3">
+        <v>4</v>
+      </c>
+      <c r="E159" s="3">
+        <v>2200</v>
+      </c>
     </row>
     <row r="160" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C160" s="3"/>
-      <c r="D160" s="3"/>
-      <c r="E160" s="3"/>
-    </row>
-    <row r="161" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C161" s="3"/>
-      <c r="E161" s="3"/>
-    </row>
-    <row r="162" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C162" s="3"/>
-      <c r="E162" s="3"/>
-    </row>
-    <row r="163" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C163" s="3"/>
-      <c r="E163" s="3"/>
-    </row>
-    <row r="164" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C164" s="3"/>
-      <c r="D164" s="3"/>
-      <c r="E164" s="3"/>
-    </row>
-    <row r="165" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C165" s="3"/>
-      <c r="E165" s="3"/>
-    </row>
-    <row r="166" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C166" s="3"/>
-      <c r="D166" s="3"/>
-      <c r="E166" s="3"/>
-    </row>
-    <row r="167" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C167" s="3"/>
-      <c r="E167" s="3"/>
-    </row>
-    <row r="168" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C168" s="3"/>
-      <c r="E168" s="3"/>
-    </row>
-    <row r="169" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="A160" t="s">
+        <v>34</v>
+      </c>
+      <c r="B160" t="s">
+        <v>1</v>
+      </c>
+      <c r="C160" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D160" s="3">
+        <v>4</v>
+      </c>
+      <c r="E160" s="3">
+        <v>2850</v>
+      </c>
+    </row>
+    <row r="161" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A161" t="s">
+        <v>34</v>
+      </c>
+      <c r="B161" t="s">
+        <v>4</v>
+      </c>
+      <c r="C161" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D161" s="3">
+        <v>4</v>
+      </c>
+      <c r="E161" s="3">
+        <v>3500</v>
+      </c>
+    </row>
+    <row r="162" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A162" t="s">
+        <v>34</v>
+      </c>
+      <c r="B162" t="s">
+        <v>11</v>
+      </c>
+      <c r="C162" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D162" s="3">
+        <v>4</v>
+      </c>
+      <c r="E162" s="3">
+        <v>3500</v>
+      </c>
+    </row>
+    <row r="163" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A163" t="s">
+        <v>34</v>
+      </c>
+      <c r="B163" t="s">
+        <v>14</v>
+      </c>
+      <c r="C163" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D163" s="3">
+        <v>4</v>
+      </c>
+      <c r="E163" s="3">
+        <v>2300</v>
+      </c>
+    </row>
+    <row r="164" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A164" t="s">
+        <v>34</v>
+      </c>
+      <c r="B164" t="s">
+        <v>16</v>
+      </c>
+      <c r="C164" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D164" s="3">
+        <v>4</v>
+      </c>
+      <c r="E164" s="3">
+        <v>5700</v>
+      </c>
+    </row>
+    <row r="165" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A165" t="s">
+        <v>34</v>
+      </c>
+      <c r="B165" t="s">
+        <v>19</v>
+      </c>
+      <c r="C165" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D165" s="3">
+        <v>4</v>
+      </c>
+      <c r="E165" s="3">
+        <v>2600</v>
+      </c>
+    </row>
+    <row r="166" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A166" t="s">
+        <v>34</v>
+      </c>
+      <c r="B166" t="s">
+        <v>15</v>
+      </c>
+      <c r="C166" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D166" s="3">
+        <v>4</v>
+      </c>
+      <c r="E166" s="3">
+        <v>2650</v>
+      </c>
+    </row>
+    <row r="167" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A167" t="s">
+        <v>34</v>
+      </c>
+      <c r="B167" t="s">
+        <v>32</v>
+      </c>
+      <c r="C167" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D167">
+        <v>4</v>
+      </c>
+      <c r="E167" s="3">
+        <v>53500</v>
+      </c>
+    </row>
+    <row r="168" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A168" t="s">
+        <v>34</v>
+      </c>
+      <c r="B168" t="s">
+        <v>35</v>
+      </c>
+      <c r="C168" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D168" s="3">
+        <v>4</v>
+      </c>
+      <c r="E168" s="3">
+        <v>5700</v>
+      </c>
+    </row>
+    <row r="169" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C169" s="3"/>
       <c r="E169" s="3"/>
     </row>
-    <row r="170" spans="3:5" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C170" s="3"/>
       <c r="D170" s="3"/>
       <c r="E170" s="3"/>
     </row>
-    <row r="171" spans="3:5" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C171" s="3"/>
       <c r="E171" s="3"/>
     </row>
-    <row r="172" spans="3:5" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C172" s="3"/>
       <c r="D172" s="3"/>
       <c r="E172" s="3"/>
     </row>
-    <row r="173" spans="3:5" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C173" s="3"/>
       <c r="E173" s="3"/>
     </row>
-    <row r="174" spans="3:5" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C174" s="3"/>
       <c r="E174" s="3"/>
     </row>
-    <row r="175" spans="3:5" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C175" s="3"/>
       <c r="E175" s="3"/>
     </row>
-    <row r="176" spans="3:5" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C176" s="3"/>
       <c r="D176" s="3"/>
       <c r="E176" s="3"/>

--- a/data/metas.xlsx
+++ b/data/metas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sercomunicaciones2-my.sharepoint.com/personal/auxcomisiones_sercomunicaciones_com/Documents/PAOLA/Liquidacióncvs/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="603" documentId="8_{787D9E49-702D-43BD-B99B-4B64F775E77B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C61F76DD-677E-4486-8090-2AFB3CF5C9A1}"/>
+  <xr:revisionPtr revIDLastSave="611" documentId="8_{787D9E49-702D-43BD-B99B-4B64F775E77B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9004CAE0-BB64-42DD-9C1D-A4FC153CB58A}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D1391136-BBFC-43C7-B899-B77B0ECC5956}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$B$1:$E$145</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$B$1:$E$169</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="506" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="509" uniqueCount="37">
   <si>
     <t>BARBOSA</t>
   </si>
@@ -3037,7 +3037,7 @@
         <v>36</v>
       </c>
       <c r="D146" s="3">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="E146" s="3">
         <v>2400</v>
@@ -3048,13 +3048,13 @@
         <v>34</v>
       </c>
       <c r="B147" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C147" s="3" t="s">
         <v>36</v>
       </c>
       <c r="D147" s="3">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="E147" s="3">
         <v>1350</v>
@@ -3065,13 +3065,13 @@
         <v>34</v>
       </c>
       <c r="B148" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C148" s="3" t="s">
         <v>36</v>
       </c>
       <c r="D148" s="3">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="E148" s="3">
         <v>1700</v>
@@ -3082,7 +3082,7 @@
         <v>34</v>
       </c>
       <c r="B149" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C149" s="3" t="s">
         <v>36</v>
@@ -3099,13 +3099,13 @@
         <v>34</v>
       </c>
       <c r="B150" t="s">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C150" s="3" t="s">
         <v>36</v>
       </c>
       <c r="D150" s="3">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E150" s="3">
         <v>1500</v>
@@ -3116,13 +3116,13 @@
         <v>34</v>
       </c>
       <c r="B151" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C151" s="3" t="s">
         <v>36</v>
       </c>
       <c r="D151" s="3">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="E151" s="3">
         <v>4000</v>
@@ -3133,13 +3133,13 @@
         <v>34</v>
       </c>
       <c r="B152" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C152" s="3" t="s">
         <v>36</v>
       </c>
       <c r="D152" s="3">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E152" s="3">
         <v>2600</v>
@@ -3150,13 +3150,13 @@
         <v>34</v>
       </c>
       <c r="B153" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C153" s="3" t="s">
         <v>36</v>
       </c>
       <c r="D153" s="3">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E153" s="3">
         <v>2000</v>
@@ -3167,13 +3167,13 @@
         <v>34</v>
       </c>
       <c r="B154" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C154" s="3" t="s">
         <v>36</v>
       </c>
       <c r="D154" s="3">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="E154" s="3">
         <v>1500</v>
@@ -3184,13 +3184,13 @@
         <v>34</v>
       </c>
       <c r="B155" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C155" s="3" t="s">
         <v>36</v>
       </c>
       <c r="D155" s="3">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="E155" s="3">
         <v>2000</v>
@@ -3201,13 +3201,13 @@
         <v>34</v>
       </c>
       <c r="B156" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C156" s="3" t="s">
         <v>36</v>
       </c>
       <c r="D156" s="3">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E156" s="3">
         <v>1100</v>
@@ -3218,13 +3218,13 @@
         <v>34</v>
       </c>
       <c r="B157" t="s">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="C157" s="3" t="s">
         <v>36</v>
       </c>
       <c r="D157" s="3">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E157" s="3">
         <v>2200</v>
@@ -3235,13 +3235,13 @@
         <v>34</v>
       </c>
       <c r="B158" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="C158" s="3" t="s">
         <v>36</v>
       </c>
       <c r="D158" s="3">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="E158" s="3">
         <v>1600</v>
@@ -3252,13 +3252,13 @@
         <v>34</v>
       </c>
       <c r="B159" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C159" s="3" t="s">
         <v>36</v>
       </c>
       <c r="D159" s="3">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="E159" s="3">
         <v>2200</v>
@@ -3269,13 +3269,13 @@
         <v>34</v>
       </c>
       <c r="B160" t="s">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C160" s="3" t="s">
         <v>36</v>
       </c>
       <c r="D160" s="3">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E160" s="3">
         <v>2850</v>
@@ -3286,13 +3286,13 @@
         <v>34</v>
       </c>
       <c r="B161" t="s">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="C161" s="3" t="s">
         <v>36</v>
       </c>
       <c r="D161" s="3">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E161" s="3">
         <v>3500</v>
@@ -3303,13 +3303,13 @@
         <v>34</v>
       </c>
       <c r="B162" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="C162" s="3" t="s">
         <v>36</v>
       </c>
       <c r="D162" s="3">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E162" s="3">
         <v>3500</v>
@@ -3320,13 +3320,13 @@
         <v>34</v>
       </c>
       <c r="B163" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="C163" s="3" t="s">
         <v>36</v>
       </c>
       <c r="D163" s="3">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="E163" s="3">
         <v>2300</v>
@@ -3337,13 +3337,13 @@
         <v>34</v>
       </c>
       <c r="B164" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C164" s="3" t="s">
         <v>36</v>
       </c>
       <c r="D164" s="3">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E164" s="3">
         <v>5700</v>
@@ -3354,13 +3354,13 @@
         <v>34</v>
       </c>
       <c r="B165" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C165" s="3" t="s">
         <v>36</v>
       </c>
       <c r="D165" s="3">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="E165" s="3">
         <v>2600</v>
@@ -3371,13 +3371,13 @@
         <v>34</v>
       </c>
       <c r="B166" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C166" s="3" t="s">
         <v>36</v>
       </c>
       <c r="D166" s="3">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E166" s="3">
         <v>2650</v>
@@ -3388,13 +3388,13 @@
         <v>34</v>
       </c>
       <c r="B167" t="s">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="C167" s="3" t="s">
         <v>36</v>
       </c>
       <c r="D167">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E167" s="3">
         <v>53500</v>
@@ -3410,16 +3410,29 @@
       <c r="C168" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="D168" s="3">
-        <v>4</v>
+      <c r="D168">
+        <v>12</v>
       </c>
       <c r="E168" s="3">
         <v>5700</v>
       </c>
     </row>
     <row r="169" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C169" s="3"/>
-      <c r="E169" s="3"/>
+      <c r="A169" t="s">
+        <v>34</v>
+      </c>
+      <c r="B169" t="s">
+        <v>32</v>
+      </c>
+      <c r="C169" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D169">
+        <v>220</v>
+      </c>
+      <c r="E169" s="3">
+        <v>53500</v>
+      </c>
     </row>
     <row r="170" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C170" s="3"/>
@@ -3887,7 +3900,7 @@
       <c r="E277" s="3"/>
     </row>
   </sheetData>
-  <autoFilter ref="B1:E145" xr:uid="{6956BB2C-DA9E-4412-BCD4-BB80A11153FE}"/>
+  <autoFilter ref="B1:E169" xr:uid="{6956BB2C-DA9E-4412-BCD4-BB80A11153FE}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/data/metas.xlsx
+++ b/data/metas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sercomunicaciones2-my.sharepoint.com/personal/auxcomisiones_sercomunicaciones_com/Documents/PAOLA/Liquidacióncvs/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="611" documentId="8_{787D9E49-702D-43BD-B99B-4B64F775E77B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9004CAE0-BB64-42DD-9C1D-A4FC153CB58A}"/>
+  <xr:revisionPtr revIDLastSave="613" documentId="8_{787D9E49-702D-43BD-B99B-4B64F775E77B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EA69A06F-5842-4B12-8D1B-0AE897DA6C73}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D1391136-BBFC-43C7-B899-B77B0ECC5956}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$B$1:$E$169</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$B$1:$E$145</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="509" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="437" uniqueCount="36">
   <si>
     <t>BARBOSA</t>
   </si>
@@ -147,9 +147,6 @@
   </si>
   <si>
     <t>NUMERARIO</t>
-  </si>
-  <si>
-    <t>PORTA PRE</t>
   </si>
 </sst>
 </file>
@@ -552,7 +549,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6956BB2C-DA9E-4412-BCD4-BB80A11153FE}">
-  <dimension ref="A1:E277"/>
+  <dimension ref="A1:E253"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.7109375" bestFit="1" customWidth="1"/>
@@ -3027,440 +3024,137 @@
       </c>
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A146" t="s">
-        <v>34</v>
-      </c>
-      <c r="B146" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C146" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="D146" s="3">
-        <v>12</v>
-      </c>
-      <c r="E146" s="3">
-        <v>2400</v>
-      </c>
+      <c r="C146" s="3"/>
+      <c r="D146" s="3"/>
+      <c r="E146" s="3"/>
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A147" t="s">
-        <v>34</v>
-      </c>
-      <c r="B147" t="s">
-        <v>1</v>
-      </c>
-      <c r="C147" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="D147" s="3">
-        <v>12</v>
-      </c>
-      <c r="E147" s="3">
-        <v>1350</v>
-      </c>
+      <c r="C147" s="3"/>
+      <c r="E147" s="3"/>
     </row>
     <row r="148" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A148" t="s">
-        <v>34</v>
-      </c>
-      <c r="B148" t="s">
-        <v>4</v>
-      </c>
-      <c r="C148" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="D148" s="3">
-        <v>12</v>
-      </c>
-      <c r="E148" s="3">
-        <v>1700</v>
-      </c>
+      <c r="C148" s="3"/>
+      <c r="D148" s="3"/>
+      <c r="E148" s="3"/>
     </row>
     <row r="149" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A149" t="s">
-        <v>34</v>
-      </c>
-      <c r="B149" t="s">
-        <v>2</v>
-      </c>
-      <c r="C149" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="D149" s="3">
-        <v>4</v>
-      </c>
-      <c r="E149" s="3">
-        <v>1450</v>
-      </c>
+      <c r="C149" s="3"/>
+      <c r="E149" s="3"/>
     </row>
     <row r="150" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A150" t="s">
-        <v>34</v>
-      </c>
-      <c r="B150" t="s">
-        <v>3</v>
-      </c>
-      <c r="C150" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="D150" s="3">
-        <v>8</v>
-      </c>
-      <c r="E150" s="3">
-        <v>1500</v>
-      </c>
+      <c r="C150" s="3"/>
+      <c r="E150" s="3"/>
     </row>
     <row r="151" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A151" t="s">
-        <v>34</v>
-      </c>
-      <c r="B151" t="s">
-        <v>5</v>
-      </c>
-      <c r="C151" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="D151" s="3">
-        <v>12</v>
-      </c>
-      <c r="E151" s="3">
-        <v>4000</v>
-      </c>
+      <c r="C151" s="3"/>
+      <c r="E151" s="3"/>
     </row>
     <row r="152" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A152" t="s">
-        <v>34</v>
-      </c>
-      <c r="B152" t="s">
-        <v>8</v>
-      </c>
-      <c r="C152" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="D152" s="3">
-        <v>8</v>
-      </c>
-      <c r="E152" s="3">
-        <v>2600</v>
-      </c>
+      <c r="C152" s="3"/>
+      <c r="D152" s="3"/>
+      <c r="E152" s="3"/>
     </row>
     <row r="153" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A153" t="s">
-        <v>34</v>
-      </c>
-      <c r="B153" t="s">
-        <v>10</v>
-      </c>
-      <c r="C153" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="D153" s="3">
-        <v>8</v>
-      </c>
-      <c r="E153" s="3">
-        <v>2000</v>
-      </c>
+      <c r="C153" s="3"/>
+      <c r="E153" s="3"/>
     </row>
     <row r="154" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A154" t="s">
-        <v>34</v>
-      </c>
-      <c r="B154" t="s">
-        <v>9</v>
-      </c>
-      <c r="C154" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="D154" s="3">
-        <v>16</v>
-      </c>
-      <c r="E154" s="3">
-        <v>1500</v>
-      </c>
+      <c r="C154" s="3"/>
+      <c r="D154" s="3"/>
+      <c r="E154" s="3"/>
     </row>
     <row r="155" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A155" t="s">
-        <v>34</v>
-      </c>
-      <c r="B155" t="s">
-        <v>11</v>
-      </c>
-      <c r="C155" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="D155" s="3">
-        <v>12</v>
-      </c>
-      <c r="E155" s="3">
-        <v>2000</v>
-      </c>
+      <c r="C155" s="3"/>
+      <c r="E155" s="3"/>
     </row>
     <row r="156" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A156" t="s">
-        <v>34</v>
-      </c>
-      <c r="B156" t="s">
-        <v>13</v>
-      </c>
-      <c r="C156" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="D156" s="3">
-        <v>8</v>
-      </c>
-      <c r="E156" s="3">
-        <v>1100</v>
-      </c>
+      <c r="C156" s="3"/>
+      <c r="E156" s="3"/>
     </row>
     <row r="157" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A157" t="s">
-        <v>34</v>
-      </c>
-      <c r="B157" t="s">
-        <v>7</v>
-      </c>
-      <c r="C157" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="D157" s="3">
-        <v>8</v>
-      </c>
-      <c r="E157" s="3">
-        <v>2200</v>
-      </c>
+      <c r="C157" s="3"/>
+      <c r="E157" s="3"/>
     </row>
     <row r="158" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A158" t="s">
-        <v>34</v>
-      </c>
-      <c r="B158" t="s">
-        <v>14</v>
-      </c>
-      <c r="C158" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="D158" s="3">
-        <v>12</v>
-      </c>
-      <c r="E158" s="3">
-        <v>1600</v>
-      </c>
+      <c r="C158" s="3"/>
+      <c r="D158" s="3"/>
+      <c r="E158" s="3"/>
     </row>
     <row r="159" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A159" t="s">
-        <v>34</v>
-      </c>
-      <c r="B159" t="s">
-        <v>16</v>
-      </c>
-      <c r="C159" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="D159" s="3">
-        <v>16</v>
-      </c>
-      <c r="E159" s="3">
-        <v>2200</v>
-      </c>
+      <c r="C159" s="3"/>
+      <c r="E159" s="3"/>
     </row>
     <row r="160" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A160" t="s">
-        <v>34</v>
-      </c>
-      <c r="B160" t="s">
-        <v>12</v>
-      </c>
-      <c r="C160" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="D160" s="3">
-        <v>8</v>
-      </c>
-      <c r="E160" s="3">
-        <v>2850</v>
-      </c>
-    </row>
-    <row r="161" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A161" t="s">
-        <v>34</v>
-      </c>
-      <c r="B161" t="s">
-        <v>17</v>
-      </c>
-      <c r="C161" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="D161" s="3">
-        <v>8</v>
-      </c>
-      <c r="E161" s="3">
-        <v>3500</v>
-      </c>
-    </row>
-    <row r="162" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A162" t="s">
-        <v>34</v>
-      </c>
-      <c r="B162" t="s">
-        <v>18</v>
-      </c>
-      <c r="C162" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="D162" s="3">
-        <v>8</v>
-      </c>
-      <c r="E162" s="3">
-        <v>3500</v>
-      </c>
-    </row>
-    <row r="163" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A163" t="s">
-        <v>34</v>
-      </c>
-      <c r="B163" t="s">
-        <v>19</v>
-      </c>
-      <c r="C163" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="D163" s="3">
-        <v>12</v>
-      </c>
-      <c r="E163" s="3">
-        <v>2300</v>
-      </c>
-    </row>
-    <row r="164" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A164" t="s">
-        <v>34</v>
-      </c>
-      <c r="B164" t="s">
-        <v>20</v>
-      </c>
-      <c r="C164" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="D164" s="3">
-        <v>8</v>
-      </c>
-      <c r="E164" s="3">
-        <v>5700</v>
-      </c>
-    </row>
-    <row r="165" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A165" t="s">
-        <v>34</v>
-      </c>
-      <c r="B165" t="s">
-        <v>15</v>
-      </c>
-      <c r="C165" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="D165" s="3">
-        <v>12</v>
-      </c>
-      <c r="E165" s="3">
-        <v>2600</v>
-      </c>
-    </row>
-    <row r="166" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A166" t="s">
-        <v>34</v>
-      </c>
-      <c r="B166" t="s">
-        <v>21</v>
-      </c>
-      <c r="C166" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="D166" s="3">
-        <v>8</v>
-      </c>
-      <c r="E166" s="3">
-        <v>2650</v>
-      </c>
-    </row>
-    <row r="167" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A167" t="s">
-        <v>34</v>
-      </c>
-      <c r="B167" t="s">
-        <v>6</v>
-      </c>
-      <c r="C167" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="D167">
-        <v>8</v>
-      </c>
-      <c r="E167" s="3">
-        <v>53500</v>
-      </c>
-    </row>
-    <row r="168" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A168" t="s">
-        <v>34</v>
-      </c>
-      <c r="B168" t="s">
-        <v>35</v>
-      </c>
-      <c r="C168" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="D168">
-        <v>12</v>
-      </c>
-      <c r="E168" s="3">
-        <v>5700</v>
-      </c>
-    </row>
-    <row r="169" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A169" t="s">
-        <v>34</v>
-      </c>
-      <c r="B169" t="s">
-        <v>32</v>
-      </c>
-      <c r="C169" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="D169">
-        <v>220</v>
-      </c>
-      <c r="E169" s="3">
-        <v>53500</v>
-      </c>
-    </row>
-    <row r="170" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C160" s="3"/>
+      <c r="D160" s="3"/>
+      <c r="E160" s="3"/>
+    </row>
+    <row r="161" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="C161" s="3"/>
+      <c r="E161" s="3"/>
+    </row>
+    <row r="162" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="C162" s="3"/>
+      <c r="E162" s="3"/>
+    </row>
+    <row r="163" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="C163" s="3"/>
+      <c r="E163" s="3"/>
+    </row>
+    <row r="164" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="C164" s="3"/>
+      <c r="D164" s="3"/>
+      <c r="E164" s="3"/>
+    </row>
+    <row r="165" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="C165" s="3"/>
+      <c r="E165" s="3"/>
+    </row>
+    <row r="166" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="C166" s="3"/>
+      <c r="D166" s="3"/>
+      <c r="E166" s="3"/>
+    </row>
+    <row r="167" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="C167" s="3"/>
+      <c r="E167" s="3"/>
+    </row>
+    <row r="168" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="C168" s="3"/>
+      <c r="E168" s="3"/>
+    </row>
+    <row r="169" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="C169" s="3"/>
+      <c r="E169" s="3"/>
+    </row>
+    <row r="170" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B170" s="1"/>
       <c r="C170" s="3"/>
       <c r="D170" s="3"/>
       <c r="E170" s="3"/>
     </row>
-    <row r="171" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="171" spans="2:5" x14ac:dyDescent="0.25">
       <c r="C171" s="3"/>
       <c r="E171" s="3"/>
     </row>
-    <row r="172" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="172" spans="2:5" x14ac:dyDescent="0.25">
       <c r="C172" s="3"/>
       <c r="D172" s="3"/>
       <c r="E172" s="3"/>
     </row>
-    <row r="173" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="173" spans="2:5" x14ac:dyDescent="0.25">
       <c r="C173" s="3"/>
       <c r="E173" s="3"/>
     </row>
-    <row r="174" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="174" spans="2:5" x14ac:dyDescent="0.25">
       <c r="C174" s="3"/>
       <c r="E174" s="3"/>
     </row>
-    <row r="175" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="175" spans="2:5" x14ac:dyDescent="0.25">
       <c r="C175" s="3"/>
       <c r="E175" s="3"/>
     </row>
-    <row r="176" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="176" spans="2:5" x14ac:dyDescent="0.25">
       <c r="C176" s="3"/>
       <c r="D176" s="3"/>
       <c r="E176" s="3"/>
@@ -3534,73 +3228,72 @@
       <c r="C192" s="3"/>
       <c r="E192" s="3"/>
     </row>
-    <row r="193" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="193" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C193" s="3"/>
       <c r="E193" s="3"/>
     </row>
-    <row r="194" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B194" s="1"/>
+    <row r="194" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C194" s="3"/>
       <c r="D194" s="3"/>
       <c r="E194" s="3"/>
     </row>
-    <row r="195" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="195" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C195" s="3"/>
       <c r="E195" s="3"/>
     </row>
-    <row r="196" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="196" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C196" s="3"/>
       <c r="D196" s="3"/>
       <c r="E196" s="3"/>
     </row>
-    <row r="197" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="197" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C197" s="3"/>
       <c r="E197" s="3"/>
     </row>
-    <row r="198" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="198" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C198" s="3"/>
       <c r="E198" s="3"/>
     </row>
-    <row r="199" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="199" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C199" s="3"/>
       <c r="E199" s="3"/>
     </row>
-    <row r="200" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="200" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C200" s="3"/>
       <c r="D200" s="3"/>
       <c r="E200" s="3"/>
     </row>
-    <row r="201" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="201" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C201" s="3"/>
       <c r="E201" s="3"/>
     </row>
-    <row r="202" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="202" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C202" s="3"/>
       <c r="D202" s="3"/>
       <c r="E202" s="3"/>
     </row>
-    <row r="203" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="203" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C203" s="3"/>
       <c r="E203" s="3"/>
     </row>
-    <row r="204" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="204" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C204" s="3"/>
       <c r="E204" s="3"/>
     </row>
-    <row r="205" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="205" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C205" s="3"/>
       <c r="E205" s="3"/>
     </row>
-    <row r="206" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="206" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C206" s="3"/>
       <c r="D206" s="3"/>
       <c r="E206" s="3"/>
     </row>
-    <row r="207" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="207" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C207" s="3"/>
       <c r="E207" s="3"/>
     </row>
-    <row r="208" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="208" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C208" s="3"/>
       <c r="D208" s="3"/>
       <c r="E208" s="3"/>
@@ -3619,7 +3312,6 @@
     </row>
     <row r="212" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C212" s="3"/>
-      <c r="D212" s="3"/>
       <c r="E212" s="3"/>
     </row>
     <row r="213" spans="3:5" x14ac:dyDescent="0.25">
@@ -3628,7 +3320,6 @@
     </row>
     <row r="214" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C214" s="3"/>
-      <c r="D214" s="3"/>
       <c r="E214" s="3"/>
     </row>
     <row r="215" spans="3:5" x14ac:dyDescent="0.25">
@@ -3723,6 +3414,7 @@
     </row>
     <row r="236" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C236" s="3"/>
+      <c r="D236" s="3"/>
       <c r="E236" s="3"/>
     </row>
     <row r="237" spans="3:5" x14ac:dyDescent="0.25">
@@ -3731,6 +3423,7 @@
     </row>
     <row r="238" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C238" s="3"/>
+      <c r="D238" s="3"/>
       <c r="E238" s="3"/>
     </row>
     <row r="239" spans="3:5" x14ac:dyDescent="0.25">
@@ -3773,7 +3466,6 @@
     </row>
     <row r="248" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C248" s="3"/>
-      <c r="D248" s="3"/>
       <c r="E248" s="3"/>
     </row>
     <row r="249" spans="3:5" x14ac:dyDescent="0.25">
@@ -3782,7 +3474,6 @@
     </row>
     <row r="250" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C250" s="3"/>
-      <c r="D250" s="3"/>
       <c r="E250" s="3"/>
     </row>
     <row r="251" spans="3:5" x14ac:dyDescent="0.25">
@@ -3797,110 +3488,8 @@
       <c r="C253" s="3"/>
       <c r="E253" s="3"/>
     </row>
-    <row r="254" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C254" s="3"/>
-      <c r="D254" s="3"/>
-      <c r="E254" s="3"/>
-    </row>
-    <row r="255" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C255" s="3"/>
-      <c r="E255" s="3"/>
-    </row>
-    <row r="256" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C256" s="3"/>
-      <c r="D256" s="3"/>
-      <c r="E256" s="3"/>
-    </row>
-    <row r="257" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C257" s="3"/>
-      <c r="E257" s="3"/>
-    </row>
-    <row r="258" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C258" s="3"/>
-      <c r="E258" s="3"/>
-    </row>
-    <row r="259" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C259" s="3"/>
-      <c r="E259" s="3"/>
-    </row>
-    <row r="260" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C260" s="3"/>
-      <c r="D260" s="3"/>
-      <c r="E260" s="3"/>
-    </row>
-    <row r="261" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C261" s="3"/>
-      <c r="E261" s="3"/>
-    </row>
-    <row r="262" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C262" s="3"/>
-      <c r="D262" s="3"/>
-      <c r="E262" s="3"/>
-    </row>
-    <row r="263" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C263" s="3"/>
-      <c r="E263" s="3"/>
-    </row>
-    <row r="264" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C264" s="3"/>
-      <c r="E264" s="3"/>
-    </row>
-    <row r="265" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C265" s="3"/>
-      <c r="E265" s="3"/>
-    </row>
-    <row r="266" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C266" s="3"/>
-      <c r="D266" s="3"/>
-      <c r="E266" s="3"/>
-    </row>
-    <row r="267" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C267" s="3"/>
-      <c r="E267" s="3"/>
-    </row>
-    <row r="268" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C268" s="3"/>
-      <c r="D268" s="3"/>
-      <c r="E268" s="3"/>
-    </row>
-    <row r="269" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C269" s="3"/>
-      <c r="E269" s="3"/>
-    </row>
-    <row r="270" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C270" s="3"/>
-      <c r="E270" s="3"/>
-    </row>
-    <row r="271" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C271" s="3"/>
-      <c r="E271" s="3"/>
-    </row>
-    <row r="272" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C272" s="3"/>
-      <c r="E272" s="3"/>
-    </row>
-    <row r="273" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C273" s="3"/>
-      <c r="E273" s="3"/>
-    </row>
-    <row r="274" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C274" s="3"/>
-      <c r="E274" s="3"/>
-    </row>
-    <row r="275" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C275" s="3"/>
-      <c r="E275" s="3"/>
-    </row>
-    <row r="276" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C276" s="3"/>
-      <c r="E276" s="3"/>
-    </row>
-    <row r="277" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C277" s="3"/>
-      <c r="E277" s="3"/>
-    </row>
   </sheetData>
-  <autoFilter ref="B1:E169" xr:uid="{6956BB2C-DA9E-4412-BCD4-BB80A11153FE}"/>
+  <autoFilter ref="B1:E145" xr:uid="{6956BB2C-DA9E-4412-BCD4-BB80A11153FE}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/data/metas.xlsx
+++ b/data/metas.xlsx
@@ -1,24 +1,28 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sercomunicaciones2-my.sharepoint.com/personal/auxcomisiones_sercomunicaciones_com/Documents/PAOLA/Liquidacióncvs/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="613" documentId="8_{787D9E49-702D-43BD-B99B-4B64F775E77B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EA69A06F-5842-4B12-8D1B-0AE897DA6C73}"/>
+  <xr:revisionPtr revIDLastSave="710" documentId="8_{787D9E49-702D-43BD-B99B-4B64F775E77B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{43E7087E-74F7-40B5-A297-51337DCF9C59}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D1391136-BBFC-43C7-B899-B77B0ECC5956}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{D1391136-BBFC-43C7-B899-B77B0ECC5956}"/>
   </bookViews>
   <sheets>
-    <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
+    <sheet name="Hoja2" sheetId="2" r:id="rId1"/>
+    <sheet name="Hoja1" sheetId="1" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$B$1:$E$145</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Hoja1!$A$1:$E$241</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
+  <pivotCaches>
+    <pivotCache cacheId="59" r:id="rId3"/>
+  </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -39,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="437" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="762" uniqueCount="40">
   <si>
     <t>BARBOSA</t>
   </si>
@@ -148,6 +152,18 @@
   <si>
     <t>NUMERARIO</t>
   </si>
+  <si>
+    <t>Marzo</t>
+  </si>
+  <si>
+    <t>Total general</t>
+  </si>
+  <si>
+    <t>(Todas)</t>
+  </si>
+  <si>
+    <t>Suma de Meta_Producto</t>
+  </si>
 </sst>
 </file>
 
@@ -205,7 +221,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -215,6 +231,9 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -230,6 +249,2311 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Aux Comisiones" refreshedDate="46092.590271759262" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="288" xr:uid="{B4970592-A96D-470A-A8C5-FC6DBD168D2D}">
+  <cacheSource type="worksheet">
+    <worksheetSource ref="A1:E241" sheet="Hoja1"/>
+  </cacheSource>
+  <cacheFields count="5">
+    <cacheField name="Mes" numFmtId="0">
+      <sharedItems count="2">
+        <s v="Febrero"/>
+        <s v="Marzo"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Sucursal" numFmtId="0">
+      <sharedItems count="24">
+        <s v="COPACABANA"/>
+        <s v="BARBOSA"/>
+        <s v="CAUCASIA"/>
+        <s v="CIUDAD BOLIVAR"/>
+        <s v="DABEIBA"/>
+        <s v="DON MATIAS"/>
+        <s v="EL BAGRE"/>
+        <s v="FRONTINO"/>
+        <s v="GIRARDOTA"/>
+        <s v="LA ESTRELLA"/>
+        <s v="NECHI"/>
+        <s v="PRADO"/>
+        <s v="SEGOVIA"/>
+        <s v="YARUMAL"/>
+        <s v="ZARAGOZA"/>
+        <s v="BELLO"/>
+        <s v="CALDAS"/>
+        <s v="ENVIGADO"/>
+        <s v="ITAGUI"/>
+        <s v="JUNIN"/>
+        <s v="SABANETA"/>
+        <s v="TERMINAL NORTE"/>
+        <s v="GENERAL"/>
+        <s v="NUMERARIO"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Producto" numFmtId="0">
+      <sharedItems count="6">
+        <s v="CVS PLUS"/>
+        <s v="POSTPAGO"/>
+        <s v="HOGAR"/>
+        <s v="TERMINALES"/>
+        <s v="FOCO"/>
+        <s v="OTROS"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Meta_Producto" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="27700"/>
+    </cacheField>
+    <cacheField name="Meta_General" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="1100" maxValue="53500" count="19">
+        <n v="2800"/>
+        <n v="2400"/>
+        <n v="1350"/>
+        <n v="1700"/>
+        <n v="1450"/>
+        <n v="1500"/>
+        <n v="4000"/>
+        <n v="2600"/>
+        <n v="2000"/>
+        <n v="1100"/>
+        <n v="2200"/>
+        <n v="1600"/>
+        <n v="2850"/>
+        <n v="3500"/>
+        <n v="2300"/>
+        <n v="5700"/>
+        <n v="2650"/>
+        <n v="53500"/>
+        <n v="6000"/>
+      </sharedItems>
+    </cacheField>
+  </cacheFields>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="288">
+  <r>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <n v="1500"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="1"/>
+    <n v="47"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="2"/>
+    <n v="10"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="3"/>
+    <n v="66"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="4"/>
+    <n v="29"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="5"/>
+    <n v="146"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="0"/>
+    <n v="1500"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="1"/>
+    <n v="37"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="2"/>
+    <n v="6"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="3"/>
+    <n v="57"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="4"/>
+    <n v="25"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="5"/>
+    <n v="95"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="2"/>
+    <x v="0"/>
+    <n v="0"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="2"/>
+    <x v="1"/>
+    <n v="12"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="2"/>
+    <x v="2"/>
+    <n v="4"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="2"/>
+    <x v="3"/>
+    <n v="35"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="2"/>
+    <x v="4"/>
+    <n v="15"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="2"/>
+    <x v="5"/>
+    <n v="32"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="3"/>
+    <x v="0"/>
+    <n v="800"/>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="3"/>
+    <x v="1"/>
+    <n v="33"/>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="3"/>
+    <x v="2"/>
+    <n v="1"/>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="3"/>
+    <x v="3"/>
+    <n v="45"/>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="3"/>
+    <x v="4"/>
+    <n v="20"/>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="3"/>
+    <x v="5"/>
+    <n v="135"/>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="4"/>
+    <x v="0"/>
+    <n v="1200"/>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="4"/>
+    <x v="1"/>
+    <n v="18"/>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="4"/>
+    <x v="2"/>
+    <n v="1"/>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="4"/>
+    <x v="3"/>
+    <n v="35"/>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="4"/>
+    <x v="4"/>
+    <n v="15"/>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="4"/>
+    <x v="5"/>
+    <n v="69"/>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="5"/>
+    <x v="0"/>
+    <n v="1200"/>
+    <x v="5"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="5"/>
+    <x v="1"/>
+    <n v="37"/>
+    <x v="5"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="5"/>
+    <x v="2"/>
+    <n v="1"/>
+    <x v="5"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="5"/>
+    <x v="3"/>
+    <n v="31"/>
+    <x v="5"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="5"/>
+    <x v="4"/>
+    <n v="14"/>
+    <x v="5"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="5"/>
+    <x v="5"/>
+    <n v="68"/>
+    <x v="5"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="6"/>
+    <x v="0"/>
+    <n v="1500"/>
+    <x v="6"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="6"/>
+    <x v="1"/>
+    <n v="42"/>
+    <x v="6"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="6"/>
+    <x v="2"/>
+    <n v="1"/>
+    <x v="6"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="6"/>
+    <x v="3"/>
+    <n v="112"/>
+    <x v="6"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="6"/>
+    <x v="4"/>
+    <n v="48"/>
+    <x v="6"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="6"/>
+    <x v="5"/>
+    <n v="176"/>
+    <x v="6"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="7"/>
+    <x v="0"/>
+    <n v="1500"/>
+    <x v="7"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="7"/>
+    <x v="1"/>
+    <n v="26"/>
+    <x v="7"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="7"/>
+    <x v="2"/>
+    <n v="1"/>
+    <x v="7"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="7"/>
+    <x v="3"/>
+    <n v="98"/>
+    <x v="7"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="7"/>
+    <x v="4"/>
+    <n v="42"/>
+    <x v="7"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="7"/>
+    <x v="5"/>
+    <n v="98"/>
+    <x v="7"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="8"/>
+    <x v="0"/>
+    <n v="1200"/>
+    <x v="8"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="8"/>
+    <x v="1"/>
+    <n v="32"/>
+    <x v="8"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="8"/>
+    <x v="2"/>
+    <n v="6"/>
+    <x v="8"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="8"/>
+    <x v="3"/>
+    <n v="39"/>
+    <x v="8"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="8"/>
+    <x v="4"/>
+    <n v="17"/>
+    <x v="8"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="8"/>
+    <x v="5"/>
+    <n v="128"/>
+    <x v="8"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="9"/>
+    <x v="0"/>
+    <n v="1200"/>
+    <x v="5"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="9"/>
+    <x v="1"/>
+    <n v="17"/>
+    <x v="5"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="9"/>
+    <x v="2"/>
+    <n v="6"/>
+    <x v="5"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="9"/>
+    <x v="3"/>
+    <n v="17"/>
+    <x v="5"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="9"/>
+    <x v="4"/>
+    <n v="8"/>
+    <x v="5"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="9"/>
+    <x v="5"/>
+    <n v="54"/>
+    <x v="5"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="10"/>
+    <x v="0"/>
+    <n v="800"/>
+    <x v="8"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="10"/>
+    <x v="1"/>
+    <n v="13"/>
+    <x v="8"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="10"/>
+    <x v="2"/>
+    <n v="1"/>
+    <x v="8"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="10"/>
+    <x v="3"/>
+    <n v="57"/>
+    <x v="8"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="10"/>
+    <x v="4"/>
+    <n v="25"/>
+    <x v="8"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="10"/>
+    <x v="5"/>
+    <n v="60"/>
+    <x v="8"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="11"/>
+    <x v="0"/>
+    <n v="1200"/>
+    <x v="9"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="11"/>
+    <x v="1"/>
+    <n v="16"/>
+    <x v="9"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="11"/>
+    <x v="2"/>
+    <n v="4"/>
+    <x v="9"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="11"/>
+    <x v="3"/>
+    <n v="21"/>
+    <x v="9"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="11"/>
+    <x v="4"/>
+    <n v="9"/>
+    <x v="9"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="11"/>
+    <x v="5"/>
+    <n v="74"/>
+    <x v="9"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="12"/>
+    <x v="0"/>
+    <n v="1200"/>
+    <x v="10"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="12"/>
+    <x v="1"/>
+    <n v="34"/>
+    <x v="10"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="12"/>
+    <x v="2"/>
+    <n v="1"/>
+    <x v="10"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="12"/>
+    <x v="3"/>
+    <n v="42"/>
+    <x v="10"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="12"/>
+    <x v="4"/>
+    <n v="18"/>
+    <x v="10"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="12"/>
+    <x v="5"/>
+    <n v="183"/>
+    <x v="10"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="13"/>
+    <x v="0"/>
+    <n v="1200"/>
+    <x v="11"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="13"/>
+    <x v="1"/>
+    <n v="22"/>
+    <x v="11"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="13"/>
+    <x v="2"/>
+    <n v="6"/>
+    <x v="11"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="13"/>
+    <x v="3"/>
+    <n v="42"/>
+    <x v="11"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="13"/>
+    <x v="4"/>
+    <n v="18"/>
+    <x v="11"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="13"/>
+    <x v="5"/>
+    <n v="168"/>
+    <x v="11"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="14"/>
+    <x v="0"/>
+    <n v="1200"/>
+    <x v="10"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="14"/>
+    <x v="1"/>
+    <n v="23"/>
+    <x v="10"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="14"/>
+    <x v="2"/>
+    <n v="1"/>
+    <x v="10"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="14"/>
+    <x v="3"/>
+    <n v="50"/>
+    <x v="10"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="14"/>
+    <x v="4"/>
+    <n v="22"/>
+    <x v="10"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="14"/>
+    <x v="5"/>
+    <n v="92"/>
+    <x v="10"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="15"/>
+    <x v="0"/>
+    <n v="1500"/>
+    <x v="12"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="15"/>
+    <x v="1"/>
+    <n v="52"/>
+    <x v="12"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="15"/>
+    <x v="2"/>
+    <n v="10"/>
+    <x v="12"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="15"/>
+    <x v="3"/>
+    <n v="71"/>
+    <x v="12"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="15"/>
+    <x v="4"/>
+    <n v="31"/>
+    <x v="12"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="15"/>
+    <x v="5"/>
+    <n v="129"/>
+    <x v="12"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="16"/>
+    <x v="0"/>
+    <n v="1500"/>
+    <x v="13"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="16"/>
+    <x v="1"/>
+    <n v="62"/>
+    <x v="13"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="16"/>
+    <x v="2"/>
+    <n v="10"/>
+    <x v="13"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="16"/>
+    <x v="3"/>
+    <n v="87"/>
+    <x v="13"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="16"/>
+    <x v="4"/>
+    <n v="37"/>
+    <x v="13"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="16"/>
+    <x v="5"/>
+    <n v="183"/>
+    <x v="13"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="17"/>
+    <x v="0"/>
+    <n v="1500"/>
+    <x v="13"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="17"/>
+    <x v="1"/>
+    <n v="78"/>
+    <x v="13"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="17"/>
+    <x v="2"/>
+    <n v="16"/>
+    <x v="13"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="17"/>
+    <x v="3"/>
+    <n v="67"/>
+    <x v="13"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="17"/>
+    <x v="4"/>
+    <n v="29"/>
+    <x v="13"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="17"/>
+    <x v="5"/>
+    <n v="198"/>
+    <x v="13"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="18"/>
+    <x v="0"/>
+    <n v="1500"/>
+    <x v="14"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="18"/>
+    <x v="1"/>
+    <n v="44"/>
+    <x v="14"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="18"/>
+    <x v="2"/>
+    <n v="10"/>
+    <x v="14"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="18"/>
+    <x v="3"/>
+    <n v="50"/>
+    <x v="14"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="18"/>
+    <x v="4"/>
+    <n v="22"/>
+    <x v="14"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="18"/>
+    <x v="5"/>
+    <n v="151"/>
+    <x v="14"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="19"/>
+    <x v="0"/>
+    <n v="1500"/>
+    <x v="15"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="19"/>
+    <x v="1"/>
+    <n v="103"/>
+    <x v="15"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="19"/>
+    <x v="2"/>
+    <n v="14"/>
+    <x v="15"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="19"/>
+    <x v="3"/>
+    <n v="165"/>
+    <x v="15"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="19"/>
+    <x v="4"/>
+    <n v="71"/>
+    <x v="15"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="19"/>
+    <x v="5"/>
+    <n v="192"/>
+    <x v="15"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="20"/>
+    <x v="0"/>
+    <n v="1500"/>
+    <x v="7"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="20"/>
+    <x v="1"/>
+    <n v="62"/>
+    <x v="7"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="20"/>
+    <x v="2"/>
+    <n v="11"/>
+    <x v="7"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="20"/>
+    <x v="3"/>
+    <n v="52"/>
+    <x v="7"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="20"/>
+    <x v="4"/>
+    <n v="22"/>
+    <x v="7"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="20"/>
+    <x v="5"/>
+    <n v="181"/>
+    <x v="7"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="21"/>
+    <x v="0"/>
+    <n v="1500"/>
+    <x v="16"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="21"/>
+    <x v="1"/>
+    <n v="30"/>
+    <x v="16"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="21"/>
+    <x v="2"/>
+    <n v="10"/>
+    <x v="16"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="21"/>
+    <x v="3"/>
+    <n v="64"/>
+    <x v="16"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="21"/>
+    <x v="4"/>
+    <n v="28"/>
+    <x v="16"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="21"/>
+    <x v="5"/>
+    <n v="126"/>
+    <x v="16"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="22"/>
+    <x v="0"/>
+    <n v="27700"/>
+    <x v="17"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="22"/>
+    <x v="1"/>
+    <n v="840"/>
+    <x v="17"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="22"/>
+    <x v="2"/>
+    <n v="131"/>
+    <x v="17"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="22"/>
+    <x v="3"/>
+    <n v="1303"/>
+    <x v="17"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="22"/>
+    <x v="4"/>
+    <n v="565"/>
+    <x v="17"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="22"/>
+    <x v="5"/>
+    <n v="2738"/>
+    <x v="17"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="23"/>
+    <x v="0"/>
+    <n v="1500"/>
+    <x v="15"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="23"/>
+    <x v="1"/>
+    <n v="103"/>
+    <x v="15"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="23"/>
+    <x v="2"/>
+    <n v="14"/>
+    <x v="15"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="23"/>
+    <x v="3"/>
+    <n v="1303"/>
+    <x v="15"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="23"/>
+    <x v="4"/>
+    <n v="71"/>
+    <x v="15"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="23"/>
+    <x v="5"/>
+    <n v="192"/>
+    <x v="15"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="0"/>
+    <n v="1500"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="1"/>
+    <n v="47"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="2"/>
+    <n v="10"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="3"/>
+    <n v="66"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="4"/>
+    <n v="29"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="5"/>
+    <n v="146"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="0"/>
+    <n v="1500"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="1"/>
+    <n v="37"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="2"/>
+    <n v="6"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="3"/>
+    <n v="57"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="4"/>
+    <n v="25"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="5"/>
+    <n v="95"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="2"/>
+    <x v="0"/>
+    <n v="0"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="2"/>
+    <x v="1"/>
+    <n v="12"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="2"/>
+    <x v="2"/>
+    <n v="4"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="2"/>
+    <x v="3"/>
+    <n v="35"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="2"/>
+    <x v="4"/>
+    <n v="15"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="2"/>
+    <x v="5"/>
+    <n v="32"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="3"/>
+    <x v="0"/>
+    <n v="800"/>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="3"/>
+    <x v="1"/>
+    <n v="33"/>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="3"/>
+    <x v="2"/>
+    <n v="1"/>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="3"/>
+    <x v="3"/>
+    <n v="45"/>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="3"/>
+    <x v="4"/>
+    <n v="20"/>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="3"/>
+    <x v="5"/>
+    <n v="135"/>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="4"/>
+    <x v="0"/>
+    <n v="1200"/>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="4"/>
+    <x v="1"/>
+    <n v="18"/>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="4"/>
+    <x v="2"/>
+    <n v="1"/>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="4"/>
+    <x v="3"/>
+    <n v="35"/>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="4"/>
+    <x v="4"/>
+    <n v="15"/>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="4"/>
+    <x v="5"/>
+    <n v="69"/>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="5"/>
+    <x v="0"/>
+    <n v="1200"/>
+    <x v="5"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="5"/>
+    <x v="1"/>
+    <n v="37"/>
+    <x v="5"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="5"/>
+    <x v="2"/>
+    <n v="1"/>
+    <x v="5"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="5"/>
+    <x v="3"/>
+    <n v="31"/>
+    <x v="5"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="5"/>
+    <x v="4"/>
+    <n v="14"/>
+    <x v="5"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="5"/>
+    <x v="5"/>
+    <n v="68"/>
+    <x v="5"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="6"/>
+    <x v="0"/>
+    <n v="1500"/>
+    <x v="6"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="6"/>
+    <x v="1"/>
+    <n v="42"/>
+    <x v="6"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="6"/>
+    <x v="2"/>
+    <n v="1"/>
+    <x v="6"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="6"/>
+    <x v="3"/>
+    <n v="112"/>
+    <x v="6"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="6"/>
+    <x v="4"/>
+    <n v="48"/>
+    <x v="6"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="6"/>
+    <x v="5"/>
+    <n v="176"/>
+    <x v="6"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="7"/>
+    <x v="0"/>
+    <n v="1500"/>
+    <x v="7"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="7"/>
+    <x v="1"/>
+    <n v="26"/>
+    <x v="7"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="7"/>
+    <x v="2"/>
+    <n v="1"/>
+    <x v="7"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="7"/>
+    <x v="3"/>
+    <n v="130"/>
+    <x v="7"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="7"/>
+    <x v="4"/>
+    <n v="42"/>
+    <x v="7"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="7"/>
+    <x v="5"/>
+    <n v="98"/>
+    <x v="7"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="8"/>
+    <x v="0"/>
+    <n v="1200"/>
+    <x v="8"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="8"/>
+    <x v="1"/>
+    <n v="32"/>
+    <x v="8"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="8"/>
+    <x v="2"/>
+    <n v="6"/>
+    <x v="8"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="8"/>
+    <x v="3"/>
+    <n v="39"/>
+    <x v="8"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="8"/>
+    <x v="4"/>
+    <n v="17"/>
+    <x v="8"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="8"/>
+    <x v="5"/>
+    <n v="128"/>
+    <x v="8"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="9"/>
+    <x v="0"/>
+    <n v="1200"/>
+    <x v="5"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="9"/>
+    <x v="1"/>
+    <n v="17"/>
+    <x v="5"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="9"/>
+    <x v="2"/>
+    <n v="6"/>
+    <x v="5"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="9"/>
+    <x v="3"/>
+    <n v="17"/>
+    <x v="5"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="9"/>
+    <x v="4"/>
+    <n v="8"/>
+    <x v="5"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="9"/>
+    <x v="5"/>
+    <n v="54"/>
+    <x v="5"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="10"/>
+    <x v="0"/>
+    <n v="800"/>
+    <x v="8"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="10"/>
+    <x v="1"/>
+    <n v="13"/>
+    <x v="8"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="10"/>
+    <x v="2"/>
+    <n v="1"/>
+    <x v="8"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="10"/>
+    <x v="3"/>
+    <n v="57"/>
+    <x v="8"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="10"/>
+    <x v="4"/>
+    <n v="25"/>
+    <x v="8"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="10"/>
+    <x v="5"/>
+    <n v="60"/>
+    <x v="8"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="11"/>
+    <x v="0"/>
+    <n v="1200"/>
+    <x v="9"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="11"/>
+    <x v="1"/>
+    <n v="16"/>
+    <x v="9"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="11"/>
+    <x v="2"/>
+    <n v="4"/>
+    <x v="9"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="11"/>
+    <x v="3"/>
+    <n v="21"/>
+    <x v="9"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="11"/>
+    <x v="4"/>
+    <n v="9"/>
+    <x v="9"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="11"/>
+    <x v="5"/>
+    <n v="74"/>
+    <x v="9"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="12"/>
+    <x v="0"/>
+    <n v="1200"/>
+    <x v="10"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="12"/>
+    <x v="1"/>
+    <n v="34"/>
+    <x v="10"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="12"/>
+    <x v="2"/>
+    <n v="1"/>
+    <x v="10"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="12"/>
+    <x v="3"/>
+    <n v="42"/>
+    <x v="10"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="12"/>
+    <x v="4"/>
+    <n v="18"/>
+    <x v="10"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="12"/>
+    <x v="5"/>
+    <n v="183"/>
+    <x v="10"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="13"/>
+    <x v="0"/>
+    <n v="1200"/>
+    <x v="11"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="13"/>
+    <x v="1"/>
+    <n v="22"/>
+    <x v="11"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="13"/>
+    <x v="2"/>
+    <n v="6"/>
+    <x v="11"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="13"/>
+    <x v="3"/>
+    <n v="42"/>
+    <x v="11"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="13"/>
+    <x v="4"/>
+    <n v="18"/>
+    <x v="11"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="13"/>
+    <x v="5"/>
+    <n v="168"/>
+    <x v="11"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="14"/>
+    <x v="0"/>
+    <n v="1200"/>
+    <x v="10"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="14"/>
+    <x v="1"/>
+    <n v="23"/>
+    <x v="10"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="14"/>
+    <x v="2"/>
+    <n v="1"/>
+    <x v="10"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="14"/>
+    <x v="3"/>
+    <n v="50"/>
+    <x v="10"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="14"/>
+    <x v="4"/>
+    <n v="22"/>
+    <x v="10"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="14"/>
+    <x v="5"/>
+    <n v="92"/>
+    <x v="10"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="15"/>
+    <x v="0"/>
+    <n v="1500"/>
+    <x v="12"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="15"/>
+    <x v="1"/>
+    <n v="52"/>
+    <x v="12"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="15"/>
+    <x v="2"/>
+    <n v="10"/>
+    <x v="12"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="15"/>
+    <x v="3"/>
+    <n v="71"/>
+    <x v="12"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="15"/>
+    <x v="4"/>
+    <n v="31"/>
+    <x v="12"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="15"/>
+    <x v="5"/>
+    <n v="129"/>
+    <x v="12"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="16"/>
+    <x v="0"/>
+    <n v="1500"/>
+    <x v="13"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="16"/>
+    <x v="1"/>
+    <n v="62"/>
+    <x v="13"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="16"/>
+    <x v="2"/>
+    <n v="10"/>
+    <x v="13"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="16"/>
+    <x v="3"/>
+    <n v="87"/>
+    <x v="13"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="16"/>
+    <x v="4"/>
+    <n v="37"/>
+    <x v="13"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="16"/>
+    <x v="5"/>
+    <n v="183"/>
+    <x v="13"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="17"/>
+    <x v="0"/>
+    <n v="1500"/>
+    <x v="13"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="17"/>
+    <x v="1"/>
+    <n v="78"/>
+    <x v="13"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="17"/>
+    <x v="2"/>
+    <n v="16"/>
+    <x v="13"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="17"/>
+    <x v="3"/>
+    <n v="67"/>
+    <x v="13"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="17"/>
+    <x v="4"/>
+    <n v="29"/>
+    <x v="13"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="17"/>
+    <x v="5"/>
+    <n v="198"/>
+    <x v="13"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="18"/>
+    <x v="0"/>
+    <n v="1500"/>
+    <x v="14"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="18"/>
+    <x v="1"/>
+    <n v="44"/>
+    <x v="14"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="18"/>
+    <x v="2"/>
+    <n v="10"/>
+    <x v="14"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="18"/>
+    <x v="3"/>
+    <n v="50"/>
+    <x v="14"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="18"/>
+    <x v="4"/>
+    <n v="22"/>
+    <x v="14"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="18"/>
+    <x v="5"/>
+    <n v="151"/>
+    <x v="14"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="19"/>
+    <x v="0"/>
+    <n v="1500"/>
+    <x v="18"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="19"/>
+    <x v="1"/>
+    <n v="103"/>
+    <x v="18"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="19"/>
+    <x v="2"/>
+    <n v="14"/>
+    <x v="18"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="19"/>
+    <x v="3"/>
+    <n v="165"/>
+    <x v="18"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="19"/>
+    <x v="4"/>
+    <n v="71"/>
+    <x v="18"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="19"/>
+    <x v="5"/>
+    <n v="192"/>
+    <x v="18"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="20"/>
+    <x v="0"/>
+    <n v="1500"/>
+    <x v="7"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="20"/>
+    <x v="1"/>
+    <n v="62"/>
+    <x v="7"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="20"/>
+    <x v="2"/>
+    <n v="11"/>
+    <x v="7"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="20"/>
+    <x v="3"/>
+    <n v="52"/>
+    <x v="7"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="20"/>
+    <x v="4"/>
+    <n v="22"/>
+    <x v="7"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="20"/>
+    <x v="5"/>
+    <n v="181"/>
+    <x v="7"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="21"/>
+    <x v="0"/>
+    <n v="1500"/>
+    <x v="16"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="21"/>
+    <x v="1"/>
+    <n v="30"/>
+    <x v="16"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="21"/>
+    <x v="2"/>
+    <n v="10"/>
+    <x v="16"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="21"/>
+    <x v="3"/>
+    <n v="64"/>
+    <x v="16"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="21"/>
+    <x v="4"/>
+    <n v="28"/>
+    <x v="16"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="21"/>
+    <x v="5"/>
+    <n v="126"/>
+    <x v="16"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="22"/>
+    <x v="0"/>
+    <n v="27700"/>
+    <x v="17"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="22"/>
+    <x v="1"/>
+    <n v="840"/>
+    <x v="17"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="22"/>
+    <x v="2"/>
+    <n v="131"/>
+    <x v="17"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="22"/>
+    <x v="3"/>
+    <n v="1303"/>
+    <x v="17"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="22"/>
+    <x v="4"/>
+    <n v="565"/>
+    <x v="17"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="22"/>
+    <x v="5"/>
+    <n v="2738"/>
+    <x v="17"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="23"/>
+    <x v="0"/>
+    <n v="1500"/>
+    <x v="15"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="23"/>
+    <x v="1"/>
+    <n v="103"/>
+    <x v="15"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="23"/>
+    <x v="2"/>
+    <n v="14"/>
+    <x v="15"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="23"/>
+    <x v="3"/>
+    <n v="1303"/>
+    <x v="15"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="23"/>
+    <x v="4"/>
+    <n v="71"/>
+    <x v="15"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="23"/>
+    <x v="5"/>
+    <n v="192"/>
+    <x v="15"/>
+  </r>
+</pivotCacheRecords>
+</file>
+
+<file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E78ED4BE-4740-4324-A20E-21AC80D7E338}" name="TablaDinámica9" cacheId="59" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+  <location ref="A3:H29" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
+  <pivotFields count="5">
+    <pivotField axis="axisPage" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0">
+      <items count="3">
+        <item x="0"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" compact="0" outline="0" showAll="0" defaultSubtotal="0">
+      <items count="24">
+        <item x="1"/>
+        <item x="15"/>
+        <item x="16"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="0"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="17"/>
+        <item x="7"/>
+        <item x="22"/>
+        <item x="8"/>
+        <item x="18"/>
+        <item x="19"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="23"/>
+        <item x="11"/>
+        <item x="20"/>
+        <item x="12"/>
+        <item x="21"/>
+        <item x="13"/>
+        <item x="14"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisCol" compact="0" outline="0" showAll="0">
+      <items count="7">
+        <item x="0"/>
+        <item x="4"/>
+        <item x="2"/>
+        <item x="5"/>
+        <item x="1"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0">
+      <items count="19">
+        <item x="9"/>
+        <item x="2"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="11"/>
+        <item x="3"/>
+        <item x="8"/>
+        <item x="10"/>
+        <item x="14"/>
+        <item x="1"/>
+        <item x="7"/>
+        <item x="16"/>
+        <item x="0"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="6"/>
+        <item x="15"/>
+        <item x="18"/>
+        <item x="17"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="1"/>
+  </rowFields>
+  <rowItems count="25">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i>
+      <x v="10"/>
+    </i>
+    <i>
+      <x v="11"/>
+    </i>
+    <i>
+      <x v="12"/>
+    </i>
+    <i>
+      <x v="13"/>
+    </i>
+    <i>
+      <x v="14"/>
+    </i>
+    <i>
+      <x v="15"/>
+    </i>
+    <i>
+      <x v="16"/>
+    </i>
+    <i>
+      <x v="17"/>
+    </i>
+    <i>
+      <x v="18"/>
+    </i>
+    <i>
+      <x v="19"/>
+    </i>
+    <i>
+      <x v="20"/>
+    </i>
+    <i>
+      <x v="21"/>
+    </i>
+    <i>
+      <x v="22"/>
+    </i>
+    <i>
+      <x v="23"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="2"/>
+  </colFields>
+  <colItems count="7">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <pageFields count="1">
+    <pageField fld="0" hier="-1"/>
+  </pageFields>
+  <dataFields count="1">
+    <dataField name="Suma de Meta_Producto" fld="3" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -548,8 +2872,715 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{045CA401-D4F5-42F5-9F33-A556D5A2E6C8}">
+  <dimension ref="A1:H29"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="22.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="7" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="B1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="B4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" t="s">
+        <v>31</v>
+      </c>
+      <c r="D4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E4" t="s">
+        <v>30</v>
+      </c>
+      <c r="F4" t="s">
+        <v>27</v>
+      </c>
+      <c r="G4" t="s">
+        <v>29</v>
+      </c>
+      <c r="H4" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B5" s="7">
+        <v>3000</v>
+      </c>
+      <c r="C5" s="7">
+        <v>50</v>
+      </c>
+      <c r="D5" s="7">
+        <v>12</v>
+      </c>
+      <c r="E5" s="7">
+        <v>190</v>
+      </c>
+      <c r="F5" s="7">
+        <v>74</v>
+      </c>
+      <c r="G5" s="7">
+        <v>114</v>
+      </c>
+      <c r="H5" s="7">
+        <v>3440</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6" s="7">
+        <v>3000</v>
+      </c>
+      <c r="C6" s="7">
+        <v>62</v>
+      </c>
+      <c r="D6" s="7">
+        <v>20</v>
+      </c>
+      <c r="E6" s="7">
+        <v>258</v>
+      </c>
+      <c r="F6" s="7">
+        <v>104</v>
+      </c>
+      <c r="G6" s="7">
+        <v>142</v>
+      </c>
+      <c r="H6" s="7">
+        <v>3586</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B7" s="7">
+        <v>3000</v>
+      </c>
+      <c r="C7" s="7">
+        <v>74</v>
+      </c>
+      <c r="D7" s="7">
+        <v>20</v>
+      </c>
+      <c r="E7" s="7">
+        <v>366</v>
+      </c>
+      <c r="F7" s="7">
+        <v>124</v>
+      </c>
+      <c r="G7" s="7">
+        <v>174</v>
+      </c>
+      <c r="H7" s="7">
+        <v>3758</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>2</v>
+      </c>
+      <c r="B8" s="7">
+        <v>0</v>
+      </c>
+      <c r="C8" s="7">
+        <v>30</v>
+      </c>
+      <c r="D8" s="7">
+        <v>8</v>
+      </c>
+      <c r="E8" s="7">
+        <v>64</v>
+      </c>
+      <c r="F8" s="7">
+        <v>24</v>
+      </c>
+      <c r="G8" s="7">
+        <v>70</v>
+      </c>
+      <c r="H8" s="7">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" s="7">
+        <v>1600</v>
+      </c>
+      <c r="C9" s="7">
+        <v>40</v>
+      </c>
+      <c r="D9" s="7">
+        <v>2</v>
+      </c>
+      <c r="E9" s="7">
+        <v>270</v>
+      </c>
+      <c r="F9" s="7">
+        <v>66</v>
+      </c>
+      <c r="G9" s="7">
+        <v>90</v>
+      </c>
+      <c r="H9" s="7">
+        <v>2068</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>5</v>
+      </c>
+      <c r="B10" s="7">
+        <v>3000</v>
+      </c>
+      <c r="C10" s="7">
+        <v>58</v>
+      </c>
+      <c r="D10" s="7">
+        <v>20</v>
+      </c>
+      <c r="E10" s="7">
+        <v>292</v>
+      </c>
+      <c r="F10" s="7">
+        <v>94</v>
+      </c>
+      <c r="G10" s="7">
+        <v>132</v>
+      </c>
+      <c r="H10" s="7">
+        <v>3596</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" s="7">
+        <v>2400</v>
+      </c>
+      <c r="C11" s="7">
+        <v>30</v>
+      </c>
+      <c r="D11" s="7">
+        <v>2</v>
+      </c>
+      <c r="E11" s="7">
+        <v>138</v>
+      </c>
+      <c r="F11" s="7">
+        <v>36</v>
+      </c>
+      <c r="G11" s="7">
+        <v>70</v>
+      </c>
+      <c r="H11" s="7">
+        <v>2676</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>10</v>
+      </c>
+      <c r="B12" s="7">
+        <v>2400</v>
+      </c>
+      <c r="C12" s="7">
+        <v>28</v>
+      </c>
+      <c r="D12" s="7">
+        <v>2</v>
+      </c>
+      <c r="E12" s="7">
+        <v>136</v>
+      </c>
+      <c r="F12" s="7">
+        <v>74</v>
+      </c>
+      <c r="G12" s="7">
+        <v>62</v>
+      </c>
+      <c r="H12" s="7">
+        <v>2702</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>9</v>
+      </c>
+      <c r="B13" s="7">
+        <v>3000</v>
+      </c>
+      <c r="C13" s="7">
+        <v>96</v>
+      </c>
+      <c r="D13" s="7">
+        <v>2</v>
+      </c>
+      <c r="E13" s="7">
+        <v>352</v>
+      </c>
+      <c r="F13" s="7">
+        <v>84</v>
+      </c>
+      <c r="G13" s="7">
+        <v>224</v>
+      </c>
+      <c r="H13" s="7">
+        <v>3758</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>11</v>
+      </c>
+      <c r="B14" s="7">
+        <v>3000</v>
+      </c>
+      <c r="C14" s="7">
+        <v>58</v>
+      </c>
+      <c r="D14" s="7">
+        <v>32</v>
+      </c>
+      <c r="E14" s="7">
+        <v>396</v>
+      </c>
+      <c r="F14" s="7">
+        <v>156</v>
+      </c>
+      <c r="G14" s="7">
+        <v>134</v>
+      </c>
+      <c r="H14" s="7">
+        <v>3776</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>13</v>
+      </c>
+      <c r="B15" s="7">
+        <v>3000</v>
+      </c>
+      <c r="C15" s="7">
+        <v>84</v>
+      </c>
+      <c r="D15" s="7">
+        <v>2</v>
+      </c>
+      <c r="E15" s="7">
+        <v>196</v>
+      </c>
+      <c r="F15" s="7">
+        <v>52</v>
+      </c>
+      <c r="G15" s="7">
+        <v>228</v>
+      </c>
+      <c r="H15" s="7">
+        <v>3562</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>32</v>
+      </c>
+      <c r="B16" s="7">
+        <v>55400</v>
+      </c>
+      <c r="C16" s="7">
+        <v>1130</v>
+      </c>
+      <c r="D16" s="7">
+        <v>262</v>
+      </c>
+      <c r="E16" s="7">
+        <v>5476</v>
+      </c>
+      <c r="F16" s="7">
+        <v>1680</v>
+      </c>
+      <c r="G16" s="7">
+        <v>2606</v>
+      </c>
+      <c r="H16" s="7">
+        <v>66554</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>7</v>
+      </c>
+      <c r="B17" s="7">
+        <v>2400</v>
+      </c>
+      <c r="C17" s="7">
+        <v>34</v>
+      </c>
+      <c r="D17" s="7">
+        <v>12</v>
+      </c>
+      <c r="E17" s="7">
+        <v>256</v>
+      </c>
+      <c r="F17" s="7">
+        <v>64</v>
+      </c>
+      <c r="G17" s="7">
+        <v>78</v>
+      </c>
+      <c r="H17" s="7">
+        <v>2844</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>14</v>
+      </c>
+      <c r="B18" s="7">
+        <v>3000</v>
+      </c>
+      <c r="C18" s="7">
+        <v>44</v>
+      </c>
+      <c r="D18" s="7">
+        <v>20</v>
+      </c>
+      <c r="E18" s="7">
+        <v>302</v>
+      </c>
+      <c r="F18" s="7">
+        <v>88</v>
+      </c>
+      <c r="G18" s="7">
+        <v>100</v>
+      </c>
+      <c r="H18" s="7">
+        <v>3554</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>16</v>
+      </c>
+      <c r="B19" s="7">
+        <v>3000</v>
+      </c>
+      <c r="C19" s="7">
+        <v>142</v>
+      </c>
+      <c r="D19" s="7">
+        <v>28</v>
+      </c>
+      <c r="E19" s="7">
+        <v>384</v>
+      </c>
+      <c r="F19" s="7">
+        <v>206</v>
+      </c>
+      <c r="G19" s="7">
+        <v>330</v>
+      </c>
+      <c r="H19" s="7">
+        <v>4090</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>12</v>
+      </c>
+      <c r="B20" s="7">
+        <v>2400</v>
+      </c>
+      <c r="C20" s="7">
+        <v>16</v>
+      </c>
+      <c r="D20" s="7">
+        <v>12</v>
+      </c>
+      <c r="E20" s="7">
+        <v>108</v>
+      </c>
+      <c r="F20" s="7">
+        <v>34</v>
+      </c>
+      <c r="G20" s="7">
+        <v>34</v>
+      </c>
+      <c r="H20" s="7">
+        <v>2604</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>17</v>
+      </c>
+      <c r="B21" s="7">
+        <v>1600</v>
+      </c>
+      <c r="C21" s="7">
+        <v>50</v>
+      </c>
+      <c r="D21" s="7">
+        <v>2</v>
+      </c>
+      <c r="E21" s="7">
+        <v>120</v>
+      </c>
+      <c r="F21" s="7">
+        <v>26</v>
+      </c>
+      <c r="G21" s="7">
+        <v>114</v>
+      </c>
+      <c r="H21" s="7">
+        <v>1912</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>35</v>
+      </c>
+      <c r="B22" s="7">
+        <v>3000</v>
+      </c>
+      <c r="C22" s="7">
+        <v>142</v>
+      </c>
+      <c r="D22" s="7">
+        <v>28</v>
+      </c>
+      <c r="E22" s="7">
+        <v>384</v>
+      </c>
+      <c r="F22" s="7">
+        <v>206</v>
+      </c>
+      <c r="G22" s="7">
+        <v>2606</v>
+      </c>
+      <c r="H22" s="7">
+        <v>6366</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>18</v>
+      </c>
+      <c r="B23" s="7">
+        <v>2400</v>
+      </c>
+      <c r="C23" s="7">
+        <v>18</v>
+      </c>
+      <c r="D23" s="7">
+        <v>8</v>
+      </c>
+      <c r="E23" s="7">
+        <v>148</v>
+      </c>
+      <c r="F23" s="7">
+        <v>32</v>
+      </c>
+      <c r="G23" s="7">
+        <v>42</v>
+      </c>
+      <c r="H23" s="7">
+        <v>2648</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>19</v>
+      </c>
+      <c r="B24" s="7">
+        <v>3000</v>
+      </c>
+      <c r="C24" s="7">
+        <v>44</v>
+      </c>
+      <c r="D24" s="7">
+        <v>22</v>
+      </c>
+      <c r="E24" s="7">
+        <v>362</v>
+      </c>
+      <c r="F24" s="7">
+        <v>124</v>
+      </c>
+      <c r="G24" s="7">
+        <v>104</v>
+      </c>
+      <c r="H24" s="7">
+        <v>3656</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>20</v>
+      </c>
+      <c r="B25" s="7">
+        <v>2400</v>
+      </c>
+      <c r="C25" s="7">
+        <v>36</v>
+      </c>
+      <c r="D25" s="7">
+        <v>2</v>
+      </c>
+      <c r="E25" s="7">
+        <v>366</v>
+      </c>
+      <c r="F25" s="7">
+        <v>68</v>
+      </c>
+      <c r="G25" s="7">
+        <v>84</v>
+      </c>
+      <c r="H25" s="7">
+        <v>2956</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>15</v>
+      </c>
+      <c r="B26" s="7">
+        <v>3000</v>
+      </c>
+      <c r="C26" s="7">
+        <v>56</v>
+      </c>
+      <c r="D26" s="7">
+        <v>20</v>
+      </c>
+      <c r="E26" s="7">
+        <v>252</v>
+      </c>
+      <c r="F26" s="7">
+        <v>60</v>
+      </c>
+      <c r="G26" s="7">
+        <v>128</v>
+      </c>
+      <c r="H26" s="7">
+        <v>3516</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>21</v>
+      </c>
+      <c r="B27" s="7">
+        <v>2400</v>
+      </c>
+      <c r="C27" s="7">
+        <v>36</v>
+      </c>
+      <c r="D27" s="7">
+        <v>12</v>
+      </c>
+      <c r="E27" s="7">
+        <v>336</v>
+      </c>
+      <c r="F27" s="7">
+        <v>44</v>
+      </c>
+      <c r="G27" s="7">
+        <v>84</v>
+      </c>
+      <c r="H27" s="7">
+        <v>2912</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>6</v>
+      </c>
+      <c r="B28" s="7">
+        <v>2400</v>
+      </c>
+      <c r="C28" s="7">
+        <v>44</v>
+      </c>
+      <c r="D28" s="7">
+        <v>2</v>
+      </c>
+      <c r="E28" s="7">
+        <v>184</v>
+      </c>
+      <c r="F28" s="7">
+        <v>46</v>
+      </c>
+      <c r="G28" s="7">
+        <v>100</v>
+      </c>
+      <c r="H28" s="7">
+        <v>2776</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>37</v>
+      </c>
+      <c r="B29" s="7">
+        <v>113800</v>
+      </c>
+      <c r="C29" s="7">
+        <v>2402</v>
+      </c>
+      <c r="D29" s="7">
+        <v>552</v>
+      </c>
+      <c r="E29" s="7">
+        <v>11336</v>
+      </c>
+      <c r="F29" s="7">
+        <v>3566</v>
+      </c>
+      <c r="G29" s="7">
+        <v>7850</v>
+      </c>
+      <c r="H29" s="7">
+        <v>139506</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6956BB2C-DA9E-4412-BCD4-BB80A11153FE}">
-  <dimension ref="A1:E253"/>
+  <dimension ref="A1:E241"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.7109375" bestFit="1" customWidth="1"/>
@@ -637,7 +3668,7 @@
         <v>29</v>
       </c>
       <c r="D5" s="3">
-        <v>66</v>
+        <v>95</v>
       </c>
       <c r="E5" s="3">
         <v>2800</v>
@@ -651,10 +3682,10 @@
         <v>5</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D6" s="3">
-        <v>29</v>
+        <v>146</v>
       </c>
       <c r="E6" s="3">
         <v>2800</v>
@@ -665,16 +3696,16 @@
         <v>34</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="D7" s="3">
-        <v>146</v>
+        <v>1500</v>
       </c>
       <c r="E7" s="3">
-        <v>2800</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -685,10 +3716,10 @@
         <v>0</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="D8" s="3">
-        <v>1500</v>
+        <v>37</v>
       </c>
       <c r="E8" s="3">
         <v>2400</v>
@@ -702,10 +3733,10 @@
         <v>0</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D9" s="3">
-        <v>37</v>
+        <v>6</v>
       </c>
       <c r="E9" s="3">
         <v>2400</v>
@@ -719,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D10" s="3">
-        <v>6</v>
+        <v>82</v>
       </c>
       <c r="E10" s="3">
         <v>2400</v>
@@ -736,10 +3767,10 @@
         <v>0</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="D11" s="3">
-        <v>57</v>
+        <v>30</v>
+      </c>
+      <c r="D11">
+        <v>95</v>
       </c>
       <c r="E11" s="3">
         <v>2400</v>
@@ -749,34 +3780,34 @@
       <c r="A12" t="s">
         <v>34</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B12" t="s">
+        <v>2</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D12" s="3">
         <v>0</v>
       </c>
-      <c r="C12" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="D12">
-        <v>25</v>
-      </c>
       <c r="E12" s="3">
-        <v>2400</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>34</v>
       </c>
-      <c r="B13" s="3" t="s">
-        <v>0</v>
+      <c r="B13" t="s">
+        <v>2</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D13">
-        <v>95</v>
+        <v>12</v>
       </c>
       <c r="E13" s="3">
-        <v>2400</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
@@ -787,10 +3818,10 @@
         <v>2</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="D14" s="3">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E14" s="3">
         <v>1350</v>
@@ -804,10 +3835,10 @@
         <v>2</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D15">
-        <v>12</v>
+        <v>29</v>
+      </c>
+      <c r="D15" s="3">
+        <v>50</v>
       </c>
       <c r="E15" s="3">
         <v>1350</v>
@@ -821,10 +3852,10 @@
         <v>2</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="D16" s="3">
-        <v>4</v>
+        <v>30</v>
+      </c>
+      <c r="D16">
+        <v>32</v>
       </c>
       <c r="E16" s="3">
         <v>1350</v>
@@ -835,16 +3866,16 @@
         <v>34</v>
       </c>
       <c r="B17" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="D17" s="3">
-        <v>35</v>
+        <v>800</v>
       </c>
       <c r="E17" s="3">
-        <v>1350</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
@@ -852,16 +3883,16 @@
         <v>34</v>
       </c>
       <c r="B18" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="D18">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="E18" s="3">
-        <v>1350</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
@@ -869,16 +3900,16 @@
         <v>34</v>
       </c>
       <c r="B19" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="D19">
-        <v>32</v>
+        <v>28</v>
+      </c>
+      <c r="D19" s="3">
+        <v>1</v>
       </c>
       <c r="E19" s="3">
-        <v>1350</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
@@ -889,10 +3920,10 @@
         <v>3</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="D20" s="3">
-        <v>800</v>
+        <v>65</v>
       </c>
       <c r="E20" s="3">
         <v>1700</v>
@@ -906,10 +3937,10 @@
         <v>3</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="D21">
-        <v>33</v>
+        <v>135</v>
       </c>
       <c r="E21" s="3">
         <v>1700</v>
@@ -920,16 +3951,16 @@
         <v>34</v>
       </c>
       <c r="B22" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="D22" s="3">
-        <v>1</v>
+        <v>1200</v>
       </c>
       <c r="E22" s="3">
-        <v>1700</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
@@ -937,16 +3968,16 @@
         <v>34</v>
       </c>
       <c r="B23" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="D23" s="3">
-        <v>45</v>
+        <v>27</v>
+      </c>
+      <c r="D23">
+        <v>18</v>
       </c>
       <c r="E23" s="3">
-        <v>1700</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
@@ -954,16 +3985,16 @@
         <v>34</v>
       </c>
       <c r="B24" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="D24">
-        <v>20</v>
+        <v>28</v>
+      </c>
+      <c r="D24" s="3">
+        <v>1</v>
       </c>
       <c r="E24" s="3">
-        <v>1700</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
@@ -971,16 +4002,16 @@
         <v>34</v>
       </c>
       <c r="B25" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="D25">
-        <v>135</v>
+        <v>29</v>
+      </c>
+      <c r="D25" s="3">
+        <v>50</v>
       </c>
       <c r="E25" s="3">
-        <v>1700</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
@@ -991,10 +4022,10 @@
         <v>8</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D26" s="3">
-        <v>1200</v>
+        <v>30</v>
+      </c>
+      <c r="D26">
+        <v>69</v>
       </c>
       <c r="E26" s="3">
         <v>1450</v>
@@ -1005,16 +4036,16 @@
         <v>34</v>
       </c>
       <c r="B27" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D27">
-        <v>18</v>
+        <v>22</v>
+      </c>
+      <c r="D27" s="3">
+        <v>1200</v>
       </c>
       <c r="E27" s="3">
-        <v>1450</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
@@ -1022,16 +4053,16 @@
         <v>34</v>
       </c>
       <c r="B28" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="D28" s="3">
-        <v>1</v>
+        <v>27</v>
+      </c>
+      <c r="D28">
+        <v>37</v>
       </c>
       <c r="E28" s="3">
-        <v>1450</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
@@ -1039,16 +4070,16 @@
         <v>34</v>
       </c>
       <c r="B29" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D29" s="3">
-        <v>35</v>
+        <v>1</v>
       </c>
       <c r="E29" s="3">
-        <v>1450</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
@@ -1056,16 +4087,16 @@
         <v>34</v>
       </c>
       <c r="B30" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="D30">
-        <v>15</v>
+        <v>29</v>
+      </c>
+      <c r="D30" s="3">
+        <v>45</v>
       </c>
       <c r="E30" s="3">
-        <v>1450</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
@@ -1073,16 +4104,16 @@
         <v>34</v>
       </c>
       <c r="B31" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C31" s="3" t="s">
         <v>30</v>
       </c>
       <c r="D31">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E31" s="3">
-        <v>1450</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
@@ -1090,16 +4121,16 @@
         <v>34</v>
       </c>
       <c r="B32" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C32" s="3" t="s">
         <v>22</v>
       </c>
       <c r="D32" s="3">
-        <v>1200</v>
+        <v>1500</v>
       </c>
       <c r="E32" s="3">
-        <v>1500</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
@@ -1107,16 +4138,16 @@
         <v>34</v>
       </c>
       <c r="B33" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C33" s="3" t="s">
         <v>27</v>
       </c>
       <c r="D33">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="E33" s="3">
-        <v>1500</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
@@ -1124,7 +4155,7 @@
         <v>34</v>
       </c>
       <c r="B34" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C34" s="3" t="s">
         <v>28</v>
@@ -1133,7 +4164,7 @@
         <v>1</v>
       </c>
       <c r="E34" s="3">
-        <v>1500</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
@@ -1141,16 +4172,16 @@
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C35" s="3" t="s">
         <v>29</v>
       </c>
       <c r="D35" s="3">
-        <v>31</v>
+        <v>160</v>
       </c>
       <c r="E35" s="3">
-        <v>1500</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
@@ -1158,16 +4189,16 @@
         <v>34</v>
       </c>
       <c r="B36" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D36">
-        <v>14</v>
+        <v>176</v>
       </c>
       <c r="E36" s="3">
-        <v>1500</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
@@ -1175,16 +4206,16 @@
         <v>34</v>
       </c>
       <c r="B37" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="D37">
-        <v>68</v>
+        <v>22</v>
+      </c>
+      <c r="D37" s="3">
+        <v>1500</v>
       </c>
       <c r="E37" s="3">
-        <v>1500</v>
+        <v>2600</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
@@ -1192,16 +4223,16 @@
         <v>34</v>
       </c>
       <c r="B38" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D38" s="3">
-        <v>1500</v>
+        <v>27</v>
+      </c>
+      <c r="D38">
+        <v>26</v>
       </c>
       <c r="E38" s="3">
-        <v>4000</v>
+        <v>2600</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
@@ -1209,16 +4240,16 @@
         <v>34</v>
       </c>
       <c r="B39" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D39">
-        <v>42</v>
+        <v>28</v>
+      </c>
+      <c r="D39" s="3">
+        <v>1</v>
       </c>
       <c r="E39" s="3">
-        <v>4000</v>
+        <v>2600</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
@@ -1226,16 +4257,16 @@
         <v>34</v>
       </c>
       <c r="B40" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D40" s="3">
-        <v>1</v>
+        <v>140</v>
       </c>
       <c r="E40" s="3">
-        <v>4000</v>
+        <v>2600</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
@@ -1243,16 +4274,16 @@
         <v>34</v>
       </c>
       <c r="B41" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="D41" s="3">
-        <v>112</v>
+        <v>30</v>
+      </c>
+      <c r="D41">
+        <v>98</v>
       </c>
       <c r="E41" s="3">
-        <v>4000</v>
+        <v>2600</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
@@ -1260,16 +4291,16 @@
         <v>34</v>
       </c>
       <c r="B42" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="D42">
-        <v>48</v>
+        <v>22</v>
+      </c>
+      <c r="D42" s="3">
+        <v>1200</v>
       </c>
       <c r="E42" s="3">
-        <v>4000</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
@@ -1277,16 +4308,16 @@
         <v>34</v>
       </c>
       <c r="B43" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D43">
-        <v>176</v>
+        <v>32</v>
       </c>
       <c r="E43" s="3">
-        <v>4000</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
@@ -1294,16 +4325,16 @@
         <v>34</v>
       </c>
       <c r="B44" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="D44" s="3">
-        <v>1500</v>
+        <v>6</v>
       </c>
       <c r="E44" s="3">
-        <v>2600</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
@@ -1311,16 +4342,16 @@
         <v>34</v>
       </c>
       <c r="B45" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D45">
-        <v>26</v>
+        <v>29</v>
+      </c>
+      <c r="D45" s="3">
+        <v>56</v>
       </c>
       <c r="E45" s="3">
-        <v>2600</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
@@ -1328,33 +4359,33 @@
         <v>34</v>
       </c>
       <c r="B46" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="D46" s="3">
-        <v>1</v>
+        <v>30</v>
+      </c>
+      <c r="D46">
+        <v>128</v>
       </c>
       <c r="E46" s="3">
-        <v>2600</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>34</v>
       </c>
-      <c r="B47" t="s">
-        <v>13</v>
+      <c r="B47" s="1" t="s">
+        <v>12</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="D47" s="3">
-        <v>98</v>
+        <v>1200</v>
       </c>
       <c r="E47" s="3">
-        <v>2600</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
@@ -1362,16 +4393,16 @@
         <v>34</v>
       </c>
       <c r="B48" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="D48">
-        <v>42</v>
+        <v>17</v>
       </c>
       <c r="E48" s="3">
-        <v>2600</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
@@ -1379,16 +4410,16 @@
         <v>34</v>
       </c>
       <c r="B49" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="D49">
-        <v>98</v>
+        <v>28</v>
+      </c>
+      <c r="D49" s="3">
+        <v>6</v>
       </c>
       <c r="E49" s="3">
-        <v>2600</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
@@ -1396,16 +4427,16 @@
         <v>34</v>
       </c>
       <c r="B50" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="D50" s="3">
-        <v>1200</v>
+        <v>25</v>
       </c>
       <c r="E50" s="3">
-        <v>2000</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
@@ -1413,16 +4444,16 @@
         <v>34</v>
       </c>
       <c r="B51" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="D51">
-        <v>32</v>
+        <v>54</v>
       </c>
       <c r="E51" s="3">
-        <v>2000</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
@@ -1430,13 +4461,13 @@
         <v>34</v>
       </c>
       <c r="B52" t="s">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="D52" s="3">
-        <v>6</v>
+        <v>800</v>
       </c>
       <c r="E52" s="3">
         <v>2000</v>
@@ -1447,13 +4478,13 @@
         <v>34</v>
       </c>
       <c r="B53" t="s">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="D53" s="3">
-        <v>39</v>
+        <v>27</v>
+      </c>
+      <c r="D53">
+        <v>13</v>
       </c>
       <c r="E53" s="3">
         <v>2000</v>
@@ -1464,13 +4495,13 @@
         <v>34</v>
       </c>
       <c r="B54" t="s">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="D54">
-        <v>17</v>
+        <v>28</v>
+      </c>
+      <c r="D54" s="3">
+        <v>1</v>
       </c>
       <c r="E54" s="3">
         <v>2000</v>
@@ -1481,13 +4512,13 @@
         <v>34</v>
       </c>
       <c r="B55" t="s">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="D55">
-        <v>128</v>
+        <v>29</v>
+      </c>
+      <c r="D55" s="3">
+        <v>82</v>
       </c>
       <c r="E55" s="3">
         <v>2000</v>
@@ -1497,17 +4528,17 @@
       <c r="A56" t="s">
         <v>34</v>
       </c>
-      <c r="B56" s="1" t="s">
-        <v>12</v>
+      <c r="B56" t="s">
+        <v>17</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D56" s="3">
-        <v>1200</v>
+        <v>30</v>
+      </c>
+      <c r="D56">
+        <v>60</v>
       </c>
       <c r="E56" s="3">
-        <v>1500</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
@@ -1515,16 +4546,16 @@
         <v>34</v>
       </c>
       <c r="B57" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D57">
-        <v>17</v>
+        <v>22</v>
+      </c>
+      <c r="D57" s="3">
+        <v>1200</v>
       </c>
       <c r="E57" s="3">
-        <v>1500</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
@@ -1532,16 +4563,16 @@
         <v>34</v>
       </c>
       <c r="B58" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="D58" s="3">
-        <v>6</v>
+        <v>27</v>
+      </c>
+      <c r="D58">
+        <v>16</v>
       </c>
       <c r="E58" s="3">
-        <v>1500</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.25">
@@ -1549,16 +4580,16 @@
         <v>34</v>
       </c>
       <c r="B59" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D59" s="3">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="E59" s="3">
-        <v>1500</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
@@ -1566,16 +4597,16 @@
         <v>34</v>
       </c>
       <c r="B60" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="D60">
-        <v>8</v>
+        <v>29</v>
+      </c>
+      <c r="D60" s="3">
+        <v>30</v>
       </c>
       <c r="E60" s="3">
-        <v>1500</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
@@ -1583,16 +4614,16 @@
         <v>34</v>
       </c>
       <c r="B61" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="C61" s="3" t="s">
         <v>30</v>
       </c>
       <c r="D61">
-        <v>54</v>
+        <v>74</v>
       </c>
       <c r="E61" s="3">
-        <v>1500</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.25">
@@ -1600,16 +4631,16 @@
         <v>34</v>
       </c>
       <c r="B62" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C62" s="3" t="s">
         <v>22</v>
       </c>
       <c r="D62" s="3">
-        <v>800</v>
+        <v>1200</v>
       </c>
       <c r="E62" s="3">
-        <v>2000</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.25">
@@ -1617,16 +4648,16 @@
         <v>34</v>
       </c>
       <c r="B63" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C63" s="3" t="s">
         <v>27</v>
       </c>
       <c r="D63">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="E63" s="3">
-        <v>2000</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.25">
@@ -1634,7 +4665,7 @@
         <v>34</v>
       </c>
       <c r="B64" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C64" s="3" t="s">
         <v>28</v>
@@ -1643,7 +4674,7 @@
         <v>1</v>
       </c>
       <c r="E64" s="3">
-        <v>2000</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.25">
@@ -1651,16 +4682,16 @@
         <v>34</v>
       </c>
       <c r="B65" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C65" s="3" t="s">
         <v>29</v>
       </c>
       <c r="D65" s="3">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E65" s="3">
-        <v>2000</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.25">
@@ -1668,16 +4699,16 @@
         <v>34</v>
       </c>
       <c r="B66" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D66">
-        <v>25</v>
+        <v>183</v>
       </c>
       <c r="E66" s="3">
-        <v>2000</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.25">
@@ -1685,16 +4716,16 @@
         <v>34</v>
       </c>
       <c r="B67" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="D67">
-        <v>60</v>
+        <v>22</v>
+      </c>
+      <c r="D67" s="3">
+        <v>1200</v>
       </c>
       <c r="E67" s="3">
-        <v>2000</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.25">
@@ -1702,16 +4733,16 @@
         <v>34</v>
       </c>
       <c r="B68" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C68" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D68">
         <v>22</v>
       </c>
-      <c r="D68" s="3">
-        <v>1200</v>
-      </c>
       <c r="E68" s="3">
-        <v>1100</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.25">
@@ -1719,33 +4750,33 @@
         <v>34</v>
       </c>
       <c r="B69" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D69">
-        <v>16</v>
+        <v>28</v>
+      </c>
+      <c r="D69" s="3">
+        <v>6</v>
       </c>
       <c r="E69" s="3">
-        <v>1100</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>34</v>
       </c>
       <c r="B70" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D70" s="3">
-        <v>4</v>
+        <v>60</v>
       </c>
       <c r="E70" s="3">
-        <v>1100</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.25">
@@ -1753,16 +4784,16 @@
         <v>34</v>
       </c>
       <c r="B71" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="D71" s="3">
-        <v>21</v>
+        <v>30</v>
+      </c>
+      <c r="D71">
+        <v>168</v>
       </c>
       <c r="E71" s="3">
-        <v>1100</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.25">
@@ -1770,16 +4801,16 @@
         <v>34</v>
       </c>
       <c r="B72" t="s">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="D72">
-        <v>9</v>
+        <v>22</v>
+      </c>
+      <c r="D72" s="3">
+        <v>1200</v>
       </c>
       <c r="E72" s="3">
-        <v>1100</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.25">
@@ -1787,16 +4818,16 @@
         <v>34</v>
       </c>
       <c r="B73" t="s">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D73">
-        <v>74</v>
+        <v>23</v>
       </c>
       <c r="E73" s="3">
-        <v>1100</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.25">
@@ -1804,13 +4835,13 @@
         <v>34</v>
       </c>
       <c r="B74" t="s">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="D74" s="3">
-        <v>1200</v>
+        <v>1</v>
       </c>
       <c r="E74" s="3">
         <v>2200</v>
@@ -1821,13 +4852,13 @@
         <v>34</v>
       </c>
       <c r="B75" t="s">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D75">
-        <v>34</v>
+        <v>29</v>
+      </c>
+      <c r="D75" s="3">
+        <v>72</v>
       </c>
       <c r="E75" s="3">
         <v>2200</v>
@@ -1838,13 +4869,13 @@
         <v>34</v>
       </c>
       <c r="B76" t="s">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="D76" s="3">
-        <v>1</v>
+        <v>30</v>
+      </c>
+      <c r="D76">
+        <v>92</v>
       </c>
       <c r="E76" s="3">
         <v>2200</v>
@@ -1855,16 +4886,16 @@
         <v>34</v>
       </c>
       <c r="B77" t="s">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="D77" s="3">
-        <v>42</v>
+        <v>1500</v>
       </c>
       <c r="E77" s="3">
-        <v>2200</v>
+        <v>2850</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.25">
@@ -1872,16 +4903,16 @@
         <v>34</v>
       </c>
       <c r="B78" t="s">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="D78">
-        <v>18</v>
+        <v>52</v>
       </c>
       <c r="E78" s="3">
-        <v>2200</v>
+        <v>2850</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.25">
@@ -1889,16 +4920,16 @@
         <v>34</v>
       </c>
       <c r="B79" t="s">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="D79">
-        <v>183</v>
+        <v>28</v>
+      </c>
+      <c r="D79" s="3">
+        <v>10</v>
       </c>
       <c r="E79" s="3">
-        <v>2200</v>
+        <v>2850</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.25">
@@ -1906,16 +4937,16 @@
         <v>34</v>
       </c>
       <c r="B80" t="s">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="D80" s="3">
-        <v>1200</v>
+        <v>102</v>
       </c>
       <c r="E80" s="3">
-        <v>1600</v>
+        <v>2850</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.25">
@@ -1923,16 +4954,16 @@
         <v>34</v>
       </c>
       <c r="B81" t="s">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="D81">
-        <v>22</v>
+        <v>129</v>
       </c>
       <c r="E81" s="3">
-        <v>1600</v>
+        <v>2850</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.25">
@@ -1940,50 +4971,50 @@
         <v>34</v>
       </c>
       <c r="B82" t="s">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="C82" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D82">
+        <v>1500</v>
+      </c>
+      <c r="E82" s="3">
+        <v>3500</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>34</v>
+      </c>
+      <c r="B83" t="s">
+        <v>4</v>
+      </c>
+      <c r="C83" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D83">
+        <v>62</v>
+      </c>
+      <c r="E83" s="3">
+        <v>3500</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>34</v>
+      </c>
+      <c r="B84" t="s">
+        <v>4</v>
+      </c>
+      <c r="C84" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="D82" s="3">
-        <v>6</v>
-      </c>
-      <c r="E82" s="3">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="83" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A83" t="s">
-        <v>34</v>
-      </c>
-      <c r="B83" t="s">
-        <v>21</v>
-      </c>
-      <c r="C83" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="D83" s="3">
-        <v>42</v>
-      </c>
-      <c r="E83" s="3">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="84" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A84" t="s">
-        <v>34</v>
-      </c>
-      <c r="B84" t="s">
-        <v>21</v>
-      </c>
-      <c r="C84" s="3" t="s">
-        <v>31</v>
-      </c>
       <c r="D84">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="E84" s="3">
-        <v>1600</v>
+        <v>3500</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.25">
@@ -1991,16 +5022,16 @@
         <v>34</v>
       </c>
       <c r="B85" t="s">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="D85">
-        <v>168</v>
+        <v>29</v>
+      </c>
+      <c r="D85" s="3">
+        <v>124</v>
       </c>
       <c r="E85" s="3">
-        <v>1600</v>
+        <v>3500</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.25">
@@ -2008,16 +5039,16 @@
         <v>34</v>
       </c>
       <c r="B86" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D86" s="3">
-        <v>1200</v>
+        <v>30</v>
+      </c>
+      <c r="D86">
+        <v>183</v>
       </c>
       <c r="E86" s="3">
-        <v>2200</v>
+        <v>3500</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.25">
@@ -2025,16 +5056,16 @@
         <v>34</v>
       </c>
       <c r="B87" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D87">
-        <v>23</v>
+        <v>22</v>
+      </c>
+      <c r="D87" s="3">
+        <v>1500</v>
       </c>
       <c r="E87" s="3">
-        <v>2200</v>
+        <v>3500</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.25">
@@ -2042,16 +5073,16 @@
         <v>34</v>
       </c>
       <c r="B88" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="D88" s="3">
-        <v>1</v>
+        <v>27</v>
+      </c>
+      <c r="D88">
+        <v>78</v>
       </c>
       <c r="E88" s="3">
-        <v>2200</v>
+        <v>3500</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.25">
@@ -2059,16 +5090,16 @@
         <v>34</v>
       </c>
       <c r="B89" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D89" s="3">
-        <v>50</v>
+        <v>16</v>
       </c>
       <c r="E89" s="3">
-        <v>2200</v>
+        <v>3500</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.25">
@@ -2076,16 +5107,16 @@
         <v>34</v>
       </c>
       <c r="B90" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="D90">
-        <v>22</v>
+        <v>29</v>
+      </c>
+      <c r="D90" s="3">
+        <v>96</v>
       </c>
       <c r="E90" s="3">
-        <v>2200</v>
+        <v>3500</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.25">
@@ -2093,16 +5124,16 @@
         <v>34</v>
       </c>
       <c r="B91" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="C91" s="3" t="s">
         <v>30</v>
       </c>
       <c r="D91">
-        <v>92</v>
+        <v>198</v>
       </c>
       <c r="E91" s="3">
-        <v>2200</v>
+        <v>3500</v>
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.25">
@@ -2110,7 +5141,7 @@
         <v>34</v>
       </c>
       <c r="B92" t="s">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="C92" s="3" t="s">
         <v>22</v>
@@ -2119,7 +5150,7 @@
         <v>1500</v>
       </c>
       <c r="E92" s="3">
-        <v>2850</v>
+        <v>2300</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.25">
@@ -2127,16 +5158,16 @@
         <v>34</v>
       </c>
       <c r="B93" t="s">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="C93" s="3" t="s">
         <v>27</v>
       </c>
       <c r="D93">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="E93" s="3">
-        <v>2850</v>
+        <v>2300</v>
       </c>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.25">
@@ -2144,7 +5175,7 @@
         <v>34</v>
       </c>
       <c r="B94" t="s">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="C94" s="3" t="s">
         <v>28</v>
@@ -2153,7 +5184,7 @@
         <v>10</v>
       </c>
       <c r="E94" s="3">
-        <v>2850</v>
+        <v>2300</v>
       </c>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.25">
@@ -2161,16 +5192,16 @@
         <v>34</v>
       </c>
       <c r="B95" t="s">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="C95" s="3" t="s">
         <v>29</v>
       </c>
       <c r="D95" s="3">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E95" s="3">
-        <v>2850</v>
+        <v>2300</v>
       </c>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.25">
@@ -2178,16 +5209,16 @@
         <v>34</v>
       </c>
       <c r="B96" t="s">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D96">
-        <v>31</v>
+        <v>151</v>
       </c>
       <c r="E96" s="3">
-        <v>2850</v>
+        <v>2300</v>
       </c>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.25">
@@ -2195,16 +5226,16 @@
         <v>34</v>
       </c>
       <c r="B97" t="s">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="D97">
-        <v>129</v>
+        <v>22</v>
+      </c>
+      <c r="D97" s="3">
+        <v>1500</v>
       </c>
       <c r="E97" s="3">
-        <v>2850</v>
+        <v>5700</v>
       </c>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.25">
@@ -2212,16 +5243,16 @@
         <v>34</v>
       </c>
       <c r="B98" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="C98" s="3" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="D98">
-        <v>1500</v>
+        <v>103</v>
       </c>
       <c r="E98" s="3">
-        <v>3500</v>
+        <v>5700</v>
       </c>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.25">
@@ -2229,16 +5260,16 @@
         <v>34</v>
       </c>
       <c r="B99" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="C99" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D99">
-        <v>62</v>
+        <v>28</v>
+      </c>
+      <c r="D99" s="3">
+        <v>14</v>
       </c>
       <c r="E99" s="3">
-        <v>3500</v>
+        <v>5700</v>
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.25">
@@ -2246,16 +5277,16 @@
         <v>34</v>
       </c>
       <c r="B100" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="C100" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="D100">
-        <v>10</v>
+        <v>29</v>
+      </c>
+      <c r="D100" s="3">
+        <v>236</v>
       </c>
       <c r="E100" s="3">
-        <v>3500</v>
+        <v>5700</v>
       </c>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.25">
@@ -2263,16 +5294,16 @@
         <v>34</v>
       </c>
       <c r="B101" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="C101" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="D101" s="3">
-        <v>87</v>
+        <v>30</v>
+      </c>
+      <c r="D101">
+        <v>192</v>
       </c>
       <c r="E101" s="3">
-        <v>3500</v>
+        <v>5700</v>
       </c>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.25">
@@ -2280,16 +5311,16 @@
         <v>34</v>
       </c>
       <c r="B102" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="C102" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="D102">
-        <v>37</v>
+        <v>22</v>
+      </c>
+      <c r="D102" s="3">
+        <v>1500</v>
       </c>
       <c r="E102" s="3">
-        <v>3500</v>
+        <v>2600</v>
       </c>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.25">
@@ -2297,16 +5328,16 @@
         <v>34</v>
       </c>
       <c r="B103" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="C103" s="3" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D103">
-        <v>183</v>
+        <v>62</v>
       </c>
       <c r="E103" s="3">
-        <v>3500</v>
+        <v>2600</v>
       </c>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.25">
@@ -2314,16 +5345,16 @@
         <v>34</v>
       </c>
       <c r="B104" t="s">
+        <v>19</v>
+      </c>
+      <c r="C104" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D104" s="3">
         <v>11</v>
       </c>
-      <c r="C104" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D104" s="3">
-        <v>1500</v>
-      </c>
       <c r="E104" s="3">
-        <v>3500</v>
+        <v>2600</v>
       </c>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.25">
@@ -2331,16 +5362,16 @@
         <v>34</v>
       </c>
       <c r="B105" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="C105" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D105">
-        <v>78</v>
+        <v>29</v>
+      </c>
+      <c r="D105" s="3">
+        <v>74</v>
       </c>
       <c r="E105" s="3">
-        <v>3500</v>
+        <v>2600</v>
       </c>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.25">
@@ -2348,16 +5379,16 @@
         <v>34</v>
       </c>
       <c r="B106" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="C106" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="D106" s="3">
-        <v>16</v>
+        <v>30</v>
+      </c>
+      <c r="D106">
+        <v>181</v>
       </c>
       <c r="E106" s="3">
-        <v>3500</v>
+        <v>2600</v>
       </c>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.25">
@@ -2365,16 +5396,16 @@
         <v>34</v>
       </c>
       <c r="B107" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C107" s="3" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="D107" s="3">
-        <v>67</v>
+        <v>1500</v>
       </c>
       <c r="E107" s="3">
-        <v>3500</v>
+        <v>2650</v>
       </c>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.25">
@@ -2382,16 +5413,16 @@
         <v>34</v>
       </c>
       <c r="B108" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C108" s="3" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="D108">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E108" s="3">
-        <v>3500</v>
+        <v>2650</v>
       </c>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.25">
@@ -2399,16 +5430,16 @@
         <v>34</v>
       </c>
       <c r="B109" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C109" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="D109">
-        <v>198</v>
+        <v>28</v>
+      </c>
+      <c r="D109" s="3">
+        <v>10</v>
       </c>
       <c r="E109" s="3">
-        <v>3500</v>
+        <v>2650</v>
       </c>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.25">
@@ -2416,16 +5447,16 @@
         <v>34</v>
       </c>
       <c r="B110" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C110" s="3" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="D110" s="3">
-        <v>1500</v>
+        <v>92</v>
       </c>
       <c r="E110" s="3">
-        <v>2300</v>
+        <v>2650</v>
       </c>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.25">
@@ -2433,16 +5464,16 @@
         <v>34</v>
       </c>
       <c r="B111" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C111" s="3" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="D111">
-        <v>44</v>
+        <v>126</v>
       </c>
       <c r="E111" s="3">
-        <v>2300</v>
+        <v>2650</v>
       </c>
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.25">
@@ -2450,16 +5481,16 @@
         <v>34</v>
       </c>
       <c r="B112" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="C112" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="D112" s="3">
-        <v>10</v>
+        <v>22</v>
+      </c>
+      <c r="D112">
+        <v>27700</v>
       </c>
       <c r="E112" s="3">
-        <v>2300</v>
+        <v>53500</v>
       </c>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.25">
@@ -2467,16 +5498,16 @@
         <v>34</v>
       </c>
       <c r="B113" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="C113" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="D113" s="3">
-        <v>50</v>
+        <v>27</v>
+      </c>
+      <c r="D113">
+        <v>840</v>
       </c>
       <c r="E113" s="3">
-        <v>2300</v>
+        <v>53500</v>
       </c>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.25">
@@ -2484,16 +5515,16 @@
         <v>34</v>
       </c>
       <c r="B114" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="C114" s="3" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D114">
-        <v>22</v>
+        <v>131</v>
       </c>
       <c r="E114" s="3">
-        <v>2300</v>
+        <v>53500</v>
       </c>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.25">
@@ -2501,16 +5532,16 @@
         <v>34</v>
       </c>
       <c r="B115" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="C115" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="D115">
-        <v>151</v>
+        <v>29</v>
+      </c>
+      <c r="D115" s="3">
+        <v>1868</v>
       </c>
       <c r="E115" s="3">
-        <v>2300</v>
+        <v>53500</v>
       </c>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.25">
@@ -2518,16 +5549,16 @@
         <v>34</v>
       </c>
       <c r="B116" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="C116" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D116" s="3">
-        <v>1500</v>
+        <v>30</v>
+      </c>
+      <c r="D116">
+        <v>2738</v>
       </c>
       <c r="E116" s="3">
-        <v>5700</v>
+        <v>53500</v>
       </c>
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.25">
@@ -2535,13 +5566,13 @@
         <v>34</v>
       </c>
       <c r="B117" t="s">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="C117" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D117">
-        <v>103</v>
+        <v>22</v>
+      </c>
+      <c r="D117" s="3">
+        <v>1500</v>
       </c>
       <c r="E117" s="3">
         <v>5700</v>
@@ -2552,13 +5583,13 @@
         <v>34</v>
       </c>
       <c r="B118" t="s">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="C118" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="D118" s="3">
-        <v>14</v>
+        <v>27</v>
+      </c>
+      <c r="D118">
+        <v>103</v>
       </c>
       <c r="E118" s="3">
         <v>5700</v>
@@ -2569,13 +5600,13 @@
         <v>34</v>
       </c>
       <c r="B119" t="s">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="C119" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D119" s="3">
-        <v>165</v>
+        <v>14</v>
       </c>
       <c r="E119" s="3">
         <v>5700</v>
@@ -2586,13 +5617,13 @@
         <v>34</v>
       </c>
       <c r="B120" t="s">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="C120" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="D120">
-        <v>71</v>
+        <v>29</v>
+      </c>
+      <c r="D120" s="3">
+        <v>1868</v>
       </c>
       <c r="E120" s="3">
         <v>5700</v>
@@ -2603,7 +5634,7 @@
         <v>34</v>
       </c>
       <c r="B121" t="s">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="C121" s="3" t="s">
         <v>30</v>
@@ -2617,10 +5648,10 @@
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>34</v>
-      </c>
-      <c r="B122" t="s">
-        <v>19</v>
+        <v>36</v>
+      </c>
+      <c r="B122" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="C122" s="3" t="s">
         <v>22</v>
@@ -2629,867 +5660,2034 @@
         <v>1500</v>
       </c>
       <c r="E122" s="3">
-        <v>2600</v>
+        <v>2800</v>
       </c>
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>34</v>
-      </c>
-      <c r="B123" t="s">
-        <v>19</v>
+        <v>36</v>
+      </c>
+      <c r="B123" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="C123" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="D123">
-        <v>62</v>
+      <c r="D123" s="3">
+        <v>47</v>
       </c>
       <c r="E123" s="3">
-        <v>2600</v>
+        <v>2800</v>
       </c>
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>34</v>
-      </c>
-      <c r="B124" t="s">
-        <v>19</v>
+        <v>36</v>
+      </c>
+      <c r="B124" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="C124" s="3" t="s">
         <v>28</v>
       </c>
       <c r="D124" s="3">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E124" s="3">
-        <v>2600</v>
+        <v>2800</v>
       </c>
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>34</v>
-      </c>
-      <c r="B125" t="s">
-        <v>19</v>
+        <v>36</v>
+      </c>
+      <c r="B125" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="C125" s="3" t="s">
         <v>29</v>
       </c>
       <c r="D125" s="3">
-        <v>52</v>
+        <v>95</v>
       </c>
       <c r="E125" s="3">
-        <v>2600</v>
+        <v>2800</v>
       </c>
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>34</v>
-      </c>
-      <c r="B126" t="s">
-        <v>19</v>
+        <v>36</v>
+      </c>
+      <c r="B126" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="C126" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="D126">
-        <v>22</v>
+        <v>30</v>
+      </c>
+      <c r="D126" s="3">
+        <v>146</v>
       </c>
       <c r="E126" s="3">
-        <v>2600</v>
+        <v>2800</v>
       </c>
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>34</v>
-      </c>
-      <c r="B127" t="s">
-        <v>19</v>
+        <v>36</v>
+      </c>
+      <c r="B127" s="3" t="s">
+        <v>0</v>
       </c>
       <c r="C127" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="D127">
-        <v>181</v>
+        <v>22</v>
+      </c>
+      <c r="D127" s="3">
+        <v>1500</v>
       </c>
       <c r="E127" s="3">
-        <v>2600</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>34</v>
-      </c>
-      <c r="B128" t="s">
-        <v>15</v>
+        <v>36</v>
+      </c>
+      <c r="B128" s="3" t="s">
+        <v>0</v>
       </c>
       <c r="C128" s="3" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="D128" s="3">
-        <v>1500</v>
+        <v>37</v>
       </c>
       <c r="E128" s="3">
-        <v>2650</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>34</v>
-      </c>
-      <c r="B129" t="s">
-        <v>15</v>
+        <v>36</v>
+      </c>
+      <c r="B129" s="3" t="s">
+        <v>0</v>
       </c>
       <c r="C129" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D129">
-        <v>30</v>
+        <v>28</v>
+      </c>
+      <c r="D129" s="3">
+        <v>6</v>
       </c>
       <c r="E129" s="3">
-        <v>2650</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>34</v>
-      </c>
-      <c r="B130" t="s">
-        <v>15</v>
+        <v>36</v>
+      </c>
+      <c r="B130" s="3" t="s">
+        <v>0</v>
       </c>
       <c r="C130" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D130" s="3">
-        <v>10</v>
+        <v>82</v>
       </c>
       <c r="E130" s="3">
-        <v>2650</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>34</v>
-      </c>
-      <c r="B131" t="s">
-        <v>15</v>
+        <v>36</v>
+      </c>
+      <c r="B131" s="3" t="s">
+        <v>0</v>
       </c>
       <c r="C131" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="D131" s="3">
-        <v>64</v>
+        <v>30</v>
+      </c>
+      <c r="D131">
+        <v>95</v>
       </c>
       <c r="E131" s="3">
-        <v>2650</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B132" t="s">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="C132" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="D132">
-        <v>28</v>
+        <v>22</v>
+      </c>
+      <c r="D132" s="3">
+        <v>0</v>
       </c>
       <c r="E132" s="3">
-        <v>2650</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B133" t="s">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="C133" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="D133">
-        <v>126</v>
+        <v>27</v>
+      </c>
+      <c r="D133" s="3">
+        <v>12</v>
       </c>
       <c r="E133" s="3">
-        <v>2650</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B134" t="s">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="C134" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D134">
-        <v>27700</v>
+        <v>28</v>
+      </c>
+      <c r="D134" s="3">
+        <v>4</v>
       </c>
       <c r="E134" s="3">
-        <v>53500</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B135" t="s">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="C135" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D135">
-        <v>840</v>
+        <v>29</v>
+      </c>
+      <c r="D135" s="3">
+        <v>50</v>
       </c>
       <c r="E135" s="3">
-        <v>53500</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B136" t="s">
+        <v>2</v>
+      </c>
+      <c r="C136" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D136">
         <v>32</v>
       </c>
-      <c r="C136" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="D136">
-        <v>131</v>
-      </c>
       <c r="E136" s="3">
-        <v>53500</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B137" t="s">
-        <v>32</v>
+        <v>3</v>
       </c>
       <c r="C137" s="3" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="D137" s="3">
-        <v>1303</v>
+        <v>800</v>
       </c>
       <c r="E137" s="3">
-        <v>53500</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B138" t="s">
-        <v>32</v>
+        <v>3</v>
       </c>
       <c r="C138" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="D138">
-        <v>565</v>
+        <v>27</v>
+      </c>
+      <c r="D138" s="3">
+        <v>33</v>
       </c>
       <c r="E138" s="3">
-        <v>53500</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B139" t="s">
-        <v>32</v>
+        <v>3</v>
       </c>
       <c r="C139" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="D139">
-        <v>2738</v>
+        <v>28</v>
+      </c>
+      <c r="D139" s="3">
+        <v>1</v>
       </c>
       <c r="E139" s="3">
-        <v>53500</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B140" t="s">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="C140" s="3" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="D140" s="3">
-        <v>1500</v>
+        <v>65</v>
       </c>
       <c r="E140" s="3">
-        <v>5700</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="141" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B141" t="s">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="C141" s="3" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="D141">
-        <v>103</v>
+        <v>135</v>
       </c>
       <c r="E141" s="3">
-        <v>5700</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="142" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B142" t="s">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="C142" s="3" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="D142" s="3">
-        <v>14</v>
+        <v>1200</v>
       </c>
       <c r="E142" s="3">
-        <v>5700</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="143" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B143" t="s">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="C143" s="3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D143" s="3">
-        <v>1303</v>
+        <v>18</v>
       </c>
       <c r="E143" s="3">
-        <v>5700</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B144" t="s">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="C144" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="D144">
-        <v>71</v>
+        <v>28</v>
+      </c>
+      <c r="D144" s="3">
+        <v>1</v>
       </c>
       <c r="E144" s="3">
-        <v>5700</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B145" t="s">
+        <v>8</v>
+      </c>
+      <c r="C145" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D145" s="3">
+        <v>50</v>
+      </c>
+      <c r="E145" s="3">
+        <v>1450</v>
+      </c>
+    </row>
+    <row r="146" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A146" t="s">
+        <v>36</v>
+      </c>
+      <c r="B146" t="s">
+        <v>8</v>
+      </c>
+      <c r="C146" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D146">
+        <v>69</v>
+      </c>
+      <c r="E146" s="3">
+        <v>1450</v>
+      </c>
+    </row>
+    <row r="147" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A147" t="s">
+        <v>36</v>
+      </c>
+      <c r="B147" t="s">
+        <v>10</v>
+      </c>
+      <c r="C147" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D147" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E147" s="3">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="148" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A148" t="s">
+        <v>36</v>
+      </c>
+      <c r="B148" t="s">
+        <v>10</v>
+      </c>
+      <c r="C148" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D148" s="3">
+        <v>37</v>
+      </c>
+      <c r="E148" s="3">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="149" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A149" t="s">
+        <v>36</v>
+      </c>
+      <c r="B149" t="s">
+        <v>10</v>
+      </c>
+      <c r="C149" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D149" s="3">
+        <v>1</v>
+      </c>
+      <c r="E149" s="3">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="150" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A150" t="s">
+        <v>36</v>
+      </c>
+      <c r="B150" t="s">
+        <v>10</v>
+      </c>
+      <c r="C150" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D150" s="3">
+        <v>45</v>
+      </c>
+      <c r="E150" s="3">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="151" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A151" t="s">
+        <v>36</v>
+      </c>
+      <c r="B151" t="s">
+        <v>10</v>
+      </c>
+      <c r="C151" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D151">
+        <v>68</v>
+      </c>
+      <c r="E151" s="3">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="152" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A152" t="s">
+        <v>36</v>
+      </c>
+      <c r="B152" t="s">
+        <v>9</v>
+      </c>
+      <c r="C152" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D152" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E152" s="3">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="153" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A153" t="s">
+        <v>36</v>
+      </c>
+      <c r="B153" t="s">
+        <v>9</v>
+      </c>
+      <c r="C153" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D153" s="3">
+        <v>42</v>
+      </c>
+      <c r="E153" s="3">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="154" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A154" t="s">
+        <v>36</v>
+      </c>
+      <c r="B154" t="s">
+        <v>9</v>
+      </c>
+      <c r="C154" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D154" s="3">
+        <v>1</v>
+      </c>
+      <c r="E154" s="3">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="155" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A155" t="s">
+        <v>36</v>
+      </c>
+      <c r="B155" t="s">
+        <v>9</v>
+      </c>
+      <c r="C155" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D155" s="3">
+        <v>160</v>
+      </c>
+      <c r="E155" s="3">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="156" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A156" t="s">
+        <v>36</v>
+      </c>
+      <c r="B156" t="s">
+        <v>9</v>
+      </c>
+      <c r="C156" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D156">
+        <v>176</v>
+      </c>
+      <c r="E156" s="3">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="157" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A157" t="s">
+        <v>36</v>
+      </c>
+      <c r="B157" t="s">
+        <v>13</v>
+      </c>
+      <c r="C157" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D157" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E157" s="3">
+        <v>2600</v>
+      </c>
+    </row>
+    <row r="158" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A158" t="s">
+        <v>36</v>
+      </c>
+      <c r="B158" t="s">
+        <v>13</v>
+      </c>
+      <c r="C158" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D158" s="3">
+        <v>26</v>
+      </c>
+      <c r="E158" s="3">
+        <v>2600</v>
+      </c>
+    </row>
+    <row r="159" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A159" t="s">
+        <v>36</v>
+      </c>
+      <c r="B159" t="s">
+        <v>13</v>
+      </c>
+      <c r="C159" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D159" s="3">
+        <v>1</v>
+      </c>
+      <c r="E159" s="3">
+        <v>2600</v>
+      </c>
+    </row>
+    <row r="160" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A160" t="s">
+        <v>36</v>
+      </c>
+      <c r="B160" t="s">
+        <v>13</v>
+      </c>
+      <c r="C160" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D160" s="3">
+        <v>130</v>
+      </c>
+      <c r="E160" s="3">
+        <v>2600</v>
+      </c>
+    </row>
+    <row r="161" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A161" t="s">
+        <v>36</v>
+      </c>
+      <c r="B161" t="s">
+        <v>13</v>
+      </c>
+      <c r="C161" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D161">
+        <v>98</v>
+      </c>
+      <c r="E161" s="3">
+        <v>2600</v>
+      </c>
+    </row>
+    <row r="162" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A162" t="s">
+        <v>36</v>
+      </c>
+      <c r="B162" t="s">
+        <v>7</v>
+      </c>
+      <c r="C162" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D162" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E162" s="3">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="163" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A163" t="s">
+        <v>36</v>
+      </c>
+      <c r="B163" t="s">
+        <v>7</v>
+      </c>
+      <c r="C163" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D163" s="3">
+        <v>32</v>
+      </c>
+      <c r="E163" s="3">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="164" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A164" t="s">
+        <v>36</v>
+      </c>
+      <c r="B164" t="s">
+        <v>7</v>
+      </c>
+      <c r="C164" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D164" s="3">
+        <v>6</v>
+      </c>
+      <c r="E164" s="3">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="165" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A165" t="s">
+        <v>36</v>
+      </c>
+      <c r="B165" t="s">
+        <v>7</v>
+      </c>
+      <c r="C165" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D165" s="3">
+        <v>56</v>
+      </c>
+      <c r="E165" s="3">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="166" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A166" t="s">
+        <v>36</v>
+      </c>
+      <c r="B166" t="s">
+        <v>7</v>
+      </c>
+      <c r="C166" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D166">
+        <v>128</v>
+      </c>
+      <c r="E166" s="3">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="167" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A167" t="s">
+        <v>36</v>
+      </c>
+      <c r="B167" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C167" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D167" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E167" s="3">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="168" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A168" t="s">
+        <v>36</v>
+      </c>
+      <c r="B168" t="s">
+        <v>12</v>
+      </c>
+      <c r="C168" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D168" s="3">
+        <v>17</v>
+      </c>
+      <c r="E168" s="3">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="169" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A169" t="s">
+        <v>36</v>
+      </c>
+      <c r="B169" t="s">
+        <v>12</v>
+      </c>
+      <c r="C169" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D169" s="3">
+        <v>6</v>
+      </c>
+      <c r="E169" s="3">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="170" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A170" t="s">
+        <v>36</v>
+      </c>
+      <c r="B170" t="s">
+        <v>12</v>
+      </c>
+      <c r="C170" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D170" s="3">
+        <v>25</v>
+      </c>
+      <c r="E170" s="3">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="171" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A171" t="s">
+        <v>36</v>
+      </c>
+      <c r="B171" t="s">
+        <v>12</v>
+      </c>
+      <c r="C171" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D171">
+        <v>54</v>
+      </c>
+      <c r="E171" s="3">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="172" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A172" t="s">
+        <v>36</v>
+      </c>
+      <c r="B172" t="s">
+        <v>17</v>
+      </c>
+      <c r="C172" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D172" s="3">
+        <v>800</v>
+      </c>
+      <c r="E172" s="3">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="173" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A173" t="s">
+        <v>36</v>
+      </c>
+      <c r="B173" t="s">
+        <v>17</v>
+      </c>
+      <c r="C173" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D173" s="3">
+        <v>13</v>
+      </c>
+      <c r="E173" s="3">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="174" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A174" t="s">
+        <v>36</v>
+      </c>
+      <c r="B174" t="s">
+        <v>17</v>
+      </c>
+      <c r="C174" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D174" s="3">
+        <v>1</v>
+      </c>
+      <c r="E174" s="3">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="175" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A175" t="s">
+        <v>36</v>
+      </c>
+      <c r="B175" t="s">
+        <v>17</v>
+      </c>
+      <c r="C175" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D175" s="3">
+        <v>82</v>
+      </c>
+      <c r="E175" s="3">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="176" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A176" t="s">
+        <v>36</v>
+      </c>
+      <c r="B176" t="s">
+        <v>17</v>
+      </c>
+      <c r="C176" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D176">
+        <v>60</v>
+      </c>
+      <c r="E176" s="3">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="177" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A177" t="s">
+        <v>36</v>
+      </c>
+      <c r="B177" t="s">
+        <v>18</v>
+      </c>
+      <c r="C177" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D177" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E177" s="3">
+        <v>1100</v>
+      </c>
+    </row>
+    <row r="178" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A178" t="s">
+        <v>36</v>
+      </c>
+      <c r="B178" t="s">
+        <v>18</v>
+      </c>
+      <c r="C178" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D178" s="3">
+        <v>16</v>
+      </c>
+      <c r="E178" s="3">
+        <v>1100</v>
+      </c>
+    </row>
+    <row r="179" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A179" t="s">
+        <v>36</v>
+      </c>
+      <c r="B179" t="s">
+        <v>18</v>
+      </c>
+      <c r="C179" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D179" s="3">
+        <v>4</v>
+      </c>
+      <c r="E179" s="3">
+        <v>1100</v>
+      </c>
+    </row>
+    <row r="180" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A180" t="s">
+        <v>36</v>
+      </c>
+      <c r="B180" t="s">
+        <v>18</v>
+      </c>
+      <c r="C180" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D180" s="3">
+        <v>30</v>
+      </c>
+      <c r="E180" s="3">
+        <v>1100</v>
+      </c>
+    </row>
+    <row r="181" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A181" t="s">
+        <v>36</v>
+      </c>
+      <c r="B181" t="s">
+        <v>18</v>
+      </c>
+      <c r="C181" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D181">
+        <v>74</v>
+      </c>
+      <c r="E181" s="3">
+        <v>1100</v>
+      </c>
+    </row>
+    <row r="182" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A182" t="s">
+        <v>36</v>
+      </c>
+      <c r="B182" t="s">
+        <v>20</v>
+      </c>
+      <c r="C182" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D182" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E182" s="3">
+        <v>2200</v>
+      </c>
+    </row>
+    <row r="183" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A183" t="s">
+        <v>36</v>
+      </c>
+      <c r="B183" t="s">
+        <v>20</v>
+      </c>
+      <c r="C183" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D183" s="3">
+        <v>34</v>
+      </c>
+      <c r="E183" s="3">
+        <v>2200</v>
+      </c>
+    </row>
+    <row r="184" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A184" t="s">
+        <v>36</v>
+      </c>
+      <c r="B184" t="s">
+        <v>20</v>
+      </c>
+      <c r="C184" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D184" s="3">
+        <v>1</v>
+      </c>
+      <c r="E184" s="3">
+        <v>2200</v>
+      </c>
+    </row>
+    <row r="185" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A185" t="s">
+        <v>36</v>
+      </c>
+      <c r="B185" t="s">
+        <v>20</v>
+      </c>
+      <c r="C185" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D185" s="3">
+        <v>60</v>
+      </c>
+      <c r="E185" s="3">
+        <v>2200</v>
+      </c>
+    </row>
+    <row r="186" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A186" t="s">
+        <v>36</v>
+      </c>
+      <c r="B186" t="s">
+        <v>20</v>
+      </c>
+      <c r="C186" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D186">
+        <v>183</v>
+      </c>
+      <c r="E186" s="3">
+        <v>2200</v>
+      </c>
+    </row>
+    <row r="187" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A187" t="s">
+        <v>36</v>
+      </c>
+      <c r="B187" t="s">
+        <v>21</v>
+      </c>
+      <c r="C187" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D187" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E187" s="3">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="188" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A188" t="s">
+        <v>36</v>
+      </c>
+      <c r="B188" t="s">
+        <v>21</v>
+      </c>
+      <c r="C188" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D188" s="3">
+        <v>22</v>
+      </c>
+      <c r="E188" s="3">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="189" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A189" t="s">
+        <v>36</v>
+      </c>
+      <c r="B189" t="s">
+        <v>21</v>
+      </c>
+      <c r="C189" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D189" s="3">
+        <v>6</v>
+      </c>
+      <c r="E189" s="3">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="190" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A190" t="s">
+        <v>36</v>
+      </c>
+      <c r="B190" t="s">
+        <v>21</v>
+      </c>
+      <c r="C190" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D190" s="3">
+        <v>60</v>
+      </c>
+      <c r="E190" s="3">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="191" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A191" t="s">
+        <v>36</v>
+      </c>
+      <c r="B191" t="s">
+        <v>21</v>
+      </c>
+      <c r="C191" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D191">
+        <v>168</v>
+      </c>
+      <c r="E191" s="3">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="192" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A192" t="s">
+        <v>36</v>
+      </c>
+      <c r="B192" t="s">
+        <v>6</v>
+      </c>
+      <c r="C192" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D192" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E192" s="3">
+        <v>2200</v>
+      </c>
+    </row>
+    <row r="193" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A193" t="s">
+        <v>36</v>
+      </c>
+      <c r="B193" t="s">
+        <v>6</v>
+      </c>
+      <c r="C193" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D193" s="3">
+        <v>23</v>
+      </c>
+      <c r="E193" s="3">
+        <v>2200</v>
+      </c>
+    </row>
+    <row r="194" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A194" t="s">
+        <v>36</v>
+      </c>
+      <c r="B194" t="s">
+        <v>6</v>
+      </c>
+      <c r="C194" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D194" s="3">
+        <v>1</v>
+      </c>
+      <c r="E194" s="3">
+        <v>2200</v>
+      </c>
+    </row>
+    <row r="195" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A195" t="s">
+        <v>36</v>
+      </c>
+      <c r="B195" t="s">
+        <v>6</v>
+      </c>
+      <c r="C195" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D195" s="3">
+        <v>72</v>
+      </c>
+      <c r="E195" s="3">
+        <v>2200</v>
+      </c>
+    </row>
+    <row r="196" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A196" t="s">
+        <v>36</v>
+      </c>
+      <c r="B196" t="s">
+        <v>6</v>
+      </c>
+      <c r="C196" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D196">
+        <v>92</v>
+      </c>
+      <c r="E196" s="3">
+        <v>2200</v>
+      </c>
+    </row>
+    <row r="197" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A197" t="s">
+        <v>36</v>
+      </c>
+      <c r="B197" t="s">
+        <v>1</v>
+      </c>
+      <c r="C197" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D197" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E197" s="3">
+        <v>2850</v>
+      </c>
+    </row>
+    <row r="198" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A198" t="s">
+        <v>36</v>
+      </c>
+      <c r="B198" t="s">
+        <v>1</v>
+      </c>
+      <c r="C198" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D198" s="3">
+        <v>52</v>
+      </c>
+      <c r="E198" s="3">
+        <v>2850</v>
+      </c>
+    </row>
+    <row r="199" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A199" t="s">
+        <v>36</v>
+      </c>
+      <c r="B199" t="s">
+        <v>1</v>
+      </c>
+      <c r="C199" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D199" s="3">
+        <v>10</v>
+      </c>
+      <c r="E199" s="3">
+        <v>2850</v>
+      </c>
+    </row>
+    <row r="200" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A200" t="s">
+        <v>36</v>
+      </c>
+      <c r="B200" t="s">
+        <v>1</v>
+      </c>
+      <c r="C200" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D200" s="3">
+        <v>102</v>
+      </c>
+      <c r="E200" s="3">
+        <v>2850</v>
+      </c>
+    </row>
+    <row r="201" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A201" t="s">
+        <v>36</v>
+      </c>
+      <c r="B201" t="s">
+        <v>1</v>
+      </c>
+      <c r="C201" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D201">
+        <v>129</v>
+      </c>
+      <c r="E201" s="3">
+        <v>2850</v>
+      </c>
+    </row>
+    <row r="202" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A202" t="s">
+        <v>36</v>
+      </c>
+      <c r="B202" t="s">
+        <v>4</v>
+      </c>
+      <c r="C202" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D202">
+        <v>1500</v>
+      </c>
+      <c r="E202" s="3">
+        <v>3500</v>
+      </c>
+    </row>
+    <row r="203" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A203" t="s">
+        <v>36</v>
+      </c>
+      <c r="B203" t="s">
+        <v>4</v>
+      </c>
+      <c r="C203" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D203" s="3">
+        <v>62</v>
+      </c>
+      <c r="E203" s="3">
+        <v>3500</v>
+      </c>
+    </row>
+    <row r="204" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A204" t="s">
+        <v>36</v>
+      </c>
+      <c r="B204" t="s">
+        <v>4</v>
+      </c>
+      <c r="C204" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D204">
+        <v>10</v>
+      </c>
+      <c r="E204" s="3">
+        <v>3500</v>
+      </c>
+    </row>
+    <row r="205" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A205" t="s">
+        <v>36</v>
+      </c>
+      <c r="B205" t="s">
+        <v>4</v>
+      </c>
+      <c r="C205" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D205" s="3">
+        <v>124</v>
+      </c>
+      <c r="E205" s="3">
+        <v>3500</v>
+      </c>
+    </row>
+    <row r="206" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A206" t="s">
+        <v>36</v>
+      </c>
+      <c r="B206" t="s">
+        <v>4</v>
+      </c>
+      <c r="C206" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D206">
+        <v>183</v>
+      </c>
+      <c r="E206" s="3">
+        <v>3500</v>
+      </c>
+    </row>
+    <row r="207" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A207" t="s">
+        <v>36</v>
+      </c>
+      <c r="B207" t="s">
+        <v>11</v>
+      </c>
+      <c r="C207" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D207" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E207" s="3">
+        <v>3500</v>
+      </c>
+    </row>
+    <row r="208" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A208" t="s">
+        <v>36</v>
+      </c>
+      <c r="B208" t="s">
+        <v>11</v>
+      </c>
+      <c r="C208" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D208" s="3">
+        <v>78</v>
+      </c>
+      <c r="E208" s="3">
+        <v>3500</v>
+      </c>
+    </row>
+    <row r="209" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A209" t="s">
+        <v>36</v>
+      </c>
+      <c r="B209" t="s">
+        <v>11</v>
+      </c>
+      <c r="C209" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D209" s="3">
+        <v>16</v>
+      </c>
+      <c r="E209" s="3">
+        <v>3500</v>
+      </c>
+    </row>
+    <row r="210" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A210" t="s">
+        <v>36</v>
+      </c>
+      <c r="B210" t="s">
+        <v>11</v>
+      </c>
+      <c r="C210" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D210" s="3">
+        <v>96</v>
+      </c>
+      <c r="E210" s="3">
+        <v>3500</v>
+      </c>
+    </row>
+    <row r="211" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A211" t="s">
+        <v>36</v>
+      </c>
+      <c r="B211" t="s">
+        <v>11</v>
+      </c>
+      <c r="C211" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D211">
+        <v>198</v>
+      </c>
+      <c r="E211" s="3">
+        <v>3500</v>
+      </c>
+    </row>
+    <row r="212" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A212" t="s">
+        <v>36</v>
+      </c>
+      <c r="B212" t="s">
+        <v>14</v>
+      </c>
+      <c r="C212" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D212" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E212" s="3">
+        <v>2300</v>
+      </c>
+    </row>
+    <row r="213" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A213" t="s">
+        <v>36</v>
+      </c>
+      <c r="B213" t="s">
+        <v>14</v>
+      </c>
+      <c r="C213" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D213" s="3">
+        <v>44</v>
+      </c>
+      <c r="E213" s="3">
+        <v>2300</v>
+      </c>
+    </row>
+    <row r="214" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A214" t="s">
+        <v>36</v>
+      </c>
+      <c r="B214" t="s">
+        <v>14</v>
+      </c>
+      <c r="C214" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D214" s="3">
+        <v>10</v>
+      </c>
+      <c r="E214" s="3">
+        <v>2300</v>
+      </c>
+    </row>
+    <row r="215" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A215" t="s">
+        <v>36</v>
+      </c>
+      <c r="B215" t="s">
+        <v>14</v>
+      </c>
+      <c r="C215" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D215" s="3">
+        <v>72</v>
+      </c>
+      <c r="E215" s="3">
+        <v>2300</v>
+      </c>
+    </row>
+    <row r="216" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A216" t="s">
+        <v>36</v>
+      </c>
+      <c r="B216" t="s">
+        <v>14</v>
+      </c>
+      <c r="C216" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D216">
+        <v>151</v>
+      </c>
+      <c r="E216" s="3">
+        <v>2300</v>
+      </c>
+    </row>
+    <row r="217" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A217" t="s">
+        <v>36</v>
+      </c>
+      <c r="B217" t="s">
+        <v>16</v>
+      </c>
+      <c r="C217" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D217" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E217" s="3">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="218" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A218" t="s">
+        <v>36</v>
+      </c>
+      <c r="B218" t="s">
+        <v>16</v>
+      </c>
+      <c r="C218" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D218" s="3">
+        <v>120</v>
+      </c>
+      <c r="E218" s="3">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="219" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A219" t="s">
+        <v>36</v>
+      </c>
+      <c r="B219" t="s">
+        <v>16</v>
+      </c>
+      <c r="C219" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D219" s="3">
+        <v>14</v>
+      </c>
+      <c r="E219" s="3">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="220" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A220" t="s">
+        <v>36</v>
+      </c>
+      <c r="B220" t="s">
+        <v>16</v>
+      </c>
+      <c r="C220" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D220" s="3">
+        <v>236</v>
+      </c>
+      <c r="E220" s="3">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="221" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A221" t="s">
+        <v>36</v>
+      </c>
+      <c r="B221" t="s">
+        <v>16</v>
+      </c>
+      <c r="C221" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D221">
+        <v>192</v>
+      </c>
+      <c r="E221" s="3">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="222" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A222" t="s">
+        <v>36</v>
+      </c>
+      <c r="B222" t="s">
+        <v>19</v>
+      </c>
+      <c r="C222" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D222" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E222" s="3">
+        <v>2600</v>
+      </c>
+    </row>
+    <row r="223" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A223" t="s">
+        <v>36</v>
+      </c>
+      <c r="B223" t="s">
+        <v>19</v>
+      </c>
+      <c r="C223" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D223" s="3">
+        <v>62</v>
+      </c>
+      <c r="E223" s="3">
+        <v>2600</v>
+      </c>
+    </row>
+    <row r="224" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A224" t="s">
+        <v>36</v>
+      </c>
+      <c r="B224" t="s">
+        <v>19</v>
+      </c>
+      <c r="C224" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D224" s="3">
+        <v>11</v>
+      </c>
+      <c r="E224" s="3">
+        <v>2600</v>
+      </c>
+    </row>
+    <row r="225" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A225" t="s">
+        <v>36</v>
+      </c>
+      <c r="B225" t="s">
+        <v>19</v>
+      </c>
+      <c r="C225" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D225" s="3">
+        <v>74</v>
+      </c>
+      <c r="E225" s="3">
+        <v>2600</v>
+      </c>
+    </row>
+    <row r="226" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A226" t="s">
+        <v>36</v>
+      </c>
+      <c r="B226" t="s">
+        <v>19</v>
+      </c>
+      <c r="C226" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D226">
+        <v>181</v>
+      </c>
+      <c r="E226" s="3">
+        <v>2600</v>
+      </c>
+    </row>
+    <row r="227" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A227" t="s">
+        <v>36</v>
+      </c>
+      <c r="B227" t="s">
+        <v>15</v>
+      </c>
+      <c r="C227" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D227" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E227" s="3">
+        <v>2650</v>
+      </c>
+    </row>
+    <row r="228" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A228" t="s">
+        <v>36</v>
+      </c>
+      <c r="B228" t="s">
+        <v>15</v>
+      </c>
+      <c r="C228" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D228" s="3">
+        <v>30</v>
+      </c>
+      <c r="E228" s="3">
+        <v>2650</v>
+      </c>
+    </row>
+    <row r="229" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A229" t="s">
+        <v>36</v>
+      </c>
+      <c r="B229" t="s">
+        <v>15</v>
+      </c>
+      <c r="C229" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D229" s="3">
+        <v>10</v>
+      </c>
+      <c r="E229" s="3">
+        <v>2650</v>
+      </c>
+    </row>
+    <row r="230" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A230" t="s">
+        <v>36</v>
+      </c>
+      <c r="B230" t="s">
+        <v>15</v>
+      </c>
+      <c r="C230" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D230" s="3">
+        <v>92</v>
+      </c>
+      <c r="E230" s="3">
+        <v>2650</v>
+      </c>
+    </row>
+    <row r="231" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A231" t="s">
+        <v>36</v>
+      </c>
+      <c r="B231" t="s">
+        <v>15</v>
+      </c>
+      <c r="C231" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D231">
+        <v>126</v>
+      </c>
+      <c r="E231" s="3">
+        <v>2650</v>
+      </c>
+    </row>
+    <row r="232" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A232" t="s">
+        <v>36</v>
+      </c>
+      <c r="B232" t="s">
+        <v>32</v>
+      </c>
+      <c r="C232" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D232">
+        <v>27700</v>
+      </c>
+      <c r="E232" s="3">
+        <v>53800</v>
+      </c>
+    </row>
+    <row r="233" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A233" t="s">
+        <v>36</v>
+      </c>
+      <c r="B233" t="s">
+        <v>32</v>
+      </c>
+      <c r="C233" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D233">
+        <v>857</v>
+      </c>
+      <c r="E233" s="3">
+        <v>53800</v>
+      </c>
+    </row>
+    <row r="234" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A234" t="s">
+        <v>36</v>
+      </c>
+      <c r="B234" t="s">
+        <v>32</v>
+      </c>
+      <c r="C234" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D234">
+        <v>131</v>
+      </c>
+      <c r="E234" s="3">
+        <v>53800</v>
+      </c>
+    </row>
+    <row r="235" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A235" t="s">
+        <v>36</v>
+      </c>
+      <c r="B235" t="s">
+        <v>32</v>
+      </c>
+      <c r="C235" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D235" s="3">
+        <v>1858</v>
+      </c>
+      <c r="E235" s="3">
+        <v>53800</v>
+      </c>
+    </row>
+    <row r="236" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A236" t="s">
+        <v>36</v>
+      </c>
+      <c r="B236" t="s">
+        <v>32</v>
+      </c>
+      <c r="C236" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D236">
+        <v>2738</v>
+      </c>
+      <c r="E236" s="3">
+        <v>53800</v>
+      </c>
+    </row>
+    <row r="237" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A237" t="s">
+        <v>36</v>
+      </c>
+      <c r="B237" t="s">
         <v>35</v>
       </c>
-      <c r="C145" s="3" t="s">
+      <c r="C237" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D237" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E237" s="3">
+        <v>5700</v>
+      </c>
+    </row>
+    <row r="238" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A238" t="s">
+        <v>36</v>
+      </c>
+      <c r="B238" t="s">
+        <v>35</v>
+      </c>
+      <c r="C238" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D238">
+        <v>17</v>
+      </c>
+      <c r="E238" s="3">
+        <v>5700</v>
+      </c>
+    </row>
+    <row r="239" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A239" t="s">
+        <v>36</v>
+      </c>
+      <c r="B239" t="s">
+        <v>35</v>
+      </c>
+      <c r="C239" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D239" s="3">
+        <v>14</v>
+      </c>
+      <c r="E239" s="3">
+        <v>5700</v>
+      </c>
+    </row>
+    <row r="240" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A240" t="s">
+        <v>36</v>
+      </c>
+      <c r="B240" t="s">
+        <v>35</v>
+      </c>
+      <c r="C240" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D240" s="3">
+        <v>1858</v>
+      </c>
+      <c r="E240" s="3">
+        <v>5700</v>
+      </c>
+    </row>
+    <row r="241" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A241" t="s">
+        <v>36</v>
+      </c>
+      <c r="B241" t="s">
+        <v>35</v>
+      </c>
+      <c r="C241" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="D145">
+      <c r="D241">
         <v>192</v>
       </c>
-      <c r="E145" s="3">
+      <c r="E241" s="3">
         <v>5700</v>
       </c>
     </row>
-    <row r="146" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C146" s="3"/>
-      <c r="D146" s="3"/>
-      <c r="E146" s="3"/>
-    </row>
-    <row r="147" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C147" s="3"/>
-      <c r="E147" s="3"/>
-    </row>
-    <row r="148" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C148" s="3"/>
-      <c r="D148" s="3"/>
-      <c r="E148" s="3"/>
-    </row>
-    <row r="149" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C149" s="3"/>
-      <c r="E149" s="3"/>
-    </row>
-    <row r="150" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C150" s="3"/>
-      <c r="E150" s="3"/>
-    </row>
-    <row r="151" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C151" s="3"/>
-      <c r="E151" s="3"/>
-    </row>
-    <row r="152" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C152" s="3"/>
-      <c r="D152" s="3"/>
-      <c r="E152" s="3"/>
-    </row>
-    <row r="153" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C153" s="3"/>
-      <c r="E153" s="3"/>
-    </row>
-    <row r="154" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C154" s="3"/>
-      <c r="D154" s="3"/>
-      <c r="E154" s="3"/>
-    </row>
-    <row r="155" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C155" s="3"/>
-      <c r="E155" s="3"/>
-    </row>
-    <row r="156" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C156" s="3"/>
-      <c r="E156" s="3"/>
-    </row>
-    <row r="157" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C157" s="3"/>
-      <c r="E157" s="3"/>
-    </row>
-    <row r="158" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C158" s="3"/>
-      <c r="D158" s="3"/>
-      <c r="E158" s="3"/>
-    </row>
-    <row r="159" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C159" s="3"/>
-      <c r="E159" s="3"/>
-    </row>
-    <row r="160" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C160" s="3"/>
-      <c r="D160" s="3"/>
-      <c r="E160" s="3"/>
-    </row>
-    <row r="161" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="C161" s="3"/>
-      <c r="E161" s="3"/>
-    </row>
-    <row r="162" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="C162" s="3"/>
-      <c r="E162" s="3"/>
-    </row>
-    <row r="163" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="C163" s="3"/>
-      <c r="E163" s="3"/>
-    </row>
-    <row r="164" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="C164" s="3"/>
-      <c r="D164" s="3"/>
-      <c r="E164" s="3"/>
-    </row>
-    <row r="165" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="C165" s="3"/>
-      <c r="E165" s="3"/>
-    </row>
-    <row r="166" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="C166" s="3"/>
-      <c r="D166" s="3"/>
-      <c r="E166" s="3"/>
-    </row>
-    <row r="167" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="C167" s="3"/>
-      <c r="E167" s="3"/>
-    </row>
-    <row r="168" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="C168" s="3"/>
-      <c r="E168" s="3"/>
-    </row>
-    <row r="169" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="C169" s="3"/>
-      <c r="E169" s="3"/>
-    </row>
-    <row r="170" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B170" s="1"/>
-      <c r="C170" s="3"/>
-      <c r="D170" s="3"/>
-      <c r="E170" s="3"/>
-    </row>
-    <row r="171" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="C171" s="3"/>
-      <c r="E171" s="3"/>
-    </row>
-    <row r="172" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="C172" s="3"/>
-      <c r="D172" s="3"/>
-      <c r="E172" s="3"/>
-    </row>
-    <row r="173" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="C173" s="3"/>
-      <c r="E173" s="3"/>
-    </row>
-    <row r="174" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="C174" s="3"/>
-      <c r="E174" s="3"/>
-    </row>
-    <row r="175" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="C175" s="3"/>
-      <c r="E175" s="3"/>
-    </row>
-    <row r="176" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="C176" s="3"/>
-      <c r="D176" s="3"/>
-      <c r="E176" s="3"/>
-    </row>
-    <row r="177" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C177" s="3"/>
-      <c r="E177" s="3"/>
-    </row>
-    <row r="178" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C178" s="3"/>
-      <c r="D178" s="3"/>
-      <c r="E178" s="3"/>
-    </row>
-    <row r="179" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C179" s="3"/>
-      <c r="E179" s="3"/>
-    </row>
-    <row r="180" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C180" s="3"/>
-      <c r="E180" s="3"/>
-    </row>
-    <row r="181" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C181" s="3"/>
-      <c r="E181" s="3"/>
-    </row>
-    <row r="182" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C182" s="3"/>
-      <c r="D182" s="3"/>
-      <c r="E182" s="3"/>
-    </row>
-    <row r="183" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C183" s="3"/>
-      <c r="E183" s="3"/>
-    </row>
-    <row r="184" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C184" s="3"/>
-      <c r="D184" s="3"/>
-      <c r="E184" s="3"/>
-    </row>
-    <row r="185" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C185" s="3"/>
-      <c r="E185" s="3"/>
-    </row>
-    <row r="186" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C186" s="3"/>
-      <c r="E186" s="3"/>
-    </row>
-    <row r="187" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C187" s="3"/>
-      <c r="E187" s="3"/>
-    </row>
-    <row r="188" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C188" s="3"/>
-      <c r="D188" s="3"/>
-      <c r="E188" s="3"/>
-    </row>
-    <row r="189" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C189" s="3"/>
-      <c r="E189" s="3"/>
-    </row>
-    <row r="190" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C190" s="3"/>
-      <c r="D190" s="3"/>
-      <c r="E190" s="3"/>
-    </row>
-    <row r="191" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C191" s="3"/>
-      <c r="E191" s="3"/>
-    </row>
-    <row r="192" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C192" s="3"/>
-      <c r="E192" s="3"/>
-    </row>
-    <row r="193" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C193" s="3"/>
-      <c r="E193" s="3"/>
-    </row>
-    <row r="194" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C194" s="3"/>
-      <c r="D194" s="3"/>
-      <c r="E194" s="3"/>
-    </row>
-    <row r="195" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C195" s="3"/>
-      <c r="E195" s="3"/>
-    </row>
-    <row r="196" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C196" s="3"/>
-      <c r="D196" s="3"/>
-      <c r="E196" s="3"/>
-    </row>
-    <row r="197" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C197" s="3"/>
-      <c r="E197" s="3"/>
-    </row>
-    <row r="198" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C198" s="3"/>
-      <c r="E198" s="3"/>
-    </row>
-    <row r="199" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C199" s="3"/>
-      <c r="E199" s="3"/>
-    </row>
-    <row r="200" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C200" s="3"/>
-      <c r="D200" s="3"/>
-      <c r="E200" s="3"/>
-    </row>
-    <row r="201" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C201" s="3"/>
-      <c r="E201" s="3"/>
-    </row>
-    <row r="202" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C202" s="3"/>
-      <c r="D202" s="3"/>
-      <c r="E202" s="3"/>
-    </row>
-    <row r="203" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C203" s="3"/>
-      <c r="E203" s="3"/>
-    </row>
-    <row r="204" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C204" s="3"/>
-      <c r="E204" s="3"/>
-    </row>
-    <row r="205" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C205" s="3"/>
-      <c r="E205" s="3"/>
-    </row>
-    <row r="206" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C206" s="3"/>
-      <c r="D206" s="3"/>
-      <c r="E206" s="3"/>
-    </row>
-    <row r="207" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C207" s="3"/>
-      <c r="E207" s="3"/>
-    </row>
-    <row r="208" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C208" s="3"/>
-      <c r="D208" s="3"/>
-      <c r="E208" s="3"/>
-    </row>
-    <row r="209" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C209" s="3"/>
-      <c r="E209" s="3"/>
-    </row>
-    <row r="210" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C210" s="3"/>
-      <c r="E210" s="3"/>
-    </row>
-    <row r="211" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C211" s="3"/>
-      <c r="E211" s="3"/>
-    </row>
-    <row r="212" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C212" s="3"/>
-      <c r="E212" s="3"/>
-    </row>
-    <row r="213" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C213" s="3"/>
-      <c r="E213" s="3"/>
-    </row>
-    <row r="214" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C214" s="3"/>
-      <c r="E214" s="3"/>
-    </row>
-    <row r="215" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C215" s="3"/>
-      <c r="E215" s="3"/>
-    </row>
-    <row r="216" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C216" s="3"/>
-      <c r="E216" s="3"/>
-    </row>
-    <row r="217" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C217" s="3"/>
-      <c r="E217" s="3"/>
-    </row>
-    <row r="218" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C218" s="3"/>
-      <c r="D218" s="3"/>
-      <c r="E218" s="3"/>
-    </row>
-    <row r="219" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C219" s="3"/>
-      <c r="E219" s="3"/>
-    </row>
-    <row r="220" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C220" s="3"/>
-      <c r="D220" s="3"/>
-      <c r="E220" s="3"/>
-    </row>
-    <row r="221" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C221" s="3"/>
-      <c r="E221" s="3"/>
-    </row>
-    <row r="222" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C222" s="3"/>
-      <c r="E222" s="3"/>
-    </row>
-    <row r="223" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C223" s="3"/>
-      <c r="E223" s="3"/>
-    </row>
-    <row r="224" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C224" s="3"/>
-      <c r="D224" s="3"/>
-      <c r="E224" s="3"/>
-    </row>
-    <row r="225" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C225" s="3"/>
-      <c r="E225" s="3"/>
-    </row>
-    <row r="226" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C226" s="3"/>
-      <c r="D226" s="3"/>
-      <c r="E226" s="3"/>
-    </row>
-    <row r="227" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C227" s="3"/>
-      <c r="E227" s="3"/>
-    </row>
-    <row r="228" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C228" s="3"/>
-      <c r="E228" s="3"/>
-    </row>
-    <row r="229" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C229" s="3"/>
-      <c r="E229" s="3"/>
-    </row>
-    <row r="230" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C230" s="3"/>
-      <c r="D230" s="3"/>
-      <c r="E230" s="3"/>
-    </row>
-    <row r="231" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C231" s="3"/>
-      <c r="E231" s="3"/>
-    </row>
-    <row r="232" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C232" s="3"/>
-      <c r="D232" s="3"/>
-      <c r="E232" s="3"/>
-    </row>
-    <row r="233" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C233" s="3"/>
-      <c r="E233" s="3"/>
-    </row>
-    <row r="234" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C234" s="3"/>
-      <c r="E234" s="3"/>
-    </row>
-    <row r="235" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C235" s="3"/>
-      <c r="E235" s="3"/>
-    </row>
-    <row r="236" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C236" s="3"/>
-      <c r="D236" s="3"/>
-      <c r="E236" s="3"/>
-    </row>
-    <row r="237" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C237" s="3"/>
-      <c r="E237" s="3"/>
-    </row>
-    <row r="238" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C238" s="3"/>
-      <c r="D238" s="3"/>
-      <c r="E238" s="3"/>
-    </row>
-    <row r="239" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C239" s="3"/>
-      <c r="E239" s="3"/>
-    </row>
-    <row r="240" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C240" s="3"/>
-      <c r="E240" s="3"/>
-    </row>
-    <row r="241" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C241" s="3"/>
-      <c r="E241" s="3"/>
-    </row>
-    <row r="242" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C242" s="3"/>
-      <c r="D242" s="3"/>
-      <c r="E242" s="3"/>
-    </row>
-    <row r="243" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C243" s="3"/>
-      <c r="E243" s="3"/>
-    </row>
-    <row r="244" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C244" s="3"/>
-      <c r="D244" s="3"/>
-      <c r="E244" s="3"/>
-    </row>
-    <row r="245" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C245" s="3"/>
-      <c r="E245" s="3"/>
-    </row>
-    <row r="246" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C246" s="3"/>
-      <c r="E246" s="3"/>
-    </row>
-    <row r="247" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C247" s="3"/>
-      <c r="E247" s="3"/>
-    </row>
-    <row r="248" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C248" s="3"/>
-      <c r="E248" s="3"/>
-    </row>
-    <row r="249" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C249" s="3"/>
-      <c r="E249" s="3"/>
-    </row>
-    <row r="250" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C250" s="3"/>
-      <c r="E250" s="3"/>
-    </row>
-    <row r="251" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C251" s="3"/>
-      <c r="E251" s="3"/>
-    </row>
-    <row r="252" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C252" s="3"/>
-      <c r="E252" s="3"/>
-    </row>
-    <row r="253" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C253" s="3"/>
-      <c r="E253" s="3"/>
-    </row>
   </sheetData>
-  <autoFilter ref="B1:E145" xr:uid="{6956BB2C-DA9E-4412-BCD4-BB80A11153FE}"/>
+  <autoFilter ref="A1:E241" xr:uid="{6956BB2C-DA9E-4412-BCD4-BB80A11153FE}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/data/metas.xlsx
+++ b/data/metas.xlsx
@@ -1,24 +1,28 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sercomunicaciones2-my.sharepoint.com/personal/auxcomisiones_sercomunicaciones_com/Documents/PAOLA/Liquidacióncvs/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="622" documentId="8_{787D9E49-702D-43BD-B99B-4B64F775E77B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{845823E0-6B0E-46F6-BFAA-397A4AD58610}"/>
+  <xr:revisionPtr revIDLastSave="710" documentId="8_{787D9E49-702D-43BD-B99B-4B64F775E77B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{43E7087E-74F7-40B5-A297-51337DCF9C59}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D1391136-BBFC-43C7-B899-B77B0ECC5956}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{D1391136-BBFC-43C7-B899-B77B0ECC5956}"/>
   </bookViews>
   <sheets>
-    <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
+    <sheet name="Hoja2" sheetId="2" r:id="rId1"/>
+    <sheet name="Hoja1" sheetId="1" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$B$1:$E$145</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Hoja1!$A$1:$E$241</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
+  <pivotCaches>
+    <pivotCache cacheId="59" r:id="rId3"/>
+  </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -39,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="437" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="762" uniqueCount="40">
   <si>
     <t>BARBOSA</t>
   </si>
@@ -148,6 +152,18 @@
   <si>
     <t>NUMERARIO</t>
   </si>
+  <si>
+    <t>Marzo</t>
+  </si>
+  <si>
+    <t>Total general</t>
+  </si>
+  <si>
+    <t>(Todas)</t>
+  </si>
+  <si>
+    <t>Suma de Meta_Producto</t>
+  </si>
 </sst>
 </file>
 
@@ -205,7 +221,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -215,6 +231,9 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -230,6 +249,2311 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Aux Comisiones" refreshedDate="46092.590271759262" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="288" xr:uid="{B4970592-A96D-470A-A8C5-FC6DBD168D2D}">
+  <cacheSource type="worksheet">
+    <worksheetSource ref="A1:E241" sheet="Hoja1"/>
+  </cacheSource>
+  <cacheFields count="5">
+    <cacheField name="Mes" numFmtId="0">
+      <sharedItems count="2">
+        <s v="Febrero"/>
+        <s v="Marzo"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Sucursal" numFmtId="0">
+      <sharedItems count="24">
+        <s v="COPACABANA"/>
+        <s v="BARBOSA"/>
+        <s v="CAUCASIA"/>
+        <s v="CIUDAD BOLIVAR"/>
+        <s v="DABEIBA"/>
+        <s v="DON MATIAS"/>
+        <s v="EL BAGRE"/>
+        <s v="FRONTINO"/>
+        <s v="GIRARDOTA"/>
+        <s v="LA ESTRELLA"/>
+        <s v="NECHI"/>
+        <s v="PRADO"/>
+        <s v="SEGOVIA"/>
+        <s v="YARUMAL"/>
+        <s v="ZARAGOZA"/>
+        <s v="BELLO"/>
+        <s v="CALDAS"/>
+        <s v="ENVIGADO"/>
+        <s v="ITAGUI"/>
+        <s v="JUNIN"/>
+        <s v="SABANETA"/>
+        <s v="TERMINAL NORTE"/>
+        <s v="GENERAL"/>
+        <s v="NUMERARIO"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Producto" numFmtId="0">
+      <sharedItems count="6">
+        <s v="CVS PLUS"/>
+        <s v="POSTPAGO"/>
+        <s v="HOGAR"/>
+        <s v="TERMINALES"/>
+        <s v="FOCO"/>
+        <s v="OTROS"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Meta_Producto" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="27700"/>
+    </cacheField>
+    <cacheField name="Meta_General" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="1100" maxValue="53500" count="19">
+        <n v="2800"/>
+        <n v="2400"/>
+        <n v="1350"/>
+        <n v="1700"/>
+        <n v="1450"/>
+        <n v="1500"/>
+        <n v="4000"/>
+        <n v="2600"/>
+        <n v="2000"/>
+        <n v="1100"/>
+        <n v="2200"/>
+        <n v="1600"/>
+        <n v="2850"/>
+        <n v="3500"/>
+        <n v="2300"/>
+        <n v="5700"/>
+        <n v="2650"/>
+        <n v="53500"/>
+        <n v="6000"/>
+      </sharedItems>
+    </cacheField>
+  </cacheFields>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="288">
+  <r>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <n v="1500"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="1"/>
+    <n v="47"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="2"/>
+    <n v="10"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="3"/>
+    <n v="66"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="4"/>
+    <n v="29"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="5"/>
+    <n v="146"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="0"/>
+    <n v="1500"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="1"/>
+    <n v="37"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="2"/>
+    <n v="6"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="3"/>
+    <n v="57"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="4"/>
+    <n v="25"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="5"/>
+    <n v="95"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="2"/>
+    <x v="0"/>
+    <n v="0"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="2"/>
+    <x v="1"/>
+    <n v="12"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="2"/>
+    <x v="2"/>
+    <n v="4"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="2"/>
+    <x v="3"/>
+    <n v="35"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="2"/>
+    <x v="4"/>
+    <n v="15"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="2"/>
+    <x v="5"/>
+    <n v="32"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="3"/>
+    <x v="0"/>
+    <n v="800"/>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="3"/>
+    <x v="1"/>
+    <n v="33"/>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="3"/>
+    <x v="2"/>
+    <n v="1"/>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="3"/>
+    <x v="3"/>
+    <n v="45"/>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="3"/>
+    <x v="4"/>
+    <n v="20"/>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="3"/>
+    <x v="5"/>
+    <n v="135"/>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="4"/>
+    <x v="0"/>
+    <n v="1200"/>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="4"/>
+    <x v="1"/>
+    <n v="18"/>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="4"/>
+    <x v="2"/>
+    <n v="1"/>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="4"/>
+    <x v="3"/>
+    <n v="35"/>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="4"/>
+    <x v="4"/>
+    <n v="15"/>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="4"/>
+    <x v="5"/>
+    <n v="69"/>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="5"/>
+    <x v="0"/>
+    <n v="1200"/>
+    <x v="5"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="5"/>
+    <x v="1"/>
+    <n v="37"/>
+    <x v="5"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="5"/>
+    <x v="2"/>
+    <n v="1"/>
+    <x v="5"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="5"/>
+    <x v="3"/>
+    <n v="31"/>
+    <x v="5"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="5"/>
+    <x v="4"/>
+    <n v="14"/>
+    <x v="5"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="5"/>
+    <x v="5"/>
+    <n v="68"/>
+    <x v="5"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="6"/>
+    <x v="0"/>
+    <n v="1500"/>
+    <x v="6"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="6"/>
+    <x v="1"/>
+    <n v="42"/>
+    <x v="6"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="6"/>
+    <x v="2"/>
+    <n v="1"/>
+    <x v="6"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="6"/>
+    <x v="3"/>
+    <n v="112"/>
+    <x v="6"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="6"/>
+    <x v="4"/>
+    <n v="48"/>
+    <x v="6"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="6"/>
+    <x v="5"/>
+    <n v="176"/>
+    <x v="6"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="7"/>
+    <x v="0"/>
+    <n v="1500"/>
+    <x v="7"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="7"/>
+    <x v="1"/>
+    <n v="26"/>
+    <x v="7"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="7"/>
+    <x v="2"/>
+    <n v="1"/>
+    <x v="7"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="7"/>
+    <x v="3"/>
+    <n v="98"/>
+    <x v="7"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="7"/>
+    <x v="4"/>
+    <n v="42"/>
+    <x v="7"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="7"/>
+    <x v="5"/>
+    <n v="98"/>
+    <x v="7"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="8"/>
+    <x v="0"/>
+    <n v="1200"/>
+    <x v="8"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="8"/>
+    <x v="1"/>
+    <n v="32"/>
+    <x v="8"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="8"/>
+    <x v="2"/>
+    <n v="6"/>
+    <x v="8"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="8"/>
+    <x v="3"/>
+    <n v="39"/>
+    <x v="8"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="8"/>
+    <x v="4"/>
+    <n v="17"/>
+    <x v="8"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="8"/>
+    <x v="5"/>
+    <n v="128"/>
+    <x v="8"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="9"/>
+    <x v="0"/>
+    <n v="1200"/>
+    <x v="5"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="9"/>
+    <x v="1"/>
+    <n v="17"/>
+    <x v="5"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="9"/>
+    <x v="2"/>
+    <n v="6"/>
+    <x v="5"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="9"/>
+    <x v="3"/>
+    <n v="17"/>
+    <x v="5"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="9"/>
+    <x v="4"/>
+    <n v="8"/>
+    <x v="5"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="9"/>
+    <x v="5"/>
+    <n v="54"/>
+    <x v="5"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="10"/>
+    <x v="0"/>
+    <n v="800"/>
+    <x v="8"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="10"/>
+    <x v="1"/>
+    <n v="13"/>
+    <x v="8"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="10"/>
+    <x v="2"/>
+    <n v="1"/>
+    <x v="8"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="10"/>
+    <x v="3"/>
+    <n v="57"/>
+    <x v="8"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="10"/>
+    <x v="4"/>
+    <n v="25"/>
+    <x v="8"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="10"/>
+    <x v="5"/>
+    <n v="60"/>
+    <x v="8"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="11"/>
+    <x v="0"/>
+    <n v="1200"/>
+    <x v="9"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="11"/>
+    <x v="1"/>
+    <n v="16"/>
+    <x v="9"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="11"/>
+    <x v="2"/>
+    <n v="4"/>
+    <x v="9"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="11"/>
+    <x v="3"/>
+    <n v="21"/>
+    <x v="9"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="11"/>
+    <x v="4"/>
+    <n v="9"/>
+    <x v="9"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="11"/>
+    <x v="5"/>
+    <n v="74"/>
+    <x v="9"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="12"/>
+    <x v="0"/>
+    <n v="1200"/>
+    <x v="10"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="12"/>
+    <x v="1"/>
+    <n v="34"/>
+    <x v="10"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="12"/>
+    <x v="2"/>
+    <n v="1"/>
+    <x v="10"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="12"/>
+    <x v="3"/>
+    <n v="42"/>
+    <x v="10"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="12"/>
+    <x v="4"/>
+    <n v="18"/>
+    <x v="10"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="12"/>
+    <x v="5"/>
+    <n v="183"/>
+    <x v="10"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="13"/>
+    <x v="0"/>
+    <n v="1200"/>
+    <x v="11"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="13"/>
+    <x v="1"/>
+    <n v="22"/>
+    <x v="11"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="13"/>
+    <x v="2"/>
+    <n v="6"/>
+    <x v="11"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="13"/>
+    <x v="3"/>
+    <n v="42"/>
+    <x v="11"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="13"/>
+    <x v="4"/>
+    <n v="18"/>
+    <x v="11"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="13"/>
+    <x v="5"/>
+    <n v="168"/>
+    <x v="11"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="14"/>
+    <x v="0"/>
+    <n v="1200"/>
+    <x v="10"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="14"/>
+    <x v="1"/>
+    <n v="23"/>
+    <x v="10"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="14"/>
+    <x v="2"/>
+    <n v="1"/>
+    <x v="10"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="14"/>
+    <x v="3"/>
+    <n v="50"/>
+    <x v="10"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="14"/>
+    <x v="4"/>
+    <n v="22"/>
+    <x v="10"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="14"/>
+    <x v="5"/>
+    <n v="92"/>
+    <x v="10"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="15"/>
+    <x v="0"/>
+    <n v="1500"/>
+    <x v="12"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="15"/>
+    <x v="1"/>
+    <n v="52"/>
+    <x v="12"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="15"/>
+    <x v="2"/>
+    <n v="10"/>
+    <x v="12"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="15"/>
+    <x v="3"/>
+    <n v="71"/>
+    <x v="12"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="15"/>
+    <x v="4"/>
+    <n v="31"/>
+    <x v="12"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="15"/>
+    <x v="5"/>
+    <n v="129"/>
+    <x v="12"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="16"/>
+    <x v="0"/>
+    <n v="1500"/>
+    <x v="13"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="16"/>
+    <x v="1"/>
+    <n v="62"/>
+    <x v="13"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="16"/>
+    <x v="2"/>
+    <n v="10"/>
+    <x v="13"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="16"/>
+    <x v="3"/>
+    <n v="87"/>
+    <x v="13"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="16"/>
+    <x v="4"/>
+    <n v="37"/>
+    <x v="13"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="16"/>
+    <x v="5"/>
+    <n v="183"/>
+    <x v="13"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="17"/>
+    <x v="0"/>
+    <n v="1500"/>
+    <x v="13"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="17"/>
+    <x v="1"/>
+    <n v="78"/>
+    <x v="13"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="17"/>
+    <x v="2"/>
+    <n v="16"/>
+    <x v="13"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="17"/>
+    <x v="3"/>
+    <n v="67"/>
+    <x v="13"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="17"/>
+    <x v="4"/>
+    <n v="29"/>
+    <x v="13"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="17"/>
+    <x v="5"/>
+    <n v="198"/>
+    <x v="13"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="18"/>
+    <x v="0"/>
+    <n v="1500"/>
+    <x v="14"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="18"/>
+    <x v="1"/>
+    <n v="44"/>
+    <x v="14"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="18"/>
+    <x v="2"/>
+    <n v="10"/>
+    <x v="14"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="18"/>
+    <x v="3"/>
+    <n v="50"/>
+    <x v="14"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="18"/>
+    <x v="4"/>
+    <n v="22"/>
+    <x v="14"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="18"/>
+    <x v="5"/>
+    <n v="151"/>
+    <x v="14"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="19"/>
+    <x v="0"/>
+    <n v="1500"/>
+    <x v="15"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="19"/>
+    <x v="1"/>
+    <n v="103"/>
+    <x v="15"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="19"/>
+    <x v="2"/>
+    <n v="14"/>
+    <x v="15"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="19"/>
+    <x v="3"/>
+    <n v="165"/>
+    <x v="15"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="19"/>
+    <x v="4"/>
+    <n v="71"/>
+    <x v="15"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="19"/>
+    <x v="5"/>
+    <n v="192"/>
+    <x v="15"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="20"/>
+    <x v="0"/>
+    <n v="1500"/>
+    <x v="7"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="20"/>
+    <x v="1"/>
+    <n v="62"/>
+    <x v="7"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="20"/>
+    <x v="2"/>
+    <n v="11"/>
+    <x v="7"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="20"/>
+    <x v="3"/>
+    <n v="52"/>
+    <x v="7"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="20"/>
+    <x v="4"/>
+    <n v="22"/>
+    <x v="7"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="20"/>
+    <x v="5"/>
+    <n v="181"/>
+    <x v="7"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="21"/>
+    <x v="0"/>
+    <n v="1500"/>
+    <x v="16"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="21"/>
+    <x v="1"/>
+    <n v="30"/>
+    <x v="16"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="21"/>
+    <x v="2"/>
+    <n v="10"/>
+    <x v="16"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="21"/>
+    <x v="3"/>
+    <n v="64"/>
+    <x v="16"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="21"/>
+    <x v="4"/>
+    <n v="28"/>
+    <x v="16"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="21"/>
+    <x v="5"/>
+    <n v="126"/>
+    <x v="16"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="22"/>
+    <x v="0"/>
+    <n v="27700"/>
+    <x v="17"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="22"/>
+    <x v="1"/>
+    <n v="840"/>
+    <x v="17"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="22"/>
+    <x v="2"/>
+    <n v="131"/>
+    <x v="17"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="22"/>
+    <x v="3"/>
+    <n v="1303"/>
+    <x v="17"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="22"/>
+    <x v="4"/>
+    <n v="565"/>
+    <x v="17"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="22"/>
+    <x v="5"/>
+    <n v="2738"/>
+    <x v="17"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="23"/>
+    <x v="0"/>
+    <n v="1500"/>
+    <x v="15"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="23"/>
+    <x v="1"/>
+    <n v="103"/>
+    <x v="15"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="23"/>
+    <x v="2"/>
+    <n v="14"/>
+    <x v="15"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="23"/>
+    <x v="3"/>
+    <n v="1303"/>
+    <x v="15"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="23"/>
+    <x v="4"/>
+    <n v="71"/>
+    <x v="15"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="23"/>
+    <x v="5"/>
+    <n v="192"/>
+    <x v="15"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="0"/>
+    <n v="1500"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="1"/>
+    <n v="47"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="2"/>
+    <n v="10"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="3"/>
+    <n v="66"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="4"/>
+    <n v="29"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="5"/>
+    <n v="146"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="0"/>
+    <n v="1500"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="1"/>
+    <n v="37"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="2"/>
+    <n v="6"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="3"/>
+    <n v="57"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="4"/>
+    <n v="25"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="5"/>
+    <n v="95"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="2"/>
+    <x v="0"/>
+    <n v="0"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="2"/>
+    <x v="1"/>
+    <n v="12"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="2"/>
+    <x v="2"/>
+    <n v="4"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="2"/>
+    <x v="3"/>
+    <n v="35"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="2"/>
+    <x v="4"/>
+    <n v="15"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="2"/>
+    <x v="5"/>
+    <n v="32"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="3"/>
+    <x v="0"/>
+    <n v="800"/>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="3"/>
+    <x v="1"/>
+    <n v="33"/>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="3"/>
+    <x v="2"/>
+    <n v="1"/>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="3"/>
+    <x v="3"/>
+    <n v="45"/>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="3"/>
+    <x v="4"/>
+    <n v="20"/>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="3"/>
+    <x v="5"/>
+    <n v="135"/>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="4"/>
+    <x v="0"/>
+    <n v="1200"/>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="4"/>
+    <x v="1"/>
+    <n v="18"/>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="4"/>
+    <x v="2"/>
+    <n v="1"/>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="4"/>
+    <x v="3"/>
+    <n v="35"/>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="4"/>
+    <x v="4"/>
+    <n v="15"/>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="4"/>
+    <x v="5"/>
+    <n v="69"/>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="5"/>
+    <x v="0"/>
+    <n v="1200"/>
+    <x v="5"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="5"/>
+    <x v="1"/>
+    <n v="37"/>
+    <x v="5"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="5"/>
+    <x v="2"/>
+    <n v="1"/>
+    <x v="5"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="5"/>
+    <x v="3"/>
+    <n v="31"/>
+    <x v="5"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="5"/>
+    <x v="4"/>
+    <n v="14"/>
+    <x v="5"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="5"/>
+    <x v="5"/>
+    <n v="68"/>
+    <x v="5"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="6"/>
+    <x v="0"/>
+    <n v="1500"/>
+    <x v="6"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="6"/>
+    <x v="1"/>
+    <n v="42"/>
+    <x v="6"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="6"/>
+    <x v="2"/>
+    <n v="1"/>
+    <x v="6"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="6"/>
+    <x v="3"/>
+    <n v="112"/>
+    <x v="6"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="6"/>
+    <x v="4"/>
+    <n v="48"/>
+    <x v="6"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="6"/>
+    <x v="5"/>
+    <n v="176"/>
+    <x v="6"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="7"/>
+    <x v="0"/>
+    <n v="1500"/>
+    <x v="7"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="7"/>
+    <x v="1"/>
+    <n v="26"/>
+    <x v="7"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="7"/>
+    <x v="2"/>
+    <n v="1"/>
+    <x v="7"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="7"/>
+    <x v="3"/>
+    <n v="130"/>
+    <x v="7"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="7"/>
+    <x v="4"/>
+    <n v="42"/>
+    <x v="7"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="7"/>
+    <x v="5"/>
+    <n v="98"/>
+    <x v="7"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="8"/>
+    <x v="0"/>
+    <n v="1200"/>
+    <x v="8"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="8"/>
+    <x v="1"/>
+    <n v="32"/>
+    <x v="8"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="8"/>
+    <x v="2"/>
+    <n v="6"/>
+    <x v="8"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="8"/>
+    <x v="3"/>
+    <n v="39"/>
+    <x v="8"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="8"/>
+    <x v="4"/>
+    <n v="17"/>
+    <x v="8"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="8"/>
+    <x v="5"/>
+    <n v="128"/>
+    <x v="8"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="9"/>
+    <x v="0"/>
+    <n v="1200"/>
+    <x v="5"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="9"/>
+    <x v="1"/>
+    <n v="17"/>
+    <x v="5"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="9"/>
+    <x v="2"/>
+    <n v="6"/>
+    <x v="5"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="9"/>
+    <x v="3"/>
+    <n v="17"/>
+    <x v="5"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="9"/>
+    <x v="4"/>
+    <n v="8"/>
+    <x v="5"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="9"/>
+    <x v="5"/>
+    <n v="54"/>
+    <x v="5"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="10"/>
+    <x v="0"/>
+    <n v="800"/>
+    <x v="8"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="10"/>
+    <x v="1"/>
+    <n v="13"/>
+    <x v="8"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="10"/>
+    <x v="2"/>
+    <n v="1"/>
+    <x v="8"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="10"/>
+    <x v="3"/>
+    <n v="57"/>
+    <x v="8"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="10"/>
+    <x v="4"/>
+    <n v="25"/>
+    <x v="8"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="10"/>
+    <x v="5"/>
+    <n v="60"/>
+    <x v="8"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="11"/>
+    <x v="0"/>
+    <n v="1200"/>
+    <x v="9"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="11"/>
+    <x v="1"/>
+    <n v="16"/>
+    <x v="9"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="11"/>
+    <x v="2"/>
+    <n v="4"/>
+    <x v="9"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="11"/>
+    <x v="3"/>
+    <n v="21"/>
+    <x v="9"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="11"/>
+    <x v="4"/>
+    <n v="9"/>
+    <x v="9"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="11"/>
+    <x v="5"/>
+    <n v="74"/>
+    <x v="9"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="12"/>
+    <x v="0"/>
+    <n v="1200"/>
+    <x v="10"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="12"/>
+    <x v="1"/>
+    <n v="34"/>
+    <x v="10"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="12"/>
+    <x v="2"/>
+    <n v="1"/>
+    <x v="10"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="12"/>
+    <x v="3"/>
+    <n v="42"/>
+    <x v="10"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="12"/>
+    <x v="4"/>
+    <n v="18"/>
+    <x v="10"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="12"/>
+    <x v="5"/>
+    <n v="183"/>
+    <x v="10"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="13"/>
+    <x v="0"/>
+    <n v="1200"/>
+    <x v="11"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="13"/>
+    <x v="1"/>
+    <n v="22"/>
+    <x v="11"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="13"/>
+    <x v="2"/>
+    <n v="6"/>
+    <x v="11"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="13"/>
+    <x v="3"/>
+    <n v="42"/>
+    <x v="11"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="13"/>
+    <x v="4"/>
+    <n v="18"/>
+    <x v="11"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="13"/>
+    <x v="5"/>
+    <n v="168"/>
+    <x v="11"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="14"/>
+    <x v="0"/>
+    <n v="1200"/>
+    <x v="10"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="14"/>
+    <x v="1"/>
+    <n v="23"/>
+    <x v="10"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="14"/>
+    <x v="2"/>
+    <n v="1"/>
+    <x v="10"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="14"/>
+    <x v="3"/>
+    <n v="50"/>
+    <x v="10"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="14"/>
+    <x v="4"/>
+    <n v="22"/>
+    <x v="10"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="14"/>
+    <x v="5"/>
+    <n v="92"/>
+    <x v="10"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="15"/>
+    <x v="0"/>
+    <n v="1500"/>
+    <x v="12"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="15"/>
+    <x v="1"/>
+    <n v="52"/>
+    <x v="12"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="15"/>
+    <x v="2"/>
+    <n v="10"/>
+    <x v="12"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="15"/>
+    <x v="3"/>
+    <n v="71"/>
+    <x v="12"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="15"/>
+    <x v="4"/>
+    <n v="31"/>
+    <x v="12"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="15"/>
+    <x v="5"/>
+    <n v="129"/>
+    <x v="12"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="16"/>
+    <x v="0"/>
+    <n v="1500"/>
+    <x v="13"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="16"/>
+    <x v="1"/>
+    <n v="62"/>
+    <x v="13"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="16"/>
+    <x v="2"/>
+    <n v="10"/>
+    <x v="13"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="16"/>
+    <x v="3"/>
+    <n v="87"/>
+    <x v="13"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="16"/>
+    <x v="4"/>
+    <n v="37"/>
+    <x v="13"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="16"/>
+    <x v="5"/>
+    <n v="183"/>
+    <x v="13"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="17"/>
+    <x v="0"/>
+    <n v="1500"/>
+    <x v="13"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="17"/>
+    <x v="1"/>
+    <n v="78"/>
+    <x v="13"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="17"/>
+    <x v="2"/>
+    <n v="16"/>
+    <x v="13"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="17"/>
+    <x v="3"/>
+    <n v="67"/>
+    <x v="13"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="17"/>
+    <x v="4"/>
+    <n v="29"/>
+    <x v="13"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="17"/>
+    <x v="5"/>
+    <n v="198"/>
+    <x v="13"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="18"/>
+    <x v="0"/>
+    <n v="1500"/>
+    <x v="14"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="18"/>
+    <x v="1"/>
+    <n v="44"/>
+    <x v="14"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="18"/>
+    <x v="2"/>
+    <n v="10"/>
+    <x v="14"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="18"/>
+    <x v="3"/>
+    <n v="50"/>
+    <x v="14"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="18"/>
+    <x v="4"/>
+    <n v="22"/>
+    <x v="14"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="18"/>
+    <x v="5"/>
+    <n v="151"/>
+    <x v="14"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="19"/>
+    <x v="0"/>
+    <n v="1500"/>
+    <x v="18"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="19"/>
+    <x v="1"/>
+    <n v="103"/>
+    <x v="18"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="19"/>
+    <x v="2"/>
+    <n v="14"/>
+    <x v="18"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="19"/>
+    <x v="3"/>
+    <n v="165"/>
+    <x v="18"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="19"/>
+    <x v="4"/>
+    <n v="71"/>
+    <x v="18"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="19"/>
+    <x v="5"/>
+    <n v="192"/>
+    <x v="18"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="20"/>
+    <x v="0"/>
+    <n v="1500"/>
+    <x v="7"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="20"/>
+    <x v="1"/>
+    <n v="62"/>
+    <x v="7"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="20"/>
+    <x v="2"/>
+    <n v="11"/>
+    <x v="7"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="20"/>
+    <x v="3"/>
+    <n v="52"/>
+    <x v="7"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="20"/>
+    <x v="4"/>
+    <n v="22"/>
+    <x v="7"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="20"/>
+    <x v="5"/>
+    <n v="181"/>
+    <x v="7"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="21"/>
+    <x v="0"/>
+    <n v="1500"/>
+    <x v="16"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="21"/>
+    <x v="1"/>
+    <n v="30"/>
+    <x v="16"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="21"/>
+    <x v="2"/>
+    <n v="10"/>
+    <x v="16"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="21"/>
+    <x v="3"/>
+    <n v="64"/>
+    <x v="16"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="21"/>
+    <x v="4"/>
+    <n v="28"/>
+    <x v="16"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="21"/>
+    <x v="5"/>
+    <n v="126"/>
+    <x v="16"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="22"/>
+    <x v="0"/>
+    <n v="27700"/>
+    <x v="17"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="22"/>
+    <x v="1"/>
+    <n v="840"/>
+    <x v="17"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="22"/>
+    <x v="2"/>
+    <n v="131"/>
+    <x v="17"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="22"/>
+    <x v="3"/>
+    <n v="1303"/>
+    <x v="17"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="22"/>
+    <x v="4"/>
+    <n v="565"/>
+    <x v="17"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="22"/>
+    <x v="5"/>
+    <n v="2738"/>
+    <x v="17"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="23"/>
+    <x v="0"/>
+    <n v="1500"/>
+    <x v="15"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="23"/>
+    <x v="1"/>
+    <n v="103"/>
+    <x v="15"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="23"/>
+    <x v="2"/>
+    <n v="14"/>
+    <x v="15"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="23"/>
+    <x v="3"/>
+    <n v="1303"/>
+    <x v="15"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="23"/>
+    <x v="4"/>
+    <n v="71"/>
+    <x v="15"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="23"/>
+    <x v="5"/>
+    <n v="192"/>
+    <x v="15"/>
+  </r>
+</pivotCacheRecords>
+</file>
+
+<file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E78ED4BE-4740-4324-A20E-21AC80D7E338}" name="TablaDinámica9" cacheId="59" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+  <location ref="A3:H29" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
+  <pivotFields count="5">
+    <pivotField axis="axisPage" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0">
+      <items count="3">
+        <item x="0"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" compact="0" outline="0" showAll="0" defaultSubtotal="0">
+      <items count="24">
+        <item x="1"/>
+        <item x="15"/>
+        <item x="16"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="0"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="17"/>
+        <item x="7"/>
+        <item x="22"/>
+        <item x="8"/>
+        <item x="18"/>
+        <item x="19"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="23"/>
+        <item x="11"/>
+        <item x="20"/>
+        <item x="12"/>
+        <item x="21"/>
+        <item x="13"/>
+        <item x="14"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisCol" compact="0" outline="0" showAll="0">
+      <items count="7">
+        <item x="0"/>
+        <item x="4"/>
+        <item x="2"/>
+        <item x="5"/>
+        <item x="1"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0">
+      <items count="19">
+        <item x="9"/>
+        <item x="2"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="11"/>
+        <item x="3"/>
+        <item x="8"/>
+        <item x="10"/>
+        <item x="14"/>
+        <item x="1"/>
+        <item x="7"/>
+        <item x="16"/>
+        <item x="0"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="6"/>
+        <item x="15"/>
+        <item x="18"/>
+        <item x="17"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="1"/>
+  </rowFields>
+  <rowItems count="25">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i>
+      <x v="10"/>
+    </i>
+    <i>
+      <x v="11"/>
+    </i>
+    <i>
+      <x v="12"/>
+    </i>
+    <i>
+      <x v="13"/>
+    </i>
+    <i>
+      <x v="14"/>
+    </i>
+    <i>
+      <x v="15"/>
+    </i>
+    <i>
+      <x v="16"/>
+    </i>
+    <i>
+      <x v="17"/>
+    </i>
+    <i>
+      <x v="18"/>
+    </i>
+    <i>
+      <x v="19"/>
+    </i>
+    <i>
+      <x v="20"/>
+    </i>
+    <i>
+      <x v="21"/>
+    </i>
+    <i>
+      <x v="22"/>
+    </i>
+    <i>
+      <x v="23"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="2"/>
+  </colFields>
+  <colItems count="7">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <pageFields count="1">
+    <pageField fld="0" hier="-1"/>
+  </pageFields>
+  <dataFields count="1">
+    <dataField name="Suma de Meta_Producto" fld="3" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -548,8 +2872,715 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{045CA401-D4F5-42F5-9F33-A556D5A2E6C8}">
+  <dimension ref="A1:H29"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="22.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="7" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="B1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="B4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" t="s">
+        <v>31</v>
+      </c>
+      <c r="D4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E4" t="s">
+        <v>30</v>
+      </c>
+      <c r="F4" t="s">
+        <v>27</v>
+      </c>
+      <c r="G4" t="s">
+        <v>29</v>
+      </c>
+      <c r="H4" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B5" s="7">
+        <v>3000</v>
+      </c>
+      <c r="C5" s="7">
+        <v>50</v>
+      </c>
+      <c r="D5" s="7">
+        <v>12</v>
+      </c>
+      <c r="E5" s="7">
+        <v>190</v>
+      </c>
+      <c r="F5" s="7">
+        <v>74</v>
+      </c>
+      <c r="G5" s="7">
+        <v>114</v>
+      </c>
+      <c r="H5" s="7">
+        <v>3440</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6" s="7">
+        <v>3000</v>
+      </c>
+      <c r="C6" s="7">
+        <v>62</v>
+      </c>
+      <c r="D6" s="7">
+        <v>20</v>
+      </c>
+      <c r="E6" s="7">
+        <v>258</v>
+      </c>
+      <c r="F6" s="7">
+        <v>104</v>
+      </c>
+      <c r="G6" s="7">
+        <v>142</v>
+      </c>
+      <c r="H6" s="7">
+        <v>3586</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B7" s="7">
+        <v>3000</v>
+      </c>
+      <c r="C7" s="7">
+        <v>74</v>
+      </c>
+      <c r="D7" s="7">
+        <v>20</v>
+      </c>
+      <c r="E7" s="7">
+        <v>366</v>
+      </c>
+      <c r="F7" s="7">
+        <v>124</v>
+      </c>
+      <c r="G7" s="7">
+        <v>174</v>
+      </c>
+      <c r="H7" s="7">
+        <v>3758</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>2</v>
+      </c>
+      <c r="B8" s="7">
+        <v>0</v>
+      </c>
+      <c r="C8" s="7">
+        <v>30</v>
+      </c>
+      <c r="D8" s="7">
+        <v>8</v>
+      </c>
+      <c r="E8" s="7">
+        <v>64</v>
+      </c>
+      <c r="F8" s="7">
+        <v>24</v>
+      </c>
+      <c r="G8" s="7">
+        <v>70</v>
+      </c>
+      <c r="H8" s="7">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" s="7">
+        <v>1600</v>
+      </c>
+      <c r="C9" s="7">
+        <v>40</v>
+      </c>
+      <c r="D9" s="7">
+        <v>2</v>
+      </c>
+      <c r="E9" s="7">
+        <v>270</v>
+      </c>
+      <c r="F9" s="7">
+        <v>66</v>
+      </c>
+      <c r="G9" s="7">
+        <v>90</v>
+      </c>
+      <c r="H9" s="7">
+        <v>2068</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>5</v>
+      </c>
+      <c r="B10" s="7">
+        <v>3000</v>
+      </c>
+      <c r="C10" s="7">
+        <v>58</v>
+      </c>
+      <c r="D10" s="7">
+        <v>20</v>
+      </c>
+      <c r="E10" s="7">
+        <v>292</v>
+      </c>
+      <c r="F10" s="7">
+        <v>94</v>
+      </c>
+      <c r="G10" s="7">
+        <v>132</v>
+      </c>
+      <c r="H10" s="7">
+        <v>3596</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" s="7">
+        <v>2400</v>
+      </c>
+      <c r="C11" s="7">
+        <v>30</v>
+      </c>
+      <c r="D11" s="7">
+        <v>2</v>
+      </c>
+      <c r="E11" s="7">
+        <v>138</v>
+      </c>
+      <c r="F11" s="7">
+        <v>36</v>
+      </c>
+      <c r="G11" s="7">
+        <v>70</v>
+      </c>
+      <c r="H11" s="7">
+        <v>2676</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>10</v>
+      </c>
+      <c r="B12" s="7">
+        <v>2400</v>
+      </c>
+      <c r="C12" s="7">
+        <v>28</v>
+      </c>
+      <c r="D12" s="7">
+        <v>2</v>
+      </c>
+      <c r="E12" s="7">
+        <v>136</v>
+      </c>
+      <c r="F12" s="7">
+        <v>74</v>
+      </c>
+      <c r="G12" s="7">
+        <v>62</v>
+      </c>
+      <c r="H12" s="7">
+        <v>2702</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>9</v>
+      </c>
+      <c r="B13" s="7">
+        <v>3000</v>
+      </c>
+      <c r="C13" s="7">
+        <v>96</v>
+      </c>
+      <c r="D13" s="7">
+        <v>2</v>
+      </c>
+      <c r="E13" s="7">
+        <v>352</v>
+      </c>
+      <c r="F13" s="7">
+        <v>84</v>
+      </c>
+      <c r="G13" s="7">
+        <v>224</v>
+      </c>
+      <c r="H13" s="7">
+        <v>3758</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>11</v>
+      </c>
+      <c r="B14" s="7">
+        <v>3000</v>
+      </c>
+      <c r="C14" s="7">
+        <v>58</v>
+      </c>
+      <c r="D14" s="7">
+        <v>32</v>
+      </c>
+      <c r="E14" s="7">
+        <v>396</v>
+      </c>
+      <c r="F14" s="7">
+        <v>156</v>
+      </c>
+      <c r="G14" s="7">
+        <v>134</v>
+      </c>
+      <c r="H14" s="7">
+        <v>3776</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>13</v>
+      </c>
+      <c r="B15" s="7">
+        <v>3000</v>
+      </c>
+      <c r="C15" s="7">
+        <v>84</v>
+      </c>
+      <c r="D15" s="7">
+        <v>2</v>
+      </c>
+      <c r="E15" s="7">
+        <v>196</v>
+      </c>
+      <c r="F15" s="7">
+        <v>52</v>
+      </c>
+      <c r="G15" s="7">
+        <v>228</v>
+      </c>
+      <c r="H15" s="7">
+        <v>3562</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>32</v>
+      </c>
+      <c r="B16" s="7">
+        <v>55400</v>
+      </c>
+      <c r="C16" s="7">
+        <v>1130</v>
+      </c>
+      <c r="D16" s="7">
+        <v>262</v>
+      </c>
+      <c r="E16" s="7">
+        <v>5476</v>
+      </c>
+      <c r="F16" s="7">
+        <v>1680</v>
+      </c>
+      <c r="G16" s="7">
+        <v>2606</v>
+      </c>
+      <c r="H16" s="7">
+        <v>66554</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>7</v>
+      </c>
+      <c r="B17" s="7">
+        <v>2400</v>
+      </c>
+      <c r="C17" s="7">
+        <v>34</v>
+      </c>
+      <c r="D17" s="7">
+        <v>12</v>
+      </c>
+      <c r="E17" s="7">
+        <v>256</v>
+      </c>
+      <c r="F17" s="7">
+        <v>64</v>
+      </c>
+      <c r="G17" s="7">
+        <v>78</v>
+      </c>
+      <c r="H17" s="7">
+        <v>2844</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>14</v>
+      </c>
+      <c r="B18" s="7">
+        <v>3000</v>
+      </c>
+      <c r="C18" s="7">
+        <v>44</v>
+      </c>
+      <c r="D18" s="7">
+        <v>20</v>
+      </c>
+      <c r="E18" s="7">
+        <v>302</v>
+      </c>
+      <c r="F18" s="7">
+        <v>88</v>
+      </c>
+      <c r="G18" s="7">
+        <v>100</v>
+      </c>
+      <c r="H18" s="7">
+        <v>3554</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>16</v>
+      </c>
+      <c r="B19" s="7">
+        <v>3000</v>
+      </c>
+      <c r="C19" s="7">
+        <v>142</v>
+      </c>
+      <c r="D19" s="7">
+        <v>28</v>
+      </c>
+      <c r="E19" s="7">
+        <v>384</v>
+      </c>
+      <c r="F19" s="7">
+        <v>206</v>
+      </c>
+      <c r="G19" s="7">
+        <v>330</v>
+      </c>
+      <c r="H19" s="7">
+        <v>4090</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>12</v>
+      </c>
+      <c r="B20" s="7">
+        <v>2400</v>
+      </c>
+      <c r="C20" s="7">
+        <v>16</v>
+      </c>
+      <c r="D20" s="7">
+        <v>12</v>
+      </c>
+      <c r="E20" s="7">
+        <v>108</v>
+      </c>
+      <c r="F20" s="7">
+        <v>34</v>
+      </c>
+      <c r="G20" s="7">
+        <v>34</v>
+      </c>
+      <c r="H20" s="7">
+        <v>2604</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>17</v>
+      </c>
+      <c r="B21" s="7">
+        <v>1600</v>
+      </c>
+      <c r="C21" s="7">
+        <v>50</v>
+      </c>
+      <c r="D21" s="7">
+        <v>2</v>
+      </c>
+      <c r="E21" s="7">
+        <v>120</v>
+      </c>
+      <c r="F21" s="7">
+        <v>26</v>
+      </c>
+      <c r="G21" s="7">
+        <v>114</v>
+      </c>
+      <c r="H21" s="7">
+        <v>1912</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>35</v>
+      </c>
+      <c r="B22" s="7">
+        <v>3000</v>
+      </c>
+      <c r="C22" s="7">
+        <v>142</v>
+      </c>
+      <c r="D22" s="7">
+        <v>28</v>
+      </c>
+      <c r="E22" s="7">
+        <v>384</v>
+      </c>
+      <c r="F22" s="7">
+        <v>206</v>
+      </c>
+      <c r="G22" s="7">
+        <v>2606</v>
+      </c>
+      <c r="H22" s="7">
+        <v>6366</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>18</v>
+      </c>
+      <c r="B23" s="7">
+        <v>2400</v>
+      </c>
+      <c r="C23" s="7">
+        <v>18</v>
+      </c>
+      <c r="D23" s="7">
+        <v>8</v>
+      </c>
+      <c r="E23" s="7">
+        <v>148</v>
+      </c>
+      <c r="F23" s="7">
+        <v>32</v>
+      </c>
+      <c r="G23" s="7">
+        <v>42</v>
+      </c>
+      <c r="H23" s="7">
+        <v>2648</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>19</v>
+      </c>
+      <c r="B24" s="7">
+        <v>3000</v>
+      </c>
+      <c r="C24" s="7">
+        <v>44</v>
+      </c>
+      <c r="D24" s="7">
+        <v>22</v>
+      </c>
+      <c r="E24" s="7">
+        <v>362</v>
+      </c>
+      <c r="F24" s="7">
+        <v>124</v>
+      </c>
+      <c r="G24" s="7">
+        <v>104</v>
+      </c>
+      <c r="H24" s="7">
+        <v>3656</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>20</v>
+      </c>
+      <c r="B25" s="7">
+        <v>2400</v>
+      </c>
+      <c r="C25" s="7">
+        <v>36</v>
+      </c>
+      <c r="D25" s="7">
+        <v>2</v>
+      </c>
+      <c r="E25" s="7">
+        <v>366</v>
+      </c>
+      <c r="F25" s="7">
+        <v>68</v>
+      </c>
+      <c r="G25" s="7">
+        <v>84</v>
+      </c>
+      <c r="H25" s="7">
+        <v>2956</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>15</v>
+      </c>
+      <c r="B26" s="7">
+        <v>3000</v>
+      </c>
+      <c r="C26" s="7">
+        <v>56</v>
+      </c>
+      <c r="D26" s="7">
+        <v>20</v>
+      </c>
+      <c r="E26" s="7">
+        <v>252</v>
+      </c>
+      <c r="F26" s="7">
+        <v>60</v>
+      </c>
+      <c r="G26" s="7">
+        <v>128</v>
+      </c>
+      <c r="H26" s="7">
+        <v>3516</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>21</v>
+      </c>
+      <c r="B27" s="7">
+        <v>2400</v>
+      </c>
+      <c r="C27" s="7">
+        <v>36</v>
+      </c>
+      <c r="D27" s="7">
+        <v>12</v>
+      </c>
+      <c r="E27" s="7">
+        <v>336</v>
+      </c>
+      <c r="F27" s="7">
+        <v>44</v>
+      </c>
+      <c r="G27" s="7">
+        <v>84</v>
+      </c>
+      <c r="H27" s="7">
+        <v>2912</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>6</v>
+      </c>
+      <c r="B28" s="7">
+        <v>2400</v>
+      </c>
+      <c r="C28" s="7">
+        <v>44</v>
+      </c>
+      <c r="D28" s="7">
+        <v>2</v>
+      </c>
+      <c r="E28" s="7">
+        <v>184</v>
+      </c>
+      <c r="F28" s="7">
+        <v>46</v>
+      </c>
+      <c r="G28" s="7">
+        <v>100</v>
+      </c>
+      <c r="H28" s="7">
+        <v>2776</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>37</v>
+      </c>
+      <c r="B29" s="7">
+        <v>113800</v>
+      </c>
+      <c r="C29" s="7">
+        <v>2402</v>
+      </c>
+      <c r="D29" s="7">
+        <v>552</v>
+      </c>
+      <c r="E29" s="7">
+        <v>11336</v>
+      </c>
+      <c r="F29" s="7">
+        <v>3566</v>
+      </c>
+      <c r="G29" s="7">
+        <v>7850</v>
+      </c>
+      <c r="H29" s="7">
+        <v>139506</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6956BB2C-DA9E-4412-BCD4-BB80A11153FE}">
-  <dimension ref="A1:E253"/>
+  <dimension ref="A1:E241"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.7109375" bestFit="1" customWidth="1"/>
@@ -637,7 +3668,7 @@
         <v>29</v>
       </c>
       <c r="D5" s="3">
-        <v>66</v>
+        <v>95</v>
       </c>
       <c r="E5" s="3">
         <v>2800</v>
@@ -651,10 +3682,10 @@
         <v>5</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D6" s="3">
-        <v>29</v>
+        <v>146</v>
       </c>
       <c r="E6" s="3">
         <v>2800</v>
@@ -665,16 +3696,16 @@
         <v>34</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="D7" s="3">
-        <v>146</v>
+        <v>1500</v>
       </c>
       <c r="E7" s="3">
-        <v>2800</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -685,10 +3716,10 @@
         <v>0</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="D8" s="3">
-        <v>1500</v>
+        <v>37</v>
       </c>
       <c r="E8" s="3">
         <v>2400</v>
@@ -702,10 +3733,10 @@
         <v>0</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D9" s="3">
-        <v>37</v>
+        <v>6</v>
       </c>
       <c r="E9" s="3">
         <v>2400</v>
@@ -719,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D10" s="3">
-        <v>6</v>
+        <v>82</v>
       </c>
       <c r="E10" s="3">
         <v>2400</v>
@@ -736,10 +3767,10 @@
         <v>0</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="D11" s="3">
-        <v>57</v>
+        <v>30</v>
+      </c>
+      <c r="D11">
+        <v>95</v>
       </c>
       <c r="E11" s="3">
         <v>2400</v>
@@ -749,34 +3780,34 @@
       <c r="A12" t="s">
         <v>34</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B12" t="s">
+        <v>2</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D12" s="3">
         <v>0</v>
       </c>
-      <c r="C12" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="D12">
-        <v>25</v>
-      </c>
       <c r="E12" s="3">
-        <v>2400</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>34</v>
       </c>
-      <c r="B13" s="3" t="s">
-        <v>0</v>
+      <c r="B13" t="s">
+        <v>2</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D13">
-        <v>95</v>
+        <v>12</v>
       </c>
       <c r="E13" s="3">
-        <v>2400</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
@@ -787,10 +3818,10 @@
         <v>2</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="D14" s="3">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E14" s="3">
         <v>1350</v>
@@ -804,10 +3835,10 @@
         <v>2</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D15">
-        <v>12</v>
+        <v>29</v>
+      </c>
+      <c r="D15" s="3">
+        <v>50</v>
       </c>
       <c r="E15" s="3">
         <v>1350</v>
@@ -821,10 +3852,10 @@
         <v>2</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="D16" s="3">
-        <v>4</v>
+        <v>30</v>
+      </c>
+      <c r="D16">
+        <v>32</v>
       </c>
       <c r="E16" s="3">
         <v>1350</v>
@@ -835,16 +3866,16 @@
         <v>34</v>
       </c>
       <c r="B17" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="D17" s="3">
-        <v>35</v>
+        <v>800</v>
       </c>
       <c r="E17" s="3">
-        <v>1350</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
@@ -852,16 +3883,16 @@
         <v>34</v>
       </c>
       <c r="B18" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="D18">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="E18" s="3">
-        <v>1350</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
@@ -869,16 +3900,16 @@
         <v>34</v>
       </c>
       <c r="B19" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="D19">
-        <v>32</v>
+        <v>28</v>
+      </c>
+      <c r="D19" s="3">
+        <v>1</v>
       </c>
       <c r="E19" s="3">
-        <v>1350</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
@@ -889,10 +3920,10 @@
         <v>3</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="D20" s="3">
-        <v>800</v>
+        <v>65</v>
       </c>
       <c r="E20" s="3">
         <v>1700</v>
@@ -906,10 +3937,10 @@
         <v>3</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="D21">
-        <v>33</v>
+        <v>135</v>
       </c>
       <c r="E21" s="3">
         <v>1700</v>
@@ -920,16 +3951,16 @@
         <v>34</v>
       </c>
       <c r="B22" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="D22" s="3">
-        <v>1</v>
+        <v>1200</v>
       </c>
       <c r="E22" s="3">
-        <v>1700</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
@@ -937,16 +3968,16 @@
         <v>34</v>
       </c>
       <c r="B23" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="D23" s="3">
-        <v>45</v>
+        <v>27</v>
+      </c>
+      <c r="D23">
+        <v>18</v>
       </c>
       <c r="E23" s="3">
-        <v>1700</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
@@ -954,16 +3985,16 @@
         <v>34</v>
       </c>
       <c r="B24" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="D24">
-        <v>20</v>
+        <v>28</v>
+      </c>
+      <c r="D24" s="3">
+        <v>1</v>
       </c>
       <c r="E24" s="3">
-        <v>1700</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
@@ -971,16 +4002,16 @@
         <v>34</v>
       </c>
       <c r="B25" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="D25">
-        <v>135</v>
+        <v>29</v>
+      </c>
+      <c r="D25" s="3">
+        <v>50</v>
       </c>
       <c r="E25" s="3">
-        <v>1700</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
@@ -991,10 +4022,10 @@
         <v>8</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D26" s="3">
-        <v>1200</v>
+        <v>30</v>
+      </c>
+      <c r="D26">
+        <v>69</v>
       </c>
       <c r="E26" s="3">
         <v>1450</v>
@@ -1005,16 +4036,16 @@
         <v>34</v>
       </c>
       <c r="B27" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D27">
-        <v>18</v>
+        <v>22</v>
+      </c>
+      <c r="D27" s="3">
+        <v>1200</v>
       </c>
       <c r="E27" s="3">
-        <v>1450</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
@@ -1022,16 +4053,16 @@
         <v>34</v>
       </c>
       <c r="B28" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="D28" s="3">
-        <v>1</v>
+        <v>27</v>
+      </c>
+      <c r="D28">
+        <v>37</v>
       </c>
       <c r="E28" s="3">
-        <v>1450</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
@@ -1039,16 +4070,16 @@
         <v>34</v>
       </c>
       <c r="B29" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D29" s="3">
-        <v>35</v>
+        <v>1</v>
       </c>
       <c r="E29" s="3">
-        <v>1450</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
@@ -1056,16 +4087,16 @@
         <v>34</v>
       </c>
       <c r="B30" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="D30">
-        <v>15</v>
+        <v>29</v>
+      </c>
+      <c r="D30" s="3">
+        <v>45</v>
       </c>
       <c r="E30" s="3">
-        <v>1450</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
@@ -1073,16 +4104,16 @@
         <v>34</v>
       </c>
       <c r="B31" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C31" s="3" t="s">
         <v>30</v>
       </c>
       <c r="D31">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E31" s="3">
-        <v>1450</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
@@ -1090,16 +4121,16 @@
         <v>34</v>
       </c>
       <c r="B32" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C32" s="3" t="s">
         <v>22</v>
       </c>
       <c r="D32" s="3">
-        <v>1200</v>
+        <v>1500</v>
       </c>
       <c r="E32" s="3">
-        <v>1500</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
@@ -1107,16 +4138,16 @@
         <v>34</v>
       </c>
       <c r="B33" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C33" s="3" t="s">
         <v>27</v>
       </c>
       <c r="D33">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="E33" s="3">
-        <v>1500</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
@@ -1124,7 +4155,7 @@
         <v>34</v>
       </c>
       <c r="B34" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C34" s="3" t="s">
         <v>28</v>
@@ -1133,7 +4164,7 @@
         <v>1</v>
       </c>
       <c r="E34" s="3">
-        <v>1500</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
@@ -1141,16 +4172,16 @@
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C35" s="3" t="s">
         <v>29</v>
       </c>
       <c r="D35" s="3">
-        <v>31</v>
+        <v>160</v>
       </c>
       <c r="E35" s="3">
-        <v>1500</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
@@ -1158,16 +4189,16 @@
         <v>34</v>
       </c>
       <c r="B36" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D36">
-        <v>14</v>
+        <v>176</v>
       </c>
       <c r="E36" s="3">
-        <v>1500</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
@@ -1175,16 +4206,16 @@
         <v>34</v>
       </c>
       <c r="B37" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="D37">
-        <v>68</v>
+        <v>22</v>
+      </c>
+      <c r="D37" s="3">
+        <v>1500</v>
       </c>
       <c r="E37" s="3">
-        <v>1500</v>
+        <v>2600</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
@@ -1192,16 +4223,16 @@
         <v>34</v>
       </c>
       <c r="B38" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D38" s="3">
-        <v>1500</v>
+        <v>27</v>
+      </c>
+      <c r="D38">
+        <v>26</v>
       </c>
       <c r="E38" s="3">
-        <v>4000</v>
+        <v>2600</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
@@ -1209,16 +4240,16 @@
         <v>34</v>
       </c>
       <c r="B39" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D39">
-        <v>42</v>
+        <v>28</v>
+      </c>
+      <c r="D39" s="3">
+        <v>1</v>
       </c>
       <c r="E39" s="3">
-        <v>4000</v>
+        <v>2600</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
@@ -1226,16 +4257,16 @@
         <v>34</v>
       </c>
       <c r="B40" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D40" s="3">
-        <v>1</v>
+        <v>140</v>
       </c>
       <c r="E40" s="3">
-        <v>4000</v>
+        <v>2600</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
@@ -1243,16 +4274,16 @@
         <v>34</v>
       </c>
       <c r="B41" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="D41" s="3">
-        <v>112</v>
+        <v>30</v>
+      </c>
+      <c r="D41">
+        <v>98</v>
       </c>
       <c r="E41" s="3">
-        <v>4000</v>
+        <v>2600</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
@@ -1260,16 +4291,16 @@
         <v>34</v>
       </c>
       <c r="B42" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="D42">
-        <v>48</v>
+        <v>22</v>
+      </c>
+      <c r="D42" s="3">
+        <v>1200</v>
       </c>
       <c r="E42" s="3">
-        <v>4000</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
@@ -1277,16 +4308,16 @@
         <v>34</v>
       </c>
       <c r="B43" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D43">
-        <v>176</v>
+        <v>32</v>
       </c>
       <c r="E43" s="3">
-        <v>4000</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
@@ -1294,16 +4325,16 @@
         <v>34</v>
       </c>
       <c r="B44" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="D44" s="3">
-        <v>1500</v>
+        <v>6</v>
       </c>
       <c r="E44" s="3">
-        <v>2600</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
@@ -1311,16 +4342,16 @@
         <v>34</v>
       </c>
       <c r="B45" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D45">
-        <v>26</v>
+        <v>29</v>
+      </c>
+      <c r="D45" s="3">
+        <v>56</v>
       </c>
       <c r="E45" s="3">
-        <v>2600</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
@@ -1328,33 +4359,33 @@
         <v>34</v>
       </c>
       <c r="B46" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="D46" s="3">
-        <v>1</v>
+        <v>30</v>
+      </c>
+      <c r="D46">
+        <v>128</v>
       </c>
       <c r="E46" s="3">
-        <v>2600</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>34</v>
       </c>
-      <c r="B47" t="s">
-        <v>13</v>
+      <c r="B47" s="1" t="s">
+        <v>12</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="D47" s="3">
-        <v>98</v>
+        <v>1200</v>
       </c>
       <c r="E47" s="3">
-        <v>2600</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
@@ -1362,16 +4393,16 @@
         <v>34</v>
       </c>
       <c r="B48" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="D48">
-        <v>42</v>
+        <v>17</v>
       </c>
       <c r="E48" s="3">
-        <v>2600</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
@@ -1379,16 +4410,16 @@
         <v>34</v>
       </c>
       <c r="B49" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="D49">
-        <v>98</v>
+        <v>28</v>
+      </c>
+      <c r="D49" s="3">
+        <v>6</v>
       </c>
       <c r="E49" s="3">
-        <v>2600</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
@@ -1396,16 +4427,16 @@
         <v>34</v>
       </c>
       <c r="B50" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="D50" s="3">
-        <v>1200</v>
+        <v>25</v>
       </c>
       <c r="E50" s="3">
-        <v>2000</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
@@ -1413,16 +4444,16 @@
         <v>34</v>
       </c>
       <c r="B51" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="D51">
-        <v>32</v>
+        <v>54</v>
       </c>
       <c r="E51" s="3">
-        <v>2000</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
@@ -1430,13 +4461,13 @@
         <v>34</v>
       </c>
       <c r="B52" t="s">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="D52" s="3">
-        <v>6</v>
+        <v>800</v>
       </c>
       <c r="E52" s="3">
         <v>2000</v>
@@ -1447,13 +4478,13 @@
         <v>34</v>
       </c>
       <c r="B53" t="s">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="D53" s="3">
-        <v>39</v>
+        <v>27</v>
+      </c>
+      <c r="D53">
+        <v>13</v>
       </c>
       <c r="E53" s="3">
         <v>2000</v>
@@ -1464,13 +4495,13 @@
         <v>34</v>
       </c>
       <c r="B54" t="s">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="D54">
-        <v>17</v>
+        <v>28</v>
+      </c>
+      <c r="D54" s="3">
+        <v>1</v>
       </c>
       <c r="E54" s="3">
         <v>2000</v>
@@ -1481,13 +4512,13 @@
         <v>34</v>
       </c>
       <c r="B55" t="s">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="D55">
-        <v>128</v>
+        <v>29</v>
+      </c>
+      <c r="D55" s="3">
+        <v>82</v>
       </c>
       <c r="E55" s="3">
         <v>2000</v>
@@ -1497,17 +4528,17 @@
       <c r="A56" t="s">
         <v>34</v>
       </c>
-      <c r="B56" s="1" t="s">
-        <v>12</v>
+      <c r="B56" t="s">
+        <v>17</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D56" s="3">
-        <v>1200</v>
+        <v>30</v>
+      </c>
+      <c r="D56">
+        <v>60</v>
       </c>
       <c r="E56" s="3">
-        <v>1500</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
@@ -1515,16 +4546,16 @@
         <v>34</v>
       </c>
       <c r="B57" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D57">
-        <v>17</v>
+        <v>22</v>
+      </c>
+      <c r="D57" s="3">
+        <v>1200</v>
       </c>
       <c r="E57" s="3">
-        <v>1500</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
@@ -1532,16 +4563,16 @@
         <v>34</v>
       </c>
       <c r="B58" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="D58" s="3">
-        <v>6</v>
+        <v>27</v>
+      </c>
+      <c r="D58">
+        <v>16</v>
       </c>
       <c r="E58" s="3">
-        <v>1500</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.25">
@@ -1549,16 +4580,16 @@
         <v>34</v>
       </c>
       <c r="B59" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D59" s="3">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="E59" s="3">
-        <v>1500</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
@@ -1566,16 +4597,16 @@
         <v>34</v>
       </c>
       <c r="B60" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="D60">
-        <v>8</v>
+        <v>29</v>
+      </c>
+      <c r="D60" s="3">
+        <v>30</v>
       </c>
       <c r="E60" s="3">
-        <v>1500</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
@@ -1583,16 +4614,16 @@
         <v>34</v>
       </c>
       <c r="B61" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="C61" s="3" t="s">
         <v>30</v>
       </c>
       <c r="D61">
-        <v>54</v>
+        <v>74</v>
       </c>
       <c r="E61" s="3">
-        <v>1500</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.25">
@@ -1600,16 +4631,16 @@
         <v>34</v>
       </c>
       <c r="B62" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C62" s="3" t="s">
         <v>22</v>
       </c>
       <c r="D62" s="3">
-        <v>800</v>
+        <v>1200</v>
       </c>
       <c r="E62" s="3">
-        <v>2000</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.25">
@@ -1617,16 +4648,16 @@
         <v>34</v>
       </c>
       <c r="B63" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C63" s="3" t="s">
         <v>27</v>
       </c>
       <c r="D63">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="E63" s="3">
-        <v>2000</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.25">
@@ -1634,7 +4665,7 @@
         <v>34</v>
       </c>
       <c r="B64" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C64" s="3" t="s">
         <v>28</v>
@@ -1643,7 +4674,7 @@
         <v>1</v>
       </c>
       <c r="E64" s="3">
-        <v>2000</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.25">
@@ -1651,16 +4682,16 @@
         <v>34</v>
       </c>
       <c r="B65" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C65" s="3" t="s">
         <v>29</v>
       </c>
       <c r="D65" s="3">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E65" s="3">
-        <v>2000</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.25">
@@ -1668,16 +4699,16 @@
         <v>34</v>
       </c>
       <c r="B66" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D66">
-        <v>25</v>
+        <v>183</v>
       </c>
       <c r="E66" s="3">
-        <v>2000</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.25">
@@ -1685,16 +4716,16 @@
         <v>34</v>
       </c>
       <c r="B67" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="D67">
-        <v>60</v>
+        <v>22</v>
+      </c>
+      <c r="D67" s="3">
+        <v>1200</v>
       </c>
       <c r="E67" s="3">
-        <v>2000</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.25">
@@ -1702,16 +4733,16 @@
         <v>34</v>
       </c>
       <c r="B68" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C68" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D68">
         <v>22</v>
       </c>
-      <c r="D68" s="3">
-        <v>1200</v>
-      </c>
       <c r="E68" s="3">
-        <v>1100</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.25">
@@ -1719,33 +4750,33 @@
         <v>34</v>
       </c>
       <c r="B69" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D69">
-        <v>16</v>
+        <v>28</v>
+      </c>
+      <c r="D69" s="3">
+        <v>6</v>
       </c>
       <c r="E69" s="3">
-        <v>1100</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>34</v>
       </c>
       <c r="B70" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D70" s="3">
-        <v>4</v>
+        <v>60</v>
       </c>
       <c r="E70" s="3">
-        <v>1100</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.25">
@@ -1753,16 +4784,16 @@
         <v>34</v>
       </c>
       <c r="B71" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="D71" s="3">
-        <v>21</v>
+        <v>30</v>
+      </c>
+      <c r="D71">
+        <v>168</v>
       </c>
       <c r="E71" s="3">
-        <v>1100</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.25">
@@ -1770,16 +4801,16 @@
         <v>34</v>
       </c>
       <c r="B72" t="s">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="D72">
-        <v>9</v>
+        <v>22</v>
+      </c>
+      <c r="D72" s="3">
+        <v>1200</v>
       </c>
       <c r="E72" s="3">
-        <v>1100</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.25">
@@ -1787,16 +4818,16 @@
         <v>34</v>
       </c>
       <c r="B73" t="s">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D73">
-        <v>74</v>
+        <v>23</v>
       </c>
       <c r="E73" s="3">
-        <v>1100</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.25">
@@ -1804,13 +4835,13 @@
         <v>34</v>
       </c>
       <c r="B74" t="s">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="D74" s="3">
-        <v>1200</v>
+        <v>1</v>
       </c>
       <c r="E74" s="3">
         <v>2200</v>
@@ -1821,13 +4852,13 @@
         <v>34</v>
       </c>
       <c r="B75" t="s">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D75">
-        <v>34</v>
+        <v>29</v>
+      </c>
+      <c r="D75" s="3">
+        <v>72</v>
       </c>
       <c r="E75" s="3">
         <v>2200</v>
@@ -1838,13 +4869,13 @@
         <v>34</v>
       </c>
       <c r="B76" t="s">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="D76" s="3">
-        <v>1</v>
+        <v>30</v>
+      </c>
+      <c r="D76">
+        <v>92</v>
       </c>
       <c r="E76" s="3">
         <v>2200</v>
@@ -1855,16 +4886,16 @@
         <v>34</v>
       </c>
       <c r="B77" t="s">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="D77" s="3">
-        <v>42</v>
+        <v>1500</v>
       </c>
       <c r="E77" s="3">
-        <v>2200</v>
+        <v>2850</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.25">
@@ -1872,16 +4903,16 @@
         <v>34</v>
       </c>
       <c r="B78" t="s">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="D78">
-        <v>18</v>
+        <v>52</v>
       </c>
       <c r="E78" s="3">
-        <v>2200</v>
+        <v>2850</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.25">
@@ -1889,16 +4920,16 @@
         <v>34</v>
       </c>
       <c r="B79" t="s">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="D79">
-        <v>183</v>
+        <v>28</v>
+      </c>
+      <c r="D79" s="3">
+        <v>10</v>
       </c>
       <c r="E79" s="3">
-        <v>2200</v>
+        <v>2850</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.25">
@@ -1906,16 +4937,16 @@
         <v>34</v>
       </c>
       <c r="B80" t="s">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="D80" s="3">
-        <v>1200</v>
+        <v>102</v>
       </c>
       <c r="E80" s="3">
-        <v>1600</v>
+        <v>2850</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.25">
@@ -1923,16 +4954,16 @@
         <v>34</v>
       </c>
       <c r="B81" t="s">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="D81">
-        <v>22</v>
+        <v>129</v>
       </c>
       <c r="E81" s="3">
-        <v>1600</v>
+        <v>2850</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.25">
@@ -1940,50 +4971,50 @@
         <v>34</v>
       </c>
       <c r="B82" t="s">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="C82" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D82">
+        <v>1500</v>
+      </c>
+      <c r="E82" s="3">
+        <v>3500</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>34</v>
+      </c>
+      <c r="B83" t="s">
+        <v>4</v>
+      </c>
+      <c r="C83" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D83">
+        <v>62</v>
+      </c>
+      <c r="E83" s="3">
+        <v>3500</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>34</v>
+      </c>
+      <c r="B84" t="s">
+        <v>4</v>
+      </c>
+      <c r="C84" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="D82" s="3">
-        <v>6</v>
-      </c>
-      <c r="E82" s="3">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="83" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A83" t="s">
-        <v>34</v>
-      </c>
-      <c r="B83" t="s">
-        <v>21</v>
-      </c>
-      <c r="C83" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="D83" s="3">
-        <v>42</v>
-      </c>
-      <c r="E83" s="3">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="84" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A84" t="s">
-        <v>34</v>
-      </c>
-      <c r="B84" t="s">
-        <v>21</v>
-      </c>
-      <c r="C84" s="3" t="s">
-        <v>31</v>
-      </c>
       <c r="D84">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="E84" s="3">
-        <v>1600</v>
+        <v>3500</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.25">
@@ -1991,16 +5022,16 @@
         <v>34</v>
       </c>
       <c r="B85" t="s">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="D85">
-        <v>168</v>
+        <v>29</v>
+      </c>
+      <c r="D85" s="3">
+        <v>124</v>
       </c>
       <c r="E85" s="3">
-        <v>1600</v>
+        <v>3500</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.25">
@@ -2008,16 +5039,16 @@
         <v>34</v>
       </c>
       <c r="B86" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D86" s="3">
-        <v>1200</v>
+        <v>30</v>
+      </c>
+      <c r="D86">
+        <v>183</v>
       </c>
       <c r="E86" s="3">
-        <v>2200</v>
+        <v>3500</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.25">
@@ -2025,16 +5056,16 @@
         <v>34</v>
       </c>
       <c r="B87" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D87">
-        <v>23</v>
+        <v>22</v>
+      </c>
+      <c r="D87" s="3">
+        <v>1500</v>
       </c>
       <c r="E87" s="3">
-        <v>2200</v>
+        <v>3500</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.25">
@@ -2042,16 +5073,16 @@
         <v>34</v>
       </c>
       <c r="B88" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="D88" s="3">
-        <v>1</v>
+        <v>27</v>
+      </c>
+      <c r="D88">
+        <v>78</v>
       </c>
       <c r="E88" s="3">
-        <v>2200</v>
+        <v>3500</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.25">
@@ -2059,16 +5090,16 @@
         <v>34</v>
       </c>
       <c r="B89" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D89" s="3">
-        <v>50</v>
+        <v>16</v>
       </c>
       <c r="E89" s="3">
-        <v>2200</v>
+        <v>3500</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.25">
@@ -2076,16 +5107,16 @@
         <v>34</v>
       </c>
       <c r="B90" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="D90">
-        <v>22</v>
+        <v>29</v>
+      </c>
+      <c r="D90" s="3">
+        <v>96</v>
       </c>
       <c r="E90" s="3">
-        <v>2200</v>
+        <v>3500</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.25">
@@ -2093,16 +5124,16 @@
         <v>34</v>
       </c>
       <c r="B91" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="C91" s="3" t="s">
         <v>30</v>
       </c>
       <c r="D91">
-        <v>92</v>
+        <v>198</v>
       </c>
       <c r="E91" s="3">
-        <v>2200</v>
+        <v>3500</v>
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.25">
@@ -2110,7 +5141,7 @@
         <v>34</v>
       </c>
       <c r="B92" t="s">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="C92" s="3" t="s">
         <v>22</v>
@@ -2119,7 +5150,7 @@
         <v>1500</v>
       </c>
       <c r="E92" s="3">
-        <v>2850</v>
+        <v>2300</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.25">
@@ -2127,16 +5158,16 @@
         <v>34</v>
       </c>
       <c r="B93" t="s">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="C93" s="3" t="s">
         <v>27</v>
       </c>
       <c r="D93">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="E93" s="3">
-        <v>2850</v>
+        <v>2300</v>
       </c>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.25">
@@ -2144,7 +5175,7 @@
         <v>34</v>
       </c>
       <c r="B94" t="s">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="C94" s="3" t="s">
         <v>28</v>
@@ -2153,7 +5184,7 @@
         <v>10</v>
       </c>
       <c r="E94" s="3">
-        <v>2850</v>
+        <v>2300</v>
       </c>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.25">
@@ -2161,16 +5192,16 @@
         <v>34</v>
       </c>
       <c r="B95" t="s">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="C95" s="3" t="s">
         <v>29</v>
       </c>
       <c r="D95" s="3">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E95" s="3">
-        <v>2850</v>
+        <v>2300</v>
       </c>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.25">
@@ -2178,16 +5209,16 @@
         <v>34</v>
       </c>
       <c r="B96" t="s">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D96">
-        <v>31</v>
+        <v>151</v>
       </c>
       <c r="E96" s="3">
-        <v>2850</v>
+        <v>2300</v>
       </c>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.25">
@@ -2195,16 +5226,16 @@
         <v>34</v>
       </c>
       <c r="B97" t="s">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="D97">
-        <v>129</v>
+        <v>22</v>
+      </c>
+      <c r="D97" s="3">
+        <v>1500</v>
       </c>
       <c r="E97" s="3">
-        <v>2850</v>
+        <v>5700</v>
       </c>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.25">
@@ -2212,16 +5243,16 @@
         <v>34</v>
       </c>
       <c r="B98" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="C98" s="3" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="D98">
-        <v>1500</v>
+        <v>103</v>
       </c>
       <c r="E98" s="3">
-        <v>3500</v>
+        <v>5700</v>
       </c>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.25">
@@ -2229,16 +5260,16 @@
         <v>34</v>
       </c>
       <c r="B99" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="C99" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D99">
-        <v>62</v>
+        <v>28</v>
+      </c>
+      <c r="D99" s="3">
+        <v>14</v>
       </c>
       <c r="E99" s="3">
-        <v>3500</v>
+        <v>5700</v>
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.25">
@@ -2246,16 +5277,16 @@
         <v>34</v>
       </c>
       <c r="B100" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="C100" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="D100">
-        <v>10</v>
+        <v>29</v>
+      </c>
+      <c r="D100" s="3">
+        <v>236</v>
       </c>
       <c r="E100" s="3">
-        <v>3500</v>
+        <v>5700</v>
       </c>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.25">
@@ -2263,16 +5294,16 @@
         <v>34</v>
       </c>
       <c r="B101" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="C101" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="D101" s="3">
-        <v>87</v>
+        <v>30</v>
+      </c>
+      <c r="D101">
+        <v>192</v>
       </c>
       <c r="E101" s="3">
-        <v>3500</v>
+        <v>5700</v>
       </c>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.25">
@@ -2280,16 +5311,16 @@
         <v>34</v>
       </c>
       <c r="B102" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="C102" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="D102">
-        <v>37</v>
+        <v>22</v>
+      </c>
+      <c r="D102" s="3">
+        <v>1500</v>
       </c>
       <c r="E102" s="3">
-        <v>3500</v>
+        <v>2600</v>
       </c>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.25">
@@ -2297,16 +5328,16 @@
         <v>34</v>
       </c>
       <c r="B103" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="C103" s="3" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D103">
-        <v>183</v>
+        <v>62</v>
       </c>
       <c r="E103" s="3">
-        <v>3500</v>
+        <v>2600</v>
       </c>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.25">
@@ -2314,16 +5345,16 @@
         <v>34</v>
       </c>
       <c r="B104" t="s">
+        <v>19</v>
+      </c>
+      <c r="C104" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D104" s="3">
         <v>11</v>
       </c>
-      <c r="C104" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D104" s="3">
-        <v>1500</v>
-      </c>
       <c r="E104" s="3">
-        <v>3500</v>
+        <v>2600</v>
       </c>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.25">
@@ -2331,16 +5362,16 @@
         <v>34</v>
       </c>
       <c r="B105" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="C105" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D105">
-        <v>78</v>
+        <v>29</v>
+      </c>
+      <c r="D105" s="3">
+        <v>74</v>
       </c>
       <c r="E105" s="3">
-        <v>3500</v>
+        <v>2600</v>
       </c>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.25">
@@ -2348,16 +5379,16 @@
         <v>34</v>
       </c>
       <c r="B106" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="C106" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="D106" s="3">
-        <v>16</v>
+        <v>30</v>
+      </c>
+      <c r="D106">
+        <v>181</v>
       </c>
       <c r="E106" s="3">
-        <v>3500</v>
+        <v>2600</v>
       </c>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.25">
@@ -2365,16 +5396,16 @@
         <v>34</v>
       </c>
       <c r="B107" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C107" s="3" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="D107" s="3">
-        <v>67</v>
+        <v>1500</v>
       </c>
       <c r="E107" s="3">
-        <v>3500</v>
+        <v>2650</v>
       </c>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.25">
@@ -2382,16 +5413,16 @@
         <v>34</v>
       </c>
       <c r="B108" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C108" s="3" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="D108">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E108" s="3">
-        <v>3500</v>
+        <v>2650</v>
       </c>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.25">
@@ -2399,16 +5430,16 @@
         <v>34</v>
       </c>
       <c r="B109" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C109" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="D109">
-        <v>198</v>
+        <v>28</v>
+      </c>
+      <c r="D109" s="3">
+        <v>10</v>
       </c>
       <c r="E109" s="3">
-        <v>3500</v>
+        <v>2650</v>
       </c>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.25">
@@ -2416,16 +5447,16 @@
         <v>34</v>
       </c>
       <c r="B110" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C110" s="3" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="D110" s="3">
-        <v>1500</v>
+        <v>92</v>
       </c>
       <c r="E110" s="3">
-        <v>2300</v>
+        <v>2650</v>
       </c>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.25">
@@ -2433,16 +5464,16 @@
         <v>34</v>
       </c>
       <c r="B111" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C111" s="3" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="D111">
-        <v>44</v>
+        <v>126</v>
       </c>
       <c r="E111" s="3">
-        <v>2300</v>
+        <v>2650</v>
       </c>
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.25">
@@ -2450,16 +5481,16 @@
         <v>34</v>
       </c>
       <c r="B112" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="C112" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="D112" s="3">
-        <v>10</v>
+        <v>22</v>
+      </c>
+      <c r="D112">
+        <v>27700</v>
       </c>
       <c r="E112" s="3">
-        <v>2300</v>
+        <v>53500</v>
       </c>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.25">
@@ -2467,16 +5498,16 @@
         <v>34</v>
       </c>
       <c r="B113" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="C113" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="D113" s="3">
-        <v>50</v>
+        <v>27</v>
+      </c>
+      <c r="D113">
+        <v>840</v>
       </c>
       <c r="E113" s="3">
-        <v>2300</v>
+        <v>53500</v>
       </c>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.25">
@@ -2484,16 +5515,16 @@
         <v>34</v>
       </c>
       <c r="B114" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="C114" s="3" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D114">
-        <v>22</v>
+        <v>131</v>
       </c>
       <c r="E114" s="3">
-        <v>2300</v>
+        <v>53500</v>
       </c>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.25">
@@ -2501,16 +5532,16 @@
         <v>34</v>
       </c>
       <c r="B115" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="C115" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="D115">
-        <v>151</v>
+        <v>29</v>
+      </c>
+      <c r="D115" s="3">
+        <v>1868</v>
       </c>
       <c r="E115" s="3">
-        <v>2300</v>
+        <v>53500</v>
       </c>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.25">
@@ -2518,16 +5549,16 @@
         <v>34</v>
       </c>
       <c r="B116" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="C116" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D116" s="3">
-        <v>1500</v>
+        <v>30</v>
+      </c>
+      <c r="D116">
+        <v>2738</v>
       </c>
       <c r="E116" s="3">
-        <v>5700</v>
+        <v>53500</v>
       </c>
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.25">
@@ -2535,13 +5566,13 @@
         <v>34</v>
       </c>
       <c r="B117" t="s">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="C117" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D117">
-        <v>103</v>
+        <v>22</v>
+      </c>
+      <c r="D117" s="3">
+        <v>1500</v>
       </c>
       <c r="E117" s="3">
         <v>5700</v>
@@ -2552,13 +5583,13 @@
         <v>34</v>
       </c>
       <c r="B118" t="s">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="C118" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="D118" s="3">
-        <v>14</v>
+        <v>27</v>
+      </c>
+      <c r="D118">
+        <v>103</v>
       </c>
       <c r="E118" s="3">
         <v>5700</v>
@@ -2569,13 +5600,13 @@
         <v>34</v>
       </c>
       <c r="B119" t="s">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="C119" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D119" s="3">
-        <v>165</v>
+        <v>14</v>
       </c>
       <c r="E119" s="3">
         <v>5700</v>
@@ -2586,13 +5617,13 @@
         <v>34</v>
       </c>
       <c r="B120" t="s">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="C120" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="D120">
-        <v>71</v>
+        <v>29</v>
+      </c>
+      <c r="D120" s="3">
+        <v>1868</v>
       </c>
       <c r="E120" s="3">
         <v>5700</v>
@@ -2603,7 +5634,7 @@
         <v>34</v>
       </c>
       <c r="B121" t="s">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="C121" s="3" t="s">
         <v>30</v>
@@ -2617,10 +5648,10 @@
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>34</v>
-      </c>
-      <c r="B122" t="s">
-        <v>19</v>
+        <v>36</v>
+      </c>
+      <c r="B122" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="C122" s="3" t="s">
         <v>22</v>
@@ -2629,867 +5660,2034 @@
         <v>1500</v>
       </c>
       <c r="E122" s="3">
-        <v>2600</v>
+        <v>2800</v>
       </c>
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>34</v>
-      </c>
-      <c r="B123" t="s">
-        <v>19</v>
+        <v>36</v>
+      </c>
+      <c r="B123" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="C123" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="D123">
-        <v>62</v>
+      <c r="D123" s="3">
+        <v>47</v>
       </c>
       <c r="E123" s="3">
-        <v>2600</v>
+        <v>2800</v>
       </c>
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>34</v>
-      </c>
-      <c r="B124" t="s">
-        <v>19</v>
+        <v>36</v>
+      </c>
+      <c r="B124" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="C124" s="3" t="s">
         <v>28</v>
       </c>
       <c r="D124" s="3">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E124" s="3">
-        <v>2600</v>
+        <v>2800</v>
       </c>
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>34</v>
-      </c>
-      <c r="B125" t="s">
-        <v>19</v>
+        <v>36</v>
+      </c>
+      <c r="B125" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="C125" s="3" t="s">
         <v>29</v>
       </c>
       <c r="D125" s="3">
-        <v>52</v>
+        <v>95</v>
       </c>
       <c r="E125" s="3">
-        <v>2600</v>
+        <v>2800</v>
       </c>
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>34</v>
-      </c>
-      <c r="B126" t="s">
-        <v>19</v>
+        <v>36</v>
+      </c>
+      <c r="B126" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="C126" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="D126">
-        <v>22</v>
+        <v>30</v>
+      </c>
+      <c r="D126" s="3">
+        <v>146</v>
       </c>
       <c r="E126" s="3">
-        <v>2600</v>
+        <v>2800</v>
       </c>
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>34</v>
-      </c>
-      <c r="B127" t="s">
-        <v>19</v>
+        <v>36</v>
+      </c>
+      <c r="B127" s="3" t="s">
+        <v>0</v>
       </c>
       <c r="C127" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="D127">
-        <v>181</v>
+        <v>22</v>
+      </c>
+      <c r="D127" s="3">
+        <v>1500</v>
       </c>
       <c r="E127" s="3">
-        <v>2600</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>34</v>
-      </c>
-      <c r="B128" t="s">
-        <v>15</v>
+        <v>36</v>
+      </c>
+      <c r="B128" s="3" t="s">
+        <v>0</v>
       </c>
       <c r="C128" s="3" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="D128" s="3">
-        <v>1500</v>
+        <v>37</v>
       </c>
       <c r="E128" s="3">
-        <v>2650</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>34</v>
-      </c>
-      <c r="B129" t="s">
-        <v>15</v>
+        <v>36</v>
+      </c>
+      <c r="B129" s="3" t="s">
+        <v>0</v>
       </c>
       <c r="C129" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D129">
-        <v>30</v>
+        <v>28</v>
+      </c>
+      <c r="D129" s="3">
+        <v>6</v>
       </c>
       <c r="E129" s="3">
-        <v>2650</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>34</v>
-      </c>
-      <c r="B130" t="s">
-        <v>15</v>
+        <v>36</v>
+      </c>
+      <c r="B130" s="3" t="s">
+        <v>0</v>
       </c>
       <c r="C130" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D130" s="3">
-        <v>10</v>
+        <v>82</v>
       </c>
       <c r="E130" s="3">
-        <v>2650</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>34</v>
-      </c>
-      <c r="B131" t="s">
-        <v>15</v>
+        <v>36</v>
+      </c>
+      <c r="B131" s="3" t="s">
+        <v>0</v>
       </c>
       <c r="C131" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="D131" s="3">
-        <v>64</v>
+        <v>30</v>
+      </c>
+      <c r="D131">
+        <v>95</v>
       </c>
       <c r="E131" s="3">
-        <v>2650</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B132" t="s">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="C132" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="D132">
-        <v>28</v>
+        <v>22</v>
+      </c>
+      <c r="D132" s="3">
+        <v>0</v>
       </c>
       <c r="E132" s="3">
-        <v>2650</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B133" t="s">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="C133" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="D133">
-        <v>126</v>
+        <v>27</v>
+      </c>
+      <c r="D133" s="3">
+        <v>12</v>
       </c>
       <c r="E133" s="3">
-        <v>2650</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B134" t="s">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="C134" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D134">
-        <v>27700</v>
+        <v>28</v>
+      </c>
+      <c r="D134" s="3">
+        <v>4</v>
       </c>
       <c r="E134" s="3">
-        <v>53500</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B135" t="s">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="C135" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D135">
-        <v>840</v>
+        <v>29</v>
+      </c>
+      <c r="D135" s="3">
+        <v>50</v>
       </c>
       <c r="E135" s="3">
-        <v>53500</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B136" t="s">
+        <v>2</v>
+      </c>
+      <c r="C136" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D136">
         <v>32</v>
       </c>
-      <c r="C136" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="D136">
-        <v>131</v>
-      </c>
       <c r="E136" s="3">
-        <v>53500</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B137" t="s">
-        <v>32</v>
+        <v>3</v>
       </c>
       <c r="C137" s="3" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="D137" s="3">
-        <v>1303</v>
+        <v>800</v>
       </c>
       <c r="E137" s="3">
-        <v>53500</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B138" t="s">
-        <v>32</v>
+        <v>3</v>
       </c>
       <c r="C138" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="D138">
-        <v>565</v>
+        <v>27</v>
+      </c>
+      <c r="D138" s="3">
+        <v>33</v>
       </c>
       <c r="E138" s="3">
-        <v>53500</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B139" t="s">
-        <v>32</v>
+        <v>3</v>
       </c>
       <c r="C139" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="D139">
-        <v>2738</v>
+        <v>28</v>
+      </c>
+      <c r="D139" s="3">
+        <v>1</v>
       </c>
       <c r="E139" s="3">
-        <v>53500</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B140" t="s">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="C140" s="3" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="D140" s="3">
-        <v>1500</v>
+        <v>65</v>
       </c>
       <c r="E140" s="3">
-        <v>5700</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="141" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B141" t="s">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="C141" s="3" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="D141">
-        <v>103</v>
+        <v>135</v>
       </c>
       <c r="E141" s="3">
-        <v>5700</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="142" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B142" t="s">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="C142" s="3" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="D142" s="3">
-        <v>14</v>
+        <v>1200</v>
       </c>
       <c r="E142" s="3">
-        <v>5700</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="143" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B143" t="s">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="C143" s="3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D143" s="3">
-        <v>1303</v>
+        <v>18</v>
       </c>
       <c r="E143" s="3">
-        <v>5700</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B144" t="s">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="C144" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="D144">
-        <v>71</v>
+        <v>28</v>
+      </c>
+      <c r="D144" s="3">
+        <v>1</v>
       </c>
       <c r="E144" s="3">
-        <v>5700</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B145" t="s">
+        <v>8</v>
+      </c>
+      <c r="C145" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D145" s="3">
+        <v>50</v>
+      </c>
+      <c r="E145" s="3">
+        <v>1450</v>
+      </c>
+    </row>
+    <row r="146" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A146" t="s">
+        <v>36</v>
+      </c>
+      <c r="B146" t="s">
+        <v>8</v>
+      </c>
+      <c r="C146" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D146">
+        <v>69</v>
+      </c>
+      <c r="E146" s="3">
+        <v>1450</v>
+      </c>
+    </row>
+    <row r="147" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A147" t="s">
+        <v>36</v>
+      </c>
+      <c r="B147" t="s">
+        <v>10</v>
+      </c>
+      <c r="C147" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D147" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E147" s="3">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="148" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A148" t="s">
+        <v>36</v>
+      </c>
+      <c r="B148" t="s">
+        <v>10</v>
+      </c>
+      <c r="C148" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D148" s="3">
+        <v>37</v>
+      </c>
+      <c r="E148" s="3">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="149" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A149" t="s">
+        <v>36</v>
+      </c>
+      <c r="B149" t="s">
+        <v>10</v>
+      </c>
+      <c r="C149" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D149" s="3">
+        <v>1</v>
+      </c>
+      <c r="E149" s="3">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="150" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A150" t="s">
+        <v>36</v>
+      </c>
+      <c r="B150" t="s">
+        <v>10</v>
+      </c>
+      <c r="C150" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D150" s="3">
+        <v>45</v>
+      </c>
+      <c r="E150" s="3">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="151" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A151" t="s">
+        <v>36</v>
+      </c>
+      <c r="B151" t="s">
+        <v>10</v>
+      </c>
+      <c r="C151" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D151">
+        <v>68</v>
+      </c>
+      <c r="E151" s="3">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="152" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A152" t="s">
+        <v>36</v>
+      </c>
+      <c r="B152" t="s">
+        <v>9</v>
+      </c>
+      <c r="C152" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D152" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E152" s="3">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="153" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A153" t="s">
+        <v>36</v>
+      </c>
+      <c r="B153" t="s">
+        <v>9</v>
+      </c>
+      <c r="C153" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D153" s="3">
+        <v>42</v>
+      </c>
+      <c r="E153" s="3">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="154" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A154" t="s">
+        <v>36</v>
+      </c>
+      <c r="B154" t="s">
+        <v>9</v>
+      </c>
+      <c r="C154" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D154" s="3">
+        <v>1</v>
+      </c>
+      <c r="E154" s="3">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="155" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A155" t="s">
+        <v>36</v>
+      </c>
+      <c r="B155" t="s">
+        <v>9</v>
+      </c>
+      <c r="C155" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D155" s="3">
+        <v>160</v>
+      </c>
+      <c r="E155" s="3">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="156" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A156" t="s">
+        <v>36</v>
+      </c>
+      <c r="B156" t="s">
+        <v>9</v>
+      </c>
+      <c r="C156" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D156">
+        <v>176</v>
+      </c>
+      <c r="E156" s="3">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="157" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A157" t="s">
+        <v>36</v>
+      </c>
+      <c r="B157" t="s">
+        <v>13</v>
+      </c>
+      <c r="C157" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D157" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E157" s="3">
+        <v>2600</v>
+      </c>
+    </row>
+    <row r="158" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A158" t="s">
+        <v>36</v>
+      </c>
+      <c r="B158" t="s">
+        <v>13</v>
+      </c>
+      <c r="C158" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D158" s="3">
+        <v>26</v>
+      </c>
+      <c r="E158" s="3">
+        <v>2600</v>
+      </c>
+    </row>
+    <row r="159" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A159" t="s">
+        <v>36</v>
+      </c>
+      <c r="B159" t="s">
+        <v>13</v>
+      </c>
+      <c r="C159" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D159" s="3">
+        <v>1</v>
+      </c>
+      <c r="E159" s="3">
+        <v>2600</v>
+      </c>
+    </row>
+    <row r="160" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A160" t="s">
+        <v>36</v>
+      </c>
+      <c r="B160" t="s">
+        <v>13</v>
+      </c>
+      <c r="C160" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D160" s="3">
+        <v>130</v>
+      </c>
+      <c r="E160" s="3">
+        <v>2600</v>
+      </c>
+    </row>
+    <row r="161" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A161" t="s">
+        <v>36</v>
+      </c>
+      <c r="B161" t="s">
+        <v>13</v>
+      </c>
+      <c r="C161" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D161">
+        <v>98</v>
+      </c>
+      <c r="E161" s="3">
+        <v>2600</v>
+      </c>
+    </row>
+    <row r="162" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A162" t="s">
+        <v>36</v>
+      </c>
+      <c r="B162" t="s">
+        <v>7</v>
+      </c>
+      <c r="C162" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D162" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E162" s="3">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="163" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A163" t="s">
+        <v>36</v>
+      </c>
+      <c r="B163" t="s">
+        <v>7</v>
+      </c>
+      <c r="C163" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D163" s="3">
+        <v>32</v>
+      </c>
+      <c r="E163" s="3">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="164" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A164" t="s">
+        <v>36</v>
+      </c>
+      <c r="B164" t="s">
+        <v>7</v>
+      </c>
+      <c r="C164" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D164" s="3">
+        <v>6</v>
+      </c>
+      <c r="E164" s="3">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="165" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A165" t="s">
+        <v>36</v>
+      </c>
+      <c r="B165" t="s">
+        <v>7</v>
+      </c>
+      <c r="C165" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D165" s="3">
+        <v>56</v>
+      </c>
+      <c r="E165" s="3">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="166" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A166" t="s">
+        <v>36</v>
+      </c>
+      <c r="B166" t="s">
+        <v>7</v>
+      </c>
+      <c r="C166" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D166">
+        <v>128</v>
+      </c>
+      <c r="E166" s="3">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="167" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A167" t="s">
+        <v>36</v>
+      </c>
+      <c r="B167" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C167" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D167" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E167" s="3">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="168" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A168" t="s">
+        <v>36</v>
+      </c>
+      <c r="B168" t="s">
+        <v>12</v>
+      </c>
+      <c r="C168" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D168" s="3">
+        <v>17</v>
+      </c>
+      <c r="E168" s="3">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="169" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A169" t="s">
+        <v>36</v>
+      </c>
+      <c r="B169" t="s">
+        <v>12</v>
+      </c>
+      <c r="C169" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D169" s="3">
+        <v>6</v>
+      </c>
+      <c r="E169" s="3">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="170" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A170" t="s">
+        <v>36</v>
+      </c>
+      <c r="B170" t="s">
+        <v>12</v>
+      </c>
+      <c r="C170" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D170" s="3">
+        <v>25</v>
+      </c>
+      <c r="E170" s="3">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="171" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A171" t="s">
+        <v>36</v>
+      </c>
+      <c r="B171" t="s">
+        <v>12</v>
+      </c>
+      <c r="C171" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D171">
+        <v>54</v>
+      </c>
+      <c r="E171" s="3">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="172" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A172" t="s">
+        <v>36</v>
+      </c>
+      <c r="B172" t="s">
+        <v>17</v>
+      </c>
+      <c r="C172" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D172" s="3">
+        <v>800</v>
+      </c>
+      <c r="E172" s="3">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="173" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A173" t="s">
+        <v>36</v>
+      </c>
+      <c r="B173" t="s">
+        <v>17</v>
+      </c>
+      <c r="C173" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D173" s="3">
+        <v>13</v>
+      </c>
+      <c r="E173" s="3">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="174" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A174" t="s">
+        <v>36</v>
+      </c>
+      <c r="B174" t="s">
+        <v>17</v>
+      </c>
+      <c r="C174" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D174" s="3">
+        <v>1</v>
+      </c>
+      <c r="E174" s="3">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="175" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A175" t="s">
+        <v>36</v>
+      </c>
+      <c r="B175" t="s">
+        <v>17</v>
+      </c>
+      <c r="C175" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D175" s="3">
+        <v>82</v>
+      </c>
+      <c r="E175" s="3">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="176" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A176" t="s">
+        <v>36</v>
+      </c>
+      <c r="B176" t="s">
+        <v>17</v>
+      </c>
+      <c r="C176" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D176">
+        <v>60</v>
+      </c>
+      <c r="E176" s="3">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="177" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A177" t="s">
+        <v>36</v>
+      </c>
+      <c r="B177" t="s">
+        <v>18</v>
+      </c>
+      <c r="C177" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D177" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E177" s="3">
+        <v>1100</v>
+      </c>
+    </row>
+    <row r="178" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A178" t="s">
+        <v>36</v>
+      </c>
+      <c r="B178" t="s">
+        <v>18</v>
+      </c>
+      <c r="C178" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D178" s="3">
+        <v>16</v>
+      </c>
+      <c r="E178" s="3">
+        <v>1100</v>
+      </c>
+    </row>
+    <row r="179" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A179" t="s">
+        <v>36</v>
+      </c>
+      <c r="B179" t="s">
+        <v>18</v>
+      </c>
+      <c r="C179" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D179" s="3">
+        <v>4</v>
+      </c>
+      <c r="E179" s="3">
+        <v>1100</v>
+      </c>
+    </row>
+    <row r="180" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A180" t="s">
+        <v>36</v>
+      </c>
+      <c r="B180" t="s">
+        <v>18</v>
+      </c>
+      <c r="C180" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D180" s="3">
+        <v>30</v>
+      </c>
+      <c r="E180" s="3">
+        <v>1100</v>
+      </c>
+    </row>
+    <row r="181" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A181" t="s">
+        <v>36</v>
+      </c>
+      <c r="B181" t="s">
+        <v>18</v>
+      </c>
+      <c r="C181" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D181">
+        <v>74</v>
+      </c>
+      <c r="E181" s="3">
+        <v>1100</v>
+      </c>
+    </row>
+    <row r="182" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A182" t="s">
+        <v>36</v>
+      </c>
+      <c r="B182" t="s">
+        <v>20</v>
+      </c>
+      <c r="C182" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D182" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E182" s="3">
+        <v>2200</v>
+      </c>
+    </row>
+    <row r="183" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A183" t="s">
+        <v>36</v>
+      </c>
+      <c r="B183" t="s">
+        <v>20</v>
+      </c>
+      <c r="C183" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D183" s="3">
+        <v>34</v>
+      </c>
+      <c r="E183" s="3">
+        <v>2200</v>
+      </c>
+    </row>
+    <row r="184" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A184" t="s">
+        <v>36</v>
+      </c>
+      <c r="B184" t="s">
+        <v>20</v>
+      </c>
+      <c r="C184" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D184" s="3">
+        <v>1</v>
+      </c>
+      <c r="E184" s="3">
+        <v>2200</v>
+      </c>
+    </row>
+    <row r="185" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A185" t="s">
+        <v>36</v>
+      </c>
+      <c r="B185" t="s">
+        <v>20</v>
+      </c>
+      <c r="C185" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D185" s="3">
+        <v>60</v>
+      </c>
+      <c r="E185" s="3">
+        <v>2200</v>
+      </c>
+    </row>
+    <row r="186" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A186" t="s">
+        <v>36</v>
+      </c>
+      <c r="B186" t="s">
+        <v>20</v>
+      </c>
+      <c r="C186" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D186">
+        <v>183</v>
+      </c>
+      <c r="E186" s="3">
+        <v>2200</v>
+      </c>
+    </row>
+    <row r="187" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A187" t="s">
+        <v>36</v>
+      </c>
+      <c r="B187" t="s">
+        <v>21</v>
+      </c>
+      <c r="C187" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D187" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E187" s="3">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="188" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A188" t="s">
+        <v>36</v>
+      </c>
+      <c r="B188" t="s">
+        <v>21</v>
+      </c>
+      <c r="C188" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D188" s="3">
+        <v>22</v>
+      </c>
+      <c r="E188" s="3">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="189" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A189" t="s">
+        <v>36</v>
+      </c>
+      <c r="B189" t="s">
+        <v>21</v>
+      </c>
+      <c r="C189" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D189" s="3">
+        <v>6</v>
+      </c>
+      <c r="E189" s="3">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="190" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A190" t="s">
+        <v>36</v>
+      </c>
+      <c r="B190" t="s">
+        <v>21</v>
+      </c>
+      <c r="C190" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D190" s="3">
+        <v>60</v>
+      </c>
+      <c r="E190" s="3">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="191" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A191" t="s">
+        <v>36</v>
+      </c>
+      <c r="B191" t="s">
+        <v>21</v>
+      </c>
+      <c r="C191" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D191">
+        <v>168</v>
+      </c>
+      <c r="E191" s="3">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="192" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A192" t="s">
+        <v>36</v>
+      </c>
+      <c r="B192" t="s">
+        <v>6</v>
+      </c>
+      <c r="C192" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D192" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E192" s="3">
+        <v>2200</v>
+      </c>
+    </row>
+    <row r="193" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A193" t="s">
+        <v>36</v>
+      </c>
+      <c r="B193" t="s">
+        <v>6</v>
+      </c>
+      <c r="C193" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D193" s="3">
+        <v>23</v>
+      </c>
+      <c r="E193" s="3">
+        <v>2200</v>
+      </c>
+    </row>
+    <row r="194" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A194" t="s">
+        <v>36</v>
+      </c>
+      <c r="B194" t="s">
+        <v>6</v>
+      </c>
+      <c r="C194" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D194" s="3">
+        <v>1</v>
+      </c>
+      <c r="E194" s="3">
+        <v>2200</v>
+      </c>
+    </row>
+    <row r="195" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A195" t="s">
+        <v>36</v>
+      </c>
+      <c r="B195" t="s">
+        <v>6</v>
+      </c>
+      <c r="C195" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D195" s="3">
+        <v>72</v>
+      </c>
+      <c r="E195" s="3">
+        <v>2200</v>
+      </c>
+    </row>
+    <row r="196" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A196" t="s">
+        <v>36</v>
+      </c>
+      <c r="B196" t="s">
+        <v>6</v>
+      </c>
+      <c r="C196" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D196">
+        <v>92</v>
+      </c>
+      <c r="E196" s="3">
+        <v>2200</v>
+      </c>
+    </row>
+    <row r="197" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A197" t="s">
+        <v>36</v>
+      </c>
+      <c r="B197" t="s">
+        <v>1</v>
+      </c>
+      <c r="C197" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D197" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E197" s="3">
+        <v>2850</v>
+      </c>
+    </row>
+    <row r="198" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A198" t="s">
+        <v>36</v>
+      </c>
+      <c r="B198" t="s">
+        <v>1</v>
+      </c>
+      <c r="C198" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D198" s="3">
+        <v>52</v>
+      </c>
+      <c r="E198" s="3">
+        <v>2850</v>
+      </c>
+    </row>
+    <row r="199" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A199" t="s">
+        <v>36</v>
+      </c>
+      <c r="B199" t="s">
+        <v>1</v>
+      </c>
+      <c r="C199" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D199" s="3">
+        <v>10</v>
+      </c>
+      <c r="E199" s="3">
+        <v>2850</v>
+      </c>
+    </row>
+    <row r="200" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A200" t="s">
+        <v>36</v>
+      </c>
+      <c r="B200" t="s">
+        <v>1</v>
+      </c>
+      <c r="C200" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D200" s="3">
+        <v>102</v>
+      </c>
+      <c r="E200" s="3">
+        <v>2850</v>
+      </c>
+    </row>
+    <row r="201" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A201" t="s">
+        <v>36</v>
+      </c>
+      <c r="B201" t="s">
+        <v>1</v>
+      </c>
+      <c r="C201" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D201">
+        <v>129</v>
+      </c>
+      <c r="E201" s="3">
+        <v>2850</v>
+      </c>
+    </row>
+    <row r="202" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A202" t="s">
+        <v>36</v>
+      </c>
+      <c r="B202" t="s">
+        <v>4</v>
+      </c>
+      <c r="C202" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D202">
+        <v>1500</v>
+      </c>
+      <c r="E202" s="3">
+        <v>3500</v>
+      </c>
+    </row>
+    <row r="203" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A203" t="s">
+        <v>36</v>
+      </c>
+      <c r="B203" t="s">
+        <v>4</v>
+      </c>
+      <c r="C203" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D203" s="3">
+        <v>62</v>
+      </c>
+      <c r="E203" s="3">
+        <v>3500</v>
+      </c>
+    </row>
+    <row r="204" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A204" t="s">
+        <v>36</v>
+      </c>
+      <c r="B204" t="s">
+        <v>4</v>
+      </c>
+      <c r="C204" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D204">
+        <v>10</v>
+      </c>
+      <c r="E204" s="3">
+        <v>3500</v>
+      </c>
+    </row>
+    <row r="205" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A205" t="s">
+        <v>36</v>
+      </c>
+      <c r="B205" t="s">
+        <v>4</v>
+      </c>
+      <c r="C205" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D205" s="3">
+        <v>124</v>
+      </c>
+      <c r="E205" s="3">
+        <v>3500</v>
+      </c>
+    </row>
+    <row r="206" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A206" t="s">
+        <v>36</v>
+      </c>
+      <c r="B206" t="s">
+        <v>4</v>
+      </c>
+      <c r="C206" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D206">
+        <v>183</v>
+      </c>
+      <c r="E206" s="3">
+        <v>3500</v>
+      </c>
+    </row>
+    <row r="207" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A207" t="s">
+        <v>36</v>
+      </c>
+      <c r="B207" t="s">
+        <v>11</v>
+      </c>
+      <c r="C207" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D207" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E207" s="3">
+        <v>3500</v>
+      </c>
+    </row>
+    <row r="208" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A208" t="s">
+        <v>36</v>
+      </c>
+      <c r="B208" t="s">
+        <v>11</v>
+      </c>
+      <c r="C208" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D208" s="3">
+        <v>78</v>
+      </c>
+      <c r="E208" s="3">
+        <v>3500</v>
+      </c>
+    </row>
+    <row r="209" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A209" t="s">
+        <v>36</v>
+      </c>
+      <c r="B209" t="s">
+        <v>11</v>
+      </c>
+      <c r="C209" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D209" s="3">
+        <v>16</v>
+      </c>
+      <c r="E209" s="3">
+        <v>3500</v>
+      </c>
+    </row>
+    <row r="210" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A210" t="s">
+        <v>36</v>
+      </c>
+      <c r="B210" t="s">
+        <v>11</v>
+      </c>
+      <c r="C210" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D210" s="3">
+        <v>96</v>
+      </c>
+      <c r="E210" s="3">
+        <v>3500</v>
+      </c>
+    </row>
+    <row r="211" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A211" t="s">
+        <v>36</v>
+      </c>
+      <c r="B211" t="s">
+        <v>11</v>
+      </c>
+      <c r="C211" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D211">
+        <v>198</v>
+      </c>
+      <c r="E211" s="3">
+        <v>3500</v>
+      </c>
+    </row>
+    <row r="212" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A212" t="s">
+        <v>36</v>
+      </c>
+      <c r="B212" t="s">
+        <v>14</v>
+      </c>
+      <c r="C212" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D212" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E212" s="3">
+        <v>2300</v>
+      </c>
+    </row>
+    <row r="213" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A213" t="s">
+        <v>36</v>
+      </c>
+      <c r="B213" t="s">
+        <v>14</v>
+      </c>
+      <c r="C213" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D213" s="3">
+        <v>44</v>
+      </c>
+      <c r="E213" s="3">
+        <v>2300</v>
+      </c>
+    </row>
+    <row r="214" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A214" t="s">
+        <v>36</v>
+      </c>
+      <c r="B214" t="s">
+        <v>14</v>
+      </c>
+      <c r="C214" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D214" s="3">
+        <v>10</v>
+      </c>
+      <c r="E214" s="3">
+        <v>2300</v>
+      </c>
+    </row>
+    <row r="215" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A215" t="s">
+        <v>36</v>
+      </c>
+      <c r="B215" t="s">
+        <v>14</v>
+      </c>
+      <c r="C215" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D215" s="3">
+        <v>72</v>
+      </c>
+      <c r="E215" s="3">
+        <v>2300</v>
+      </c>
+    </row>
+    <row r="216" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A216" t="s">
+        <v>36</v>
+      </c>
+      <c r="B216" t="s">
+        <v>14</v>
+      </c>
+      <c r="C216" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D216">
+        <v>151</v>
+      </c>
+      <c r="E216" s="3">
+        <v>2300</v>
+      </c>
+    </row>
+    <row r="217" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A217" t="s">
+        <v>36</v>
+      </c>
+      <c r="B217" t="s">
+        <v>16</v>
+      </c>
+      <c r="C217" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D217" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E217" s="3">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="218" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A218" t="s">
+        <v>36</v>
+      </c>
+      <c r="B218" t="s">
+        <v>16</v>
+      </c>
+      <c r="C218" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D218" s="3">
+        <v>120</v>
+      </c>
+      <c r="E218" s="3">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="219" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A219" t="s">
+        <v>36</v>
+      </c>
+      <c r="B219" t="s">
+        <v>16</v>
+      </c>
+      <c r="C219" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D219" s="3">
+        <v>14</v>
+      </c>
+      <c r="E219" s="3">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="220" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A220" t="s">
+        <v>36</v>
+      </c>
+      <c r="B220" t="s">
+        <v>16</v>
+      </c>
+      <c r="C220" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D220" s="3">
+        <v>236</v>
+      </c>
+      <c r="E220" s="3">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="221" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A221" t="s">
+        <v>36</v>
+      </c>
+      <c r="B221" t="s">
+        <v>16</v>
+      </c>
+      <c r="C221" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D221">
+        <v>192</v>
+      </c>
+      <c r="E221" s="3">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="222" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A222" t="s">
+        <v>36</v>
+      </c>
+      <c r="B222" t="s">
+        <v>19</v>
+      </c>
+      <c r="C222" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D222" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E222" s="3">
+        <v>2600</v>
+      </c>
+    </row>
+    <row r="223" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A223" t="s">
+        <v>36</v>
+      </c>
+      <c r="B223" t="s">
+        <v>19</v>
+      </c>
+      <c r="C223" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D223" s="3">
+        <v>62</v>
+      </c>
+      <c r="E223" s="3">
+        <v>2600</v>
+      </c>
+    </row>
+    <row r="224" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A224" t="s">
+        <v>36</v>
+      </c>
+      <c r="B224" t="s">
+        <v>19</v>
+      </c>
+      <c r="C224" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D224" s="3">
+        <v>11</v>
+      </c>
+      <c r="E224" s="3">
+        <v>2600</v>
+      </c>
+    </row>
+    <row r="225" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A225" t="s">
+        <v>36</v>
+      </c>
+      <c r="B225" t="s">
+        <v>19</v>
+      </c>
+      <c r="C225" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D225" s="3">
+        <v>74</v>
+      </c>
+      <c r="E225" s="3">
+        <v>2600</v>
+      </c>
+    </row>
+    <row r="226" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A226" t="s">
+        <v>36</v>
+      </c>
+      <c r="B226" t="s">
+        <v>19</v>
+      </c>
+      <c r="C226" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D226">
+        <v>181</v>
+      </c>
+      <c r="E226" s="3">
+        <v>2600</v>
+      </c>
+    </row>
+    <row r="227" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A227" t="s">
+        <v>36</v>
+      </c>
+      <c r="B227" t="s">
+        <v>15</v>
+      </c>
+      <c r="C227" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D227" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E227" s="3">
+        <v>2650</v>
+      </c>
+    </row>
+    <row r="228" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A228" t="s">
+        <v>36</v>
+      </c>
+      <c r="B228" t="s">
+        <v>15</v>
+      </c>
+      <c r="C228" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D228" s="3">
+        <v>30</v>
+      </c>
+      <c r="E228" s="3">
+        <v>2650</v>
+      </c>
+    </row>
+    <row r="229" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A229" t="s">
+        <v>36</v>
+      </c>
+      <c r="B229" t="s">
+        <v>15</v>
+      </c>
+      <c r="C229" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D229" s="3">
+        <v>10</v>
+      </c>
+      <c r="E229" s="3">
+        <v>2650</v>
+      </c>
+    </row>
+    <row r="230" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A230" t="s">
+        <v>36</v>
+      </c>
+      <c r="B230" t="s">
+        <v>15</v>
+      </c>
+      <c r="C230" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D230" s="3">
+        <v>92</v>
+      </c>
+      <c r="E230" s="3">
+        <v>2650</v>
+      </c>
+    </row>
+    <row r="231" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A231" t="s">
+        <v>36</v>
+      </c>
+      <c r="B231" t="s">
+        <v>15</v>
+      </c>
+      <c r="C231" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D231">
+        <v>126</v>
+      </c>
+      <c r="E231" s="3">
+        <v>2650</v>
+      </c>
+    </row>
+    <row r="232" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A232" t="s">
+        <v>36</v>
+      </c>
+      <c r="B232" t="s">
+        <v>32</v>
+      </c>
+      <c r="C232" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D232">
+        <v>27700</v>
+      </c>
+      <c r="E232" s="3">
+        <v>53800</v>
+      </c>
+    </row>
+    <row r="233" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A233" t="s">
+        <v>36</v>
+      </c>
+      <c r="B233" t="s">
+        <v>32</v>
+      </c>
+      <c r="C233" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D233">
+        <v>857</v>
+      </c>
+      <c r="E233" s="3">
+        <v>53800</v>
+      </c>
+    </row>
+    <row r="234" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A234" t="s">
+        <v>36</v>
+      </c>
+      <c r="B234" t="s">
+        <v>32</v>
+      </c>
+      <c r="C234" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D234">
+        <v>131</v>
+      </c>
+      <c r="E234" s="3">
+        <v>53800</v>
+      </c>
+    </row>
+    <row r="235" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A235" t="s">
+        <v>36</v>
+      </c>
+      <c r="B235" t="s">
+        <v>32</v>
+      </c>
+      <c r="C235" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D235" s="3">
+        <v>1858</v>
+      </c>
+      <c r="E235" s="3">
+        <v>53800</v>
+      </c>
+    </row>
+    <row r="236" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A236" t="s">
+        <v>36</v>
+      </c>
+      <c r="B236" t="s">
+        <v>32</v>
+      </c>
+      <c r="C236" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D236">
+        <v>2738</v>
+      </c>
+      <c r="E236" s="3">
+        <v>53800</v>
+      </c>
+    </row>
+    <row r="237" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A237" t="s">
+        <v>36</v>
+      </c>
+      <c r="B237" t="s">
         <v>35</v>
       </c>
-      <c r="C145" s="3" t="s">
+      <c r="C237" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D237" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E237" s="3">
+        <v>5700</v>
+      </c>
+    </row>
+    <row r="238" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A238" t="s">
+        <v>36</v>
+      </c>
+      <c r="B238" t="s">
+        <v>35</v>
+      </c>
+      <c r="C238" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D238">
+        <v>17</v>
+      </c>
+      <c r="E238" s="3">
+        <v>5700</v>
+      </c>
+    </row>
+    <row r="239" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A239" t="s">
+        <v>36</v>
+      </c>
+      <c r="B239" t="s">
+        <v>35</v>
+      </c>
+      <c r="C239" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D239" s="3">
+        <v>14</v>
+      </c>
+      <c r="E239" s="3">
+        <v>5700</v>
+      </c>
+    </row>
+    <row r="240" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A240" t="s">
+        <v>36</v>
+      </c>
+      <c r="B240" t="s">
+        <v>35</v>
+      </c>
+      <c r="C240" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D240" s="3">
+        <v>1858</v>
+      </c>
+      <c r="E240" s="3">
+        <v>5700</v>
+      </c>
+    </row>
+    <row r="241" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A241" t="s">
+        <v>36</v>
+      </c>
+      <c r="B241" t="s">
+        <v>35</v>
+      </c>
+      <c r="C241" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="D145">
+      <c r="D241">
         <v>192</v>
       </c>
-      <c r="E145" s="3">
+      <c r="E241" s="3">
         <v>5700</v>
       </c>
     </row>
-    <row r="146" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C146" s="3"/>
-      <c r="D146" s="3"/>
-      <c r="E146" s="3"/>
-    </row>
-    <row r="147" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C147" s="3"/>
-      <c r="E147" s="3"/>
-    </row>
-    <row r="148" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C148" s="3"/>
-      <c r="D148" s="3"/>
-      <c r="E148" s="3"/>
-    </row>
-    <row r="149" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C149" s="3"/>
-      <c r="E149" s="3"/>
-    </row>
-    <row r="150" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C150" s="3"/>
-      <c r="E150" s="3"/>
-    </row>
-    <row r="151" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C151" s="3"/>
-      <c r="E151" s="3"/>
-    </row>
-    <row r="152" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C152" s="3"/>
-      <c r="D152" s="3"/>
-      <c r="E152" s="3"/>
-    </row>
-    <row r="153" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C153" s="3"/>
-      <c r="E153" s="3"/>
-    </row>
-    <row r="154" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C154" s="3"/>
-      <c r="D154" s="3"/>
-      <c r="E154" s="3"/>
-    </row>
-    <row r="155" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C155" s="3"/>
-      <c r="E155" s="3"/>
-    </row>
-    <row r="156" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C156" s="3"/>
-      <c r="E156" s="3"/>
-    </row>
-    <row r="157" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C157" s="3"/>
-      <c r="E157" s="3"/>
-    </row>
-    <row r="158" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C158" s="3"/>
-      <c r="D158" s="3"/>
-      <c r="E158" s="3"/>
-    </row>
-    <row r="159" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C159" s="3"/>
-      <c r="E159" s="3"/>
-    </row>
-    <row r="160" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C160" s="3"/>
-      <c r="D160" s="3"/>
-      <c r="E160" s="3"/>
-    </row>
-    <row r="161" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="C161" s="3"/>
-      <c r="E161" s="3"/>
-    </row>
-    <row r="162" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="C162" s="3"/>
-      <c r="E162" s="3"/>
-    </row>
-    <row r="163" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="C163" s="3"/>
-      <c r="E163" s="3"/>
-    </row>
-    <row r="164" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="C164" s="3"/>
-      <c r="D164" s="3"/>
-      <c r="E164" s="3"/>
-    </row>
-    <row r="165" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="C165" s="3"/>
-      <c r="E165" s="3"/>
-    </row>
-    <row r="166" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="C166" s="3"/>
-      <c r="D166" s="3"/>
-      <c r="E166" s="3"/>
-    </row>
-    <row r="167" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="C167" s="3"/>
-      <c r="E167" s="3"/>
-    </row>
-    <row r="168" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="C168" s="3"/>
-      <c r="E168" s="3"/>
-    </row>
-    <row r="169" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="C169" s="3"/>
-      <c r="E169" s="3"/>
-    </row>
-    <row r="170" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B170" s="1"/>
-      <c r="C170" s="3"/>
-      <c r="D170" s="3"/>
-      <c r="E170" s="3"/>
-    </row>
-    <row r="171" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="C171" s="3"/>
-      <c r="E171" s="3"/>
-    </row>
-    <row r="172" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="C172" s="3"/>
-      <c r="D172" s="3"/>
-      <c r="E172" s="3"/>
-    </row>
-    <row r="173" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="C173" s="3"/>
-      <c r="E173" s="3"/>
-    </row>
-    <row r="174" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="C174" s="3"/>
-      <c r="E174" s="3"/>
-    </row>
-    <row r="175" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="C175" s="3"/>
-      <c r="E175" s="3"/>
-    </row>
-    <row r="176" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="C176" s="3"/>
-      <c r="D176" s="3"/>
-      <c r="E176" s="3"/>
-    </row>
-    <row r="177" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C177" s="3"/>
-      <c r="E177" s="3"/>
-    </row>
-    <row r="178" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C178" s="3"/>
-      <c r="D178" s="3"/>
-      <c r="E178" s="3"/>
-    </row>
-    <row r="179" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C179" s="3"/>
-      <c r="E179" s="3"/>
-    </row>
-    <row r="180" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C180" s="3"/>
-      <c r="E180" s="3"/>
-    </row>
-    <row r="181" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C181" s="3"/>
-      <c r="E181" s="3"/>
-    </row>
-    <row r="182" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C182" s="3"/>
-      <c r="D182" s="3"/>
-      <c r="E182" s="3"/>
-    </row>
-    <row r="183" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C183" s="3"/>
-      <c r="E183" s="3"/>
-    </row>
-    <row r="184" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C184" s="3"/>
-      <c r="D184" s="3"/>
-      <c r="E184" s="3"/>
-    </row>
-    <row r="185" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C185" s="3"/>
-      <c r="E185" s="3"/>
-    </row>
-    <row r="186" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C186" s="3"/>
-      <c r="E186" s="3"/>
-    </row>
-    <row r="187" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C187" s="3"/>
-      <c r="E187" s="3"/>
-    </row>
-    <row r="188" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C188" s="3"/>
-      <c r="D188" s="3"/>
-      <c r="E188" s="3"/>
-    </row>
-    <row r="189" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C189" s="3"/>
-      <c r="E189" s="3"/>
-    </row>
-    <row r="190" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C190" s="3"/>
-      <c r="D190" s="3"/>
-      <c r="E190" s="3"/>
-    </row>
-    <row r="191" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C191" s="3"/>
-      <c r="E191" s="3"/>
-    </row>
-    <row r="192" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C192" s="3"/>
-      <c r="E192" s="3"/>
-    </row>
-    <row r="193" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C193" s="3"/>
-      <c r="E193" s="3"/>
-    </row>
-    <row r="194" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C194" s="3"/>
-      <c r="D194" s="3"/>
-      <c r="E194" s="3"/>
-    </row>
-    <row r="195" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C195" s="3"/>
-      <c r="E195" s="3"/>
-    </row>
-    <row r="196" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C196" s="3"/>
-      <c r="D196" s="3"/>
-      <c r="E196" s="3"/>
-    </row>
-    <row r="197" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C197" s="3"/>
-      <c r="E197" s="3"/>
-    </row>
-    <row r="198" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C198" s="3"/>
-      <c r="E198" s="3"/>
-    </row>
-    <row r="199" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C199" s="3"/>
-      <c r="E199" s="3"/>
-    </row>
-    <row r="200" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C200" s="3"/>
-      <c r="D200" s="3"/>
-      <c r="E200" s="3"/>
-    </row>
-    <row r="201" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C201" s="3"/>
-      <c r="E201" s="3"/>
-    </row>
-    <row r="202" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C202" s="3"/>
-      <c r="D202" s="3"/>
-      <c r="E202" s="3"/>
-    </row>
-    <row r="203" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C203" s="3"/>
-      <c r="E203" s="3"/>
-    </row>
-    <row r="204" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C204" s="3"/>
-      <c r="E204" s="3"/>
-    </row>
-    <row r="205" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C205" s="3"/>
-      <c r="E205" s="3"/>
-    </row>
-    <row r="206" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C206" s="3"/>
-      <c r="D206" s="3"/>
-      <c r="E206" s="3"/>
-    </row>
-    <row r="207" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C207" s="3"/>
-      <c r="E207" s="3"/>
-    </row>
-    <row r="208" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C208" s="3"/>
-      <c r="D208" s="3"/>
-      <c r="E208" s="3"/>
-    </row>
-    <row r="209" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C209" s="3"/>
-      <c r="E209" s="3"/>
-    </row>
-    <row r="210" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C210" s="3"/>
-      <c r="E210" s="3"/>
-    </row>
-    <row r="211" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C211" s="3"/>
-      <c r="E211" s="3"/>
-    </row>
-    <row r="212" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C212" s="3"/>
-      <c r="E212" s="3"/>
-    </row>
-    <row r="213" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C213" s="3"/>
-      <c r="E213" s="3"/>
-    </row>
-    <row r="214" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C214" s="3"/>
-      <c r="E214" s="3"/>
-    </row>
-    <row r="215" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C215" s="3"/>
-      <c r="E215" s="3"/>
-    </row>
-    <row r="216" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C216" s="3"/>
-      <c r="E216" s="3"/>
-    </row>
-    <row r="217" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C217" s="3"/>
-      <c r="E217" s="3"/>
-    </row>
-    <row r="218" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C218" s="3"/>
-      <c r="D218" s="3"/>
-      <c r="E218" s="3"/>
-    </row>
-    <row r="219" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C219" s="3"/>
-      <c r="E219" s="3"/>
-    </row>
-    <row r="220" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C220" s="3"/>
-      <c r="D220" s="3"/>
-      <c r="E220" s="3"/>
-    </row>
-    <row r="221" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C221" s="3"/>
-      <c r="E221" s="3"/>
-    </row>
-    <row r="222" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C222" s="3"/>
-      <c r="E222" s="3"/>
-    </row>
-    <row r="223" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C223" s="3"/>
-      <c r="E223" s="3"/>
-    </row>
-    <row r="224" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C224" s="3"/>
-      <c r="D224" s="3"/>
-      <c r="E224" s="3"/>
-    </row>
-    <row r="225" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C225" s="3"/>
-      <c r="E225" s="3"/>
-    </row>
-    <row r="226" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C226" s="3"/>
-      <c r="D226" s="3"/>
-      <c r="E226" s="3"/>
-    </row>
-    <row r="227" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C227" s="3"/>
-      <c r="E227" s="3"/>
-    </row>
-    <row r="228" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C228" s="3"/>
-      <c r="E228" s="3"/>
-    </row>
-    <row r="229" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C229" s="3"/>
-      <c r="E229" s="3"/>
-    </row>
-    <row r="230" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C230" s="3"/>
-      <c r="D230" s="3"/>
-      <c r="E230" s="3"/>
-    </row>
-    <row r="231" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C231" s="3"/>
-      <c r="E231" s="3"/>
-    </row>
-    <row r="232" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C232" s="3"/>
-      <c r="D232" s="3"/>
-      <c r="E232" s="3"/>
-    </row>
-    <row r="233" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C233" s="3"/>
-      <c r="E233" s="3"/>
-    </row>
-    <row r="234" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C234" s="3"/>
-      <c r="E234" s="3"/>
-    </row>
-    <row r="235" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C235" s="3"/>
-      <c r="E235" s="3"/>
-    </row>
-    <row r="236" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C236" s="3"/>
-      <c r="D236" s="3"/>
-      <c r="E236" s="3"/>
-    </row>
-    <row r="237" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C237" s="3"/>
-      <c r="E237" s="3"/>
-    </row>
-    <row r="238" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C238" s="3"/>
-      <c r="D238" s="3"/>
-      <c r="E238" s="3"/>
-    </row>
-    <row r="239" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C239" s="3"/>
-      <c r="E239" s="3"/>
-    </row>
-    <row r="240" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C240" s="3"/>
-      <c r="E240" s="3"/>
-    </row>
-    <row r="241" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C241" s="3"/>
-      <c r="E241" s="3"/>
-    </row>
-    <row r="242" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C242" s="3"/>
-      <c r="D242" s="3"/>
-      <c r="E242" s="3"/>
-    </row>
-    <row r="243" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C243" s="3"/>
-      <c r="E243" s="3"/>
-    </row>
-    <row r="244" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C244" s="3"/>
-      <c r="D244" s="3"/>
-      <c r="E244" s="3"/>
-    </row>
-    <row r="245" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C245" s="3"/>
-      <c r="E245" s="3"/>
-    </row>
-    <row r="246" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C246" s="3"/>
-      <c r="E246" s="3"/>
-    </row>
-    <row r="247" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C247" s="3"/>
-      <c r="E247" s="3"/>
-    </row>
-    <row r="248" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C248" s="3"/>
-      <c r="E248" s="3"/>
-    </row>
-    <row r="249" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C249" s="3"/>
-      <c r="E249" s="3"/>
-    </row>
-    <row r="250" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C250" s="3"/>
-      <c r="E250" s="3"/>
-    </row>
-    <row r="251" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C251" s="3"/>
-      <c r="E251" s="3"/>
-    </row>
-    <row r="252" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C252" s="3"/>
-      <c r="E252" s="3"/>
-    </row>
-    <row r="253" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C253" s="3"/>
-      <c r="E253" s="3"/>
-    </row>
   </sheetData>
-  <autoFilter ref="B1:E145" xr:uid="{6956BB2C-DA9E-4412-BCD4-BB80A11153FE}"/>
+  <autoFilter ref="A1:E241" xr:uid="{6956BB2C-DA9E-4412-BCD4-BB80A11153FE}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/data/metas.xlsx
+++ b/data/metas.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sercomunicaciones2-my.sharepoint.com/personal/auxcomisiones_sercomunicaciones_com/Documents/PAOLA/AUXCOMISIÓN/3 Liquidación CVS comerciales/2026/02 Febrero/Liquidacióncvs/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sercomunicaciones2-my.sharepoint.com/personal/auxcomisiones_sercomunicaciones_com/Documents/PAOLA/Liquidacióncvs/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="625" documentId="8_{787D9E49-702D-43BD-B99B-4B64F775E77B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FD909384-53D5-4AC4-8A39-627982AAB964}"/>
+  <xr:revisionPtr revIDLastSave="514" documentId="8_{787D9E49-702D-43BD-B99B-4B64F775E77B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{212945BE-825C-4D35-AD01-AE528E1CC2B2}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D1391136-BBFC-43C7-B899-B77B0ECC5956}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$B$1:$E$145</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$B$1:$E$133</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="437" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="437" uniqueCount="36">
   <si>
     <t>BARBOSA</t>
   </si>
@@ -132,6 +132,9 @@
   </si>
   <si>
     <t>OTROS</t>
+  </si>
+  <si>
+    <t>FOCO</t>
   </si>
   <si>
     <t>GENERAL</t>
@@ -546,7 +549,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6956BB2C-DA9E-4412-BCD4-BB80A11153FE}">
-  <dimension ref="A1:E253"/>
+  <dimension ref="A1:E277"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.7109375" bestFit="1" customWidth="1"/>
@@ -557,7 +560,7 @@
   <sheetData>
     <row r="1" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>23</v>
@@ -574,7 +577,7 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>5</v>
@@ -591,7 +594,7 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>5</v>
@@ -608,7 +611,7 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>5</v>
@@ -625,7 +628,7 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>5</v>
@@ -634,7 +637,7 @@
         <v>29</v>
       </c>
       <c r="D5" s="3">
-        <v>66</v>
+        <v>95</v>
       </c>
       <c r="E5" s="3">
         <v>2800</v>
@@ -642,13 +645,13 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>5</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D6" s="3">
         <v>29</v>
@@ -659,7 +662,7 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>5</v>
@@ -676,7 +679,7 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>0</v>
@@ -693,7 +696,7 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>0</v>
@@ -710,7 +713,7 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>0</v>
@@ -727,7 +730,7 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>0</v>
@@ -735,8 +738,8 @@
       <c r="C11" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="D11" s="3">
-        <v>57</v>
+      <c r="D11">
+        <v>82</v>
       </c>
       <c r="E11" s="3">
         <v>2400</v>
@@ -744,13 +747,13 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>0</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D12">
         <v>25</v>
@@ -761,7 +764,7 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>0</v>
@@ -778,7 +781,7 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B14" t="s">
         <v>2</v>
@@ -795,7 +798,7 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B15" t="s">
         <v>2</v>
@@ -812,7 +815,7 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B16" t="s">
         <v>2</v>
@@ -829,7 +832,7 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B17" t="s">
         <v>2</v>
@@ -837,8 +840,8 @@
       <c r="C17" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="D17" s="3">
-        <v>35</v>
+      <c r="D17">
+        <v>50</v>
       </c>
       <c r="E17" s="3">
         <v>1350</v>
@@ -846,13 +849,13 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B18" t="s">
         <v>2</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D18">
         <v>15</v>
@@ -863,7 +866,7 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B19" t="s">
         <v>2</v>
@@ -880,7 +883,7 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B20" t="s">
         <v>3</v>
@@ -897,7 +900,7 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B21" t="s">
         <v>3</v>
@@ -914,7 +917,7 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B22" t="s">
         <v>3</v>
@@ -931,7 +934,7 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B23" t="s">
         <v>3</v>
@@ -939,8 +942,8 @@
       <c r="C23" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="D23" s="3">
-        <v>45</v>
+      <c r="D23">
+        <v>65</v>
       </c>
       <c r="E23" s="3">
         <v>1700</v>
@@ -948,13 +951,13 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B24" t="s">
         <v>3</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D24">
         <v>20</v>
@@ -965,7 +968,7 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B25" t="s">
         <v>3</v>
@@ -982,7 +985,7 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B26" t="s">
         <v>8</v>
@@ -999,7 +1002,7 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B27" t="s">
         <v>8</v>
@@ -1016,7 +1019,7 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B28" t="s">
         <v>8</v>
@@ -1033,7 +1036,7 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B29" t="s">
         <v>8</v>
@@ -1041,8 +1044,8 @@
       <c r="C29" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="D29" s="3">
-        <v>35</v>
+      <c r="D29">
+        <v>50</v>
       </c>
       <c r="E29" s="3">
         <v>1450</v>
@@ -1050,13 +1053,13 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B30" t="s">
         <v>8</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D30">
         <v>15</v>
@@ -1067,7 +1070,7 @@
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B31" t="s">
         <v>8</v>
@@ -1084,7 +1087,7 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B32" t="s">
         <v>10</v>
@@ -1101,7 +1104,7 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B33" t="s">
         <v>10</v>
@@ -1118,7 +1121,7 @@
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B34" t="s">
         <v>10</v>
@@ -1135,7 +1138,7 @@
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B35" t="s">
         <v>10</v>
@@ -1143,8 +1146,8 @@
       <c r="C35" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="D35" s="3">
-        <v>31</v>
+      <c r="D35">
+        <v>45</v>
       </c>
       <c r="E35" s="3">
         <v>1500</v>
@@ -1152,13 +1155,13 @@
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B36" t="s">
         <v>10</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D36">
         <v>14</v>
@@ -1169,7 +1172,7 @@
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B37" t="s">
         <v>10</v>
@@ -1186,7 +1189,7 @@
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B38" t="s">
         <v>9</v>
@@ -1203,7 +1206,7 @@
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B39" t="s">
         <v>9</v>
@@ -1220,7 +1223,7 @@
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B40" t="s">
         <v>9</v>
@@ -1237,7 +1240,7 @@
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B41" t="s">
         <v>9</v>
@@ -1245,8 +1248,8 @@
       <c r="C41" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="D41" s="3">
-        <v>112</v>
+      <c r="D41">
+        <v>160</v>
       </c>
       <c r="E41" s="3">
         <v>4000</v>
@@ -1254,13 +1257,13 @@
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B42" t="s">
         <v>9</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D42">
         <v>48</v>
@@ -1271,7 +1274,7 @@
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B43" t="s">
         <v>9</v>
@@ -1288,7 +1291,7 @@
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B44" t="s">
         <v>13</v>
@@ -1305,7 +1308,7 @@
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B45" t="s">
         <v>13</v>
@@ -1322,7 +1325,7 @@
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B46" t="s">
         <v>13</v>
@@ -1339,7 +1342,7 @@
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B47" t="s">
         <v>13</v>
@@ -1347,8 +1350,8 @@
       <c r="C47" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="D47" s="3">
-        <v>98</v>
+      <c r="D47">
+        <v>140</v>
       </c>
       <c r="E47" s="3">
         <v>2600</v>
@@ -1356,13 +1359,13 @@
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B48" t="s">
         <v>13</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D48">
         <v>42</v>
@@ -1373,7 +1376,7 @@
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B49" t="s">
         <v>13</v>
@@ -1390,7 +1393,7 @@
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B50" t="s">
         <v>7</v>
@@ -1407,7 +1410,7 @@
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B51" t="s">
         <v>7</v>
@@ -1424,7 +1427,7 @@
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B52" t="s">
         <v>7</v>
@@ -1441,7 +1444,7 @@
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B53" t="s">
         <v>7</v>
@@ -1449,8 +1452,8 @@
       <c r="C53" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="D53" s="3">
-        <v>39</v>
+      <c r="D53">
+        <v>56</v>
       </c>
       <c r="E53" s="3">
         <v>2000</v>
@@ -1458,13 +1461,13 @@
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B54" t="s">
         <v>7</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D54">
         <v>17</v>
@@ -1475,7 +1478,7 @@
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B55" t="s">
         <v>7</v>
@@ -1492,7 +1495,7 @@
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>12</v>
@@ -1509,7 +1512,7 @@
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B57" t="s">
         <v>12</v>
@@ -1526,7 +1529,7 @@
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B58" t="s">
         <v>12</v>
@@ -1543,7 +1546,7 @@
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B59" t="s">
         <v>12</v>
@@ -1551,8 +1554,8 @@
       <c r="C59" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="D59" s="3">
-        <v>17</v>
+      <c r="D59">
+        <v>25</v>
       </c>
       <c r="E59" s="3">
         <v>1500</v>
@@ -1560,13 +1563,13 @@
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B60" t="s">
         <v>12</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D60">
         <v>8</v>
@@ -1577,7 +1580,7 @@
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B61" t="s">
         <v>12</v>
@@ -1594,7 +1597,7 @@
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B62" t="s">
         <v>17</v>
@@ -1611,7 +1614,7 @@
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B63" t="s">
         <v>17</v>
@@ -1628,7 +1631,7 @@
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B64" t="s">
         <v>17</v>
@@ -1645,7 +1648,7 @@
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B65" t="s">
         <v>17</v>
@@ -1653,8 +1656,8 @@
       <c r="C65" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="D65" s="3">
-        <v>57</v>
+      <c r="D65">
+        <v>82</v>
       </c>
       <c r="E65" s="3">
         <v>2000</v>
@@ -1662,13 +1665,13 @@
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B66" t="s">
         <v>17</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D66">
         <v>25</v>
@@ -1679,7 +1682,7 @@
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B67" t="s">
         <v>17</v>
@@ -1696,7 +1699,7 @@
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B68" t="s">
         <v>18</v>
@@ -1713,7 +1716,7 @@
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B69" t="s">
         <v>18</v>
@@ -1730,7 +1733,7 @@
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B70" t="s">
         <v>18</v>
@@ -1747,7 +1750,7 @@
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B71" t="s">
         <v>18</v>
@@ -1755,8 +1758,8 @@
       <c r="C71" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="D71" s="3">
-        <v>21</v>
+      <c r="D71">
+        <v>30</v>
       </c>
       <c r="E71" s="3">
         <v>1100</v>
@@ -1764,13 +1767,13 @@
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B72" t="s">
         <v>18</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D72">
         <v>9</v>
@@ -1781,7 +1784,7 @@
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B73" t="s">
         <v>18</v>
@@ -1798,7 +1801,7 @@
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B74" t="s">
         <v>20</v>
@@ -1815,7 +1818,7 @@
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B75" t="s">
         <v>20</v>
@@ -1832,7 +1835,7 @@
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B76" t="s">
         <v>20</v>
@@ -1849,7 +1852,7 @@
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B77" t="s">
         <v>20</v>
@@ -1857,8 +1860,8 @@
       <c r="C77" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="D77" s="3">
-        <v>42</v>
+      <c r="D77">
+        <v>60</v>
       </c>
       <c r="E77" s="3">
         <v>2200</v>
@@ -1866,13 +1869,13 @@
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B78" t="s">
         <v>20</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D78">
         <v>18</v>
@@ -1883,7 +1886,7 @@
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B79" t="s">
         <v>20</v>
@@ -1900,7 +1903,7 @@
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B80" t="s">
         <v>21</v>
@@ -1917,7 +1920,7 @@
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B81" t="s">
         <v>21</v>
@@ -1934,7 +1937,7 @@
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B82" t="s">
         <v>21</v>
@@ -1951,7 +1954,7 @@
     </row>
     <row r="83" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B83" t="s">
         <v>21</v>
@@ -1959,8 +1962,8 @@
       <c r="C83" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="D83" s="3">
-        <v>42</v>
+      <c r="D83">
+        <v>60</v>
       </c>
       <c r="E83" s="3">
         <v>1600</v>
@@ -1968,13 +1971,13 @@
     </row>
     <row r="84" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B84" t="s">
         <v>21</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D84">
         <v>18</v>
@@ -1985,7 +1988,7 @@
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B85" t="s">
         <v>21</v>
@@ -2002,7 +2005,7 @@
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B86" t="s">
         <v>6</v>
@@ -2019,7 +2022,7 @@
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B87" t="s">
         <v>6</v>
@@ -2036,7 +2039,7 @@
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B88" t="s">
         <v>6</v>
@@ -2053,7 +2056,7 @@
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B89" t="s">
         <v>6</v>
@@ -2061,8 +2064,8 @@
       <c r="C89" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="D89" s="3">
-        <v>50</v>
+      <c r="D89">
+        <v>72</v>
       </c>
       <c r="E89" s="3">
         <v>2200</v>
@@ -2070,13 +2073,13 @@
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B90" t="s">
         <v>6</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D90">
         <v>22</v>
@@ -2087,7 +2090,7 @@
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B91" t="s">
         <v>6</v>
@@ -2104,7 +2107,7 @@
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B92" t="s">
         <v>1</v>
@@ -2121,7 +2124,7 @@
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B93" t="s">
         <v>1</v>
@@ -2138,7 +2141,7 @@
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B94" t="s">
         <v>1</v>
@@ -2155,7 +2158,7 @@
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B95" t="s">
         <v>1</v>
@@ -2163,8 +2166,8 @@
       <c r="C95" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="D95" s="3">
-        <v>71</v>
+      <c r="D95">
+        <v>102</v>
       </c>
       <c r="E95" s="3">
         <v>2850</v>
@@ -2172,13 +2175,13 @@
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B96" t="s">
         <v>1</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D96">
         <v>31</v>
@@ -2189,7 +2192,7 @@
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B97" t="s">
         <v>1</v>
@@ -2206,7 +2209,7 @@
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B98" t="s">
         <v>4</v>
@@ -2223,7 +2226,7 @@
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B99" t="s">
         <v>4</v>
@@ -2240,7 +2243,7 @@
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B100" t="s">
         <v>4</v>
@@ -2257,7 +2260,7 @@
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B101" t="s">
         <v>4</v>
@@ -2265,8 +2268,8 @@
       <c r="C101" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="D101" s="3">
-        <v>87</v>
+      <c r="D101">
+        <v>124</v>
       </c>
       <c r="E101" s="3">
         <v>3500</v>
@@ -2274,13 +2277,13 @@
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B102" t="s">
         <v>4</v>
       </c>
       <c r="C102" s="3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D102">
         <v>37</v>
@@ -2291,7 +2294,7 @@
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B103" t="s">
         <v>4</v>
@@ -2308,7 +2311,7 @@
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B104" t="s">
         <v>11</v>
@@ -2325,7 +2328,7 @@
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B105" t="s">
         <v>11</v>
@@ -2342,7 +2345,7 @@
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B106" t="s">
         <v>11</v>
@@ -2359,7 +2362,7 @@
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B107" t="s">
         <v>11</v>
@@ -2367,8 +2370,8 @@
       <c r="C107" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="D107" s="3">
-        <v>67</v>
+      <c r="D107">
+        <v>96</v>
       </c>
       <c r="E107" s="3">
         <v>3500</v>
@@ -2376,13 +2379,13 @@
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B108" t="s">
         <v>11</v>
       </c>
       <c r="C108" s="3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D108">
         <v>29</v>
@@ -2393,7 +2396,7 @@
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B109" t="s">
         <v>11</v>
@@ -2410,7 +2413,7 @@
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B110" t="s">
         <v>14</v>
@@ -2427,7 +2430,7 @@
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B111" t="s">
         <v>14</v>
@@ -2444,7 +2447,7 @@
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B112" t="s">
         <v>14</v>
@@ -2461,7 +2464,7 @@
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B113" t="s">
         <v>14</v>
@@ -2469,8 +2472,8 @@
       <c r="C113" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="D113" s="3">
-        <v>50</v>
+      <c r="D113">
+        <v>72</v>
       </c>
       <c r="E113" s="3">
         <v>2300</v>
@@ -2478,13 +2481,13 @@
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B114" t="s">
         <v>14</v>
       </c>
       <c r="C114" s="3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D114">
         <v>22</v>
@@ -2495,7 +2498,7 @@
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B115" t="s">
         <v>14</v>
@@ -2512,7 +2515,7 @@
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B116" t="s">
         <v>16</v>
@@ -2529,7 +2532,7 @@
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B117" t="s">
         <v>16</v>
@@ -2546,7 +2549,7 @@
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B118" t="s">
         <v>16</v>
@@ -2563,7 +2566,7 @@
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B119" t="s">
         <v>16</v>
@@ -2571,8 +2574,8 @@
       <c r="C119" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="D119" s="3">
-        <v>165</v>
+      <c r="D119">
+        <v>236</v>
       </c>
       <c r="E119" s="3">
         <v>5700</v>
@@ -2580,13 +2583,13 @@
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B120" t="s">
         <v>16</v>
       </c>
       <c r="C120" s="3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D120">
         <v>71</v>
@@ -2597,7 +2600,7 @@
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B121" t="s">
         <v>16</v>
@@ -2614,7 +2617,7 @@
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B122" t="s">
         <v>19</v>
@@ -2631,7 +2634,7 @@
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B123" t="s">
         <v>19</v>
@@ -2648,7 +2651,7 @@
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B124" t="s">
         <v>19</v>
@@ -2665,7 +2668,7 @@
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B125" t="s">
         <v>19</v>
@@ -2673,8 +2676,8 @@
       <c r="C125" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="D125" s="3">
-        <v>52</v>
+      <c r="D125">
+        <v>74</v>
       </c>
       <c r="E125" s="3">
         <v>2600</v>
@@ -2682,13 +2685,13 @@
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B126" t="s">
         <v>19</v>
       </c>
       <c r="C126" s="3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D126">
         <v>22</v>
@@ -2699,7 +2702,7 @@
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B127" t="s">
         <v>19</v>
@@ -2716,7 +2719,7 @@
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B128" t="s">
         <v>15</v>
@@ -2733,7 +2736,7 @@
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B129" t="s">
         <v>15</v>
@@ -2750,7 +2753,7 @@
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B130" t="s">
         <v>15</v>
@@ -2767,7 +2770,7 @@
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B131" t="s">
         <v>15</v>
@@ -2775,8 +2778,8 @@
       <c r="C131" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="D131" s="3">
-        <v>64</v>
+      <c r="D131">
+        <v>92</v>
       </c>
       <c r="E131" s="3">
         <v>2650</v>
@@ -2784,13 +2787,13 @@
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B132" t="s">
         <v>15</v>
       </c>
       <c r="C132" s="3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D132">
         <v>28</v>
@@ -2801,7 +2804,7 @@
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B133" t="s">
         <v>15</v>
@@ -2818,10 +2821,10 @@
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B134" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C134" s="3" t="s">
         <v>22</v>
@@ -2835,10 +2838,10 @@
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B135" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C135" s="3" t="s">
         <v>27</v>
@@ -2852,10 +2855,10 @@
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B136" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C136" s="3" t="s">
         <v>28</v>
@@ -2869,16 +2872,16 @@
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B137" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C137" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="D137" s="3">
-        <v>1303</v>
+      <c r="D137">
+        <v>1868</v>
       </c>
       <c r="E137" s="3">
         <v>53500</v>
@@ -2886,13 +2889,13 @@
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B138" t="s">
+        <v>32</v>
+      </c>
+      <c r="C138" s="3" t="s">
         <v>31</v>
-      </c>
-      <c r="C138" s="3" t="s">
-        <v>29</v>
       </c>
       <c r="D138">
         <v>565</v>
@@ -2903,10 +2906,10 @@
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B139" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C139" s="3" t="s">
         <v>30</v>
@@ -2920,10 +2923,10 @@
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B140" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C140" s="3" t="s">
         <v>22</v>
@@ -2937,10 +2940,10 @@
     </row>
     <row r="141" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B141" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C141" s="3" t="s">
         <v>27</v>
@@ -2954,10 +2957,10 @@
     </row>
     <row r="142" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B142" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C142" s="3" t="s">
         <v>28</v>
@@ -2971,16 +2974,16 @@
     </row>
     <row r="143" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B143" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C143" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="D143" s="3">
-        <v>1303</v>
+      <c r="D143">
+        <v>236</v>
       </c>
       <c r="E143" s="3">
         <v>5700</v>
@@ -2988,13 +2991,13 @@
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B144" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C144" s="3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D144">
         <v>71</v>
@@ -3005,10 +3008,10 @@
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B145" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C145" s="3" t="s">
         <v>30</v>
@@ -3021,28 +3024,35 @@
       </c>
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B146" s="3"/>
       <c r="C146" s="3"/>
       <c r="D146" s="3"/>
       <c r="E146" s="3"/>
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B147" s="3"/>
       <c r="C147" s="3"/>
+      <c r="D147" s="3"/>
       <c r="E147" s="3"/>
     </row>
     <row r="148" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B148" s="3"/>
       <c r="C148" s="3"/>
       <c r="D148" s="3"/>
       <c r="E148" s="3"/>
     </row>
     <row r="149" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B149" s="3"/>
       <c r="C149" s="3"/>
       <c r="E149" s="3"/>
     </row>
     <row r="150" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B150" s="3"/>
       <c r="C150" s="3"/>
       <c r="E150" s="3"/>
     </row>
     <row r="151" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B151" s="3"/>
       <c r="C151" s="3"/>
       <c r="E151" s="3"/>
     </row>
@@ -3086,72 +3096,71 @@
       <c r="D160" s="3"/>
       <c r="E160" s="3"/>
     </row>
-    <row r="161" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="161" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C161" s="3"/>
       <c r="E161" s="3"/>
     </row>
-    <row r="162" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="162" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C162" s="3"/>
       <c r="E162" s="3"/>
     </row>
-    <row r="163" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="163" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C163" s="3"/>
       <c r="E163" s="3"/>
     </row>
-    <row r="164" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="164" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C164" s="3"/>
       <c r="D164" s="3"/>
       <c r="E164" s="3"/>
     </row>
-    <row r="165" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="165" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C165" s="3"/>
       <c r="E165" s="3"/>
     </row>
-    <row r="166" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="166" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C166" s="3"/>
       <c r="D166" s="3"/>
       <c r="E166" s="3"/>
     </row>
-    <row r="167" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="167" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C167" s="3"/>
       <c r="E167" s="3"/>
     </row>
-    <row r="168" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="168" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C168" s="3"/>
       <c r="E168" s="3"/>
     </row>
-    <row r="169" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="169" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C169" s="3"/>
       <c r="E169" s="3"/>
     </row>
-    <row r="170" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B170" s="1"/>
+    <row r="170" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C170" s="3"/>
       <c r="D170" s="3"/>
       <c r="E170" s="3"/>
     </row>
-    <row r="171" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="171" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C171" s="3"/>
       <c r="E171" s="3"/>
     </row>
-    <row r="172" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="172" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C172" s="3"/>
       <c r="D172" s="3"/>
       <c r="E172" s="3"/>
     </row>
-    <row r="173" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="173" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C173" s="3"/>
       <c r="E173" s="3"/>
     </row>
-    <row r="174" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="174" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C174" s="3"/>
       <c r="E174" s="3"/>
     </row>
-    <row r="175" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="175" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C175" s="3"/>
       <c r="E175" s="3"/>
     </row>
-    <row r="176" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="176" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C176" s="3"/>
       <c r="D176" s="3"/>
       <c r="E176" s="3"/>
@@ -3225,72 +3234,73 @@
       <c r="C192" s="3"/>
       <c r="E192" s="3"/>
     </row>
-    <row r="193" spans="3:5" x14ac:dyDescent="0.25">
+    <row r="193" spans="2:5" x14ac:dyDescent="0.25">
       <c r="C193" s="3"/>
       <c r="E193" s="3"/>
     </row>
-    <row r="194" spans="3:5" x14ac:dyDescent="0.25">
+    <row r="194" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B194" s="1"/>
       <c r="C194" s="3"/>
       <c r="D194" s="3"/>
       <c r="E194" s="3"/>
     </row>
-    <row r="195" spans="3:5" x14ac:dyDescent="0.25">
+    <row r="195" spans="2:5" x14ac:dyDescent="0.25">
       <c r="C195" s="3"/>
       <c r="E195" s="3"/>
     </row>
-    <row r="196" spans="3:5" x14ac:dyDescent="0.25">
+    <row r="196" spans="2:5" x14ac:dyDescent="0.25">
       <c r="C196" s="3"/>
       <c r="D196" s="3"/>
       <c r="E196" s="3"/>
     </row>
-    <row r="197" spans="3:5" x14ac:dyDescent="0.25">
+    <row r="197" spans="2:5" x14ac:dyDescent="0.25">
       <c r="C197" s="3"/>
       <c r="E197" s="3"/>
     </row>
-    <row r="198" spans="3:5" x14ac:dyDescent="0.25">
+    <row r="198" spans="2:5" x14ac:dyDescent="0.25">
       <c r="C198" s="3"/>
       <c r="E198" s="3"/>
     </row>
-    <row r="199" spans="3:5" x14ac:dyDescent="0.25">
+    <row r="199" spans="2:5" x14ac:dyDescent="0.25">
       <c r="C199" s="3"/>
       <c r="E199" s="3"/>
     </row>
-    <row r="200" spans="3:5" x14ac:dyDescent="0.25">
+    <row r="200" spans="2:5" x14ac:dyDescent="0.25">
       <c r="C200" s="3"/>
       <c r="D200" s="3"/>
       <c r="E200" s="3"/>
     </row>
-    <row r="201" spans="3:5" x14ac:dyDescent="0.25">
+    <row r="201" spans="2:5" x14ac:dyDescent="0.25">
       <c r="C201" s="3"/>
       <c r="E201" s="3"/>
     </row>
-    <row r="202" spans="3:5" x14ac:dyDescent="0.25">
+    <row r="202" spans="2:5" x14ac:dyDescent="0.25">
       <c r="C202" s="3"/>
       <c r="D202" s="3"/>
       <c r="E202" s="3"/>
     </row>
-    <row r="203" spans="3:5" x14ac:dyDescent="0.25">
+    <row r="203" spans="2:5" x14ac:dyDescent="0.25">
       <c r="C203" s="3"/>
       <c r="E203" s="3"/>
     </row>
-    <row r="204" spans="3:5" x14ac:dyDescent="0.25">
+    <row r="204" spans="2:5" x14ac:dyDescent="0.25">
       <c r="C204" s="3"/>
       <c r="E204" s="3"/>
     </row>
-    <row r="205" spans="3:5" x14ac:dyDescent="0.25">
+    <row r="205" spans="2:5" x14ac:dyDescent="0.25">
       <c r="C205" s="3"/>
       <c r="E205" s="3"/>
     </row>
-    <row r="206" spans="3:5" x14ac:dyDescent="0.25">
+    <row r="206" spans="2:5" x14ac:dyDescent="0.25">
       <c r="C206" s="3"/>
       <c r="D206" s="3"/>
       <c r="E206" s="3"/>
     </row>
-    <row r="207" spans="3:5" x14ac:dyDescent="0.25">
+    <row r="207" spans="2:5" x14ac:dyDescent="0.25">
       <c r="C207" s="3"/>
       <c r="E207" s="3"/>
     </row>
-    <row r="208" spans="3:5" x14ac:dyDescent="0.25">
+    <row r="208" spans="2:5" x14ac:dyDescent="0.25">
       <c r="C208" s="3"/>
       <c r="D208" s="3"/>
       <c r="E208" s="3"/>
@@ -3309,6 +3319,7 @@
     </row>
     <row r="212" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C212" s="3"/>
+      <c r="D212" s="3"/>
       <c r="E212" s="3"/>
     </row>
     <row r="213" spans="3:5" x14ac:dyDescent="0.25">
@@ -3317,6 +3328,7 @@
     </row>
     <row r="214" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C214" s="3"/>
+      <c r="D214" s="3"/>
       <c r="E214" s="3"/>
     </row>
     <row r="215" spans="3:5" x14ac:dyDescent="0.25">
@@ -3411,7 +3423,6 @@
     </row>
     <row r="236" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C236" s="3"/>
-      <c r="D236" s="3"/>
       <c r="E236" s="3"/>
     </row>
     <row r="237" spans="3:5" x14ac:dyDescent="0.25">
@@ -3420,7 +3431,6 @@
     </row>
     <row r="238" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C238" s="3"/>
-      <c r="D238" s="3"/>
       <c r="E238" s="3"/>
     </row>
     <row r="239" spans="3:5" x14ac:dyDescent="0.25">
@@ -3463,6 +3473,7 @@
     </row>
     <row r="248" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C248" s="3"/>
+      <c r="D248" s="3"/>
       <c r="E248" s="3"/>
     </row>
     <row r="249" spans="3:5" x14ac:dyDescent="0.25">
@@ -3471,6 +3482,7 @@
     </row>
     <row r="250" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C250" s="3"/>
+      <c r="D250" s="3"/>
       <c r="E250" s="3"/>
     </row>
     <row r="251" spans="3:5" x14ac:dyDescent="0.25">
@@ -3485,8 +3497,110 @@
       <c r="C253" s="3"/>
       <c r="E253" s="3"/>
     </row>
+    <row r="254" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C254" s="3"/>
+      <c r="D254" s="3"/>
+      <c r="E254" s="3"/>
+    </row>
+    <row r="255" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C255" s="3"/>
+      <c r="E255" s="3"/>
+    </row>
+    <row r="256" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C256" s="3"/>
+      <c r="D256" s="3"/>
+      <c r="E256" s="3"/>
+    </row>
+    <row r="257" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C257" s="3"/>
+      <c r="E257" s="3"/>
+    </row>
+    <row r="258" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C258" s="3"/>
+      <c r="E258" s="3"/>
+    </row>
+    <row r="259" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C259" s="3"/>
+      <c r="E259" s="3"/>
+    </row>
+    <row r="260" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C260" s="3"/>
+      <c r="D260" s="3"/>
+      <c r="E260" s="3"/>
+    </row>
+    <row r="261" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C261" s="3"/>
+      <c r="E261" s="3"/>
+    </row>
+    <row r="262" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C262" s="3"/>
+      <c r="D262" s="3"/>
+      <c r="E262" s="3"/>
+    </row>
+    <row r="263" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C263" s="3"/>
+      <c r="E263" s="3"/>
+    </row>
+    <row r="264" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C264" s="3"/>
+      <c r="E264" s="3"/>
+    </row>
+    <row r="265" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C265" s="3"/>
+      <c r="E265" s="3"/>
+    </row>
+    <row r="266" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C266" s="3"/>
+      <c r="D266" s="3"/>
+      <c r="E266" s="3"/>
+    </row>
+    <row r="267" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C267" s="3"/>
+      <c r="E267" s="3"/>
+    </row>
+    <row r="268" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C268" s="3"/>
+      <c r="D268" s="3"/>
+      <c r="E268" s="3"/>
+    </row>
+    <row r="269" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C269" s="3"/>
+      <c r="E269" s="3"/>
+    </row>
+    <row r="270" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C270" s="3"/>
+      <c r="E270" s="3"/>
+    </row>
+    <row r="271" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C271" s="3"/>
+      <c r="E271" s="3"/>
+    </row>
+    <row r="272" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C272" s="3"/>
+      <c r="E272" s="3"/>
+    </row>
+    <row r="273" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C273" s="3"/>
+      <c r="E273" s="3"/>
+    </row>
+    <row r="274" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C274" s="3"/>
+      <c r="E274" s="3"/>
+    </row>
+    <row r="275" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C275" s="3"/>
+      <c r="E275" s="3"/>
+    </row>
+    <row r="276" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C276" s="3"/>
+      <c r="E276" s="3"/>
+    </row>
+    <row r="277" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C277" s="3"/>
+      <c r="E277" s="3"/>
+    </row>
   </sheetData>
-  <autoFilter ref="B1:E145" xr:uid="{6956BB2C-DA9E-4412-BCD4-BB80A11153FE}"/>
+  <autoFilter ref="B1:E133" xr:uid="{6956BB2C-DA9E-4412-BCD4-BB80A11153FE}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/data/metas.xlsx
+++ b/data/metas.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sercomunicaciones2-my.sharepoint.com/personal/auxcomisiones_sercomunicaciones_com/Documents/PAOLA/Liquidacióncvs/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sercomunicaciones2-my.sharepoint.com/personal/auxcomisiones_sercomunicaciones_com/Documents/PAOLA/AUXCOMISIÓN/3 Liquidación CVS comerciales/2026/02 Febrero/Liquidacióncvs - copia/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="514" documentId="8_{787D9E49-702D-43BD-B99B-4B64F775E77B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{212945BE-825C-4D35-AD01-AE528E1CC2B2}"/>
+  <xr:revisionPtr revIDLastSave="554" documentId="8_{787D9E49-702D-43BD-B99B-4B64F775E77B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B8BA1849-1829-4ACB-997B-547C10867E8F}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D1391136-BBFC-43C7-B899-B77B0ECC5956}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$B$1:$E$133</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$B$1:$E$121</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="437" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="365" uniqueCount="35">
   <si>
     <t>BARBOSA</t>
   </si>
@@ -132,9 +132,6 @@
   </si>
   <si>
     <t>OTROS</t>
-  </si>
-  <si>
-    <t>FOCO</t>
   </si>
   <si>
     <t>GENERAL</t>
@@ -549,7 +546,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6956BB2C-DA9E-4412-BCD4-BB80A11153FE}">
-  <dimension ref="A1:E277"/>
+  <dimension ref="A1:E253"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.7109375" bestFit="1" customWidth="1"/>
@@ -560,7 +557,7 @@
   <sheetData>
     <row r="1" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>23</v>
@@ -577,7 +574,7 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>5</v>
@@ -594,7 +591,7 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>5</v>
@@ -611,7 +608,7 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>5</v>
@@ -628,7 +625,7 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>5</v>
@@ -637,7 +634,7 @@
         <v>29</v>
       </c>
       <c r="D5" s="3">
-        <v>95</v>
+        <v>124</v>
       </c>
       <c r="E5" s="3">
         <v>2800</v>
@@ -645,16 +642,16 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>5</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D6" s="3">
-        <v>29</v>
+        <v>146</v>
       </c>
       <c r="E6" s="3">
         <v>2800</v>
@@ -662,33 +659,33 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="D7" s="3">
-        <v>146</v>
+        <v>1500</v>
       </c>
       <c r="E7" s="3">
-        <v>2800</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>0</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="D8" s="3">
-        <v>1500</v>
+        <v>37</v>
       </c>
       <c r="E8" s="3">
         <v>2400</v>
@@ -696,16 +693,16 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>0</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D9" s="3">
-        <v>37</v>
+        <v>6</v>
       </c>
       <c r="E9" s="3">
         <v>2400</v>
@@ -713,16 +710,16 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>0</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="D10" s="3">
-        <v>6</v>
+        <v>29</v>
+      </c>
+      <c r="D10">
+        <v>107</v>
       </c>
       <c r="E10" s="3">
         <v>2400</v>
@@ -730,16 +727,16 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>0</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D11">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="E11" s="3">
         <v>2400</v>
@@ -747,50 +744,50 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>34</v>
-      </c>
-      <c r="B12" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B12" t="s">
+        <v>2</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D12" s="3">
         <v>0</v>
       </c>
-      <c r="C12" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="D12">
-        <v>25</v>
-      </c>
       <c r="E12" s="3">
-        <v>2400</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>34</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>0</v>
+        <v>33</v>
+      </c>
+      <c r="B13" t="s">
+        <v>2</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D13">
-        <v>95</v>
+        <v>12</v>
       </c>
       <c r="E13" s="3">
-        <v>2400</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B14" t="s">
         <v>2</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="D14" s="3">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E14" s="3">
         <v>1350</v>
@@ -798,16 +795,16 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B15" t="s">
         <v>2</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D15">
-        <v>12</v>
+        <v>65</v>
       </c>
       <c r="E15" s="3">
         <v>1350</v>
@@ -815,16 +812,16 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B16" t="s">
         <v>2</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="D16" s="3">
-        <v>4</v>
+        <v>30</v>
+      </c>
+      <c r="D16">
+        <v>32</v>
       </c>
       <c r="E16" s="3">
         <v>1350</v>
@@ -832,67 +829,67 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B17" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="D17">
-        <v>50</v>
+        <v>22</v>
+      </c>
+      <c r="D17" s="3">
+        <v>800</v>
       </c>
       <c r="E17" s="3">
-        <v>1350</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B18" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="D18">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="E18" s="3">
-        <v>1350</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B19" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="D19">
-        <v>32</v>
+        <v>28</v>
+      </c>
+      <c r="D19" s="3">
+        <v>1</v>
       </c>
       <c r="E19" s="3">
-        <v>1350</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B20" t="s">
         <v>3</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D20" s="3">
-        <v>800</v>
+        <v>29</v>
+      </c>
+      <c r="D20">
+        <v>85</v>
       </c>
       <c r="E20" s="3">
         <v>1700</v>
@@ -900,16 +897,16 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B21" t="s">
         <v>3</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="D21">
-        <v>33</v>
+        <v>135</v>
       </c>
       <c r="E21" s="3">
         <v>1700</v>
@@ -917,84 +914,84 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B22" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="D22" s="3">
-        <v>1</v>
+        <v>1200</v>
       </c>
       <c r="E22" s="3">
-        <v>1700</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B23" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D23">
-        <v>65</v>
+        <v>18</v>
       </c>
       <c r="E23" s="3">
-        <v>1700</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B24" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="D24">
-        <v>20</v>
+        <v>28</v>
+      </c>
+      <c r="D24" s="3">
+        <v>1</v>
       </c>
       <c r="E24" s="3">
-        <v>1700</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B25" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D25">
-        <v>135</v>
+        <v>65</v>
       </c>
       <c r="E25" s="3">
-        <v>1700</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B26" t="s">
         <v>8</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D26" s="3">
-        <v>1200</v>
+        <v>30</v>
+      </c>
+      <c r="D26">
+        <v>69</v>
       </c>
       <c r="E26" s="3">
         <v>1450</v>
@@ -1002,129 +999,129 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B27" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D27">
-        <v>18</v>
+        <v>22</v>
+      </c>
+      <c r="D27" s="3">
+        <v>1200</v>
       </c>
       <c r="E27" s="3">
-        <v>1450</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B28" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="D28" s="3">
-        <v>1</v>
+        <v>27</v>
+      </c>
+      <c r="D28">
+        <v>37</v>
       </c>
       <c r="E28" s="3">
-        <v>1450</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B29" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="D29">
-        <v>50</v>
+        <v>28</v>
+      </c>
+      <c r="D29" s="3">
+        <v>1</v>
       </c>
       <c r="E29" s="3">
-        <v>1450</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B30" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D30">
-        <v>15</v>
+        <v>59</v>
       </c>
       <c r="E30" s="3">
-        <v>1450</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B31" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C31" s="3" t="s">
         <v>30</v>
       </c>
       <c r="D31">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E31" s="3">
-        <v>1450</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B32" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C32" s="3" t="s">
         <v>22</v>
       </c>
       <c r="D32" s="3">
-        <v>1200</v>
+        <v>1500</v>
       </c>
       <c r="E32" s="3">
-        <v>1500</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B33" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C33" s="3" t="s">
         <v>27</v>
       </c>
       <c r="D33">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="E33" s="3">
-        <v>1500</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C34" s="3" t="s">
         <v>28</v>
@@ -1133,310 +1130,310 @@
         <v>1</v>
       </c>
       <c r="E34" s="3">
-        <v>1500</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B35" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C35" s="3" t="s">
         <v>29</v>
       </c>
       <c r="D35">
-        <v>45</v>
+        <v>208</v>
       </c>
       <c r="E35" s="3">
-        <v>1500</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B36" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D36">
-        <v>14</v>
+        <v>176</v>
       </c>
       <c r="E36" s="3">
-        <v>1500</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B37" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="D37">
-        <v>68</v>
+        <v>22</v>
+      </c>
+      <c r="D37" s="3">
+        <v>1500</v>
       </c>
       <c r="E37" s="3">
-        <v>1500</v>
+        <v>2600</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B38" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D38" s="3">
-        <v>1500</v>
+        <v>27</v>
+      </c>
+      <c r="D38">
+        <v>26</v>
       </c>
       <c r="E38" s="3">
-        <v>4000</v>
+        <v>2600</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B39" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D39">
-        <v>42</v>
+        <v>28</v>
+      </c>
+      <c r="D39" s="3">
+        <v>1</v>
       </c>
       <c r="E39" s="3">
-        <v>4000</v>
+        <v>2600</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B40" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="D40" s="3">
-        <v>1</v>
+        <v>29</v>
+      </c>
+      <c r="D40">
+        <v>182</v>
       </c>
       <c r="E40" s="3">
-        <v>4000</v>
+        <v>2600</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B41" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D41">
-        <v>160</v>
+        <v>98</v>
       </c>
       <c r="E41" s="3">
-        <v>4000</v>
+        <v>2600</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B42" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="D42">
-        <v>48</v>
+        <v>22</v>
+      </c>
+      <c r="D42" s="3">
+        <v>1200</v>
       </c>
       <c r="E42" s="3">
-        <v>4000</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B43" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D43">
-        <v>176</v>
+        <v>32</v>
       </c>
       <c r="E43" s="3">
-        <v>4000</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B44" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="D44" s="3">
-        <v>1500</v>
+        <v>6</v>
       </c>
       <c r="E44" s="3">
-        <v>2600</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B45" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D45">
-        <v>26</v>
+        <v>73</v>
       </c>
       <c r="E45" s="3">
-        <v>2600</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B46" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="D46" s="3">
-        <v>1</v>
+        <v>30</v>
+      </c>
+      <c r="D46">
+        <v>128</v>
       </c>
       <c r="E46" s="3">
-        <v>2600</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>34</v>
-      </c>
-      <c r="B47" t="s">
-        <v>13</v>
+        <v>33</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>12</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="D47">
-        <v>140</v>
+        <v>22</v>
+      </c>
+      <c r="D47" s="3">
+        <v>1200</v>
       </c>
       <c r="E47" s="3">
-        <v>2600</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B48" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="D48">
-        <v>42</v>
+        <v>17</v>
       </c>
       <c r="E48" s="3">
-        <v>2600</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B49" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="D49">
-        <v>98</v>
+        <v>28</v>
+      </c>
+      <c r="D49" s="3">
+        <v>6</v>
       </c>
       <c r="E49" s="3">
-        <v>2600</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B50" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D50" s="3">
-        <v>1200</v>
+        <v>29</v>
+      </c>
+      <c r="D50">
+        <v>33</v>
       </c>
       <c r="E50" s="3">
-        <v>2000</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B51" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="D51">
-        <v>32</v>
+        <v>54</v>
       </c>
       <c r="E51" s="3">
-        <v>2000</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B52" t="s">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="D52" s="3">
-        <v>6</v>
+        <v>800</v>
       </c>
       <c r="E52" s="3">
         <v>2000</v>
@@ -1444,16 +1441,16 @@
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B53" t="s">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D53">
-        <v>56</v>
+        <v>13</v>
       </c>
       <c r="E53" s="3">
         <v>2000</v>
@@ -1461,16 +1458,16 @@
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B54" t="s">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="D54">
-        <v>17</v>
+        <v>28</v>
+      </c>
+      <c r="D54" s="3">
+        <v>1</v>
       </c>
       <c r="E54" s="3">
         <v>2000</v>
@@ -1478,16 +1475,16 @@
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B55" t="s">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D55">
-        <v>128</v>
+        <v>107</v>
       </c>
       <c r="E55" s="3">
         <v>2000</v>
@@ -1495,146 +1492,146 @@
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>34</v>
-      </c>
-      <c r="B56" s="1" t="s">
-        <v>12</v>
+        <v>33</v>
+      </c>
+      <c r="B56" t="s">
+        <v>17</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D56" s="3">
-        <v>1200</v>
+        <v>30</v>
+      </c>
+      <c r="D56">
+        <v>60</v>
       </c>
       <c r="E56" s="3">
-        <v>1500</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B57" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D57">
-        <v>17</v>
+        <v>22</v>
+      </c>
+      <c r="D57" s="3">
+        <v>1200</v>
       </c>
       <c r="E57" s="3">
-        <v>1500</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B58" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="D58" s="3">
-        <v>6</v>
+        <v>27</v>
+      </c>
+      <c r="D58">
+        <v>16</v>
       </c>
       <c r="E58" s="3">
-        <v>1500</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B59" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="D59">
-        <v>25</v>
+        <v>28</v>
+      </c>
+      <c r="D59" s="3">
+        <v>4</v>
       </c>
       <c r="E59" s="3">
-        <v>1500</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B60" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D60">
-        <v>8</v>
+        <v>39</v>
       </c>
       <c r="E60" s="3">
-        <v>1500</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B61" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="C61" s="3" t="s">
         <v>30</v>
       </c>
       <c r="D61">
-        <v>54</v>
+        <v>74</v>
       </c>
       <c r="E61" s="3">
-        <v>1500</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B62" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C62" s="3" t="s">
         <v>22</v>
       </c>
       <c r="D62" s="3">
-        <v>800</v>
+        <v>1200</v>
       </c>
       <c r="E62" s="3">
-        <v>2000</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B63" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C63" s="3" t="s">
         <v>27</v>
       </c>
       <c r="D63">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="E63" s="3">
-        <v>2000</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B64" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C64" s="3" t="s">
         <v>28</v>
@@ -1643,174 +1640,174 @@
         <v>1</v>
       </c>
       <c r="E64" s="3">
-        <v>2000</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B65" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C65" s="3" t="s">
         <v>29</v>
       </c>
       <c r="D65">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="E65" s="3">
-        <v>2000</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B66" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D66">
-        <v>25</v>
+        <v>183</v>
       </c>
       <c r="E66" s="3">
-        <v>2000</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B67" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="D67">
-        <v>60</v>
+        <v>22</v>
+      </c>
+      <c r="D67" s="3">
+        <v>1200</v>
       </c>
       <c r="E67" s="3">
-        <v>2000</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B68" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C68" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D68">
         <v>22</v>
       </c>
-      <c r="D68" s="3">
-        <v>1200</v>
-      </c>
       <c r="E68" s="3">
-        <v>1100</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B69" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D69">
-        <v>16</v>
+        <v>28</v>
+      </c>
+      <c r="D69" s="3">
+        <v>6</v>
       </c>
       <c r="E69" s="3">
-        <v>1100</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B70" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="D70" s="3">
-        <v>4</v>
+        <v>29</v>
+      </c>
+      <c r="D70">
+        <v>78</v>
       </c>
       <c r="E70" s="3">
-        <v>1100</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B71" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D71">
-        <v>30</v>
+        <v>168</v>
       </c>
       <c r="E71" s="3">
-        <v>1100</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B72" t="s">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="D72">
-        <v>9</v>
+        <v>22</v>
+      </c>
+      <c r="D72" s="3">
+        <v>1200</v>
       </c>
       <c r="E72" s="3">
-        <v>1100</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B73" t="s">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D73">
-        <v>74</v>
+        <v>23</v>
       </c>
       <c r="E73" s="3">
-        <v>1100</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B74" t="s">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="D74" s="3">
-        <v>1200</v>
+        <v>1</v>
       </c>
       <c r="E74" s="3">
         <v>2200</v>
@@ -1818,16 +1815,16 @@
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B75" t="s">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D75">
-        <v>34</v>
+        <v>94</v>
       </c>
       <c r="E75" s="3">
         <v>2200</v>
@@ -1835,16 +1832,16 @@
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B76" t="s">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="D76" s="3">
-        <v>1</v>
+        <v>30</v>
+      </c>
+      <c r="D76">
+        <v>92</v>
       </c>
       <c r="E76" s="3">
         <v>2200</v>
@@ -1852,265 +1849,265 @@
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B77" t="s">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="D77">
-        <v>60</v>
+        <v>22</v>
+      </c>
+      <c r="D77" s="3">
+        <v>1500</v>
       </c>
       <c r="E77" s="3">
-        <v>2200</v>
+        <v>2850</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B78" t="s">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="D78">
-        <v>18</v>
+        <v>52</v>
       </c>
       <c r="E78" s="3">
-        <v>2200</v>
+        <v>2850</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B79" t="s">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="D79">
-        <v>183</v>
+        <v>28</v>
+      </c>
+      <c r="D79" s="3">
+        <v>10</v>
       </c>
       <c r="E79" s="3">
-        <v>2200</v>
+        <v>2850</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B80" t="s">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D80" s="3">
-        <v>1200</v>
+        <v>29</v>
+      </c>
+      <c r="D80">
+        <v>133</v>
       </c>
       <c r="E80" s="3">
-        <v>1600</v>
+        <v>2850</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B81" t="s">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="D81">
-        <v>22</v>
+        <v>129</v>
       </c>
       <c r="E81" s="3">
-        <v>1600</v>
+        <v>2850</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B82" t="s">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="C82" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D82">
+        <v>1500</v>
+      </c>
+      <c r="E82" s="3">
+        <v>3500</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>33</v>
+      </c>
+      <c r="B83" t="s">
+        <v>4</v>
+      </c>
+      <c r="C83" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D83">
+        <v>62</v>
+      </c>
+      <c r="E83" s="3">
+        <v>3500</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>33</v>
+      </c>
+      <c r="B84" t="s">
+        <v>4</v>
+      </c>
+      <c r="C84" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="D82" s="3">
-        <v>6</v>
-      </c>
-      <c r="E82" s="3">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="83" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A83" t="s">
-        <v>34</v>
-      </c>
-      <c r="B83" t="s">
-        <v>21</v>
-      </c>
-      <c r="C83" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="D83">
-        <v>60</v>
-      </c>
-      <c r="E83" s="3">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="84" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A84" t="s">
-        <v>34</v>
-      </c>
-      <c r="B84" t="s">
-        <v>21</v>
-      </c>
-      <c r="C84" s="3" t="s">
-        <v>31</v>
-      </c>
       <c r="D84">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="E84" s="3">
-        <v>1600</v>
+        <v>3500</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B85" t="s">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D85">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="E85" s="3">
-        <v>1600</v>
+        <v>3500</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B86" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D86" s="3">
-        <v>1200</v>
+        <v>30</v>
+      </c>
+      <c r="D86">
+        <v>183</v>
       </c>
       <c r="E86" s="3">
-        <v>2200</v>
+        <v>3500</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B87" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D87">
-        <v>23</v>
+        <v>22</v>
+      </c>
+      <c r="D87" s="3">
+        <v>1500</v>
       </c>
       <c r="E87" s="3">
-        <v>2200</v>
+        <v>3500</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B88" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="D88" s="3">
-        <v>1</v>
+        <v>27</v>
+      </c>
+      <c r="D88">
+        <v>78</v>
       </c>
       <c r="E88" s="3">
-        <v>2200</v>
+        <v>3500</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B89" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="D89">
-        <v>72</v>
+        <v>28</v>
+      </c>
+      <c r="D89" s="3">
+        <v>16</v>
       </c>
       <c r="E89" s="3">
-        <v>2200</v>
+        <v>3500</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B90" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D90">
-        <v>22</v>
+        <v>125</v>
       </c>
       <c r="E90" s="3">
-        <v>2200</v>
+        <v>3500</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B91" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="C91" s="3" t="s">
         <v>30</v>
       </c>
       <c r="D91">
-        <v>92</v>
+        <v>198</v>
       </c>
       <c r="E91" s="3">
-        <v>2200</v>
+        <v>3500</v>
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B92" t="s">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="C92" s="3" t="s">
         <v>22</v>
@@ -2119,32 +2116,32 @@
         <v>1500</v>
       </c>
       <c r="E92" s="3">
-        <v>2850</v>
+        <v>2300</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B93" t="s">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="C93" s="3" t="s">
         <v>27</v>
       </c>
       <c r="D93">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="E93" s="3">
-        <v>2850</v>
+        <v>2300</v>
       </c>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B94" t="s">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="C94" s="3" t="s">
         <v>28</v>
@@ -2153,395 +2150,395 @@
         <v>10</v>
       </c>
       <c r="E94" s="3">
-        <v>2850</v>
+        <v>2300</v>
       </c>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B95" t="s">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="C95" s="3" t="s">
         <v>29</v>
       </c>
       <c r="D95">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="E95" s="3">
-        <v>2850</v>
+        <v>2300</v>
       </c>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B96" t="s">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D96">
-        <v>31</v>
+        <v>151</v>
       </c>
       <c r="E96" s="3">
-        <v>2850</v>
+        <v>2300</v>
       </c>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B97" t="s">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="D97">
-        <v>129</v>
+        <v>22</v>
+      </c>
+      <c r="D97" s="3">
+        <v>1500</v>
       </c>
       <c r="E97" s="3">
-        <v>2850</v>
+        <v>5700</v>
       </c>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B98" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="C98" s="3" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="D98">
-        <v>1500</v>
+        <v>103</v>
       </c>
       <c r="E98" s="3">
-        <v>3500</v>
+        <v>5700</v>
       </c>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B99" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="C99" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D99">
-        <v>62</v>
+        <v>28</v>
+      </c>
+      <c r="D99" s="3">
+        <v>14</v>
       </c>
       <c r="E99" s="3">
-        <v>3500</v>
+        <v>5700</v>
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B100" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="C100" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D100">
-        <v>10</v>
+        <v>307</v>
       </c>
       <c r="E100" s="3">
-        <v>3500</v>
+        <v>5700</v>
       </c>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B101" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="C101" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D101">
-        <v>124</v>
+        <v>192</v>
       </c>
       <c r="E101" s="3">
-        <v>3500</v>
+        <v>5700</v>
       </c>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B102" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="C102" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="D102">
-        <v>37</v>
+        <v>22</v>
+      </c>
+      <c r="D102" s="3">
+        <v>1500</v>
       </c>
       <c r="E102" s="3">
-        <v>3500</v>
+        <v>2600</v>
       </c>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B103" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="C103" s="3" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D103">
-        <v>183</v>
+        <v>62</v>
       </c>
       <c r="E103" s="3">
-        <v>3500</v>
+        <v>2600</v>
       </c>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B104" t="s">
+        <v>19</v>
+      </c>
+      <c r="C104" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D104" s="3">
         <v>11</v>
       </c>
-      <c r="C104" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D104" s="3">
-        <v>1500</v>
-      </c>
       <c r="E104" s="3">
-        <v>3500</v>
+        <v>2600</v>
       </c>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B105" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="C105" s="3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D105">
-        <v>78</v>
+        <v>96</v>
       </c>
       <c r="E105" s="3">
-        <v>3500</v>
+        <v>2600</v>
       </c>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B106" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="C106" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="D106" s="3">
-        <v>16</v>
+        <v>30</v>
+      </c>
+      <c r="D106">
+        <v>181</v>
       </c>
       <c r="E106" s="3">
-        <v>3500</v>
+        <v>2600</v>
       </c>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B107" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C107" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="D107">
-        <v>96</v>
+        <v>22</v>
+      </c>
+      <c r="D107" s="3">
+        <v>1500</v>
       </c>
       <c r="E107" s="3">
-        <v>3500</v>
+        <v>2650</v>
       </c>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B108" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C108" s="3" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="D108">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E108" s="3">
-        <v>3500</v>
+        <v>2650</v>
       </c>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B109" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C109" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="D109">
-        <v>198</v>
+        <v>28</v>
+      </c>
+      <c r="D109" s="3">
+        <v>10</v>
       </c>
       <c r="E109" s="3">
-        <v>3500</v>
+        <v>2650</v>
       </c>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B110" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C110" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D110" s="3">
-        <v>1500</v>
+        <v>29</v>
+      </c>
+      <c r="D110">
+        <v>120</v>
       </c>
       <c r="E110" s="3">
-        <v>2300</v>
+        <v>2650</v>
       </c>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B111" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C111" s="3" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="D111">
-        <v>44</v>
+        <v>126</v>
       </c>
       <c r="E111" s="3">
-        <v>2300</v>
+        <v>2650</v>
       </c>
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B112" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="C112" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="D112" s="3">
-        <v>10</v>
+        <v>22</v>
+      </c>
+      <c r="D112">
+        <v>27700</v>
       </c>
       <c r="E112" s="3">
-        <v>2300</v>
+        <v>53500</v>
       </c>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B113" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="C113" s="3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D113">
-        <v>72</v>
+        <v>840</v>
       </c>
       <c r="E113" s="3">
-        <v>2300</v>
+        <v>53500</v>
       </c>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B114" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="C114" s="3" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D114">
-        <v>22</v>
+        <v>131</v>
       </c>
       <c r="E114" s="3">
-        <v>2300</v>
+        <v>53500</v>
       </c>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B115" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="C115" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D115">
-        <v>151</v>
+        <v>2433</v>
       </c>
       <c r="E115" s="3">
-        <v>2300</v>
+        <v>53500</v>
       </c>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B116" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C116" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D116" s="3">
-        <v>1500</v>
+        <v>30</v>
+      </c>
+      <c r="D116">
+        <v>2738</v>
       </c>
       <c r="E116" s="3">
-        <v>5700</v>
+        <v>53500</v>
       </c>
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
+        <v>33</v>
+      </c>
+      <c r="B117" t="s">
         <v>34</v>
       </c>
-      <c r="B117" t="s">
-        <v>16</v>
-      </c>
       <c r="C117" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D117">
-        <v>103</v>
+        <v>22</v>
+      </c>
+      <c r="D117" s="3">
+        <v>1500</v>
       </c>
       <c r="E117" s="3">
         <v>5700</v>
@@ -2549,16 +2546,16 @@
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
+        <v>33</v>
+      </c>
+      <c r="B118" t="s">
         <v>34</v>
       </c>
-      <c r="B118" t="s">
-        <v>16</v>
-      </c>
       <c r="C118" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="D118" s="3">
-        <v>14</v>
+        <v>27</v>
+      </c>
+      <c r="D118">
+        <v>103</v>
       </c>
       <c r="E118" s="3">
         <v>5700</v>
@@ -2566,16 +2563,16 @@
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
+        <v>33</v>
+      </c>
+      <c r="B119" t="s">
         <v>34</v>
       </c>
-      <c r="B119" t="s">
-        <v>16</v>
-      </c>
       <c r="C119" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="D119">
-        <v>236</v>
+        <v>28</v>
+      </c>
+      <c r="D119" s="3">
+        <v>14</v>
       </c>
       <c r="E119" s="3">
         <v>5700</v>
@@ -2583,16 +2580,16 @@
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
+        <v>33</v>
+      </c>
+      <c r="B120" t="s">
         <v>34</v>
       </c>
-      <c r="B120" t="s">
-        <v>16</v>
-      </c>
       <c r="C120" s="3" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D120">
-        <v>71</v>
+        <v>2433</v>
       </c>
       <c r="E120" s="3">
         <v>5700</v>
@@ -2600,10 +2597,10 @@
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
+        <v>33</v>
+      </c>
+      <c r="B121" t="s">
         <v>34</v>
-      </c>
-      <c r="B121" t="s">
-        <v>16</v>
       </c>
       <c r="C121" s="3" t="s">
         <v>30</v>
@@ -2616,551 +2613,248 @@
       </c>
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A122" t="s">
-        <v>34</v>
-      </c>
-      <c r="B122" t="s">
-        <v>19</v>
-      </c>
-      <c r="C122" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D122" s="3">
-        <v>1500</v>
-      </c>
-      <c r="E122" s="3">
-        <v>2600</v>
-      </c>
+      <c r="B122" s="3"/>
+      <c r="C122" s="3"/>
+      <c r="D122" s="3"/>
+      <c r="E122" s="3"/>
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A123" t="s">
-        <v>34</v>
-      </c>
-      <c r="B123" t="s">
-        <v>19</v>
-      </c>
-      <c r="C123" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D123">
-        <v>62</v>
-      </c>
-      <c r="E123" s="3">
-        <v>2600</v>
-      </c>
+      <c r="B123" s="3"/>
+      <c r="C123" s="3"/>
+      <c r="D123" s="3"/>
+      <c r="E123" s="3"/>
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A124" t="s">
-        <v>34</v>
-      </c>
-      <c r="B124" t="s">
-        <v>19</v>
-      </c>
-      <c r="C124" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="D124" s="3">
-        <v>11</v>
-      </c>
-      <c r="E124" s="3">
-        <v>2600</v>
-      </c>
+      <c r="B124" s="3"/>
+      <c r="C124" s="3"/>
+      <c r="D124" s="3"/>
+      <c r="E124" s="3"/>
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A125" t="s">
-        <v>34</v>
-      </c>
-      <c r="B125" t="s">
-        <v>19</v>
-      </c>
-      <c r="C125" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="D125">
-        <v>74</v>
-      </c>
-      <c r="E125" s="3">
-        <v>2600</v>
-      </c>
+      <c r="B125" s="3"/>
+      <c r="C125" s="3"/>
+      <c r="E125" s="3"/>
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A126" t="s">
-        <v>34</v>
-      </c>
-      <c r="B126" t="s">
-        <v>19</v>
-      </c>
-      <c r="C126" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="D126">
-        <v>22</v>
-      </c>
-      <c r="E126" s="3">
-        <v>2600</v>
-      </c>
+      <c r="B126" s="3"/>
+      <c r="C126" s="3"/>
+      <c r="E126" s="3"/>
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A127" t="s">
-        <v>34</v>
-      </c>
-      <c r="B127" t="s">
-        <v>19</v>
-      </c>
-      <c r="C127" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="D127">
-        <v>181</v>
-      </c>
-      <c r="E127" s="3">
-        <v>2600</v>
-      </c>
+      <c r="B127" s="3"/>
+      <c r="C127" s="3"/>
+      <c r="E127" s="3"/>
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A128" t="s">
-        <v>34</v>
-      </c>
-      <c r="B128" t="s">
-        <v>15</v>
-      </c>
-      <c r="C128" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D128" s="3">
-        <v>1500</v>
-      </c>
-      <c r="E128" s="3">
-        <v>2650</v>
-      </c>
-    </row>
-    <row r="129" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A129" t="s">
-        <v>34</v>
-      </c>
-      <c r="B129" t="s">
-        <v>15</v>
-      </c>
-      <c r="C129" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D129">
-        <v>30</v>
-      </c>
-      <c r="E129" s="3">
-        <v>2650</v>
-      </c>
-    </row>
-    <row r="130" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A130" t="s">
-        <v>34</v>
-      </c>
-      <c r="B130" t="s">
-        <v>15</v>
-      </c>
-      <c r="C130" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="D130" s="3">
-        <v>10</v>
-      </c>
-      <c r="E130" s="3">
-        <v>2650</v>
-      </c>
-    </row>
-    <row r="131" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A131" t="s">
-        <v>34</v>
-      </c>
-      <c r="B131" t="s">
-        <v>15</v>
-      </c>
-      <c r="C131" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="D131">
-        <v>92</v>
-      </c>
-      <c r="E131" s="3">
-        <v>2650</v>
-      </c>
-    </row>
-    <row r="132" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A132" t="s">
-        <v>34</v>
-      </c>
-      <c r="B132" t="s">
-        <v>15</v>
-      </c>
-      <c r="C132" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="D132">
-        <v>28</v>
-      </c>
-      <c r="E132" s="3">
-        <v>2650</v>
-      </c>
-    </row>
-    <row r="133" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A133" t="s">
-        <v>34</v>
-      </c>
-      <c r="B133" t="s">
-        <v>15</v>
-      </c>
-      <c r="C133" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="D133">
-        <v>126</v>
-      </c>
-      <c r="E133" s="3">
-        <v>2650</v>
-      </c>
-    </row>
-    <row r="134" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A134" t="s">
-        <v>34</v>
-      </c>
-      <c r="B134" t="s">
-        <v>32</v>
-      </c>
-      <c r="C134" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D134">
-        <v>27700</v>
-      </c>
-      <c r="E134" s="3">
-        <v>53500</v>
-      </c>
-    </row>
-    <row r="135" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A135" t="s">
-        <v>34</v>
-      </c>
-      <c r="B135" t="s">
-        <v>32</v>
-      </c>
-      <c r="C135" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D135">
-        <v>840</v>
-      </c>
-      <c r="E135" s="3">
-        <v>53500</v>
-      </c>
-    </row>
-    <row r="136" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A136" t="s">
-        <v>34</v>
-      </c>
-      <c r="B136" t="s">
-        <v>32</v>
-      </c>
-      <c r="C136" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="D136">
-        <v>131</v>
-      </c>
-      <c r="E136" s="3">
-        <v>53500</v>
-      </c>
-    </row>
-    <row r="137" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A137" t="s">
-        <v>34</v>
-      </c>
-      <c r="B137" t="s">
-        <v>32</v>
-      </c>
-      <c r="C137" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="D137">
-        <v>1868</v>
-      </c>
-      <c r="E137" s="3">
-        <v>53500</v>
-      </c>
-    </row>
-    <row r="138" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A138" t="s">
-        <v>34</v>
-      </c>
-      <c r="B138" t="s">
-        <v>32</v>
-      </c>
-      <c r="C138" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="D138">
-        <v>565</v>
-      </c>
-      <c r="E138" s="3">
-        <v>53500</v>
-      </c>
-    </row>
-    <row r="139" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A139" t="s">
-        <v>34</v>
-      </c>
-      <c r="B139" t="s">
-        <v>32</v>
-      </c>
-      <c r="C139" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="D139">
-        <v>2738</v>
-      </c>
-      <c r="E139" s="3">
-        <v>53500</v>
-      </c>
-    </row>
-    <row r="140" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A140" t="s">
-        <v>34</v>
-      </c>
-      <c r="B140" t="s">
-        <v>35</v>
-      </c>
-      <c r="C140" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D140" s="3">
-        <v>1500</v>
-      </c>
-      <c r="E140" s="3">
-        <v>5700</v>
-      </c>
-    </row>
-    <row r="141" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A141" t="s">
-        <v>34</v>
-      </c>
-      <c r="B141" t="s">
-        <v>35</v>
-      </c>
-      <c r="C141" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D141">
-        <v>103</v>
-      </c>
-      <c r="E141" s="3">
-        <v>5700</v>
-      </c>
-    </row>
-    <row r="142" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A142" t="s">
-        <v>34</v>
-      </c>
-      <c r="B142" t="s">
-        <v>35</v>
-      </c>
-      <c r="C142" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="D142" s="3">
-        <v>14</v>
-      </c>
-      <c r="E142" s="3">
-        <v>5700</v>
-      </c>
-    </row>
-    <row r="143" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A143" t="s">
-        <v>34</v>
-      </c>
-      <c r="B143" t="s">
-        <v>35</v>
-      </c>
-      <c r="C143" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="D143">
-        <v>236</v>
-      </c>
-      <c r="E143" s="3">
-        <v>5700</v>
-      </c>
-    </row>
-    <row r="144" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A144" t="s">
-        <v>34</v>
-      </c>
-      <c r="B144" t="s">
-        <v>35</v>
-      </c>
-      <c r="C144" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="D144">
-        <v>71</v>
-      </c>
-      <c r="E144" s="3">
-        <v>5700</v>
-      </c>
-    </row>
-    <row r="145" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A145" t="s">
-        <v>34</v>
-      </c>
-      <c r="B145" t="s">
-        <v>35</v>
-      </c>
-      <c r="C145" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="D145">
-        <v>192</v>
-      </c>
-      <c r="E145" s="3">
-        <v>5700</v>
-      </c>
-    </row>
-    <row r="146" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B146" s="3"/>
+      <c r="C128" s="3"/>
+      <c r="D128" s="3"/>
+      <c r="E128" s="3"/>
+    </row>
+    <row r="129" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C129" s="3"/>
+      <c r="E129" s="3"/>
+    </row>
+    <row r="130" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C130" s="3"/>
+      <c r="D130" s="3"/>
+      <c r="E130" s="3"/>
+    </row>
+    <row r="131" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C131" s="3"/>
+      <c r="E131" s="3"/>
+    </row>
+    <row r="132" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C132" s="3"/>
+      <c r="E132" s="3"/>
+    </row>
+    <row r="133" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C133" s="3"/>
+      <c r="E133" s="3"/>
+    </row>
+    <row r="134" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C134" s="3"/>
+      <c r="D134" s="3"/>
+      <c r="E134" s="3"/>
+    </row>
+    <row r="135" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C135" s="3"/>
+      <c r="E135" s="3"/>
+    </row>
+    <row r="136" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C136" s="3"/>
+      <c r="D136" s="3"/>
+      <c r="E136" s="3"/>
+    </row>
+    <row r="137" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C137" s="3"/>
+      <c r="E137" s="3"/>
+    </row>
+    <row r="138" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C138" s="3"/>
+      <c r="E138" s="3"/>
+    </row>
+    <row r="139" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C139" s="3"/>
+      <c r="E139" s="3"/>
+    </row>
+    <row r="140" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C140" s="3"/>
+      <c r="D140" s="3"/>
+      <c r="E140" s="3"/>
+    </row>
+    <row r="141" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C141" s="3"/>
+      <c r="E141" s="3"/>
+    </row>
+    <row r="142" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C142" s="3"/>
+      <c r="D142" s="3"/>
+      <c r="E142" s="3"/>
+    </row>
+    <row r="143" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C143" s="3"/>
+      <c r="E143" s="3"/>
+    </row>
+    <row r="144" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C144" s="3"/>
+      <c r="E144" s="3"/>
+    </row>
+    <row r="145" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C145" s="3"/>
+      <c r="E145" s="3"/>
+    </row>
+    <row r="146" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C146" s="3"/>
       <c r="D146" s="3"/>
       <c r="E146" s="3"/>
     </row>
-    <row r="147" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B147" s="3"/>
+    <row r="147" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C147" s="3"/>
-      <c r="D147" s="3"/>
       <c r="E147" s="3"/>
     </row>
-    <row r="148" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B148" s="3"/>
+    <row r="148" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C148" s="3"/>
       <c r="D148" s="3"/>
       <c r="E148" s="3"/>
     </row>
-    <row r="149" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B149" s="3"/>
+    <row r="149" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C149" s="3"/>
       <c r="E149" s="3"/>
     </row>
-    <row r="150" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B150" s="3"/>
+    <row r="150" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C150" s="3"/>
       <c r="E150" s="3"/>
     </row>
-    <row r="151" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B151" s="3"/>
+    <row r="151" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C151" s="3"/>
       <c r="E151" s="3"/>
     </row>
-    <row r="152" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="152" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C152" s="3"/>
       <c r="D152" s="3"/>
       <c r="E152" s="3"/>
     </row>
-    <row r="153" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="153" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C153" s="3"/>
       <c r="E153" s="3"/>
     </row>
-    <row r="154" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="154" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C154" s="3"/>
       <c r="D154" s="3"/>
       <c r="E154" s="3"/>
     </row>
-    <row r="155" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="155" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C155" s="3"/>
       <c r="E155" s="3"/>
     </row>
-    <row r="156" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="156" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C156" s="3"/>
       <c r="E156" s="3"/>
     </row>
-    <row r="157" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="157" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C157" s="3"/>
       <c r="E157" s="3"/>
     </row>
-    <row r="158" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="158" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C158" s="3"/>
       <c r="D158" s="3"/>
       <c r="E158" s="3"/>
     </row>
-    <row r="159" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="159" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C159" s="3"/>
       <c r="E159" s="3"/>
     </row>
-    <row r="160" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="160" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C160" s="3"/>
       <c r="D160" s="3"/>
       <c r="E160" s="3"/>
     </row>
-    <row r="161" spans="3:5" x14ac:dyDescent="0.25">
+    <row r="161" spans="2:5" x14ac:dyDescent="0.25">
       <c r="C161" s="3"/>
       <c r="E161" s="3"/>
     </row>
-    <row r="162" spans="3:5" x14ac:dyDescent="0.25">
+    <row r="162" spans="2:5" x14ac:dyDescent="0.25">
       <c r="C162" s="3"/>
       <c r="E162" s="3"/>
     </row>
-    <row r="163" spans="3:5" x14ac:dyDescent="0.25">
+    <row r="163" spans="2:5" x14ac:dyDescent="0.25">
       <c r="C163" s="3"/>
       <c r="E163" s="3"/>
     </row>
-    <row r="164" spans="3:5" x14ac:dyDescent="0.25">
+    <row r="164" spans="2:5" x14ac:dyDescent="0.25">
       <c r="C164" s="3"/>
       <c r="D164" s="3"/>
       <c r="E164" s="3"/>
     </row>
-    <row r="165" spans="3:5" x14ac:dyDescent="0.25">
+    <row r="165" spans="2:5" x14ac:dyDescent="0.25">
       <c r="C165" s="3"/>
       <c r="E165" s="3"/>
     </row>
-    <row r="166" spans="3:5" x14ac:dyDescent="0.25">
+    <row r="166" spans="2:5" x14ac:dyDescent="0.25">
       <c r="C166" s="3"/>
       <c r="D166" s="3"/>
       <c r="E166" s="3"/>
     </row>
-    <row r="167" spans="3:5" x14ac:dyDescent="0.25">
+    <row r="167" spans="2:5" x14ac:dyDescent="0.25">
       <c r="C167" s="3"/>
       <c r="E167" s="3"/>
     </row>
-    <row r="168" spans="3:5" x14ac:dyDescent="0.25">
+    <row r="168" spans="2:5" x14ac:dyDescent="0.25">
       <c r="C168" s="3"/>
       <c r="E168" s="3"/>
     </row>
-    <row r="169" spans="3:5" x14ac:dyDescent="0.25">
+    <row r="169" spans="2:5" x14ac:dyDescent="0.25">
       <c r="C169" s="3"/>
       <c r="E169" s="3"/>
     </row>
-    <row r="170" spans="3:5" x14ac:dyDescent="0.25">
+    <row r="170" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B170" s="1"/>
       <c r="C170" s="3"/>
       <c r="D170" s="3"/>
       <c r="E170" s="3"/>
     </row>
-    <row r="171" spans="3:5" x14ac:dyDescent="0.25">
+    <row r="171" spans="2:5" x14ac:dyDescent="0.25">
       <c r="C171" s="3"/>
       <c r="E171" s="3"/>
     </row>
-    <row r="172" spans="3:5" x14ac:dyDescent="0.25">
+    <row r="172" spans="2:5" x14ac:dyDescent="0.25">
       <c r="C172" s="3"/>
       <c r="D172" s="3"/>
       <c r="E172" s="3"/>
     </row>
-    <row r="173" spans="3:5" x14ac:dyDescent="0.25">
+    <row r="173" spans="2:5" x14ac:dyDescent="0.25">
       <c r="C173" s="3"/>
       <c r="E173" s="3"/>
     </row>
-    <row r="174" spans="3:5" x14ac:dyDescent="0.25">
+    <row r="174" spans="2:5" x14ac:dyDescent="0.25">
       <c r="C174" s="3"/>
       <c r="E174" s="3"/>
     </row>
-    <row r="175" spans="3:5" x14ac:dyDescent="0.25">
+    <row r="175" spans="2:5" x14ac:dyDescent="0.25">
       <c r="C175" s="3"/>
       <c r="E175" s="3"/>
     </row>
-    <row r="176" spans="3:5" x14ac:dyDescent="0.25">
+    <row r="176" spans="2:5" x14ac:dyDescent="0.25">
       <c r="C176" s="3"/>
       <c r="D176" s="3"/>
       <c r="E176" s="3"/>
@@ -3234,73 +2928,72 @@
       <c r="C192" s="3"/>
       <c r="E192" s="3"/>
     </row>
-    <row r="193" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="193" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C193" s="3"/>
       <c r="E193" s="3"/>
     </row>
-    <row r="194" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B194" s="1"/>
+    <row r="194" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C194" s="3"/>
       <c r="D194" s="3"/>
       <c r="E194" s="3"/>
     </row>
-    <row r="195" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="195" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C195" s="3"/>
       <c r="E195" s="3"/>
     </row>
-    <row r="196" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="196" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C196" s="3"/>
       <c r="D196" s="3"/>
       <c r="E196" s="3"/>
     </row>
-    <row r="197" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="197" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C197" s="3"/>
       <c r="E197" s="3"/>
     </row>
-    <row r="198" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="198" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C198" s="3"/>
       <c r="E198" s="3"/>
     </row>
-    <row r="199" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="199" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C199" s="3"/>
       <c r="E199" s="3"/>
     </row>
-    <row r="200" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="200" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C200" s="3"/>
       <c r="D200" s="3"/>
       <c r="E200" s="3"/>
     </row>
-    <row r="201" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="201" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C201" s="3"/>
       <c r="E201" s="3"/>
     </row>
-    <row r="202" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="202" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C202" s="3"/>
       <c r="D202" s="3"/>
       <c r="E202" s="3"/>
     </row>
-    <row r="203" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="203" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C203" s="3"/>
       <c r="E203" s="3"/>
     </row>
-    <row r="204" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="204" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C204" s="3"/>
       <c r="E204" s="3"/>
     </row>
-    <row r="205" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="205" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C205" s="3"/>
       <c r="E205" s="3"/>
     </row>
-    <row r="206" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="206" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C206" s="3"/>
       <c r="D206" s="3"/>
       <c r="E206" s="3"/>
     </row>
-    <row r="207" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="207" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C207" s="3"/>
       <c r="E207" s="3"/>
     </row>
-    <row r="208" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="208" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C208" s="3"/>
       <c r="D208" s="3"/>
       <c r="E208" s="3"/>
@@ -3319,7 +3012,6 @@
     </row>
     <row r="212" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C212" s="3"/>
-      <c r="D212" s="3"/>
       <c r="E212" s="3"/>
     </row>
     <row r="213" spans="3:5" x14ac:dyDescent="0.25">
@@ -3328,7 +3020,6 @@
     </row>
     <row r="214" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C214" s="3"/>
-      <c r="D214" s="3"/>
       <c r="E214" s="3"/>
     </row>
     <row r="215" spans="3:5" x14ac:dyDescent="0.25">
@@ -3423,6 +3114,7 @@
     </row>
     <row r="236" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C236" s="3"/>
+      <c r="D236" s="3"/>
       <c r="E236" s="3"/>
     </row>
     <row r="237" spans="3:5" x14ac:dyDescent="0.25">
@@ -3431,6 +3123,7 @@
     </row>
     <row r="238" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C238" s="3"/>
+      <c r="D238" s="3"/>
       <c r="E238" s="3"/>
     </row>
     <row r="239" spans="3:5" x14ac:dyDescent="0.25">
@@ -3473,7 +3166,6 @@
     </row>
     <row r="248" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C248" s="3"/>
-      <c r="D248" s="3"/>
       <c r="E248" s="3"/>
     </row>
     <row r="249" spans="3:5" x14ac:dyDescent="0.25">
@@ -3482,7 +3174,6 @@
     </row>
     <row r="250" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C250" s="3"/>
-      <c r="D250" s="3"/>
       <c r="E250" s="3"/>
     </row>
     <row r="251" spans="3:5" x14ac:dyDescent="0.25">
@@ -3497,110 +3188,8 @@
       <c r="C253" s="3"/>
       <c r="E253" s="3"/>
     </row>
-    <row r="254" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C254" s="3"/>
-      <c r="D254" s="3"/>
-      <c r="E254" s="3"/>
-    </row>
-    <row r="255" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C255" s="3"/>
-      <c r="E255" s="3"/>
-    </row>
-    <row r="256" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C256" s="3"/>
-      <c r="D256" s="3"/>
-      <c r="E256" s="3"/>
-    </row>
-    <row r="257" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C257" s="3"/>
-      <c r="E257" s="3"/>
-    </row>
-    <row r="258" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C258" s="3"/>
-      <c r="E258" s="3"/>
-    </row>
-    <row r="259" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C259" s="3"/>
-      <c r="E259" s="3"/>
-    </row>
-    <row r="260" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C260" s="3"/>
-      <c r="D260" s="3"/>
-      <c r="E260" s="3"/>
-    </row>
-    <row r="261" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C261" s="3"/>
-      <c r="E261" s="3"/>
-    </row>
-    <row r="262" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C262" s="3"/>
-      <c r="D262" s="3"/>
-      <c r="E262" s="3"/>
-    </row>
-    <row r="263" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C263" s="3"/>
-      <c r="E263" s="3"/>
-    </row>
-    <row r="264" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C264" s="3"/>
-      <c r="E264" s="3"/>
-    </row>
-    <row r="265" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C265" s="3"/>
-      <c r="E265" s="3"/>
-    </row>
-    <row r="266" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C266" s="3"/>
-      <c r="D266" s="3"/>
-      <c r="E266" s="3"/>
-    </row>
-    <row r="267" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C267" s="3"/>
-      <c r="E267" s="3"/>
-    </row>
-    <row r="268" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C268" s="3"/>
-      <c r="D268" s="3"/>
-      <c r="E268" s="3"/>
-    </row>
-    <row r="269" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C269" s="3"/>
-      <c r="E269" s="3"/>
-    </row>
-    <row r="270" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C270" s="3"/>
-      <c r="E270" s="3"/>
-    </row>
-    <row r="271" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C271" s="3"/>
-      <c r="E271" s="3"/>
-    </row>
-    <row r="272" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C272" s="3"/>
-      <c r="E272" s="3"/>
-    </row>
-    <row r="273" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C273" s="3"/>
-      <c r="E273" s="3"/>
-    </row>
-    <row r="274" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C274" s="3"/>
-      <c r="E274" s="3"/>
-    </row>
-    <row r="275" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C275" s="3"/>
-      <c r="E275" s="3"/>
-    </row>
-    <row r="276" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C276" s="3"/>
-      <c r="E276" s="3"/>
-    </row>
-    <row r="277" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C277" s="3"/>
-      <c r="E277" s="3"/>
-    </row>
   </sheetData>
-  <autoFilter ref="B1:E133" xr:uid="{6956BB2C-DA9E-4412-BCD4-BB80A11153FE}"/>
+  <autoFilter ref="B1:E121" xr:uid="{6956BB2C-DA9E-4412-BCD4-BB80A11153FE}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/data/metas.xlsx
+++ b/data/metas.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sercomunicaciones2-my.sharepoint.com/personal/auxcomisiones_sercomunicaciones_com/Documents/PAOLA/AUXCOMISIÓN/3 Liquidación CVS comerciales/2026/02 Febrero/Liquidacióncvs - copia/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sercomunicaciones2-my.sharepoint.com/personal/auxcomisiones_sercomunicaciones_com/Documents/PAOLA/AUXCOMISIÓN/3 Liquidación CVS comerciales/2026/03 Marzo/Liquidacióncvs/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="554" documentId="8_{787D9E49-702D-43BD-B99B-4B64F775E77B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B8BA1849-1829-4ACB-997B-547C10867E8F}"/>
+  <xr:revisionPtr revIDLastSave="716" documentId="8_{787D9E49-702D-43BD-B99B-4B64F775E77B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F09CCFEB-F04B-42F9-99CA-A38399CBEAA4}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D1391136-BBFC-43C7-B899-B77B0ECC5956}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$B$1:$E$121</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$A$1:$E$121</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -140,10 +140,10 @@
     <t>Mes</t>
   </si>
   <si>
-    <t>Febrero</t>
-  </si>
-  <si>
     <t>NUMERARIO</t>
+  </si>
+  <si>
+    <t>Marzo</t>
   </si>
 </sst>
 </file>
@@ -175,7 +175,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -183,28 +183,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -546,7 +530,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6956BB2C-DA9E-4412-BCD4-BB80A11153FE}">
-  <dimension ref="A1:E253"/>
+  <dimension ref="A1:E121"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.7109375" bestFit="1" customWidth="1"/>
@@ -556,2640 +540,2064 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>33</v>
-      </c>
-      <c r="B2" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="D2" s="3">
+      <c r="D2" s="2">
         <v>1500</v>
       </c>
-      <c r="E2" s="3">
+      <c r="E2" s="2">
         <v>2800</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>33</v>
-      </c>
-      <c r="B3" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="D3" s="3">
+      <c r="D3" s="2">
         <v>47</v>
       </c>
-      <c r="E3" s="3">
+      <c r="E3" s="2">
         <v>2800</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>33</v>
-      </c>
-      <c r="B4" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="D4" s="3">
+      <c r="D4" s="2">
         <v>10</v>
       </c>
-      <c r="E4" s="3">
+      <c r="E4" s="2">
         <v>2800</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>33</v>
-      </c>
-      <c r="B5" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="D5" s="3">
-        <v>124</v>
-      </c>
-      <c r="E5" s="3">
+      <c r="D5" s="2">
+        <v>95</v>
+      </c>
+      <c r="E5" s="2">
         <v>2800</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>33</v>
-      </c>
-      <c r="B6" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="D6" s="3">
+      <c r="D6" s="2">
         <v>146</v>
       </c>
-      <c r="E6" s="3">
+      <c r="E6" s="2">
         <v>2800</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>33</v>
-      </c>
-      <c r="B7" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="D7" s="3">
+      <c r="D7" s="2">
         <v>1500</v>
       </c>
-      <c r="E7" s="3">
+      <c r="E7" s="2">
         <v>2400</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>33</v>
-      </c>
-      <c r="B8" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C8" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="D8" s="3">
+      <c r="D8" s="2">
         <v>37</v>
       </c>
-      <c r="E8" s="3">
+      <c r="E8" s="2">
         <v>2400</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>33</v>
-      </c>
-      <c r="B9" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="C9" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="D9" s="3">
+      <c r="D9" s="2">
         <v>6</v>
       </c>
-      <c r="E9" s="3">
+      <c r="E9" s="2">
         <v>2400</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>33</v>
-      </c>
-      <c r="B10" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B10" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="C10" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="D10">
-        <v>107</v>
-      </c>
-      <c r="E10" s="3">
+      <c r="D10" s="2">
+        <v>82</v>
+      </c>
+      <c r="E10" s="2">
         <v>2400</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>33</v>
-      </c>
-      <c r="B11" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="C11" s="2" t="s">
         <v>30</v>
       </c>
       <c r="D11">
         <v>95</v>
       </c>
-      <c r="E11" s="3">
+      <c r="E11" s="2">
         <v>2400</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B12" t="s">
         <v>2</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="C12" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="D12" s="3">
+      <c r="D12" s="2">
         <v>0</v>
       </c>
-      <c r="E12" s="3">
+      <c r="E12" s="2">
         <v>1350</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B13" t="s">
         <v>2</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="C13" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="D13">
+      <c r="D13" s="2">
         <v>12</v>
       </c>
-      <c r="E13" s="3">
+      <c r="E13" s="2">
         <v>1350</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B14" t="s">
         <v>2</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="C14" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="2">
         <v>4</v>
       </c>
-      <c r="E14" s="3">
+      <c r="E14" s="2">
         <v>1350</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B15" t="s">
         <v>2</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="C15" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="D15">
-        <v>65</v>
-      </c>
-      <c r="E15" s="3">
+      <c r="D15" s="2">
+        <v>50</v>
+      </c>
+      <c r="E15" s="2">
         <v>1350</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B16" t="s">
         <v>2</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="C16" s="2" t="s">
         <v>30</v>
       </c>
       <c r="D16">
         <v>32</v>
       </c>
-      <c r="E16" s="3">
+      <c r="E16" s="2">
         <v>1350</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B17" t="s">
         <v>3</v>
       </c>
-      <c r="C17" s="3" t="s">
+      <c r="C17" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="D17" s="3">
+      <c r="D17" s="2">
         <v>800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="E17" s="2">
         <v>1700</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B18" t="s">
         <v>3</v>
       </c>
-      <c r="C18" s="3" t="s">
+      <c r="C18" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="D18">
+      <c r="D18" s="2">
         <v>33</v>
       </c>
-      <c r="E18" s="3">
+      <c r="E18" s="2">
         <v>1700</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B19" t="s">
         <v>3</v>
       </c>
-      <c r="C19" s="3" t="s">
+      <c r="C19" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="D19" s="3">
+      <c r="D19" s="2">
         <v>1</v>
       </c>
-      <c r="E19" s="3">
+      <c r="E19" s="2">
         <v>1700</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B20" t="s">
         <v>3</v>
       </c>
-      <c r="C20" s="3" t="s">
+      <c r="C20" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="D20">
-        <v>85</v>
-      </c>
-      <c r="E20" s="3">
+      <c r="D20" s="2">
+        <v>65</v>
+      </c>
+      <c r="E20" s="2">
         <v>1700</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B21" t="s">
         <v>3</v>
       </c>
-      <c r="C21" s="3" t="s">
+      <c r="C21" s="2" t="s">
         <v>30</v>
       </c>
       <c r="D21">
         <v>135</v>
       </c>
-      <c r="E21" s="3">
+      <c r="E21" s="2">
         <v>1700</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B22" t="s">
         <v>8</v>
       </c>
-      <c r="C22" s="3" t="s">
+      <c r="C22" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="D22" s="3">
+      <c r="D22" s="2">
         <v>1200</v>
       </c>
-      <c r="E22" s="3">
+      <c r="E22" s="2">
         <v>1450</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B23" t="s">
         <v>8</v>
       </c>
-      <c r="C23" s="3" t="s">
+      <c r="C23" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="D23">
+      <c r="D23" s="2">
         <v>18</v>
       </c>
-      <c r="E23" s="3">
+      <c r="E23" s="2">
         <v>1450</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B24" t="s">
         <v>8</v>
       </c>
-      <c r="C24" s="3" t="s">
+      <c r="C24" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="D24" s="3">
+      <c r="D24" s="2">
         <v>1</v>
       </c>
-      <c r="E24" s="3">
+      <c r="E24" s="2">
         <v>1450</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B25" t="s">
         <v>8</v>
       </c>
-      <c r="C25" s="3" t="s">
+      <c r="C25" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="D25">
-        <v>65</v>
-      </c>
-      <c r="E25" s="3">
+      <c r="D25" s="2">
+        <v>50</v>
+      </c>
+      <c r="E25" s="2">
         <v>1450</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B26" t="s">
         <v>8</v>
       </c>
-      <c r="C26" s="3" t="s">
+      <c r="C26" s="2" t="s">
         <v>30</v>
       </c>
       <c r="D26">
         <v>69</v>
       </c>
-      <c r="E26" s="3">
+      <c r="E26" s="2">
         <v>1450</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B27" t="s">
         <v>10</v>
       </c>
-      <c r="C27" s="3" t="s">
+      <c r="C27" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="3">
+      <c r="D27" s="2">
         <v>1200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="E27" s="2">
         <v>1500</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B28" t="s">
         <v>10</v>
       </c>
-      <c r="C28" s="3" t="s">
+      <c r="C28" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="D28">
+      <c r="D28" s="2">
         <v>37</v>
       </c>
-      <c r="E28" s="3">
+      <c r="E28" s="2">
         <v>1500</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B29" t="s">
         <v>10</v>
       </c>
-      <c r="C29" s="3" t="s">
+      <c r="C29" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="D29" s="3">
+      <c r="D29" s="2">
         <v>1</v>
       </c>
-      <c r="E29" s="3">
+      <c r="E29" s="2">
         <v>1500</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B30" t="s">
         <v>10</v>
       </c>
-      <c r="C30" s="3" t="s">
+      <c r="C30" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="D30">
-        <v>59</v>
-      </c>
-      <c r="E30" s="3">
+      <c r="D30" s="2">
+        <v>45</v>
+      </c>
+      <c r="E30" s="2">
         <v>1500</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B31" t="s">
         <v>10</v>
       </c>
-      <c r="C31" s="3" t="s">
+      <c r="C31" s="2" t="s">
         <v>30</v>
       </c>
       <c r="D31">
         <v>68</v>
       </c>
-      <c r="E31" s="3">
+      <c r="E31" s="2">
         <v>1500</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B32" t="s">
         <v>9</v>
       </c>
-      <c r="C32" s="3" t="s">
+      <c r="C32" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="D32" s="3">
+      <c r="D32" s="2">
         <v>1500</v>
       </c>
-      <c r="E32" s="3">
+      <c r="E32" s="2">
         <v>4000</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B33" t="s">
         <v>9</v>
       </c>
-      <c r="C33" s="3" t="s">
+      <c r="C33" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="D33">
+      <c r="D33" s="2">
         <v>42</v>
       </c>
-      <c r="E33" s="3">
+      <c r="E33" s="2">
         <v>4000</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B34" t="s">
         <v>9</v>
       </c>
-      <c r="C34" s="3" t="s">
+      <c r="C34" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="D34" s="3">
+      <c r="D34" s="2">
         <v>1</v>
       </c>
-      <c r="E34" s="3">
+      <c r="E34" s="2">
         <v>4000</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B35" t="s">
         <v>9</v>
       </c>
-      <c r="C35" s="3" t="s">
+      <c r="C35" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="D35">
-        <v>208</v>
-      </c>
-      <c r="E35" s="3">
+      <c r="D35" s="2">
+        <v>160</v>
+      </c>
+      <c r="E35" s="2">
         <v>4000</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B36" t="s">
         <v>9</v>
       </c>
-      <c r="C36" s="3" t="s">
+      <c r="C36" s="2" t="s">
         <v>30</v>
       </c>
       <c r="D36">
         <v>176</v>
       </c>
-      <c r="E36" s="3">
+      <c r="E36" s="2">
         <v>4000</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B37" t="s">
         <v>13</v>
       </c>
-      <c r="C37" s="3" t="s">
+      <c r="C37" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="D37" s="3">
+      <c r="D37" s="2">
         <v>1500</v>
       </c>
-      <c r="E37" s="3">
+      <c r="E37" s="2">
         <v>2600</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B38" t="s">
         <v>13</v>
       </c>
-      <c r="C38" s="3" t="s">
+      <c r="C38" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="D38">
+      <c r="D38" s="2">
         <v>26</v>
       </c>
-      <c r="E38" s="3">
+      <c r="E38" s="2">
         <v>2600</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B39" t="s">
         <v>13</v>
       </c>
-      <c r="C39" s="3" t="s">
+      <c r="C39" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="D39" s="3">
+      <c r="D39" s="2">
         <v>1</v>
       </c>
-      <c r="E39" s="3">
+      <c r="E39" s="2">
         <v>2600</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B40" t="s">
         <v>13</v>
       </c>
-      <c r="C40" s="3" t="s">
+      <c r="C40" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="D40">
-        <v>182</v>
-      </c>
-      <c r="E40" s="3">
+      <c r="D40" s="2">
+        <v>130</v>
+      </c>
+      <c r="E40" s="2">
         <v>2600</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B41" t="s">
         <v>13</v>
       </c>
-      <c r="C41" s="3" t="s">
+      <c r="C41" s="2" t="s">
         <v>30</v>
       </c>
       <c r="D41">
         <v>98</v>
       </c>
-      <c r="E41" s="3">
+      <c r="E41" s="2">
         <v>2600</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B42" t="s">
         <v>7</v>
       </c>
-      <c r="C42" s="3" t="s">
+      <c r="C42" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="D42" s="3">
+      <c r="D42" s="2">
         <v>1200</v>
       </c>
-      <c r="E42" s="3">
+      <c r="E42" s="2">
         <v>2000</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B43" t="s">
         <v>7</v>
       </c>
-      <c r="C43" s="3" t="s">
+      <c r="C43" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="D43">
+      <c r="D43" s="2">
         <v>32</v>
       </c>
-      <c r="E43" s="3">
+      <c r="E43" s="2">
         <v>2000</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B44" t="s">
         <v>7</v>
       </c>
-      <c r="C44" s="3" t="s">
+      <c r="C44" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="D44" s="3">
+      <c r="D44" s="2">
         <v>6</v>
       </c>
-      <c r="E44" s="3">
+      <c r="E44" s="2">
         <v>2000</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B45" t="s">
         <v>7</v>
       </c>
-      <c r="C45" s="3" t="s">
+      <c r="C45" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="D45">
-        <v>73</v>
-      </c>
-      <c r="E45" s="3">
+      <c r="D45" s="2">
+        <v>56</v>
+      </c>
+      <c r="E45" s="2">
         <v>2000</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B46" t="s">
         <v>7</v>
       </c>
-      <c r="C46" s="3" t="s">
+      <c r="C46" s="2" t="s">
         <v>30</v>
       </c>
       <c r="D46">
         <v>128</v>
       </c>
-      <c r="E46" s="3">
+      <c r="E46" s="2">
         <v>2000</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>33</v>
-      </c>
-      <c r="B47" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B47" t="s">
         <v>12</v>
       </c>
-      <c r="C47" s="3" t="s">
+      <c r="C47" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="D47" s="3">
+      <c r="D47" s="2">
         <v>1200</v>
       </c>
-      <c r="E47" s="3">
+      <c r="E47" s="2">
         <v>1500</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B48" t="s">
         <v>12</v>
       </c>
-      <c r="C48" s="3" t="s">
+      <c r="C48" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="D48">
+      <c r="D48" s="2">
         <v>17</v>
       </c>
-      <c r="E48" s="3">
+      <c r="E48" s="2">
         <v>1500</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B49" t="s">
         <v>12</v>
       </c>
-      <c r="C49" s="3" t="s">
+      <c r="C49" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="D49" s="3">
+      <c r="D49" s="2">
         <v>6</v>
       </c>
-      <c r="E49" s="3">
+      <c r="E49" s="2">
         <v>1500</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B50" t="s">
         <v>12</v>
       </c>
-      <c r="C50" s="3" t="s">
+      <c r="C50" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="D50">
-        <v>33</v>
-      </c>
-      <c r="E50" s="3">
+      <c r="D50" s="2">
+        <v>25</v>
+      </c>
+      <c r="E50" s="2">
         <v>1500</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B51" t="s">
         <v>12</v>
       </c>
-      <c r="C51" s="3" t="s">
+      <c r="C51" s="2" t="s">
         <v>30</v>
       </c>
       <c r="D51">
         <v>54</v>
       </c>
-      <c r="E51" s="3">
+      <c r="E51" s="2">
         <v>1500</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B52" t="s">
         <v>17</v>
       </c>
-      <c r="C52" s="3" t="s">
+      <c r="C52" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="D52" s="3">
+      <c r="D52" s="2">
         <v>800</v>
       </c>
-      <c r="E52" s="3">
+      <c r="E52" s="2">
         <v>2000</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B53" t="s">
         <v>17</v>
       </c>
-      <c r="C53" s="3" t="s">
+      <c r="C53" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="D53">
+      <c r="D53" s="2">
         <v>13</v>
       </c>
-      <c r="E53" s="3">
+      <c r="E53" s="2">
         <v>2000</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B54" t="s">
         <v>17</v>
       </c>
-      <c r="C54" s="3" t="s">
+      <c r="C54" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="D54" s="3">
+      <c r="D54" s="2">
         <v>1</v>
       </c>
-      <c r="E54" s="3">
+      <c r="E54" s="2">
         <v>2000</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B55" t="s">
         <v>17</v>
       </c>
-      <c r="C55" s="3" t="s">
+      <c r="C55" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="D55">
-        <v>107</v>
-      </c>
-      <c r="E55" s="3">
+      <c r="D55" s="2">
+        <v>82</v>
+      </c>
+      <c r="E55" s="2">
         <v>2000</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B56" t="s">
         <v>17</v>
       </c>
-      <c r="C56" s="3" t="s">
+      <c r="C56" s="2" t="s">
         <v>30</v>
       </c>
       <c r="D56">
         <v>60</v>
       </c>
-      <c r="E56" s="3">
+      <c r="E56" s="2">
         <v>2000</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B57" t="s">
         <v>18</v>
       </c>
-      <c r="C57" s="3" t="s">
+      <c r="C57" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="D57" s="3">
+      <c r="D57" s="2">
         <v>1200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="E57" s="2">
         <v>1100</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B58" t="s">
         <v>18</v>
       </c>
-      <c r="C58" s="3" t="s">
+      <c r="C58" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="D58">
+      <c r="D58" s="2">
         <v>16</v>
       </c>
-      <c r="E58" s="3">
+      <c r="E58" s="2">
         <v>1100</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B59" t="s">
         <v>18</v>
       </c>
-      <c r="C59" s="3" t="s">
+      <c r="C59" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="D59" s="3">
+      <c r="D59" s="2">
         <v>4</v>
       </c>
-      <c r="E59" s="3">
+      <c r="E59" s="2">
         <v>1100</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B60" t="s">
         <v>18</v>
       </c>
-      <c r="C60" s="3" t="s">
+      <c r="C60" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="D60">
-        <v>39</v>
-      </c>
-      <c r="E60" s="3">
+      <c r="D60" s="2">
+        <v>30</v>
+      </c>
+      <c r="E60" s="2">
         <v>1100</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B61" t="s">
         <v>18</v>
       </c>
-      <c r="C61" s="3" t="s">
+      <c r="C61" s="2" t="s">
         <v>30</v>
       </c>
       <c r="D61">
         <v>74</v>
       </c>
-      <c r="E61" s="3">
+      <c r="E61" s="2">
         <v>1100</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B62" t="s">
         <v>20</v>
       </c>
-      <c r="C62" s="3" t="s">
+      <c r="C62" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="D62" s="3">
+      <c r="D62" s="2">
         <v>1200</v>
       </c>
-      <c r="E62" s="3">
+      <c r="E62" s="2">
         <v>2200</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B63" t="s">
         <v>20</v>
       </c>
-      <c r="C63" s="3" t="s">
+      <c r="C63" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="D63">
-        <v>34</v>
-      </c>
-      <c r="E63" s="3">
+      <c r="D63" s="2">
+        <v>34</v>
+      </c>
+      <c r="E63" s="2">
         <v>2200</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B64" t="s">
         <v>20</v>
       </c>
-      <c r="C64" s="3" t="s">
+      <c r="C64" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="D64" s="3">
+      <c r="D64" s="2">
         <v>1</v>
       </c>
-      <c r="E64" s="3">
+      <c r="E64" s="2">
         <v>2200</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B65" t="s">
         <v>20</v>
       </c>
-      <c r="C65" s="3" t="s">
+      <c r="C65" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="D65">
-        <v>78</v>
-      </c>
-      <c r="E65" s="3">
+      <c r="D65" s="2">
+        <v>60</v>
+      </c>
+      <c r="E65" s="2">
         <v>2200</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B66" t="s">
         <v>20</v>
       </c>
-      <c r="C66" s="3" t="s">
+      <c r="C66" s="2" t="s">
         <v>30</v>
       </c>
       <c r="D66">
         <v>183</v>
       </c>
-      <c r="E66" s="3">
+      <c r="E66" s="2">
         <v>2200</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B67" t="s">
         <v>21</v>
       </c>
-      <c r="C67" s="3" t="s">
+      <c r="C67" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="D67" s="3">
+      <c r="D67" s="2">
         <v>1200</v>
       </c>
-      <c r="E67" s="3">
+      <c r="E67" s="2">
         <v>1600</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B68" t="s">
         <v>21</v>
       </c>
-      <c r="C68" s="3" t="s">
+      <c r="C68" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="D68">
+      <c r="D68" s="2">
         <v>22</v>
       </c>
-      <c r="E68" s="3">
+      <c r="E68" s="2">
         <v>1600</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B69" t="s">
         <v>21</v>
       </c>
-      <c r="C69" s="3" t="s">
+      <c r="C69" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="D69" s="3">
+      <c r="D69" s="2">
         <v>6</v>
       </c>
-      <c r="E69" s="3">
+      <c r="E69" s="2">
         <v>1600</v>
       </c>
     </row>
-    <row r="70" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B70" t="s">
         <v>21</v>
       </c>
-      <c r="C70" s="3" t="s">
+      <c r="C70" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="D70">
-        <v>78</v>
-      </c>
-      <c r="E70" s="3">
+      <c r="D70" s="2">
+        <v>60</v>
+      </c>
+      <c r="E70" s="2">
         <v>1600</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B71" t="s">
         <v>21</v>
       </c>
-      <c r="C71" s="3" t="s">
+      <c r="C71" s="2" t="s">
         <v>30</v>
       </c>
       <c r="D71">
         <v>168</v>
       </c>
-      <c r="E71" s="3">
+      <c r="E71" s="2">
         <v>1600</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B72" t="s">
         <v>6</v>
       </c>
-      <c r="C72" s="3" t="s">
+      <c r="C72" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="D72" s="3">
+      <c r="D72" s="2">
         <v>1200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="E72" s="2">
         <v>2200</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B73" t="s">
         <v>6</v>
       </c>
-      <c r="C73" s="3" t="s">
+      <c r="C73" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="D73">
+      <c r="D73" s="2">
         <v>23</v>
       </c>
-      <c r="E73" s="3">
+      <c r="E73" s="2">
         <v>2200</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B74" t="s">
         <v>6</v>
       </c>
-      <c r="C74" s="3" t="s">
+      <c r="C74" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="D74" s="3">
+      <c r="D74" s="2">
         <v>1</v>
       </c>
-      <c r="E74" s="3">
+      <c r="E74" s="2">
         <v>2200</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B75" t="s">
         <v>6</v>
       </c>
-      <c r="C75" s="3" t="s">
+      <c r="C75" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="D75">
-        <v>94</v>
-      </c>
-      <c r="E75" s="3">
+      <c r="D75" s="2">
+        <v>72</v>
+      </c>
+      <c r="E75" s="2">
         <v>2200</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B76" t="s">
         <v>6</v>
       </c>
-      <c r="C76" s="3" t="s">
+      <c r="C76" s="2" t="s">
         <v>30</v>
       </c>
       <c r="D76">
         <v>92</v>
       </c>
-      <c r="E76" s="3">
+      <c r="E76" s="2">
         <v>2200</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B77" t="s">
         <v>1</v>
       </c>
-      <c r="C77" s="3" t="s">
+      <c r="C77" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="D77" s="3">
+      <c r="D77" s="2">
         <v>1500</v>
       </c>
-      <c r="E77" s="3">
+      <c r="E77" s="2">
         <v>2850</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B78" t="s">
         <v>1</v>
       </c>
-      <c r="C78" s="3" t="s">
+      <c r="C78" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="D78">
+      <c r="D78" s="2">
         <v>52</v>
       </c>
-      <c r="E78" s="3">
+      <c r="E78" s="2">
         <v>2850</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B79" t="s">
         <v>1</v>
       </c>
-      <c r="C79" s="3" t="s">
+      <c r="C79" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="D79" s="3">
+      <c r="D79" s="2">
         <v>10</v>
       </c>
-      <c r="E79" s="3">
+      <c r="E79" s="2">
         <v>2850</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B80" t="s">
         <v>1</v>
       </c>
-      <c r="C80" s="3" t="s">
+      <c r="C80" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="D80">
-        <v>133</v>
-      </c>
-      <c r="E80" s="3">
+      <c r="D80" s="2">
+        <v>102</v>
+      </c>
+      <c r="E80" s="2">
         <v>2850</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B81" t="s">
         <v>1</v>
       </c>
-      <c r="C81" s="3" t="s">
+      <c r="C81" s="2" t="s">
         <v>30</v>
       </c>
       <c r="D81">
         <v>129</v>
       </c>
-      <c r="E81" s="3">
+      <c r="E81" s="2">
         <v>2850</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B82" t="s">
         <v>4</v>
       </c>
-      <c r="C82" s="3" t="s">
+      <c r="C82" s="2" t="s">
         <v>22</v>
       </c>
       <c r="D82">
         <v>1500</v>
       </c>
-      <c r="E82" s="3">
+      <c r="E82" s="2">
         <v>3500</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B83" t="s">
         <v>4</v>
       </c>
-      <c r="C83" s="3" t="s">
+      <c r="C83" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="D83">
+      <c r="D83" s="2">
         <v>62</v>
       </c>
-      <c r="E83" s="3">
+      <c r="E83" s="2">
         <v>3500</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B84" t="s">
         <v>4</v>
       </c>
-      <c r="C84" s="3" t="s">
+      <c r="C84" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D84">
         <v>10</v>
       </c>
-      <c r="E84" s="3">
+      <c r="E84" s="2">
         <v>3500</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B85" t="s">
         <v>4</v>
       </c>
-      <c r="C85" s="3" t="s">
+      <c r="C85" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="D85">
-        <v>161</v>
-      </c>
-      <c r="E85" s="3">
+      <c r="D85" s="2">
+        <v>124</v>
+      </c>
+      <c r="E85" s="2">
         <v>3500</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B86" t="s">
         <v>4</v>
       </c>
-      <c r="C86" s="3" t="s">
+      <c r="C86" s="2" t="s">
         <v>30</v>
       </c>
       <c r="D86">
         <v>183</v>
       </c>
-      <c r="E86" s="3">
+      <c r="E86" s="2">
         <v>3500</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B87" t="s">
         <v>11</v>
       </c>
-      <c r="C87" s="3" t="s">
+      <c r="C87" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="D87" s="3">
+      <c r="D87" s="2">
         <v>1500</v>
       </c>
-      <c r="E87" s="3">
+      <c r="E87" s="2">
         <v>3500</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B88" t="s">
         <v>11</v>
       </c>
-      <c r="C88" s="3" t="s">
+      <c r="C88" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="D88">
+      <c r="D88" s="2">
         <v>78</v>
       </c>
-      <c r="E88" s="3">
+      <c r="E88" s="2">
         <v>3500</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B89" t="s">
         <v>11</v>
       </c>
-      <c r="C89" s="3" t="s">
+      <c r="C89" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="D89" s="3">
+      <c r="D89" s="2">
         <v>16</v>
       </c>
-      <c r="E89" s="3">
+      <c r="E89" s="2">
         <v>3500</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B90" t="s">
         <v>11</v>
       </c>
-      <c r="C90" s="3" t="s">
+      <c r="C90" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="D90">
-        <v>125</v>
-      </c>
-      <c r="E90" s="3">
+      <c r="D90" s="2">
+        <v>96</v>
+      </c>
+      <c r="E90" s="2">
         <v>3500</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B91" t="s">
         <v>11</v>
       </c>
-      <c r="C91" s="3" t="s">
+      <c r="C91" s="2" t="s">
         <v>30</v>
       </c>
       <c r="D91">
         <v>198</v>
       </c>
-      <c r="E91" s="3">
+      <c r="E91" s="2">
         <v>3500</v>
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B92" t="s">
         <v>14</v>
       </c>
-      <c r="C92" s="3" t="s">
+      <c r="C92" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="D92" s="3">
+      <c r="D92" s="2">
         <v>1500</v>
       </c>
-      <c r="E92" s="3">
+      <c r="E92" s="2">
         <v>2300</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B93" t="s">
         <v>14</v>
       </c>
-      <c r="C93" s="3" t="s">
+      <c r="C93" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="D93">
+      <c r="D93" s="2">
         <v>44</v>
       </c>
-      <c r="E93" s="3">
+      <c r="E93" s="2">
         <v>2300</v>
       </c>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B94" t="s">
         <v>14</v>
       </c>
-      <c r="C94" s="3" t="s">
+      <c r="C94" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="D94" s="3">
+      <c r="D94" s="2">
         <v>10</v>
       </c>
-      <c r="E94" s="3">
+      <c r="E94" s="2">
         <v>2300</v>
       </c>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B95" t="s">
         <v>14</v>
       </c>
-      <c r="C95" s="3" t="s">
+      <c r="C95" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="D95">
-        <v>94</v>
-      </c>
-      <c r="E95" s="3">
+      <c r="D95" s="2">
+        <v>72</v>
+      </c>
+      <c r="E95" s="2">
         <v>2300</v>
       </c>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B96" t="s">
         <v>14</v>
       </c>
-      <c r="C96" s="3" t="s">
+      <c r="C96" s="2" t="s">
         <v>30</v>
       </c>
       <c r="D96">
         <v>151</v>
       </c>
-      <c r="E96" s="3">
+      <c r="E96" s="2">
         <v>2300</v>
       </c>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B97" t="s">
         <v>16</v>
       </c>
-      <c r="C97" s="3" t="s">
+      <c r="C97" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="D97" s="3">
+      <c r="D97" s="2">
         <v>1500</v>
       </c>
-      <c r="E97" s="3">
-        <v>5700</v>
+      <c r="E97" s="2">
+        <v>6000</v>
       </c>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B98" t="s">
         <v>16</v>
       </c>
-      <c r="C98" s="3" t="s">
+      <c r="C98" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="D98">
-        <v>103</v>
-      </c>
-      <c r="E98" s="3">
-        <v>5700</v>
+      <c r="D98" s="2">
+        <v>120</v>
+      </c>
+      <c r="E98" s="2">
+        <v>6000</v>
       </c>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B99" t="s">
         <v>16</v>
       </c>
-      <c r="C99" s="3" t="s">
+      <c r="C99" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="D99" s="3">
+      <c r="D99" s="2">
         <v>14</v>
       </c>
-      <c r="E99" s="3">
-        <v>5700</v>
+      <c r="E99" s="2">
+        <v>6000</v>
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B100" t="s">
         <v>16</v>
       </c>
-      <c r="C100" s="3" t="s">
+      <c r="C100" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="D100">
-        <v>307</v>
-      </c>
-      <c r="E100" s="3">
-        <v>5700</v>
+      <c r="D100" s="2">
+        <v>236</v>
+      </c>
+      <c r="E100" s="2">
+        <v>6000</v>
       </c>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B101" t="s">
         <v>16</v>
       </c>
-      <c r="C101" s="3" t="s">
+      <c r="C101" s="2" t="s">
         <v>30</v>
       </c>
       <c r="D101">
         <v>192</v>
       </c>
-      <c r="E101" s="3">
-        <v>5700</v>
+      <c r="E101" s="2">
+        <v>6000</v>
       </c>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B102" t="s">
         <v>19</v>
       </c>
-      <c r="C102" s="3" t="s">
+      <c r="C102" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="D102" s="3">
+      <c r="D102" s="2">
         <v>1500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="E102" s="2">
         <v>2600</v>
       </c>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B103" t="s">
         <v>19</v>
       </c>
-      <c r="C103" s="3" t="s">
+      <c r="C103" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="D103">
+      <c r="D103" s="2">
         <v>62</v>
       </c>
-      <c r="E103" s="3">
+      <c r="E103" s="2">
         <v>2600</v>
       </c>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B104" t="s">
         <v>19</v>
       </c>
-      <c r="C104" s="3" t="s">
+      <c r="C104" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="D104" s="3">
+      <c r="D104" s="2">
         <v>11</v>
       </c>
-      <c r="E104" s="3">
+      <c r="E104" s="2">
         <v>2600</v>
       </c>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B105" t="s">
         <v>19</v>
       </c>
-      <c r="C105" s="3" t="s">
+      <c r="C105" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="D105">
-        <v>96</v>
-      </c>
-      <c r="E105" s="3">
+      <c r="D105" s="2">
+        <v>74</v>
+      </c>
+      <c r="E105" s="2">
         <v>2600</v>
       </c>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B106" t="s">
         <v>19</v>
       </c>
-      <c r="C106" s="3" t="s">
+      <c r="C106" s="2" t="s">
         <v>30</v>
       </c>
       <c r="D106">
         <v>181</v>
       </c>
-      <c r="E106" s="3">
+      <c r="E106" s="2">
         <v>2600</v>
       </c>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B107" t="s">
         <v>15</v>
       </c>
-      <c r="C107" s="3" t="s">
+      <c r="C107" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="D107" s="3">
+      <c r="D107" s="2">
         <v>1500</v>
       </c>
-      <c r="E107" s="3">
+      <c r="E107" s="2">
         <v>2650</v>
       </c>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B108" t="s">
         <v>15</v>
       </c>
-      <c r="C108" s="3" t="s">
+      <c r="C108" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="D108">
+      <c r="D108" s="2">
         <v>30</v>
       </c>
-      <c r="E108" s="3">
+      <c r="E108" s="2">
         <v>2650</v>
       </c>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B109" t="s">
         <v>15</v>
       </c>
-      <c r="C109" s="3" t="s">
+      <c r="C109" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="D109" s="3">
+      <c r="D109" s="2">
         <v>10</v>
       </c>
-      <c r="E109" s="3">
+      <c r="E109" s="2">
         <v>2650</v>
       </c>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B110" t="s">
         <v>15</v>
       </c>
-      <c r="C110" s="3" t="s">
+      <c r="C110" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="D110">
-        <v>120</v>
-      </c>
-      <c r="E110" s="3">
+      <c r="D110" s="2">
+        <v>92</v>
+      </c>
+      <c r="E110" s="2">
         <v>2650</v>
       </c>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B111" t="s">
         <v>15</v>
       </c>
-      <c r="C111" s="3" t="s">
+      <c r="C111" s="2" t="s">
         <v>30</v>
       </c>
       <c r="D111">
         <v>126</v>
       </c>
-      <c r="E111" s="3">
+      <c r="E111" s="2">
         <v>2650</v>
       </c>
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B112" t="s">
         <v>31</v>
       </c>
-      <c r="C112" s="3" t="s">
+      <c r="C112" s="2" t="s">
         <v>22</v>
       </c>
       <c r="D112">
         <v>27700</v>
       </c>
-      <c r="E112" s="3">
-        <v>53500</v>
+      <c r="E112" s="2">
+        <v>53800</v>
       </c>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B113" t="s">
         <v>31</v>
       </c>
-      <c r="C113" s="3" t="s">
+      <c r="C113" s="2" t="s">
         <v>27</v>
       </c>
       <c r="D113">
-        <v>840</v>
-      </c>
-      <c r="E113" s="3">
-        <v>53500</v>
+        <v>857</v>
+      </c>
+      <c r="E113" s="2">
+        <v>53800</v>
       </c>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B114" t="s">
         <v>31</v>
       </c>
-      <c r="C114" s="3" t="s">
+      <c r="C114" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D114">
         <v>131</v>
       </c>
-      <c r="E114" s="3">
-        <v>53500</v>
+      <c r="E114" s="2">
+        <v>53800</v>
       </c>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B115" t="s">
         <v>31</v>
       </c>
-      <c r="C115" s="3" t="s">
+      <c r="C115" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="D115">
-        <v>2433</v>
-      </c>
-      <c r="E115" s="3">
-        <v>53500</v>
+      <c r="D115" s="2">
+        <v>1858</v>
+      </c>
+      <c r="E115" s="2">
+        <v>53800</v>
       </c>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B116" t="s">
         <v>31</v>
       </c>
-      <c r="C116" s="3" t="s">
+      <c r="C116" s="2" t="s">
         <v>30</v>
       </c>
       <c r="D116">
         <v>2738</v>
       </c>
-      <c r="E116" s="3">
-        <v>53500</v>
+      <c r="E116" s="2">
+        <v>53800</v>
       </c>
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
+        <v>34</v>
+      </c>
+      <c r="B117" t="s">
         <v>33</v>
       </c>
-      <c r="B117" t="s">
-        <v>34</v>
-      </c>
-      <c r="C117" s="3" t="s">
+      <c r="C117" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="D117" s="3">
+      <c r="D117" s="2">
         <v>1500</v>
       </c>
-      <c r="E117" s="3">
+      <c r="E117" s="2">
         <v>5700</v>
       </c>
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
+        <v>34</v>
+      </c>
+      <c r="B118" t="s">
         <v>33</v>
       </c>
-      <c r="B118" t="s">
-        <v>34</v>
-      </c>
-      <c r="C118" s="3" t="s">
+      <c r="C118" s="2" t="s">
         <v>27</v>
       </c>
       <c r="D118">
-        <v>103</v>
-      </c>
-      <c r="E118" s="3">
+        <v>17</v>
+      </c>
+      <c r="E118" s="2">
         <v>5700</v>
       </c>
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
+        <v>34</v>
+      </c>
+      <c r="B119" t="s">
         <v>33</v>
       </c>
-      <c r="B119" t="s">
-        <v>34</v>
-      </c>
-      <c r="C119" s="3" t="s">
+      <c r="C119" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="D119" s="3">
+      <c r="D119" s="2">
         <v>14</v>
       </c>
-      <c r="E119" s="3">
+      <c r="E119" s="2">
         <v>5700</v>
       </c>
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
+        <v>34</v>
+      </c>
+      <c r="B120" t="s">
         <v>33</v>
       </c>
-      <c r="B120" t="s">
-        <v>34</v>
-      </c>
-      <c r="C120" s="3" t="s">
+      <c r="C120" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="D120">
-        <v>2433</v>
-      </c>
-      <c r="E120" s="3">
+      <c r="D120" s="2">
+        <v>1858</v>
+      </c>
+      <c r="E120" s="2">
         <v>5700</v>
       </c>
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
+        <v>34</v>
+      </c>
+      <c r="B121" t="s">
         <v>33</v>
       </c>
-      <c r="B121" t="s">
-        <v>34</v>
-      </c>
-      <c r="C121" s="3" t="s">
+      <c r="C121" s="2" t="s">
         <v>30</v>
       </c>
       <c r="D121">
         <v>192</v>
       </c>
-      <c r="E121" s="3">
+      <c r="E121" s="2">
         <v>5700</v>
       </c>
     </row>
-    <row r="122" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B122" s="3"/>
-      <c r="C122" s="3"/>
-      <c r="D122" s="3"/>
-      <c r="E122" s="3"/>
-    </row>
-    <row r="123" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B123" s="3"/>
-      <c r="C123" s="3"/>
-      <c r="D123" s="3"/>
-      <c r="E123" s="3"/>
-    </row>
-    <row r="124" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B124" s="3"/>
-      <c r="C124" s="3"/>
-      <c r="D124" s="3"/>
-      <c r="E124" s="3"/>
-    </row>
-    <row r="125" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B125" s="3"/>
-      <c r="C125" s="3"/>
-      <c r="E125" s="3"/>
-    </row>
-    <row r="126" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B126" s="3"/>
-      <c r="C126" s="3"/>
-      <c r="E126" s="3"/>
-    </row>
-    <row r="127" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B127" s="3"/>
-      <c r="C127" s="3"/>
-      <c r="E127" s="3"/>
-    </row>
-    <row r="128" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C128" s="3"/>
-      <c r="D128" s="3"/>
-      <c r="E128" s="3"/>
-    </row>
-    <row r="129" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C129" s="3"/>
-      <c r="E129" s="3"/>
-    </row>
-    <row r="130" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C130" s="3"/>
-      <c r="D130" s="3"/>
-      <c r="E130" s="3"/>
-    </row>
-    <row r="131" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C131" s="3"/>
-      <c r="E131" s="3"/>
-    </row>
-    <row r="132" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C132" s="3"/>
-      <c r="E132" s="3"/>
-    </row>
-    <row r="133" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C133" s="3"/>
-      <c r="E133" s="3"/>
-    </row>
-    <row r="134" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C134" s="3"/>
-      <c r="D134" s="3"/>
-      <c r="E134" s="3"/>
-    </row>
-    <row r="135" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C135" s="3"/>
-      <c r="E135" s="3"/>
-    </row>
-    <row r="136" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C136" s="3"/>
-      <c r="D136" s="3"/>
-      <c r="E136" s="3"/>
-    </row>
-    <row r="137" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C137" s="3"/>
-      <c r="E137" s="3"/>
-    </row>
-    <row r="138" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C138" s="3"/>
-      <c r="E138" s="3"/>
-    </row>
-    <row r="139" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C139" s="3"/>
-      <c r="E139" s="3"/>
-    </row>
-    <row r="140" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C140" s="3"/>
-      <c r="D140" s="3"/>
-      <c r="E140" s="3"/>
-    </row>
-    <row r="141" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C141" s="3"/>
-      <c r="E141" s="3"/>
-    </row>
-    <row r="142" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C142" s="3"/>
-      <c r="D142" s="3"/>
-      <c r="E142" s="3"/>
-    </row>
-    <row r="143" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C143" s="3"/>
-      <c r="E143" s="3"/>
-    </row>
-    <row r="144" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C144" s="3"/>
-      <c r="E144" s="3"/>
-    </row>
-    <row r="145" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C145" s="3"/>
-      <c r="E145" s="3"/>
-    </row>
-    <row r="146" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C146" s="3"/>
-      <c r="D146" s="3"/>
-      <c r="E146" s="3"/>
-    </row>
-    <row r="147" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C147" s="3"/>
-      <c r="E147" s="3"/>
-    </row>
-    <row r="148" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C148" s="3"/>
-      <c r="D148" s="3"/>
-      <c r="E148" s="3"/>
-    </row>
-    <row r="149" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C149" s="3"/>
-      <c r="E149" s="3"/>
-    </row>
-    <row r="150" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C150" s="3"/>
-      <c r="E150" s="3"/>
-    </row>
-    <row r="151" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C151" s="3"/>
-      <c r="E151" s="3"/>
-    </row>
-    <row r="152" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C152" s="3"/>
-      <c r="D152" s="3"/>
-      <c r="E152" s="3"/>
-    </row>
-    <row r="153" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C153" s="3"/>
-      <c r="E153" s="3"/>
-    </row>
-    <row r="154" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C154" s="3"/>
-      <c r="D154" s="3"/>
-      <c r="E154" s="3"/>
-    </row>
-    <row r="155" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C155" s="3"/>
-      <c r="E155" s="3"/>
-    </row>
-    <row r="156" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C156" s="3"/>
-      <c r="E156" s="3"/>
-    </row>
-    <row r="157" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C157" s="3"/>
-      <c r="E157" s="3"/>
-    </row>
-    <row r="158" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C158" s="3"/>
-      <c r="D158" s="3"/>
-      <c r="E158" s="3"/>
-    </row>
-    <row r="159" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C159" s="3"/>
-      <c r="E159" s="3"/>
-    </row>
-    <row r="160" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C160" s="3"/>
-      <c r="D160" s="3"/>
-      <c r="E160" s="3"/>
-    </row>
-    <row r="161" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="C161" s="3"/>
-      <c r="E161" s="3"/>
-    </row>
-    <row r="162" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="C162" s="3"/>
-      <c r="E162" s="3"/>
-    </row>
-    <row r="163" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="C163" s="3"/>
-      <c r="E163" s="3"/>
-    </row>
-    <row r="164" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="C164" s="3"/>
-      <c r="D164" s="3"/>
-      <c r="E164" s="3"/>
-    </row>
-    <row r="165" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="C165" s="3"/>
-      <c r="E165" s="3"/>
-    </row>
-    <row r="166" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="C166" s="3"/>
-      <c r="D166" s="3"/>
-      <c r="E166" s="3"/>
-    </row>
-    <row r="167" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="C167" s="3"/>
-      <c r="E167" s="3"/>
-    </row>
-    <row r="168" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="C168" s="3"/>
-      <c r="E168" s="3"/>
-    </row>
-    <row r="169" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="C169" s="3"/>
-      <c r="E169" s="3"/>
-    </row>
-    <row r="170" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B170" s="1"/>
-      <c r="C170" s="3"/>
-      <c r="D170" s="3"/>
-      <c r="E170" s="3"/>
-    </row>
-    <row r="171" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="C171" s="3"/>
-      <c r="E171" s="3"/>
-    </row>
-    <row r="172" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="C172" s="3"/>
-      <c r="D172" s="3"/>
-      <c r="E172" s="3"/>
-    </row>
-    <row r="173" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="C173" s="3"/>
-      <c r="E173" s="3"/>
-    </row>
-    <row r="174" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="C174" s="3"/>
-      <c r="E174" s="3"/>
-    </row>
-    <row r="175" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="C175" s="3"/>
-      <c r="E175" s="3"/>
-    </row>
-    <row r="176" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="C176" s="3"/>
-      <c r="D176" s="3"/>
-      <c r="E176" s="3"/>
-    </row>
-    <row r="177" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C177" s="3"/>
-      <c r="E177" s="3"/>
-    </row>
-    <row r="178" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C178" s="3"/>
-      <c r="D178" s="3"/>
-      <c r="E178" s="3"/>
-    </row>
-    <row r="179" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C179" s="3"/>
-      <c r="E179" s="3"/>
-    </row>
-    <row r="180" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C180" s="3"/>
-      <c r="E180" s="3"/>
-    </row>
-    <row r="181" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C181" s="3"/>
-      <c r="E181" s="3"/>
-    </row>
-    <row r="182" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C182" s="3"/>
-      <c r="D182" s="3"/>
-      <c r="E182" s="3"/>
-    </row>
-    <row r="183" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C183" s="3"/>
-      <c r="E183" s="3"/>
-    </row>
-    <row r="184" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C184" s="3"/>
-      <c r="D184" s="3"/>
-      <c r="E184" s="3"/>
-    </row>
-    <row r="185" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C185" s="3"/>
-      <c r="E185" s="3"/>
-    </row>
-    <row r="186" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C186" s="3"/>
-      <c r="E186" s="3"/>
-    </row>
-    <row r="187" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C187" s="3"/>
-      <c r="E187" s="3"/>
-    </row>
-    <row r="188" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C188" s="3"/>
-      <c r="D188" s="3"/>
-      <c r="E188" s="3"/>
-    </row>
-    <row r="189" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C189" s="3"/>
-      <c r="E189" s="3"/>
-    </row>
-    <row r="190" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C190" s="3"/>
-      <c r="D190" s="3"/>
-      <c r="E190" s="3"/>
-    </row>
-    <row r="191" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C191" s="3"/>
-      <c r="E191" s="3"/>
-    </row>
-    <row r="192" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C192" s="3"/>
-      <c r="E192" s="3"/>
-    </row>
-    <row r="193" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C193" s="3"/>
-      <c r="E193" s="3"/>
-    </row>
-    <row r="194" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C194" s="3"/>
-      <c r="D194" s="3"/>
-      <c r="E194" s="3"/>
-    </row>
-    <row r="195" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C195" s="3"/>
-      <c r="E195" s="3"/>
-    </row>
-    <row r="196" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C196" s="3"/>
-      <c r="D196" s="3"/>
-      <c r="E196" s="3"/>
-    </row>
-    <row r="197" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C197" s="3"/>
-      <c r="E197" s="3"/>
-    </row>
-    <row r="198" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C198" s="3"/>
-      <c r="E198" s="3"/>
-    </row>
-    <row r="199" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C199" s="3"/>
-      <c r="E199" s="3"/>
-    </row>
-    <row r="200" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C200" s="3"/>
-      <c r="D200" s="3"/>
-      <c r="E200" s="3"/>
-    </row>
-    <row r="201" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C201" s="3"/>
-      <c r="E201" s="3"/>
-    </row>
-    <row r="202" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C202" s="3"/>
-      <c r="D202" s="3"/>
-      <c r="E202" s="3"/>
-    </row>
-    <row r="203" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C203" s="3"/>
-      <c r="E203" s="3"/>
-    </row>
-    <row r="204" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C204" s="3"/>
-      <c r="E204" s="3"/>
-    </row>
-    <row r="205" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C205" s="3"/>
-      <c r="E205" s="3"/>
-    </row>
-    <row r="206" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C206" s="3"/>
-      <c r="D206" s="3"/>
-      <c r="E206" s="3"/>
-    </row>
-    <row r="207" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C207" s="3"/>
-      <c r="E207" s="3"/>
-    </row>
-    <row r="208" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C208" s="3"/>
-      <c r="D208" s="3"/>
-      <c r="E208" s="3"/>
-    </row>
-    <row r="209" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C209" s="3"/>
-      <c r="E209" s="3"/>
-    </row>
-    <row r="210" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C210" s="3"/>
-      <c r="E210" s="3"/>
-    </row>
-    <row r="211" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C211" s="3"/>
-      <c r="E211" s="3"/>
-    </row>
-    <row r="212" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C212" s="3"/>
-      <c r="E212" s="3"/>
-    </row>
-    <row r="213" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C213" s="3"/>
-      <c r="E213" s="3"/>
-    </row>
-    <row r="214" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C214" s="3"/>
-      <c r="E214" s="3"/>
-    </row>
-    <row r="215" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C215" s="3"/>
-      <c r="E215" s="3"/>
-    </row>
-    <row r="216" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C216" s="3"/>
-      <c r="E216" s="3"/>
-    </row>
-    <row r="217" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C217" s="3"/>
-      <c r="E217" s="3"/>
-    </row>
-    <row r="218" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C218" s="3"/>
-      <c r="D218" s="3"/>
-      <c r="E218" s="3"/>
-    </row>
-    <row r="219" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C219" s="3"/>
-      <c r="E219" s="3"/>
-    </row>
-    <row r="220" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C220" s="3"/>
-      <c r="D220" s="3"/>
-      <c r="E220" s="3"/>
-    </row>
-    <row r="221" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C221" s="3"/>
-      <c r="E221" s="3"/>
-    </row>
-    <row r="222" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C222" s="3"/>
-      <c r="E222" s="3"/>
-    </row>
-    <row r="223" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C223" s="3"/>
-      <c r="E223" s="3"/>
-    </row>
-    <row r="224" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C224" s="3"/>
-      <c r="D224" s="3"/>
-      <c r="E224" s="3"/>
-    </row>
-    <row r="225" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C225" s="3"/>
-      <c r="E225" s="3"/>
-    </row>
-    <row r="226" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C226" s="3"/>
-      <c r="D226" s="3"/>
-      <c r="E226" s="3"/>
-    </row>
-    <row r="227" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C227" s="3"/>
-      <c r="E227" s="3"/>
-    </row>
-    <row r="228" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C228" s="3"/>
-      <c r="E228" s="3"/>
-    </row>
-    <row r="229" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C229" s="3"/>
-      <c r="E229" s="3"/>
-    </row>
-    <row r="230" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C230" s="3"/>
-      <c r="D230" s="3"/>
-      <c r="E230" s="3"/>
-    </row>
-    <row r="231" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C231" s="3"/>
-      <c r="E231" s="3"/>
-    </row>
-    <row r="232" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C232" s="3"/>
-      <c r="D232" s="3"/>
-      <c r="E232" s="3"/>
-    </row>
-    <row r="233" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C233" s="3"/>
-      <c r="E233" s="3"/>
-    </row>
-    <row r="234" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C234" s="3"/>
-      <c r="E234" s="3"/>
-    </row>
-    <row r="235" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C235" s="3"/>
-      <c r="E235" s="3"/>
-    </row>
-    <row r="236" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C236" s="3"/>
-      <c r="D236" s="3"/>
-      <c r="E236" s="3"/>
-    </row>
-    <row r="237" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C237" s="3"/>
-      <c r="E237" s="3"/>
-    </row>
-    <row r="238" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C238" s="3"/>
-      <c r="D238" s="3"/>
-      <c r="E238" s="3"/>
-    </row>
-    <row r="239" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C239" s="3"/>
-      <c r="E239" s="3"/>
-    </row>
-    <row r="240" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C240" s="3"/>
-      <c r="E240" s="3"/>
-    </row>
-    <row r="241" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C241" s="3"/>
-      <c r="E241" s="3"/>
-    </row>
-    <row r="242" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C242" s="3"/>
-      <c r="D242" s="3"/>
-      <c r="E242" s="3"/>
-    </row>
-    <row r="243" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C243" s="3"/>
-      <c r="E243" s="3"/>
-    </row>
-    <row r="244" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C244" s="3"/>
-      <c r="D244" s="3"/>
-      <c r="E244" s="3"/>
-    </row>
-    <row r="245" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C245" s="3"/>
-      <c r="E245" s="3"/>
-    </row>
-    <row r="246" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C246" s="3"/>
-      <c r="E246" s="3"/>
-    </row>
-    <row r="247" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C247" s="3"/>
-      <c r="E247" s="3"/>
-    </row>
-    <row r="248" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C248" s="3"/>
-      <c r="E248" s="3"/>
-    </row>
-    <row r="249" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C249" s="3"/>
-      <c r="E249" s="3"/>
-    </row>
-    <row r="250" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C250" s="3"/>
-      <c r="E250" s="3"/>
-    </row>
-    <row r="251" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C251" s="3"/>
-      <c r="E251" s="3"/>
-    </row>
-    <row r="252" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C252" s="3"/>
-      <c r="E252" s="3"/>
-    </row>
-    <row r="253" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C253" s="3"/>
-      <c r="E253" s="3"/>
-    </row>
   </sheetData>
-  <autoFilter ref="B1:E121" xr:uid="{6956BB2C-DA9E-4412-BCD4-BB80A11153FE}"/>
+  <autoFilter ref="A1:E121" xr:uid="{6956BB2C-DA9E-4412-BCD4-BB80A11153FE}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/data/metas.xlsx
+++ b/data/metas.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sercomunicaciones2-my.sharepoint.com/personal/auxcomisiones_sercomunicaciones_com/Documents/PAOLA/AUXCOMISIÓN/3 Liquidación CVS comerciales/2026/03 Marzo/Liquidacióncvs/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sercomunicaciones2-my.sharepoint.com/personal/auxcomisiones_sercomunicaciones_com/Documents/PAOLA/AUXCOMISIÓN/3 Liquidación CVS comerciales/2026/02 Febrero/Liquidacióncvs - copia/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="716" documentId="8_{787D9E49-702D-43BD-B99B-4B64F775E77B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F09CCFEB-F04B-42F9-99CA-A38399CBEAA4}"/>
+  <xr:revisionPtr revIDLastSave="554" documentId="8_{787D9E49-702D-43BD-B99B-4B64F775E77B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B8BA1849-1829-4ACB-997B-547C10867E8F}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D1391136-BBFC-43C7-B899-B77B0ECC5956}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$A$1:$E$121</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$B$1:$E$121</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -140,10 +140,10 @@
     <t>Mes</t>
   </si>
   <si>
+    <t>Febrero</t>
+  </si>
+  <si>
     <t>NUMERARIO</t>
-  </si>
-  <si>
-    <t>Marzo</t>
   </si>
 </sst>
 </file>
@@ -175,7 +175,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -183,12 +183,28 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -530,7 +546,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6956BB2C-DA9E-4412-BCD4-BB80A11153FE}">
-  <dimension ref="A1:E121"/>
+  <dimension ref="A1:E253"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.7109375" bestFit="1" customWidth="1"/>
@@ -540,2064 +556,2640 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B2" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D2" s="2">
+      <c r="D2" s="3">
         <v>1500</v>
       </c>
-      <c r="E2" s="2">
+      <c r="E2" s="3">
         <v>2800</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>34</v>
-      </c>
-      <c r="B3" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="D3" s="2">
+      <c r="D3" s="3">
         <v>47</v>
       </c>
-      <c r="E3" s="2">
+      <c r="E3" s="3">
         <v>2800</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>34</v>
-      </c>
-      <c r="B4" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="D4" s="2">
+      <c r="D4" s="3">
         <v>10</v>
       </c>
-      <c r="E4" s="2">
+      <c r="E4" s="3">
         <v>2800</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>34</v>
-      </c>
-      <c r="B5" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="D5" s="2">
-        <v>95</v>
-      </c>
-      <c r="E5" s="2">
+      <c r="D5" s="3">
+        <v>124</v>
+      </c>
+      <c r="E5" s="3">
         <v>2800</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>34</v>
-      </c>
-      <c r="B6" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="D6" s="2">
+      <c r="D6" s="3">
         <v>146</v>
       </c>
-      <c r="E6" s="2">
+      <c r="E6" s="3">
         <v>2800</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>34</v>
-      </c>
-      <c r="B7" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B7" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D7" s="2">
+      <c r="D7" s="3">
         <v>1500</v>
       </c>
-      <c r="E7" s="2">
+      <c r="E7" s="3">
         <v>2400</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>34</v>
-      </c>
-      <c r="B8" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B8" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C8" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="D8" s="2">
+      <c r="D8" s="3">
         <v>37</v>
       </c>
-      <c r="E8" s="2">
+      <c r="E8" s="3">
         <v>2400</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>34</v>
-      </c>
-      <c r="B9" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B9" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="C9" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="D9" s="2">
+      <c r="D9" s="3">
         <v>6</v>
       </c>
-      <c r="E9" s="2">
+      <c r="E9" s="3">
         <v>2400</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>34</v>
-      </c>
-      <c r="B10" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B10" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="C10" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="D10" s="2">
-        <v>82</v>
-      </c>
-      <c r="E10" s="2">
+      <c r="D10">
+        <v>107</v>
+      </c>
+      <c r="E10" s="3">
         <v>2400</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>34</v>
-      </c>
-      <c r="B11" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B11" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="C11" s="3" t="s">
         <v>30</v>
       </c>
       <c r="D11">
         <v>95</v>
       </c>
-      <c r="E11" s="2">
+      <c r="E11" s="3">
         <v>2400</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B12" t="s">
         <v>2</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="C12" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D12" s="2">
+      <c r="D12" s="3">
         <v>0</v>
       </c>
-      <c r="E12" s="2">
+      <c r="E12" s="3">
         <v>1350</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B13" t="s">
         <v>2</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="C13" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="D13" s="2">
+      <c r="D13">
         <v>12</v>
       </c>
-      <c r="E13" s="2">
+      <c r="E13" s="3">
         <v>1350</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B14" t="s">
         <v>2</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="C14" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="D14" s="2">
+      <c r="D14" s="3">
         <v>4</v>
       </c>
-      <c r="E14" s="2">
+      <c r="E14" s="3">
         <v>1350</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B15" t="s">
         <v>2</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="C15" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="D15" s="2">
-        <v>50</v>
-      </c>
-      <c r="E15" s="2">
+      <c r="D15">
+        <v>65</v>
+      </c>
+      <c r="E15" s="3">
         <v>1350</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B16" t="s">
         <v>2</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="C16" s="3" t="s">
         <v>30</v>
       </c>
       <c r="D16">
         <v>32</v>
       </c>
-      <c r="E16" s="2">
+      <c r="E16" s="3">
         <v>1350</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B17" t="s">
         <v>3</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="C17" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D17" s="2">
+      <c r="D17" s="3">
         <v>800</v>
       </c>
-      <c r="E17" s="2">
+      <c r="E17" s="3">
         <v>1700</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B18" t="s">
         <v>3</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="C18" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="D18" s="2">
-        <v>33</v>
-      </c>
-      <c r="E18" s="2">
+      <c r="D18">
+        <v>33</v>
+      </c>
+      <c r="E18" s="3">
         <v>1700</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B19" t="s">
         <v>3</v>
       </c>
-      <c r="C19" s="2" t="s">
+      <c r="C19" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="D19" s="2">
+      <c r="D19" s="3">
         <v>1</v>
       </c>
-      <c r="E19" s="2">
+      <c r="E19" s="3">
         <v>1700</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B20" t="s">
         <v>3</v>
       </c>
-      <c r="C20" s="2" t="s">
+      <c r="C20" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="D20" s="2">
-        <v>65</v>
-      </c>
-      <c r="E20" s="2">
+      <c r="D20">
+        <v>85</v>
+      </c>
+      <c r="E20" s="3">
         <v>1700</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B21" t="s">
         <v>3</v>
       </c>
-      <c r="C21" s="2" t="s">
+      <c r="C21" s="3" t="s">
         <v>30</v>
       </c>
       <c r="D21">
         <v>135</v>
       </c>
-      <c r="E21" s="2">
+      <c r="E21" s="3">
         <v>1700</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B22" t="s">
         <v>8</v>
       </c>
-      <c r="C22" s="2" t="s">
+      <c r="C22" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D22" s="2">
+      <c r="D22" s="3">
         <v>1200</v>
       </c>
-      <c r="E22" s="2">
+      <c r="E22" s="3">
         <v>1450</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B23" t="s">
         <v>8</v>
       </c>
-      <c r="C23" s="2" t="s">
+      <c r="C23" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="D23" s="2">
+      <c r="D23">
         <v>18</v>
       </c>
-      <c r="E23" s="2">
+      <c r="E23" s="3">
         <v>1450</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B24" t="s">
         <v>8</v>
       </c>
-      <c r="C24" s="2" t="s">
+      <c r="C24" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="D24" s="2">
+      <c r="D24" s="3">
         <v>1</v>
       </c>
-      <c r="E24" s="2">
+      <c r="E24" s="3">
         <v>1450</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B25" t="s">
         <v>8</v>
       </c>
-      <c r="C25" s="2" t="s">
+      <c r="C25" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="D25" s="2">
-        <v>50</v>
-      </c>
-      <c r="E25" s="2">
+      <c r="D25">
+        <v>65</v>
+      </c>
+      <c r="E25" s="3">
         <v>1450</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B26" t="s">
         <v>8</v>
       </c>
-      <c r="C26" s="2" t="s">
+      <c r="C26" s="3" t="s">
         <v>30</v>
       </c>
       <c r="D26">
         <v>69</v>
       </c>
-      <c r="E26" s="2">
+      <c r="E26" s="3">
         <v>1450</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B27" t="s">
         <v>10</v>
       </c>
-      <c r="C27" s="2" t="s">
+      <c r="C27" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="2">
+      <c r="D27" s="3">
         <v>1200</v>
       </c>
-      <c r="E27" s="2">
+      <c r="E27" s="3">
         <v>1500</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B28" t="s">
         <v>10</v>
       </c>
-      <c r="C28" s="2" t="s">
+      <c r="C28" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="D28" s="2">
+      <c r="D28">
         <v>37</v>
       </c>
-      <c r="E28" s="2">
+      <c r="E28" s="3">
         <v>1500</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B29" t="s">
         <v>10</v>
       </c>
-      <c r="C29" s="2" t="s">
+      <c r="C29" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="D29" s="2">
+      <c r="D29" s="3">
         <v>1</v>
       </c>
-      <c r="E29" s="2">
+      <c r="E29" s="3">
         <v>1500</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B30" t="s">
         <v>10</v>
       </c>
-      <c r="C30" s="2" t="s">
+      <c r="C30" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="D30" s="2">
-        <v>45</v>
-      </c>
-      <c r="E30" s="2">
+      <c r="D30">
+        <v>59</v>
+      </c>
+      <c r="E30" s="3">
         <v>1500</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B31" t="s">
         <v>10</v>
       </c>
-      <c r="C31" s="2" t="s">
+      <c r="C31" s="3" t="s">
         <v>30</v>
       </c>
       <c r="D31">
         <v>68</v>
       </c>
-      <c r="E31" s="2">
+      <c r="E31" s="3">
         <v>1500</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B32" t="s">
         <v>9</v>
       </c>
-      <c r="C32" s="2" t="s">
+      <c r="C32" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D32" s="2">
+      <c r="D32" s="3">
         <v>1500</v>
       </c>
-      <c r="E32" s="2">
+      <c r="E32" s="3">
         <v>4000</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B33" t="s">
         <v>9</v>
       </c>
-      <c r="C33" s="2" t="s">
+      <c r="C33" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="D33" s="2">
+      <c r="D33">
         <v>42</v>
       </c>
-      <c r="E33" s="2">
+      <c r="E33" s="3">
         <v>4000</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B34" t="s">
         <v>9</v>
       </c>
-      <c r="C34" s="2" t="s">
+      <c r="C34" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="D34" s="2">
+      <c r="D34" s="3">
         <v>1</v>
       </c>
-      <c r="E34" s="2">
+      <c r="E34" s="3">
         <v>4000</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B35" t="s">
         <v>9</v>
       </c>
-      <c r="C35" s="2" t="s">
+      <c r="C35" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="D35" s="2">
-        <v>160</v>
-      </c>
-      <c r="E35" s="2">
+      <c r="D35">
+        <v>208</v>
+      </c>
+      <c r="E35" s="3">
         <v>4000</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B36" t="s">
         <v>9</v>
       </c>
-      <c r="C36" s="2" t="s">
+      <c r="C36" s="3" t="s">
         <v>30</v>
       </c>
       <c r="D36">
         <v>176</v>
       </c>
-      <c r="E36" s="2">
+      <c r="E36" s="3">
         <v>4000</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B37" t="s">
         <v>13</v>
       </c>
-      <c r="C37" s="2" t="s">
+      <c r="C37" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D37" s="2">
+      <c r="D37" s="3">
         <v>1500</v>
       </c>
-      <c r="E37" s="2">
+      <c r="E37" s="3">
         <v>2600</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B38" t="s">
         <v>13</v>
       </c>
-      <c r="C38" s="2" t="s">
+      <c r="C38" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="D38" s="2">
+      <c r="D38">
         <v>26</v>
       </c>
-      <c r="E38" s="2">
+      <c r="E38" s="3">
         <v>2600</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B39" t="s">
         <v>13</v>
       </c>
-      <c r="C39" s="2" t="s">
+      <c r="C39" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="D39" s="2">
+      <c r="D39" s="3">
         <v>1</v>
       </c>
-      <c r="E39" s="2">
+      <c r="E39" s="3">
         <v>2600</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B40" t="s">
         <v>13</v>
       </c>
-      <c r="C40" s="2" t="s">
+      <c r="C40" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="D40" s="2">
-        <v>130</v>
-      </c>
-      <c r="E40" s="2">
+      <c r="D40">
+        <v>182</v>
+      </c>
+      <c r="E40" s="3">
         <v>2600</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B41" t="s">
         <v>13</v>
       </c>
-      <c r="C41" s="2" t="s">
+      <c r="C41" s="3" t="s">
         <v>30</v>
       </c>
       <c r="D41">
         <v>98</v>
       </c>
-      <c r="E41" s="2">
+      <c r="E41" s="3">
         <v>2600</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B42" t="s">
         <v>7</v>
       </c>
-      <c r="C42" s="2" t="s">
+      <c r="C42" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D42" s="2">
+      <c r="D42" s="3">
         <v>1200</v>
       </c>
-      <c r="E42" s="2">
+      <c r="E42" s="3">
         <v>2000</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B43" t="s">
         <v>7</v>
       </c>
-      <c r="C43" s="2" t="s">
+      <c r="C43" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="D43" s="2">
+      <c r="D43">
         <v>32</v>
       </c>
-      <c r="E43" s="2">
+      <c r="E43" s="3">
         <v>2000</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B44" t="s">
         <v>7</v>
       </c>
-      <c r="C44" s="2" t="s">
+      <c r="C44" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="D44" s="2">
+      <c r="D44" s="3">
         <v>6</v>
       </c>
-      <c r="E44" s="2">
+      <c r="E44" s="3">
         <v>2000</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B45" t="s">
         <v>7</v>
       </c>
-      <c r="C45" s="2" t="s">
+      <c r="C45" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="D45" s="2">
-        <v>56</v>
-      </c>
-      <c r="E45" s="2">
+      <c r="D45">
+        <v>73</v>
+      </c>
+      <c r="E45" s="3">
         <v>2000</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B46" t="s">
         <v>7</v>
       </c>
-      <c r="C46" s="2" t="s">
+      <c r="C46" s="3" t="s">
         <v>30</v>
       </c>
       <c r="D46">
         <v>128</v>
       </c>
-      <c r="E46" s="2">
+      <c r="E46" s="3">
         <v>2000</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>34</v>
-      </c>
-      <c r="B47" t="s">
+        <v>33</v>
+      </c>
+      <c r="B47" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C47" s="2" t="s">
+      <c r="C47" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D47" s="2">
+      <c r="D47" s="3">
         <v>1200</v>
       </c>
-      <c r="E47" s="2">
+      <c r="E47" s="3">
         <v>1500</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B48" t="s">
         <v>12</v>
       </c>
-      <c r="C48" s="2" t="s">
+      <c r="C48" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="D48" s="2">
+      <c r="D48">
         <v>17</v>
       </c>
-      <c r="E48" s="2">
+      <c r="E48" s="3">
         <v>1500</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B49" t="s">
         <v>12</v>
       </c>
-      <c r="C49" s="2" t="s">
+      <c r="C49" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="D49" s="2">
+      <c r="D49" s="3">
         <v>6</v>
       </c>
-      <c r="E49" s="2">
+      <c r="E49" s="3">
         <v>1500</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B50" t="s">
         <v>12</v>
       </c>
-      <c r="C50" s="2" t="s">
+      <c r="C50" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="D50" s="2">
-        <v>25</v>
-      </c>
-      <c r="E50" s="2">
+      <c r="D50">
+        <v>33</v>
+      </c>
+      <c r="E50" s="3">
         <v>1500</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B51" t="s">
         <v>12</v>
       </c>
-      <c r="C51" s="2" t="s">
+      <c r="C51" s="3" t="s">
         <v>30</v>
       </c>
       <c r="D51">
         <v>54</v>
       </c>
-      <c r="E51" s="2">
+      <c r="E51" s="3">
         <v>1500</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B52" t="s">
         <v>17</v>
       </c>
-      <c r="C52" s="2" t="s">
+      <c r="C52" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D52" s="2">
+      <c r="D52" s="3">
         <v>800</v>
       </c>
-      <c r="E52" s="2">
+      <c r="E52" s="3">
         <v>2000</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B53" t="s">
         <v>17</v>
       </c>
-      <c r="C53" s="2" t="s">
+      <c r="C53" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="D53" s="2">
+      <c r="D53">
         <v>13</v>
       </c>
-      <c r="E53" s="2">
+      <c r="E53" s="3">
         <v>2000</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B54" t="s">
         <v>17</v>
       </c>
-      <c r="C54" s="2" t="s">
+      <c r="C54" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="D54" s="2">
+      <c r="D54" s="3">
         <v>1</v>
       </c>
-      <c r="E54" s="2">
+      <c r="E54" s="3">
         <v>2000</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B55" t="s">
         <v>17</v>
       </c>
-      <c r="C55" s="2" t="s">
+      <c r="C55" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="D55" s="2">
-        <v>82</v>
-      </c>
-      <c r="E55" s="2">
+      <c r="D55">
+        <v>107</v>
+      </c>
+      <c r="E55" s="3">
         <v>2000</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B56" t="s">
         <v>17</v>
       </c>
-      <c r="C56" s="2" t="s">
+      <c r="C56" s="3" t="s">
         <v>30</v>
       </c>
       <c r="D56">
         <v>60</v>
       </c>
-      <c r="E56" s="2">
+      <c r="E56" s="3">
         <v>2000</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B57" t="s">
         <v>18</v>
       </c>
-      <c r="C57" s="2" t="s">
+      <c r="C57" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D57" s="2">
+      <c r="D57" s="3">
         <v>1200</v>
       </c>
-      <c r="E57" s="2">
+      <c r="E57" s="3">
         <v>1100</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B58" t="s">
         <v>18</v>
       </c>
-      <c r="C58" s="2" t="s">
+      <c r="C58" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="D58" s="2">
+      <c r="D58">
         <v>16</v>
       </c>
-      <c r="E58" s="2">
+      <c r="E58" s="3">
         <v>1100</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B59" t="s">
         <v>18</v>
       </c>
-      <c r="C59" s="2" t="s">
+      <c r="C59" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="D59" s="2">
+      <c r="D59" s="3">
         <v>4</v>
       </c>
-      <c r="E59" s="2">
+      <c r="E59" s="3">
         <v>1100</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B60" t="s">
         <v>18</v>
       </c>
-      <c r="C60" s="2" t="s">
+      <c r="C60" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="D60" s="2">
-        <v>30</v>
-      </c>
-      <c r="E60" s="2">
+      <c r="D60">
+        <v>39</v>
+      </c>
+      <c r="E60" s="3">
         <v>1100</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B61" t="s">
         <v>18</v>
       </c>
-      <c r="C61" s="2" t="s">
+      <c r="C61" s="3" t="s">
         <v>30</v>
       </c>
       <c r="D61">
         <v>74</v>
       </c>
-      <c r="E61" s="2">
+      <c r="E61" s="3">
         <v>1100</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B62" t="s">
         <v>20</v>
       </c>
-      <c r="C62" s="2" t="s">
+      <c r="C62" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D62" s="2">
+      <c r="D62" s="3">
         <v>1200</v>
       </c>
-      <c r="E62" s="2">
+      <c r="E62" s="3">
         <v>2200</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B63" t="s">
         <v>20</v>
       </c>
-      <c r="C63" s="2" t="s">
+      <c r="C63" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="D63" s="2">
+      <c r="D63">
         <v>34</v>
       </c>
-      <c r="E63" s="2">
+      <c r="E63" s="3">
         <v>2200</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B64" t="s">
         <v>20</v>
       </c>
-      <c r="C64" s="2" t="s">
+      <c r="C64" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="D64" s="2">
+      <c r="D64" s="3">
         <v>1</v>
       </c>
-      <c r="E64" s="2">
+      <c r="E64" s="3">
         <v>2200</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B65" t="s">
         <v>20</v>
       </c>
-      <c r="C65" s="2" t="s">
+      <c r="C65" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="D65" s="2">
-        <v>60</v>
-      </c>
-      <c r="E65" s="2">
+      <c r="D65">
+        <v>78</v>
+      </c>
+      <c r="E65" s="3">
         <v>2200</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B66" t="s">
         <v>20</v>
       </c>
-      <c r="C66" s="2" t="s">
+      <c r="C66" s="3" t="s">
         <v>30</v>
       </c>
       <c r="D66">
         <v>183</v>
       </c>
-      <c r="E66" s="2">
+      <c r="E66" s="3">
         <v>2200</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B67" t="s">
         <v>21</v>
       </c>
-      <c r="C67" s="2" t="s">
+      <c r="C67" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D67" s="2">
+      <c r="D67" s="3">
         <v>1200</v>
       </c>
-      <c r="E67" s="2">
+      <c r="E67" s="3">
         <v>1600</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B68" t="s">
         <v>21</v>
       </c>
-      <c r="C68" s="2" t="s">
+      <c r="C68" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="D68" s="2">
+      <c r="D68">
         <v>22</v>
       </c>
-      <c r="E68" s="2">
+      <c r="E68" s="3">
         <v>1600</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B69" t="s">
         <v>21</v>
       </c>
-      <c r="C69" s="2" t="s">
+      <c r="C69" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="D69" s="2">
+      <c r="D69" s="3">
         <v>6</v>
       </c>
-      <c r="E69" s="2">
+      <c r="E69" s="3">
         <v>1600</v>
       </c>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B70" t="s">
         <v>21</v>
       </c>
-      <c r="C70" s="2" t="s">
+      <c r="C70" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="D70" s="2">
-        <v>60</v>
-      </c>
-      <c r="E70" s="2">
+      <c r="D70">
+        <v>78</v>
+      </c>
+      <c r="E70" s="3">
         <v>1600</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B71" t="s">
         <v>21</v>
       </c>
-      <c r="C71" s="2" t="s">
+      <c r="C71" s="3" t="s">
         <v>30</v>
       </c>
       <c r="D71">
         <v>168</v>
       </c>
-      <c r="E71" s="2">
+      <c r="E71" s="3">
         <v>1600</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B72" t="s">
         <v>6</v>
       </c>
-      <c r="C72" s="2" t="s">
+      <c r="C72" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D72" s="2">
+      <c r="D72" s="3">
         <v>1200</v>
       </c>
-      <c r="E72" s="2">
+      <c r="E72" s="3">
         <v>2200</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B73" t="s">
         <v>6</v>
       </c>
-      <c r="C73" s="2" t="s">
+      <c r="C73" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="D73" s="2">
+      <c r="D73">
         <v>23</v>
       </c>
-      <c r="E73" s="2">
+      <c r="E73" s="3">
         <v>2200</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B74" t="s">
         <v>6</v>
       </c>
-      <c r="C74" s="2" t="s">
+      <c r="C74" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="D74" s="2">
+      <c r="D74" s="3">
         <v>1</v>
       </c>
-      <c r="E74" s="2">
+      <c r="E74" s="3">
         <v>2200</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B75" t="s">
         <v>6</v>
       </c>
-      <c r="C75" s="2" t="s">
+      <c r="C75" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="D75" s="2">
-        <v>72</v>
-      </c>
-      <c r="E75" s="2">
+      <c r="D75">
+        <v>94</v>
+      </c>
+      <c r="E75" s="3">
         <v>2200</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B76" t="s">
         <v>6</v>
       </c>
-      <c r="C76" s="2" t="s">
+      <c r="C76" s="3" t="s">
         <v>30</v>
       </c>
       <c r="D76">
         <v>92</v>
       </c>
-      <c r="E76" s="2">
+      <c r="E76" s="3">
         <v>2200</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B77" t="s">
         <v>1</v>
       </c>
-      <c r="C77" s="2" t="s">
+      <c r="C77" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D77" s="2">
+      <c r="D77" s="3">
         <v>1500</v>
       </c>
-      <c r="E77" s="2">
+      <c r="E77" s="3">
         <v>2850</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B78" t="s">
         <v>1</v>
       </c>
-      <c r="C78" s="2" t="s">
+      <c r="C78" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="D78" s="2">
+      <c r="D78">
         <v>52</v>
       </c>
-      <c r="E78" s="2">
+      <c r="E78" s="3">
         <v>2850</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B79" t="s">
         <v>1</v>
       </c>
-      <c r="C79" s="2" t="s">
+      <c r="C79" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="D79" s="2">
+      <c r="D79" s="3">
         <v>10</v>
       </c>
-      <c r="E79" s="2">
+      <c r="E79" s="3">
         <v>2850</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B80" t="s">
         <v>1</v>
       </c>
-      <c r="C80" s="2" t="s">
+      <c r="C80" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="D80" s="2">
-        <v>102</v>
-      </c>
-      <c r="E80" s="2">
+      <c r="D80">
+        <v>133</v>
+      </c>
+      <c r="E80" s="3">
         <v>2850</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B81" t="s">
         <v>1</v>
       </c>
-      <c r="C81" s="2" t="s">
+      <c r="C81" s="3" t="s">
         <v>30</v>
       </c>
       <c r="D81">
         <v>129</v>
       </c>
-      <c r="E81" s="2">
+      <c r="E81" s="3">
         <v>2850</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B82" t="s">
         <v>4</v>
       </c>
-      <c r="C82" s="2" t="s">
+      <c r="C82" s="3" t="s">
         <v>22</v>
       </c>
       <c r="D82">
         <v>1500</v>
       </c>
-      <c r="E82" s="2">
+      <c r="E82" s="3">
         <v>3500</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B83" t="s">
         <v>4</v>
       </c>
-      <c r="C83" s="2" t="s">
+      <c r="C83" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="D83" s="2">
+      <c r="D83">
         <v>62</v>
       </c>
-      <c r="E83" s="2">
+      <c r="E83" s="3">
         <v>3500</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B84" t="s">
         <v>4</v>
       </c>
-      <c r="C84" s="2" t="s">
+      <c r="C84" s="3" t="s">
         <v>28</v>
       </c>
       <c r="D84">
         <v>10</v>
       </c>
-      <c r="E84" s="2">
+      <c r="E84" s="3">
         <v>3500</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B85" t="s">
         <v>4</v>
       </c>
-      <c r="C85" s="2" t="s">
+      <c r="C85" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="D85" s="2">
-        <v>124</v>
-      </c>
-      <c r="E85" s="2">
+      <c r="D85">
+        <v>161</v>
+      </c>
+      <c r="E85" s="3">
         <v>3500</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B86" t="s">
         <v>4</v>
       </c>
-      <c r="C86" s="2" t="s">
+      <c r="C86" s="3" t="s">
         <v>30</v>
       </c>
       <c r="D86">
         <v>183</v>
       </c>
-      <c r="E86" s="2">
+      <c r="E86" s="3">
         <v>3500</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B87" t="s">
         <v>11</v>
       </c>
-      <c r="C87" s="2" t="s">
+      <c r="C87" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D87" s="2">
+      <c r="D87" s="3">
         <v>1500</v>
       </c>
-      <c r="E87" s="2">
+      <c r="E87" s="3">
         <v>3500</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B88" t="s">
         <v>11</v>
       </c>
-      <c r="C88" s="2" t="s">
+      <c r="C88" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="D88" s="2">
+      <c r="D88">
         <v>78</v>
       </c>
-      <c r="E88" s="2">
+      <c r="E88" s="3">
         <v>3500</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B89" t="s">
         <v>11</v>
       </c>
-      <c r="C89" s="2" t="s">
+      <c r="C89" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="D89" s="2">
+      <c r="D89" s="3">
         <v>16</v>
       </c>
-      <c r="E89" s="2">
+      <c r="E89" s="3">
         <v>3500</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B90" t="s">
         <v>11</v>
       </c>
-      <c r="C90" s="2" t="s">
+      <c r="C90" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="D90" s="2">
-        <v>96</v>
-      </c>
-      <c r="E90" s="2">
+      <c r="D90">
+        <v>125</v>
+      </c>
+      <c r="E90" s="3">
         <v>3500</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B91" t="s">
         <v>11</v>
       </c>
-      <c r="C91" s="2" t="s">
+      <c r="C91" s="3" t="s">
         <v>30</v>
       </c>
       <c r="D91">
         <v>198</v>
       </c>
-      <c r="E91" s="2">
+      <c r="E91" s="3">
         <v>3500</v>
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B92" t="s">
         <v>14</v>
       </c>
-      <c r="C92" s="2" t="s">
+      <c r="C92" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D92" s="2">
+      <c r="D92" s="3">
         <v>1500</v>
       </c>
-      <c r="E92" s="2">
+      <c r="E92" s="3">
         <v>2300</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B93" t="s">
         <v>14</v>
       </c>
-      <c r="C93" s="2" t="s">
+      <c r="C93" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="D93" s="2">
+      <c r="D93">
         <v>44</v>
       </c>
-      <c r="E93" s="2">
+      <c r="E93" s="3">
         <v>2300</v>
       </c>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B94" t="s">
         <v>14</v>
       </c>
-      <c r="C94" s="2" t="s">
+      <c r="C94" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="D94" s="2">
+      <c r="D94" s="3">
         <v>10</v>
       </c>
-      <c r="E94" s="2">
+      <c r="E94" s="3">
         <v>2300</v>
       </c>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B95" t="s">
         <v>14</v>
       </c>
-      <c r="C95" s="2" t="s">
+      <c r="C95" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="D95" s="2">
-        <v>72</v>
-      </c>
-      <c r="E95" s="2">
+      <c r="D95">
+        <v>94</v>
+      </c>
+      <c r="E95" s="3">
         <v>2300</v>
       </c>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B96" t="s">
         <v>14</v>
       </c>
-      <c r="C96" s="2" t="s">
+      <c r="C96" s="3" t="s">
         <v>30</v>
       </c>
       <c r="D96">
         <v>151</v>
       </c>
-      <c r="E96" s="2">
+      <c r="E96" s="3">
         <v>2300</v>
       </c>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B97" t="s">
         <v>16</v>
       </c>
-      <c r="C97" s="2" t="s">
+      <c r="C97" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D97" s="2">
+      <c r="D97" s="3">
         <v>1500</v>
       </c>
-      <c r="E97" s="2">
-        <v>6000</v>
+      <c r="E97" s="3">
+        <v>5700</v>
       </c>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B98" t="s">
         <v>16</v>
       </c>
-      <c r="C98" s="2" t="s">
+      <c r="C98" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="D98" s="2">
-        <v>120</v>
-      </c>
-      <c r="E98" s="2">
-        <v>6000</v>
+      <c r="D98">
+        <v>103</v>
+      </c>
+      <c r="E98" s="3">
+        <v>5700</v>
       </c>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B99" t="s">
         <v>16</v>
       </c>
-      <c r="C99" s="2" t="s">
+      <c r="C99" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="D99" s="2">
+      <c r="D99" s="3">
         <v>14</v>
       </c>
-      <c r="E99" s="2">
-        <v>6000</v>
+      <c r="E99" s="3">
+        <v>5700</v>
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B100" t="s">
         <v>16</v>
       </c>
-      <c r="C100" s="2" t="s">
+      <c r="C100" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="D100" s="2">
-        <v>236</v>
-      </c>
-      <c r="E100" s="2">
-        <v>6000</v>
+      <c r="D100">
+        <v>307</v>
+      </c>
+      <c r="E100" s="3">
+        <v>5700</v>
       </c>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B101" t="s">
         <v>16</v>
       </c>
-      <c r="C101" s="2" t="s">
+      <c r="C101" s="3" t="s">
         <v>30</v>
       </c>
       <c r="D101">
         <v>192</v>
       </c>
-      <c r="E101" s="2">
-        <v>6000</v>
+      <c r="E101" s="3">
+        <v>5700</v>
       </c>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B102" t="s">
         <v>19</v>
       </c>
-      <c r="C102" s="2" t="s">
+      <c r="C102" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D102" s="2">
+      <c r="D102" s="3">
         <v>1500</v>
       </c>
-      <c r="E102" s="2">
+      <c r="E102" s="3">
         <v>2600</v>
       </c>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B103" t="s">
         <v>19</v>
       </c>
-      <c r="C103" s="2" t="s">
+      <c r="C103" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="D103" s="2">
+      <c r="D103">
         <v>62</v>
       </c>
-      <c r="E103" s="2">
+      <c r="E103" s="3">
         <v>2600</v>
       </c>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B104" t="s">
         <v>19</v>
       </c>
-      <c r="C104" s="2" t="s">
+      <c r="C104" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="D104" s="2">
+      <c r="D104" s="3">
         <v>11</v>
       </c>
-      <c r="E104" s="2">
+      <c r="E104" s="3">
         <v>2600</v>
       </c>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B105" t="s">
         <v>19</v>
       </c>
-      <c r="C105" s="2" t="s">
+      <c r="C105" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="D105" s="2">
-        <v>74</v>
-      </c>
-      <c r="E105" s="2">
+      <c r="D105">
+        <v>96</v>
+      </c>
+      <c r="E105" s="3">
         <v>2600</v>
       </c>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B106" t="s">
         <v>19</v>
       </c>
-      <c r="C106" s="2" t="s">
+      <c r="C106" s="3" t="s">
         <v>30</v>
       </c>
       <c r="D106">
         <v>181</v>
       </c>
-      <c r="E106" s="2">
+      <c r="E106" s="3">
         <v>2600</v>
       </c>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B107" t="s">
         <v>15</v>
       </c>
-      <c r="C107" s="2" t="s">
+      <c r="C107" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D107" s="2">
+      <c r="D107" s="3">
         <v>1500</v>
       </c>
-      <c r="E107" s="2">
+      <c r="E107" s="3">
         <v>2650</v>
       </c>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B108" t="s">
         <v>15</v>
       </c>
-      <c r="C108" s="2" t="s">
+      <c r="C108" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="D108" s="2">
+      <c r="D108">
         <v>30</v>
       </c>
-      <c r="E108" s="2">
+      <c r="E108" s="3">
         <v>2650</v>
       </c>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B109" t="s">
         <v>15</v>
       </c>
-      <c r="C109" s="2" t="s">
+      <c r="C109" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="D109" s="2">
+      <c r="D109" s="3">
         <v>10</v>
       </c>
-      <c r="E109" s="2">
+      <c r="E109" s="3">
         <v>2650</v>
       </c>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B110" t="s">
         <v>15</v>
       </c>
-      <c r="C110" s="2" t="s">
+      <c r="C110" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="D110" s="2">
-        <v>92</v>
-      </c>
-      <c r="E110" s="2">
+      <c r="D110">
+        <v>120</v>
+      </c>
+      <c r="E110" s="3">
         <v>2650</v>
       </c>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B111" t="s">
         <v>15</v>
       </c>
-      <c r="C111" s="2" t="s">
+      <c r="C111" s="3" t="s">
         <v>30</v>
       </c>
       <c r="D111">
         <v>126</v>
       </c>
-      <c r="E111" s="2">
+      <c r="E111" s="3">
         <v>2650</v>
       </c>
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B112" t="s">
         <v>31</v>
       </c>
-      <c r="C112" s="2" t="s">
+      <c r="C112" s="3" t="s">
         <v>22</v>
       </c>
       <c r="D112">
         <v>27700</v>
       </c>
-      <c r="E112" s="2">
-        <v>53800</v>
+      <c r="E112" s="3">
+        <v>53500</v>
       </c>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B113" t="s">
         <v>31</v>
       </c>
-      <c r="C113" s="2" t="s">
+      <c r="C113" s="3" t="s">
         <v>27</v>
       </c>
       <c r="D113">
-        <v>857</v>
-      </c>
-      <c r="E113" s="2">
-        <v>53800</v>
+        <v>840</v>
+      </c>
+      <c r="E113" s="3">
+        <v>53500</v>
       </c>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B114" t="s">
         <v>31</v>
       </c>
-      <c r="C114" s="2" t="s">
+      <c r="C114" s="3" t="s">
         <v>28</v>
       </c>
       <c r="D114">
         <v>131</v>
       </c>
-      <c r="E114" s="2">
-        <v>53800</v>
+      <c r="E114" s="3">
+        <v>53500</v>
       </c>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B115" t="s">
         <v>31</v>
       </c>
-      <c r="C115" s="2" t="s">
+      <c r="C115" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="D115" s="2">
-        <v>1858</v>
-      </c>
-      <c r="E115" s="2">
-        <v>53800</v>
+      <c r="D115">
+        <v>2433</v>
+      </c>
+      <c r="E115" s="3">
+        <v>53500</v>
       </c>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B116" t="s">
         <v>31</v>
       </c>
-      <c r="C116" s="2" t="s">
+      <c r="C116" s="3" t="s">
         <v>30</v>
       </c>
       <c r="D116">
         <v>2738</v>
       </c>
-      <c r="E116" s="2">
-        <v>53800</v>
+      <c r="E116" s="3">
+        <v>53500</v>
       </c>
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
+        <v>33</v>
+      </c>
+      <c r="B117" t="s">
         <v>34</v>
       </c>
-      <c r="B117" t="s">
-        <v>33</v>
-      </c>
-      <c r="C117" s="2" t="s">
+      <c r="C117" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D117" s="2">
+      <c r="D117" s="3">
         <v>1500</v>
       </c>
-      <c r="E117" s="2">
+      <c r="E117" s="3">
         <v>5700</v>
       </c>
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
+        <v>33</v>
+      </c>
+      <c r="B118" t="s">
         <v>34</v>
       </c>
-      <c r="B118" t="s">
-        <v>33</v>
-      </c>
-      <c r="C118" s="2" t="s">
+      <c r="C118" s="3" t="s">
         <v>27</v>
       </c>
       <c r="D118">
-        <v>17</v>
-      </c>
-      <c r="E118" s="2">
+        <v>103</v>
+      </c>
+      <c r="E118" s="3">
         <v>5700</v>
       </c>
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
+        <v>33</v>
+      </c>
+      <c r="B119" t="s">
         <v>34</v>
       </c>
-      <c r="B119" t="s">
-        <v>33</v>
-      </c>
-      <c r="C119" s="2" t="s">
+      <c r="C119" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="D119" s="2">
+      <c r="D119" s="3">
         <v>14</v>
       </c>
-      <c r="E119" s="2">
+      <c r="E119" s="3">
         <v>5700</v>
       </c>
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
+        <v>33</v>
+      </c>
+      <c r="B120" t="s">
         <v>34</v>
       </c>
-      <c r="B120" t="s">
-        <v>33</v>
-      </c>
-      <c r="C120" s="2" t="s">
+      <c r="C120" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="D120" s="2">
-        <v>1858</v>
-      </c>
-      <c r="E120" s="2">
+      <c r="D120">
+        <v>2433</v>
+      </c>
+      <c r="E120" s="3">
         <v>5700</v>
       </c>
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
+        <v>33</v>
+      </c>
+      <c r="B121" t="s">
         <v>34</v>
       </c>
-      <c r="B121" t="s">
-        <v>33</v>
-      </c>
-      <c r="C121" s="2" t="s">
+      <c r="C121" s="3" t="s">
         <v>30</v>
       </c>
       <c r="D121">
         <v>192</v>
       </c>
-      <c r="E121" s="2">
+      <c r="E121" s="3">
         <v>5700</v>
       </c>
     </row>
+    <row r="122" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B122" s="3"/>
+      <c r="C122" s="3"/>
+      <c r="D122" s="3"/>
+      <c r="E122" s="3"/>
+    </row>
+    <row r="123" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B123" s="3"/>
+      <c r="C123" s="3"/>
+      <c r="D123" s="3"/>
+      <c r="E123" s="3"/>
+    </row>
+    <row r="124" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B124" s="3"/>
+      <c r="C124" s="3"/>
+      <c r="D124" s="3"/>
+      <c r="E124" s="3"/>
+    </row>
+    <row r="125" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B125" s="3"/>
+      <c r="C125" s="3"/>
+      <c r="E125" s="3"/>
+    </row>
+    <row r="126" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B126" s="3"/>
+      <c r="C126" s="3"/>
+      <c r="E126" s="3"/>
+    </row>
+    <row r="127" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B127" s="3"/>
+      <c r="C127" s="3"/>
+      <c r="E127" s="3"/>
+    </row>
+    <row r="128" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C128" s="3"/>
+      <c r="D128" s="3"/>
+      <c r="E128" s="3"/>
+    </row>
+    <row r="129" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C129" s="3"/>
+      <c r="E129" s="3"/>
+    </row>
+    <row r="130" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C130" s="3"/>
+      <c r="D130" s="3"/>
+      <c r="E130" s="3"/>
+    </row>
+    <row r="131" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C131" s="3"/>
+      <c r="E131" s="3"/>
+    </row>
+    <row r="132" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C132" s="3"/>
+      <c r="E132" s="3"/>
+    </row>
+    <row r="133" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C133" s="3"/>
+      <c r="E133" s="3"/>
+    </row>
+    <row r="134" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C134" s="3"/>
+      <c r="D134" s="3"/>
+      <c r="E134" s="3"/>
+    </row>
+    <row r="135" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C135" s="3"/>
+      <c r="E135" s="3"/>
+    </row>
+    <row r="136" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C136" s="3"/>
+      <c r="D136" s="3"/>
+      <c r="E136" s="3"/>
+    </row>
+    <row r="137" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C137" s="3"/>
+      <c r="E137" s="3"/>
+    </row>
+    <row r="138" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C138" s="3"/>
+      <c r="E138" s="3"/>
+    </row>
+    <row r="139" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C139" s="3"/>
+      <c r="E139" s="3"/>
+    </row>
+    <row r="140" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C140" s="3"/>
+      <c r="D140" s="3"/>
+      <c r="E140" s="3"/>
+    </row>
+    <row r="141" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C141" s="3"/>
+      <c r="E141" s="3"/>
+    </row>
+    <row r="142" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C142" s="3"/>
+      <c r="D142" s="3"/>
+      <c r="E142" s="3"/>
+    </row>
+    <row r="143" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C143" s="3"/>
+      <c r="E143" s="3"/>
+    </row>
+    <row r="144" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C144" s="3"/>
+      <c r="E144" s="3"/>
+    </row>
+    <row r="145" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C145" s="3"/>
+      <c r="E145" s="3"/>
+    </row>
+    <row r="146" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C146" s="3"/>
+      <c r="D146" s="3"/>
+      <c r="E146" s="3"/>
+    </row>
+    <row r="147" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C147" s="3"/>
+      <c r="E147" s="3"/>
+    </row>
+    <row r="148" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C148" s="3"/>
+      <c r="D148" s="3"/>
+      <c r="E148" s="3"/>
+    </row>
+    <row r="149" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C149" s="3"/>
+      <c r="E149" s="3"/>
+    </row>
+    <row r="150" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C150" s="3"/>
+      <c r="E150" s="3"/>
+    </row>
+    <row r="151" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C151" s="3"/>
+      <c r="E151" s="3"/>
+    </row>
+    <row r="152" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C152" s="3"/>
+      <c r="D152" s="3"/>
+      <c r="E152" s="3"/>
+    </row>
+    <row r="153" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C153" s="3"/>
+      <c r="E153" s="3"/>
+    </row>
+    <row r="154" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C154" s="3"/>
+      <c r="D154" s="3"/>
+      <c r="E154" s="3"/>
+    </row>
+    <row r="155" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C155" s="3"/>
+      <c r="E155" s="3"/>
+    </row>
+    <row r="156" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C156" s="3"/>
+      <c r="E156" s="3"/>
+    </row>
+    <row r="157" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C157" s="3"/>
+      <c r="E157" s="3"/>
+    </row>
+    <row r="158" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C158" s="3"/>
+      <c r="D158" s="3"/>
+      <c r="E158" s="3"/>
+    </row>
+    <row r="159" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C159" s="3"/>
+      <c r="E159" s="3"/>
+    </row>
+    <row r="160" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C160" s="3"/>
+      <c r="D160" s="3"/>
+      <c r="E160" s="3"/>
+    </row>
+    <row r="161" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="C161" s="3"/>
+      <c r="E161" s="3"/>
+    </row>
+    <row r="162" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="C162" s="3"/>
+      <c r="E162" s="3"/>
+    </row>
+    <row r="163" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="C163" s="3"/>
+      <c r="E163" s="3"/>
+    </row>
+    <row r="164" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="C164" s="3"/>
+      <c r="D164" s="3"/>
+      <c r="E164" s="3"/>
+    </row>
+    <row r="165" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="C165" s="3"/>
+      <c r="E165" s="3"/>
+    </row>
+    <row r="166" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="C166" s="3"/>
+      <c r="D166" s="3"/>
+      <c r="E166" s="3"/>
+    </row>
+    <row r="167" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="C167" s="3"/>
+      <c r="E167" s="3"/>
+    </row>
+    <row r="168" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="C168" s="3"/>
+      <c r="E168" s="3"/>
+    </row>
+    <row r="169" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="C169" s="3"/>
+      <c r="E169" s="3"/>
+    </row>
+    <row r="170" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B170" s="1"/>
+      <c r="C170" s="3"/>
+      <c r="D170" s="3"/>
+      <c r="E170" s="3"/>
+    </row>
+    <row r="171" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="C171" s="3"/>
+      <c r="E171" s="3"/>
+    </row>
+    <row r="172" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="C172" s="3"/>
+      <c r="D172" s="3"/>
+      <c r="E172" s="3"/>
+    </row>
+    <row r="173" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="C173" s="3"/>
+      <c r="E173" s="3"/>
+    </row>
+    <row r="174" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="C174" s="3"/>
+      <c r="E174" s="3"/>
+    </row>
+    <row r="175" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="C175" s="3"/>
+      <c r="E175" s="3"/>
+    </row>
+    <row r="176" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="C176" s="3"/>
+      <c r="D176" s="3"/>
+      <c r="E176" s="3"/>
+    </row>
+    <row r="177" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C177" s="3"/>
+      <c r="E177" s="3"/>
+    </row>
+    <row r="178" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C178" s="3"/>
+      <c r="D178" s="3"/>
+      <c r="E178" s="3"/>
+    </row>
+    <row r="179" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C179" s="3"/>
+      <c r="E179" s="3"/>
+    </row>
+    <row r="180" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C180" s="3"/>
+      <c r="E180" s="3"/>
+    </row>
+    <row r="181" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C181" s="3"/>
+      <c r="E181" s="3"/>
+    </row>
+    <row r="182" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C182" s="3"/>
+      <c r="D182" s="3"/>
+      <c r="E182" s="3"/>
+    </row>
+    <row r="183" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C183" s="3"/>
+      <c r="E183" s="3"/>
+    </row>
+    <row r="184" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C184" s="3"/>
+      <c r="D184" s="3"/>
+      <c r="E184" s="3"/>
+    </row>
+    <row r="185" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C185" s="3"/>
+      <c r="E185" s="3"/>
+    </row>
+    <row r="186" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C186" s="3"/>
+      <c r="E186" s="3"/>
+    </row>
+    <row r="187" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C187" s="3"/>
+      <c r="E187" s="3"/>
+    </row>
+    <row r="188" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C188" s="3"/>
+      <c r="D188" s="3"/>
+      <c r="E188" s="3"/>
+    </row>
+    <row r="189" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C189" s="3"/>
+      <c r="E189" s="3"/>
+    </row>
+    <row r="190" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C190" s="3"/>
+      <c r="D190" s="3"/>
+      <c r="E190" s="3"/>
+    </row>
+    <row r="191" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C191" s="3"/>
+      <c r="E191" s="3"/>
+    </row>
+    <row r="192" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C192" s="3"/>
+      <c r="E192" s="3"/>
+    </row>
+    <row r="193" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C193" s="3"/>
+      <c r="E193" s="3"/>
+    </row>
+    <row r="194" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C194" s="3"/>
+      <c r="D194" s="3"/>
+      <c r="E194" s="3"/>
+    </row>
+    <row r="195" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C195" s="3"/>
+      <c r="E195" s="3"/>
+    </row>
+    <row r="196" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C196" s="3"/>
+      <c r="D196" s="3"/>
+      <c r="E196" s="3"/>
+    </row>
+    <row r="197" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C197" s="3"/>
+      <c r="E197" s="3"/>
+    </row>
+    <row r="198" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C198" s="3"/>
+      <c r="E198" s="3"/>
+    </row>
+    <row r="199" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C199" s="3"/>
+      <c r="E199" s="3"/>
+    </row>
+    <row r="200" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C200" s="3"/>
+      <c r="D200" s="3"/>
+      <c r="E200" s="3"/>
+    </row>
+    <row r="201" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C201" s="3"/>
+      <c r="E201" s="3"/>
+    </row>
+    <row r="202" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C202" s="3"/>
+      <c r="D202" s="3"/>
+      <c r="E202" s="3"/>
+    </row>
+    <row r="203" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C203" s="3"/>
+      <c r="E203" s="3"/>
+    </row>
+    <row r="204" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C204" s="3"/>
+      <c r="E204" s="3"/>
+    </row>
+    <row r="205" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C205" s="3"/>
+      <c r="E205" s="3"/>
+    </row>
+    <row r="206" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C206" s="3"/>
+      <c r="D206" s="3"/>
+      <c r="E206" s="3"/>
+    </row>
+    <row r="207" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C207" s="3"/>
+      <c r="E207" s="3"/>
+    </row>
+    <row r="208" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C208" s="3"/>
+      <c r="D208" s="3"/>
+      <c r="E208" s="3"/>
+    </row>
+    <row r="209" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C209" s="3"/>
+      <c r="E209" s="3"/>
+    </row>
+    <row r="210" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C210" s="3"/>
+      <c r="E210" s="3"/>
+    </row>
+    <row r="211" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C211" s="3"/>
+      <c r="E211" s="3"/>
+    </row>
+    <row r="212" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C212" s="3"/>
+      <c r="E212" s="3"/>
+    </row>
+    <row r="213" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C213" s="3"/>
+      <c r="E213" s="3"/>
+    </row>
+    <row r="214" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C214" s="3"/>
+      <c r="E214" s="3"/>
+    </row>
+    <row r="215" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C215" s="3"/>
+      <c r="E215" s="3"/>
+    </row>
+    <row r="216" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C216" s="3"/>
+      <c r="E216" s="3"/>
+    </row>
+    <row r="217" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C217" s="3"/>
+      <c r="E217" s="3"/>
+    </row>
+    <row r="218" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C218" s="3"/>
+      <c r="D218" s="3"/>
+      <c r="E218" s="3"/>
+    </row>
+    <row r="219" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C219" s="3"/>
+      <c r="E219" s="3"/>
+    </row>
+    <row r="220" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C220" s="3"/>
+      <c r="D220" s="3"/>
+      <c r="E220" s="3"/>
+    </row>
+    <row r="221" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C221" s="3"/>
+      <c r="E221" s="3"/>
+    </row>
+    <row r="222" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C222" s="3"/>
+      <c r="E222" s="3"/>
+    </row>
+    <row r="223" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C223" s="3"/>
+      <c r="E223" s="3"/>
+    </row>
+    <row r="224" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C224" s="3"/>
+      <c r="D224" s="3"/>
+      <c r="E224" s="3"/>
+    </row>
+    <row r="225" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C225" s="3"/>
+      <c r="E225" s="3"/>
+    </row>
+    <row r="226" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C226" s="3"/>
+      <c r="D226" s="3"/>
+      <c r="E226" s="3"/>
+    </row>
+    <row r="227" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C227" s="3"/>
+      <c r="E227" s="3"/>
+    </row>
+    <row r="228" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C228" s="3"/>
+      <c r="E228" s="3"/>
+    </row>
+    <row r="229" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C229" s="3"/>
+      <c r="E229" s="3"/>
+    </row>
+    <row r="230" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C230" s="3"/>
+      <c r="D230" s="3"/>
+      <c r="E230" s="3"/>
+    </row>
+    <row r="231" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C231" s="3"/>
+      <c r="E231" s="3"/>
+    </row>
+    <row r="232" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C232" s="3"/>
+      <c r="D232" s="3"/>
+      <c r="E232" s="3"/>
+    </row>
+    <row r="233" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C233" s="3"/>
+      <c r="E233" s="3"/>
+    </row>
+    <row r="234" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C234" s="3"/>
+      <c r="E234" s="3"/>
+    </row>
+    <row r="235" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C235" s="3"/>
+      <c r="E235" s="3"/>
+    </row>
+    <row r="236" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C236" s="3"/>
+      <c r="D236" s="3"/>
+      <c r="E236" s="3"/>
+    </row>
+    <row r="237" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C237" s="3"/>
+      <c r="E237" s="3"/>
+    </row>
+    <row r="238" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C238" s="3"/>
+      <c r="D238" s="3"/>
+      <c r="E238" s="3"/>
+    </row>
+    <row r="239" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C239" s="3"/>
+      <c r="E239" s="3"/>
+    </row>
+    <row r="240" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C240" s="3"/>
+      <c r="E240" s="3"/>
+    </row>
+    <row r="241" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C241" s="3"/>
+      <c r="E241" s="3"/>
+    </row>
+    <row r="242" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C242" s="3"/>
+      <c r="D242" s="3"/>
+      <c r="E242" s="3"/>
+    </row>
+    <row r="243" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C243" s="3"/>
+      <c r="E243" s="3"/>
+    </row>
+    <row r="244" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C244" s="3"/>
+      <c r="D244" s="3"/>
+      <c r="E244" s="3"/>
+    </row>
+    <row r="245" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C245" s="3"/>
+      <c r="E245" s="3"/>
+    </row>
+    <row r="246" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C246" s="3"/>
+      <c r="E246" s="3"/>
+    </row>
+    <row r="247" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C247" s="3"/>
+      <c r="E247" s="3"/>
+    </row>
+    <row r="248" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C248" s="3"/>
+      <c r="E248" s="3"/>
+    </row>
+    <row r="249" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C249" s="3"/>
+      <c r="E249" s="3"/>
+    </row>
+    <row r="250" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C250" s="3"/>
+      <c r="E250" s="3"/>
+    </row>
+    <row r="251" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C251" s="3"/>
+      <c r="E251" s="3"/>
+    </row>
+    <row r="252" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C252" s="3"/>
+      <c r="E252" s="3"/>
+    </row>
+    <row r="253" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C253" s="3"/>
+      <c r="E253" s="3"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E121" xr:uid="{6956BB2C-DA9E-4412-BCD4-BB80A11153FE}"/>
+  <autoFilter ref="B1:E121" xr:uid="{6956BB2C-DA9E-4412-BCD4-BB80A11153FE}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/data/metas.xlsx
+++ b/data/metas.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sercomunicaciones2-my.sharepoint.com/personal/auxcomisiones_sercomunicaciones_com/Documents/PAOLA/AUXCOMISIÓN/3 Liquidación CVS comerciales/2026/02 Febrero/Liquidacióncvs - copia/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sercomunicaciones2-my.sharepoint.com/personal/auxcomisiones_sercomunicaciones_com/Documents/PAOLA/AUXCOMISIÓN/3 Liquidación CVS comerciales/2026/02 Febrero/Liquidacióncvs - liquidación/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="554" documentId="8_{787D9E49-702D-43BD-B99B-4B64F775E77B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B8BA1849-1829-4ACB-997B-547C10867E8F}"/>
+  <xr:revisionPtr revIDLastSave="586" documentId="8_{787D9E49-702D-43BD-B99B-4B64F775E77B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C0CA9870-9B81-4CF3-A2CF-8623E5EE38BE}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D1391136-BBFC-43C7-B899-B77B0ECC5956}"/>
   </bookViews>
@@ -634,7 +634,7 @@
         <v>29</v>
       </c>
       <c r="D5" s="3">
-        <v>124</v>
+        <v>95</v>
       </c>
       <c r="E5" s="3">
         <v>2800</v>
@@ -719,7 +719,7 @@
         <v>29</v>
       </c>
       <c r="D10">
-        <v>107</v>
+        <v>82</v>
       </c>
       <c r="E10" s="3">
         <v>2400</v>
@@ -804,7 +804,7 @@
         <v>29</v>
       </c>
       <c r="D15">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="E15" s="3">
         <v>1350</v>
@@ -889,7 +889,7 @@
         <v>29</v>
       </c>
       <c r="D20">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="E20" s="3">
         <v>1700</v>
@@ -974,7 +974,7 @@
         <v>29</v>
       </c>
       <c r="D25">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="E25" s="3">
         <v>1450</v>
@@ -1059,7 +1059,7 @@
         <v>29</v>
       </c>
       <c r="D30">
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="E30" s="3">
         <v>1500</v>
@@ -1144,7 +1144,7 @@
         <v>29</v>
       </c>
       <c r="D35">
-        <v>208</v>
+        <v>160</v>
       </c>
       <c r="E35" s="3">
         <v>4000</v>
@@ -1229,7 +1229,7 @@
         <v>29</v>
       </c>
       <c r="D40">
-        <v>182</v>
+        <v>140</v>
       </c>
       <c r="E40" s="3">
         <v>2600</v>
@@ -1314,7 +1314,7 @@
         <v>29</v>
       </c>
       <c r="D45">
-        <v>73</v>
+        <v>56</v>
       </c>
       <c r="E45" s="3">
         <v>2000</v>
@@ -1399,7 +1399,7 @@
         <v>29</v>
       </c>
       <c r="D50">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="E50" s="3">
         <v>1500</v>
@@ -1484,7 +1484,7 @@
         <v>29</v>
       </c>
       <c r="D55">
-        <v>107</v>
+        <v>82</v>
       </c>
       <c r="E55" s="3">
         <v>2000</v>
@@ -1569,7 +1569,7 @@
         <v>29</v>
       </c>
       <c r="D60">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="E60" s="3">
         <v>1100</v>
@@ -1654,7 +1654,7 @@
         <v>29</v>
       </c>
       <c r="D65">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="E65" s="3">
         <v>2200</v>
@@ -1739,7 +1739,7 @@
         <v>29</v>
       </c>
       <c r="D70">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="E70" s="3">
         <v>1600</v>
@@ -1824,7 +1824,7 @@
         <v>29</v>
       </c>
       <c r="D75">
-        <v>94</v>
+        <v>72</v>
       </c>
       <c r="E75" s="3">
         <v>2200</v>
@@ -1909,7 +1909,7 @@
         <v>29</v>
       </c>
       <c r="D80">
-        <v>133</v>
+        <v>102</v>
       </c>
       <c r="E80" s="3">
         <v>2850</v>
@@ -1994,7 +1994,7 @@
         <v>29</v>
       </c>
       <c r="D85">
-        <v>161</v>
+        <v>124</v>
       </c>
       <c r="E85" s="3">
         <v>3500</v>
@@ -2079,7 +2079,7 @@
         <v>29</v>
       </c>
       <c r="D90">
-        <v>125</v>
+        <v>96</v>
       </c>
       <c r="E90" s="3">
         <v>3500</v>
@@ -2164,7 +2164,7 @@
         <v>29</v>
       </c>
       <c r="D95">
-        <v>94</v>
+        <v>72</v>
       </c>
       <c r="E95" s="3">
         <v>2300</v>
@@ -2249,7 +2249,7 @@
         <v>29</v>
       </c>
       <c r="D100">
-        <v>307</v>
+        <v>236</v>
       </c>
       <c r="E100" s="3">
         <v>5700</v>
@@ -2334,7 +2334,7 @@
         <v>29</v>
       </c>
       <c r="D105">
-        <v>96</v>
+        <v>74</v>
       </c>
       <c r="E105" s="3">
         <v>2600</v>
@@ -2419,7 +2419,7 @@
         <v>29</v>
       </c>
       <c r="D110">
-        <v>120</v>
+        <v>92</v>
       </c>
       <c r="E110" s="3">
         <v>2650</v>
@@ -2507,7 +2507,7 @@
         <v>2433</v>
       </c>
       <c r="E115" s="3">
-        <v>53500</v>
+        <v>1868</v>
       </c>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.25">
@@ -2592,7 +2592,7 @@
         <v>2433</v>
       </c>
       <c r="E120" s="3">
-        <v>5700</v>
+        <v>1868</v>
       </c>
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.25">
